--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,6 +875,466 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Trustous Men’s Pure Cotton Kurta Dhoti Set | Traditional Ethnic Wear for Festive, Wedding &amp; Puja Occasion</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51a2QdCIA4L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H2FVJRHK?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Men’s Traditional Kurta for Men | Ethnic Wear Kurta for Festive, Wedding &amp; Casual Occasion | Stylish Regular Fit Kurta for Men</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51KXtvGVB0L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H34STXNS?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cotton Blend Self Design Printed Casual Short Kurta for Men Long Sleeve Mandarin Collar Stylish Kurta Shirt for Men</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51n05rjWoiL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GK98CZPC?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ROYALSCOUT Men's Cotton Polyester Blend Solid Regular Fit Full Sleeve Short Kurta | Ethnic, Lightweight Summer Kurta for Daily &amp; Occasion Use</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61FWZ9dcQML._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DHXFHNCH?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LookMark Men’s Printed Silk Blend Kurta with Mandarin Collar, Full Sleeves, Straight Fit Traditional Ethnic Wear</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51qygTxpJOL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GGC6H8YZ?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Zombom Cotton Polyester Blend Solid Casual Regular Fit Mandarin/Chinese Collor Short Kurta for Men</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71nEy2iSx-L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D3XJHFJK?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Majestic Man Men's Cotton Regular Fit Casual Mandarin Collar Ethnic Motifs Printed Long Regular Kurta</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/711YfcFNl+L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CPWBVGLR?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FINIVO FASHION Men’s Cotton Blend Short Kurta with Bold Printed Front Design | Full Sleeve Ethnic Casual Kurta with Mandarin Collar | Artistic Festival &amp; Travel Wear for Modern Ethnic Style</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51XUrcCln+L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FJF7N7WD?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Trustous Men's Printed Kurta Dhoti Set Traditional Ethnic Wear for Festivals &amp; Weddings | Men's Stylish Printed Kurta with Dhoti Set | Traditional Indian Ethnic Wear for Men</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41r5ITgctcL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H72RYHBY?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DEELMO Men’s Cotton Blend Printed Long Sleeve Short Kurta | Stylish Casual &amp; Ethnic Wear | Comfortable Mandarin Collar Kurta for Daily, Festive &amp; Party Outfits</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71vsX4HQH-L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FZJPMWRQ?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Men’s Lakhnawi Chikankari Cotton Blend Ethnic Wear Kurta for Men Knee Length Embroidered Kurta Mandarin Collar Full Sleeve Wedding Festive Party</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71CMf5jpAFL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GXQ28WND?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Men’s Madhubani Printed Khadi Silk Kurta | Premium Ethnic Wear for Weddings &amp; Festivals | Traditional Art Design | Comfortable &amp; Stylish Outfit</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41lfv5Bne2L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G448V51K?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Men Ethnic Gold Leaves 100% pure Jacquard Kurta &amp; Aladdin salwar special for Lohri &amp; New Year, In Panjabi Style</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71MYoHK0krL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BS19ZN4K?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ROYALSCOUT Men's Short Kurta | Solid Mandarin Collar Full Sleeve Pullover Style Kurta | Regular Fit Casual Ethnic Wear for Men</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61xL-c8CR6L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CW1V697B?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ROYALSCOUT Men's Cotton Polyester Blend Kurta Style Shirt with Mandarin Collar, Half Button Placket, Dual Chest Pockets, Long Sleeve Casual Ethnic Fusion Wear for Office, Festive and Daily Use</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61BCD0tyMeL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GKVMSQWX?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Tavasya Men Printed Kurta with Ethnic Motif Border | Special Haldi Kurta | Festive Embellished Long Kurta | Embroidery Kurta | Ethnic Wear | Mandarin Collar | Knee Length</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51MqzAFtWcL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GHYVS5SN?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Isha Life Organic Cotton Men Dhoti Pant | Elastic Waist Traditional Style Bottom Wear | Regular Fit Comfortable Casual &amp; Ethnic Wear for Men (S–XL)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61Ql4IqEenL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GMXXKV27?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Logass Kurta Pyjama Set for Mens Ethnic and Designer Wear Kurta Pyjama</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51FE21IGnyS._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BNJB7FZX?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LATEST CHIKAN Men's Cotton Regular Textured Long Kurta Full Sleeves - Casual Ethnic Wear</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/611poKYvqQL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08HK2ZRLP?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DIVISIVE Men's Sequince Embroidered Cotton Blend Only Slim Fit Kurta</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71xULJlZzCL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CR9446X2?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,466 +875,6 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Trustous Men’s Pure Cotton Kurta Dhoti Set | Traditional Ethnic Wear for Festive, Wedding &amp; Puja Occasion</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51a2QdCIA4L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H2FVJRHK?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Men’s Traditional Kurta for Men | Ethnic Wear Kurta for Festive, Wedding &amp; Casual Occasion | Stylish Regular Fit Kurta for Men</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51KXtvGVB0L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H34STXNS?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cotton Blend Self Design Printed Casual Short Kurta for Men Long Sleeve Mandarin Collar Stylish Kurta Shirt for Men</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51n05rjWoiL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GK98CZPC?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ROYALSCOUT Men's Cotton Polyester Blend Solid Regular Fit Full Sleeve Short Kurta | Ethnic, Lightweight Summer Kurta for Daily &amp; Occasion Use</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61FWZ9dcQML._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DHXFHNCH?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LookMark Men’s Printed Silk Blend Kurta with Mandarin Collar, Full Sleeves, Straight Fit Traditional Ethnic Wear</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51qygTxpJOL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GGC6H8YZ?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Zombom Cotton Polyester Blend Solid Casual Regular Fit Mandarin/Chinese Collor Short Kurta for Men</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71nEy2iSx-L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D3XJHFJK?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Majestic Man Men's Cotton Regular Fit Casual Mandarin Collar Ethnic Motifs Printed Long Regular Kurta</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/711YfcFNl+L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CPWBVGLR?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>FINIVO FASHION Men’s Cotton Blend Short Kurta with Bold Printed Front Design | Full Sleeve Ethnic Casual Kurta with Mandarin Collar | Artistic Festival &amp; Travel Wear for Modern Ethnic Style</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51XUrcCln+L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FJF7N7WD?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Trustous Men's Printed Kurta Dhoti Set Traditional Ethnic Wear for Festivals &amp; Weddings | Men's Stylish Printed Kurta with Dhoti Set | Traditional Indian Ethnic Wear for Men</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41r5ITgctcL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H72RYHBY?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>DEELMO Men’s Cotton Blend Printed Long Sleeve Short Kurta | Stylish Casual &amp; Ethnic Wear | Comfortable Mandarin Collar Kurta for Daily, Festive &amp; Party Outfits</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71vsX4HQH-L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FZJPMWRQ?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Men’s Lakhnawi Chikankari Cotton Blend Ethnic Wear Kurta for Men Knee Length Embroidered Kurta Mandarin Collar Full Sleeve Wedding Festive Party</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71CMf5jpAFL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GXQ28WND?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Men’s Madhubani Printed Khadi Silk Kurta | Premium Ethnic Wear for Weddings &amp; Festivals | Traditional Art Design | Comfortable &amp; Stylish Outfit</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41lfv5Bne2L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G448V51K?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Men Ethnic Gold Leaves 100% pure Jacquard Kurta &amp; Aladdin salwar special for Lohri &amp; New Year, In Panjabi Style</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71MYoHK0krL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BS19ZN4K?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ROYALSCOUT Men's Short Kurta | Solid Mandarin Collar Full Sleeve Pullover Style Kurta | Regular Fit Casual Ethnic Wear for Men</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61xL-c8CR6L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CW1V697B?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ROYALSCOUT Men's Cotton Polyester Blend Kurta Style Shirt with Mandarin Collar, Half Button Placket, Dual Chest Pockets, Long Sleeve Casual Ethnic Fusion Wear for Office, Festive and Daily Use</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61BCD0tyMeL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GKVMSQWX?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Amazon Brand - Tavasya Men Printed Kurta with Ethnic Motif Border | Special Haldi Kurta | Festive Embellished Long Kurta | Embroidery Kurta | Ethnic Wear | Mandarin Collar | Knee Length</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51MqzAFtWcL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GHYVS5SN?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Isha Life Organic Cotton Men Dhoti Pant | Elastic Waist Traditional Style Bottom Wear | Regular Fit Comfortable Casual &amp; Ethnic Wear for Men (S–XL)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61Ql4IqEenL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GMXXKV27?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Logass Kurta Pyjama Set for Mens Ethnic and Designer Wear Kurta Pyjama</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51FE21IGnyS._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BNJB7FZX?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>LATEST CHIKAN Men's Cotton Regular Textured Long Kurta Full Sleeves - Casual Ethnic Wear</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/611poKYvqQL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B08HK2ZRLP?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>DIVISIVE Men's Sequince Embroidered Cotton Blend Only Slim Fit Kurta</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71xULJlZzCL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CR9446X2?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,6 +875,546 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cello Prima 3 pcs Non-Stick Aluminium Cookware Set, Cherry Red (28 cm Dosa Tawa, 22 cm Kadai with Glass Lid, 22 cm Fry Pan) | Induction Base, PFOA-Free, Sturdy Handles, Ideal for Gifting</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61YACQ7VkVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07H94YY16?th=1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Upgrade your everyday cooking with the Cello Prima Non-Stick Aluminium Cookware Set, featuring a stylish and modern finish that enhances the look of your kitchen while providing a practical and reliable solution for preparing a wide variety of meals for your family. | This versatile cookware set includes a 22 cm Kadhai with a durable glass lid, a 22 cm Fry Pan, and a spacious 28 cm Dosa Tawa, making it perfect for cooking curries, stir-fries, sautéed vegetables, dosas, pancakes, omelets, and many other delicious recipes with ease. | Crafted from high quality aluminium, each cookware piece delivers quick and even heat distribution to ensure consistent cooking results, reduce cooking time, and improve energy efficiency, allowing you to prepare meals more effectively every day. | The premium non-stick coating promotes healthier cooking by requiring less oil while preventing food from sticking to the surface, making cooking smoother and cleanup faster, while the dishwasher-safe construction adds extra convenience for busy households. | Designed with a sturdy induction-compatible base that works efficiently on both gas stoves and induction cooktops, this durable cookware set combines functionality, convenience, and long-lasting performance, making it an ideal choice for modern kitchens and everyday cooking needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Judge by Prestige ACE Aluminium Non-Stick cookware BYK Set-Tawa 25cm-1U, Fry Pan 20cm-1U, Kadai 20cm-1U with Lid-1U + 3U Nylon Tools|Black</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71XddeECOFL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DG8N3MTV</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Durable Body | Low Oil Cooking | Elegant Design | Cool Touch Handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Judge by Prestige Ace Aluminium Non-Stick Cookware Set - Kadai 20 cm, Fry Pan 20 cm, Omni Tawa 25 cm - 1 Unit Each, Black</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/515a2mz5TOL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DG8M74Z8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Durable Body | Low Oil Cooking | Easy to Maintain | Cool Touch Handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Impex Migo Nonstick Cookware Set 3 Pcs | Induction Bottom | 5 Layer Super Granite Coating | 3mm Thick Aluminium | PFOA Free | Gas &amp; Induction Compatible | Detachable Chrome Handle | 1 Yr Warranty</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/713olRvDhHL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CW3G6ZQC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>🍳 𝐀𝐃𝐕𝐀𝐍𝐂𝐄𝐃 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Premium non-stick surface is 10X tougher than ordinary coatings, delivering smooth food release, effortless everyday cooking and easy cleanup for busy Indian kitchens. | ⚡ 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄: Versatile induction bottom cookware works seamlessly across gas stoves, induction cooktops and other cooking surfaces, making it a flexible pick for modern and traditional kitchens alike. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖 𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free, non-toxic aluminium construction lets you cook nutritious, healthier meals with minimal oil, while keeping harmful chemicals away from your everyday family food and health. | 🔥 𝐎𝐏𝐓𝐈𝐌𝐀𝐋 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊𝐍𝐄𝐒𝐒: Sturdy 3mm thick aluminium body ensures even heat distribution, faster heating and consistent cooking results, preventing hot spots so every dish cooks evenly and thoroughly every time. | ✋ 𝐃𝐄𝐓𝐀𝐂𝐇𝐀𝐁𝐋𝐄 𝐂𝐇𝐑𝐎𝐌𝐄 𝐇𝐀𝐍𝐃𝐋𝐄: Chrome-plated, sturdy detachable handle and knob provide a secure, comfortable grip while cooking, and allow for compact, space-saving storage in small, modern Indian kitchens. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓: Granite-finish non-stick surface is scratch resistant and simple to wipe clean, saving valuable time on daily kitchen chores while keeping the shine looking brand new. | 🍲 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟑 𝐏𝐂𝐒 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓: Ideal for frying, sauteing, tadka, curries and everyday Indian cooking, this practical cookware set gives you the essential pans needed for a fully equipped modern kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄 &amp; 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂: Health-conscious, food-grade aluminium construction is completely free from PFOA and harmful chemicals, ensuring safe, worry-free cooking for you and your entire family, every day. | 💎 𝐌𝐈𝐑𝐑𝐎𝐑-𝐋𝐈𝐊𝐄 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐅𝐈𝐍𝐈𝐒𝐇: Elegant granite finish gives your cookware a premium, modern look that enhances your kitchen decor while offering long-lasting, durable non-stick performance you can trust daily. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Backed by a 1 year manufacturer warranty, this Impex nonstick cookware set is reliable, durable and a perfect gift choice for new homes, weddings and housewarmings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Crystal Aluminum 6 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, Laddle &amp; Spatula | Durable 4 Layer Non Stick Coating | PFOA Free | Black</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Ks1TI+7TL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41G23NC?th=1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Stylish granite finish cookware combo for modern kitchens | Compatible with induction and gas stove cooking | Durable nonstick surface for smooth cooking experience | Uniform heat distribution for efficient cooking | Scratch resistant and easy to maintain</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Crystal Aluminum 6 Pcs Non Stick Cookware Set | Gas Stove Friendly | Tawa, Fry Pan, Kadhai with Lid, Laddle &amp; Spatula | Durable 4 Layer Non Stick Coating | PFOA Free | White</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81kqe9V4CML._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41D4CXQ?th=1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Premium white marble coating for stylish appearance | Gas stove compatible cookware set | Smooth nonstick surface for easy cooking and cleaning | Ideal for healthy low oil cooking | Durable and sturdy construction for long-term use</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|22 Cm Fry Pan,22 Cm Kadai,1 Glass Lid|Grey</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71NSco75mOL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYDWLMV</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 22 cm Fry Pan, 22 cm Kadai, 1 Glass Lid</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Crystal Classic Series 7-pc Non-Stick Induction Bottom Cookware Set, PFOA Free, Tawa, Fry-Pan, Kadhai with Glass Lid, Sauce Pan with 2 Serving Spoons, Red</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71-v9RBpQfL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09313HZ8B?th=1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | All items induction base except Sauce pan | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pigeon Aluminium Nonstick Duo Pack Flat Tawa 250 and Fry Pan 200 Gift Set (Red)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/510yXR4GoNL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07KYPZHJ9</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>5 Layer Durable Nonstick Coating. Broiler :Safe | Made with High End Italian Technology | Oil Free Cooking | Ergonomic Bakelite Handle | Free from Peel-Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Impex Non-Stick Cookware Set of 4 Pcs | Tawa Pan, Fry Pan &amp; Kadai with Glass Lid | PFOA-Free Triple Layer Coated Aluminium Kitchen Cookware Set | Bakelite Handle, Gas Stove Compatible | 1 Yr Warranty</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/717khrN3Z0L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CH1B2M1S</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟒-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐊𝐈𝐓𝐂𝐇𝐄𝐍: Includes a 24cm Kadai with Glass Lid, 24cm Tawa Pan and 24cm Fry Pan – a versatile non-stick cookware set for frying, roasting, sautéing, tadka and everyday Indian cooking needs at home. | 🥘 𝐓𝐑𝐈𝐏𝐋𝐄-𝐋𝐀𝐘𝐄𝐑 𝐍𝐎𝐍-𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐀𝐓𝐈𝐍𝐆 𝐅𝐎𝐑 𝐇𝐄𝐀𝐋𝐓𝐇𝐈𝐄𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free non-stick coated aluminium cookware ensures healthier low-oil cooking, effortless food release and quick, easy cleanup after every single meal you prepare. | 🔥 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐀𝐋𝐔𝐌𝐈𝐍𝐈𝐔𝐌 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝐄𝐕𝐄𝐍 𝐇𝐄𝐀𝐓 𝐃𝐈𝐒𝐓𝐑𝐈𝐁𝐔𝐓𝐈𝐎𝐍: Superior aluminium construction with heat-resistant exterior paint delivers fast, even heating and long-lasting performance for your everyday cooking in the kitchen. | ✋ 𝐂𝐎𝐌𝐅𝐎𝐑𝐓𝐀𝐁𝐋𝐄, 𝐒𝐄𝐂𝐔𝐑𝐄 𝐁𝐀𝐊𝐄𝐋𝐈𝐓𝐄 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy, heat-resistant bakelite handles are designed for a comfortable, secure grip while cooking, reducing the risk of burns and slips during daily kitchen use at home. | 🔍 𝐓𝐄𝐌𝐏𝐄𝐑𝐄𝐃 𝐆𝐋𝐀𝐒𝐒 𝐋𝐈𝐃 𝐅𝐎𝐑 𝐄𝐀𝐒𝐘 𝐌𝐎𝐍𝐈𝐓𝐎𝐑𝐈𝐍𝐆: The toughened glass lid on the Kadai lets you monitor food while it cooks, while retaining heat and moisture for evenly cooked, flavourful, delicious home-style dishes. | ⚡ 𝐆𝐀𝐒 𝐒𝐓𝐎𝐕𝐄 𝐅𝐑𝐈𝐄𝐍𝐃𝐋𝐘 𝐍𝐎𝐍-𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Designed with a non-induction bottom, this non-stick cookware set is ideal for gas stove kitchens, delivering consistent, reliable everyday cooking performance every time. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍, 𝐋𝐎𝐖 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: The smooth non-stick coated surface allows quick, effortless cleaning after cooking, saving valuable time on daily kitchen chores with no heavy scrubbing ever required. | 🎁 𝐈𝐃𝐄𝐀𝐋 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐍𝐄𝐖 𝐇𝐎𝐌𝐄𝐒: This multicolor 4-piece cookware set makes a thoughtful gift for weddings, housewarmings, anniversaries, or new homemakers setting up their very first kitchen space. | ✅ 𝐈𝐒𝐎 𝐂𝐄𝐑𝐓𝐈𝐅𝐈𝐄𝐃 𝐅𝐎𝐑 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Manufactured under ISO certification standards, this cookware set ensures premium quality, safety, and consistent performance you can rely on across every single piece. | 🛡️ 𝐖𝐎𝐑𝐑𝐘-𝐅𝐑𝐄𝐄 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 𝐀𝐒𝐒𝐔𝐑𝐀𝐍𝐂𝐄: Backed by Impex's 1-year manufacturer warranty, this cookware set gives you complete peace of mind and confidence in your everyday kitchen investment for years to come.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DOZY 5-Piece Non-Stick Cookware Combo Set with Kadhai, Tawa &amp; Tadka Pan Induction Bottom Non-Stick Coated Cookware Set (Iron-Rich Nonstick Cookware Combo)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61c2sc0TNjL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H1WBB126?th=1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>COMPLETE 5-PIECE SET: Includes a Kadhai, Tawa, Tadka Pan, and additional cookware pieces to cover all your everyday Indian cooking needs. | PREMIUM NON-STICK COATING: Superior non-stick surface ensures food slides off effortlessly, making cooking and cleaning quick and hassle-free. | INDUCTION COMPATIBLE: Specially designed with an induction-friendly bottom, making this cookware set compatible with all types of cooktops. | ERGONOMIC HANDLES: Fitted with sturdy, heat-resistant handles for a secure and comfortable grip while cooking, ensuring safe handling at all times. | DURABLE CONSTRUCTION: Handcrafted from high-quality materials with even heat distribution for consistent, perfectly cooked results every time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Amazon Solimo Aluminium 4 Piece Non-Stick Cookware Set | Granite Finish | Induction Base | PFOA Free | HTR Exterior Coating | 25 Cm Tawa, 22 Cm Kadai, 22 Cm Fry Pan, 1 Glass Lid | Grey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71g3Y8X9hQL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZY9PTHF?th=1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: with die-cast aluminium, the fry pan provides high conductivity which enables quick heat distribution and even cooking | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | ELEGANT FINISH: It has a granite finish on the interior and the exterior which gives it an elegant look</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hawkins Futura 5 Pieces Cookware Set 4 - Non Stick Kadhai, Two Frying Pans, Saucepan, Saute Pan and Two Glass Lids, Black (NSET4)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61T0Fe6un2S._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B00EVR0CRY?th=1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PFOA Free Non-stick coating locked into tough Hard Anodised Aluminium - lasts longer | The cookware set consists two Frying Pans, Deep-Fry Pan (Stir-Fry Pan), Saucepan with glass lid and Curry Pan (Sauté Pan) with glass lid to cater to most of your cooking needs | There is attractive saving on the purchase of the Set when compared with buying individual items separately | Each item included in the Set is accompanied by its own Instruction Manual / Cookbook and its own Guarantee Card | Suitable for use on domestic gas, electric, ceramic and halogen stoves</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Crystal Aluminum 11 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 3 Containers | 4 Layer Non Stick Coating | PFOA Free | White</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71VFfXMdmeL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41FL5NG?th=1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Complete cookware set for versatile cooking requirements | Induction and gas stove compatible base | Elegant white marble nonstick interior and exterior | Even heat distribution for faster cooking | Heat resistant handles for safe and easy use</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Crystal 11 Pcs Non Stick Cookware Set with Storage Containers | Gas Stove Friendly | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 2 Containers &amp; Grater Set | PFOA Free Coating</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71q-5-ENFCL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41FFYYF?th=1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Attractive white marble coated cookware combo | Gas stove compatible design for convenient cooking | Nonstick coating supports healthy cooking with less oil | Durable body for long-lasting usage | Elegant appearance suitable for every kitchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Amazon Basics Granite Finish Non Stick 5 Pcs Induction Base Cookware Set-Granito Grey (24cm Fry Pan, 24 cm Kadai, 28cm Tawa and 2 Nylon Spatulas)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71fcuPgHEBL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C2J76WPF?th=1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DURABLE IMPORTED COATING: It comes with water-based coating imported from Japan which is compliant with US FDA and European Food Safety Authority (EFSA) standards. This cookware features three granite-finished coats each on its interior and exterior. It has been tested to last for more than 10,000 cycles. | HEALTHIER CHOICE: Its granite coating is free from PFOA, PTFE, lead, cadmiumm nickel and arsenic. This makes it safer and healthier to use than traditional non-stick cookware, which may contain harmful chemicals. | FAST, EVEN COOKING: Made from pressed aluminium, this cookware is ultra-conductive and corrosion-resistant. Its granite coating and flat, thick skillet bottom offer exceptional heat distribution to ensure even cooking and prevent hot spots. Overall, this cookware offers quick heating, thus using less energy. | REQUIRES LESS OIL: Cook a variety of healthy, delicious recipes for Indian households using this non-stick cookware set from Amazon Basics. It requires very little oil and cooks evenly and quickly without using much power. | CONDUCTIVE BASE: Its base is made from Aluminium and is highly magnetic and conductive. It features grooves that help retain heat. | COMPATIBLE WITH ALL COOKTOPS: The induction base with small perforation boosts faster cooking while helping you consume less electricity. This cookware is compatible with both gas-stove and induction cooktops. | COMFORTABLE TO HANDLE: The coookware is 3.5 MM thick with ideal weight distribution throughout the material for comfortable handling. | EASY TO CLEAN: Food particles are less likely to stick to the surface of the non-stick coating, making this cookware easy to clean. | CLEANING AND TEMPERATURE: We recommend hand-washing this cookware. Alternatively, you may clean it in a dishwasher with liquid detergent. It may be safely even at temperatures up to (200° and (260° C. | COLOUR: Granito Grey; PACKAGE CONTENTS: 1 tawa (28 cm), 1 fry pan (24 cm), 1 kadai (24 cm), 1 glass lid and 2 nylon spatulas; Thickness: 3.5 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo 3-Piece Aluminium Cookware Set - Fry Pan,Kadhai&amp;Tawa|2-Way 3 Layer Non-Stick Coating|Induction Friendly Design|Pfoa Free|High Temperature Resistant Exterior Coating,Maroon</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71bwxsfTaeL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08637F7W2?th=1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3 piece non-stick cookware set; frypan, kadhai with glass lid and tawa for convenient everyday cooking | Made using virgin aluminium for even heat distribution | Durable and long lasting with 3 layers of food grade non-stick coating facilitating minimal oil use while preventing stickiness and mess | Premium metallic finish with High Temperature Resistance (HTR) and a sleek shiny appeal | Bakelite handles provide a safe and firm ergonomic grip | Prepare rotis, chapatis, dosa, stir-fries, pulao, korma, sauteed vegetables as well as sear meats and fish, and fry eggs with this 3 piece cookware set | Can be used on gas stove and induction cooktops | Easy to clean and maintain; dishwasher safe | Warranty: 1 year warranty against manufacturing defects | Dimensions- Fry Pan:- Diameter: 220 mm (22 cm); Thickness: 3 mm; Depth: 45 mm (4.5 cm); Capacity: 1650 ml; Weight: 610 gm; Tawa:- Diameter: 265 mm (26.5 cm); Thickness: 3 mm; Depth: 13 mm (1.3 cm); Weight 615 gm; Kadhai:- Diameter: 220 mm (22 cm); Thickness: 3mm; Depth: 73 mm (7.3 cm); Capacity: 2500 ml; Weight: 1125 gm;Package Contents:- 1 Fry Pan, 1 Flat Tawa &amp; 1 Kadhai with 1 Glass Lid</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Wonderchef Valencia Plus Non-Stick Cookware 3 Piece Set | Kadhai, Glass Lid, Dosa Tawa | Cool Touch Bakelite Handles | Pure Grade Aluminium| PFOA Free| 1 Year Warranty | Purple</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51i43QAE0UL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GNT31PLH?th=1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VERSATILE 3-PIECE SET - Kadhai, Glass Lid, Dosa Tawa let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | HEALTHY COOKING MADE EASY: MetaTuff 5-layer non-stick coating ensures minimal oil use, excellent abrasion resistance and is 00% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | VERSATILE: Cook delicious cutlets, stir-fry veggies, curries, dosas, uttapams, sandwiches, omelets, and parathas with the fry pan, kadhai, and tawa. Complete your cookware needs with Valencia set! | ENERGY-EFFICIENT: Pure grade virgin aluminium offers 9-times better heat conduction, cooking your meals faster while saving energy and time. | COMPATIBLE WITH ALL COOKING SURFACES - Use on gas cooktops, hot plates, infrared cooktops, and ceramic cooktops for maximum flexibility in your kitchen. | COMFORTABLE &amp; STYLISH - Cool touch Bakelite handles provide a firm grip and utmost convenience. Enjoy cooking with comfort and ease. | CONVENIENT: Easy to clean and dishwasher safe. Lightweight for daily use. | IDEAL FOR GIFTING - Loaded with features and beautiful looks, the Valencia cookware set is an ideal choice for gifting. Surprise your loved ones with a perfect addition to their kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Crystal Classic Series 7-pc Non-Stick Cookware Set, PFOA Free, Red</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71bYDdKns5L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BD1JHYS7?th=1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart. | Soft touch bakelite handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Crystal Eco Plus 8-pc Non-Stick Cookware Set, PFOA Free, Tawa, Kadhai with SS Lid, Fry Pan, Vagariya, Mini Grill Pan, 2 Spatulas, Multicolor</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71oGMB2shTL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BD1JLNKM?th=1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart. | Soft touch bakelite handle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,22 +937,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Judge by Prestige Ace Aluminium Non-Stick Cookware Set - Kadai 20 cm, Fry Pan 20 cm, Omni Tawa 25 cm - 1 Unit Each, Black</t>
+          <t>Impex Migo Nonstick Cookware Set 3 Pcs | Induction Bottom | 5 Layer Super Granite Coating | 3mm Thick Aluminium | PFOA Free | Gas &amp; Induction Compatible | Detachable Chrome Handle | 1 Yr Warranty</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/515a2mz5TOL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/713olRvDhHL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0DG8M74Z8</t>
+          <t>https://www.amazon.in/dp/B0CW3G6ZQC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Durable Body | Low Oil Cooking | Easy to Maintain | Cool Touch Handle</t>
+          <t>🍳 𝐀𝐃𝐕𝐀𝐍𝐂𝐄𝐃 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Premium non-stick surface is 10X tougher than ordinary coatings, delivering smooth food release, effortless everyday cooking and easy cleanup for busy Indian kitchens. | ⚡ 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄: Versatile induction bottom cookware works seamlessly across gas stoves, induction cooktops and other cooking surfaces, making it a flexible pick for modern and traditional kitchens alike. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖 𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free, non-toxic aluminium construction lets you cook nutritious, healthier meals with minimal oil, while keeping harmful chemicals away from your everyday family food and health. | 🔥 𝐎𝐏𝐓𝐈𝐌𝐀𝐋 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊𝐍𝐄𝐒𝐒: Sturdy 3mm thick aluminium body ensures even heat distribution, faster heating and consistent cooking results, preventing hot spots so every dish cooks evenly and thoroughly every time. | ✋ 𝐃𝐄𝐓𝐀𝐂𝐇𝐀𝐁𝐋𝐄 𝐂𝐇𝐑𝐎𝐌𝐄 𝐇𝐀𝐍𝐃𝐋𝐄: Chrome-plated, sturdy detachable handle and knob provide a secure, comfortable grip while cooking, and allow for compact, space-saving storage in small, modern Indian kitchens. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓: Granite-finish non-stick surface is scratch resistant and simple to wipe clean, saving valuable time on daily kitchen chores while keeping the shine looking brand new. | 🍲 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟑 𝐏𝐂𝐒 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓: Ideal for frying, sauteing, tadka, curries and everyday Indian cooking, this practical cookware set gives you the essential pans needed for a fully equipped modern kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄 &amp; 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂: Health-conscious, food-grade aluminium construction is completely free from PFOA and harmful chemicals, ensuring safe, worry-free cooking for you and your entire family, every day. | 💎 𝐌𝐈𝐑𝐑𝐎𝐑-𝐋𝐈𝐊𝐄 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐅𝐈𝐍𝐈𝐒𝐇: Elegant granite finish gives your cookware a premium, modern look that enhances your kitchen decor while offering long-lasting, durable non-stick performance you can trust daily. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Backed by a 1 year manufacturer warranty, this Impex nonstick cookware set is reliable, durable and a perfect gift choice for new homes, weddings and housewarmings.</t>
         </is>
       </c>
     </row>
@@ -964,22 +964,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Impex Migo Nonstick Cookware Set 3 Pcs | Induction Bottom | 5 Layer Super Granite Coating | 3mm Thick Aluminium | PFOA Free | Gas &amp; Induction Compatible | Detachable Chrome Handle | 1 Yr Warranty</t>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|22 Cm Fry Pan,22 Cm Kadai,1 Glass Lid|Grey</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/713olRvDhHL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71NSco75mOL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CW3G6ZQC</t>
+          <t>https://www.amazon.in/dp/B0BZYDWLMV</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>🍳 𝐀𝐃𝐕𝐀𝐍𝐂𝐄𝐃 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Premium non-stick surface is 10X tougher than ordinary coatings, delivering smooth food release, effortless everyday cooking and easy cleanup for busy Indian kitchens. | ⚡ 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄: Versatile induction bottom cookware works seamlessly across gas stoves, induction cooktops and other cooking surfaces, making it a flexible pick for modern and traditional kitchens alike. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖 𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free, non-toxic aluminium construction lets you cook nutritious, healthier meals with minimal oil, while keeping harmful chemicals away from your everyday family food and health. | 🔥 𝐎𝐏𝐓𝐈𝐌𝐀𝐋 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊𝐍𝐄𝐒𝐒: Sturdy 3mm thick aluminium body ensures even heat distribution, faster heating and consistent cooking results, preventing hot spots so every dish cooks evenly and thoroughly every time. | ✋ 𝐃𝐄𝐓𝐀𝐂𝐇𝐀𝐁𝐋𝐄 𝐂𝐇𝐑𝐎𝐌𝐄 𝐇𝐀𝐍𝐃𝐋𝐄: Chrome-plated, sturdy detachable handle and knob provide a secure, comfortable grip while cooking, and allow for compact, space-saving storage in small, modern Indian kitchens. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓: Granite-finish non-stick surface is scratch resistant and simple to wipe clean, saving valuable time on daily kitchen chores while keeping the shine looking brand new. | 🍲 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟑 𝐏𝐂𝐒 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓: Ideal for frying, sauteing, tadka, curries and everyday Indian cooking, this practical cookware set gives you the essential pans needed for a fully equipped modern kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄 &amp; 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂: Health-conscious, food-grade aluminium construction is completely free from PFOA and harmful chemicals, ensuring safe, worry-free cooking for you and your entire family, every day. | 💎 𝐌𝐈𝐑𝐑𝐎𝐑-𝐋𝐈𝐊𝐄 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐅𝐈𝐍𝐈𝐒𝐇: Elegant granite finish gives your cookware a premium, modern look that enhances your kitchen decor while offering long-lasting, durable non-stick performance you can trust daily. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Backed by a 1 year manufacturer warranty, this Impex nonstick cookware set is reliable, durable and a perfect gift choice for new homes, weddings and housewarmings.</t>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 22 cm Fry Pan, 22 cm Kadai, 1 Glass Lid</t>
         </is>
       </c>
     </row>
@@ -991,22 +991,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Crystal Aluminum 6 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, Laddle &amp; Spatula | Durable 4 Layer Non Stick Coating | PFOA Free | Black</t>
+          <t>Pigeon Aluminium Nonstick Duo Pack Flat Tawa 250 and Fry Pan 200 Gift Set (Red)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Ks1TI+7TL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/510yXR4GoNL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H41G23NC?th=1</t>
+          <t>https://www.amazon.in/dp/B07KYPZHJ9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stylish granite finish cookware combo for modern kitchens | Compatible with induction and gas stove cooking | Durable nonstick surface for smooth cooking experience | Uniform heat distribution for efficient cooking | Scratch resistant and easy to maintain</t>
+          <t>5 Layer Durable Nonstick Coating. Broiler :Safe | Made with High End Italian Technology | Oil Free Cooking | Ergonomic Bakelite Handle | Free from Peel-Off</t>
         </is>
       </c>
     </row>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crystal Aluminum 6 Pcs Non Stick Cookware Set | Gas Stove Friendly | Tawa, Fry Pan, Kadhai with Lid, Laddle &amp; Spatula | Durable 4 Layer Non Stick Coating | PFOA Free | White</t>
+          <t>DOZY 5-Piece Non-Stick Cookware Combo Set with Kadhai, Tawa &amp; Tadka Pan Induction Bottom Non-Stick Coated Cookware Set (Iron-Rich Nonstick Cookware Combo)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81kqe9V4CML._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61c2sc0TNjL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H41D4CXQ?th=1</t>
+          <t>https://www.amazon.in/dp/B0H1WBB126?th=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Premium white marble coating for stylish appearance | Gas stove compatible cookware set | Smooth nonstick surface for easy cooking and cleaning | Ideal for healthy low oil cooking | Durable and sturdy construction for long-term use</t>
+          <t>COMPLETE 5-PIECE SET: Includes a Kadhai, Tawa, Tadka Pan, and additional cookware pieces to cover all your everyday Indian cooking needs. | PREMIUM NON-STICK COATING: Superior non-stick surface ensures food slides off effortlessly, making cooking and cleaning quick and hassle-free. | INDUCTION COMPATIBLE: Specially designed with an induction-friendly bottom, making this cookware set compatible with all types of cooktops. | ERGONOMIC HANDLES: Fitted with sturdy, heat-resistant handles for a secure and comfortable grip while cooking, ensuring safe handling at all times. | DURABLE CONSTRUCTION: Handcrafted from high-quality materials with even heat distribution for consistent, perfectly cooked results every time.</t>
         </is>
       </c>
     </row>
@@ -1045,22 +1045,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|22 Cm Fry Pan,22 Cm Kadai,1 Glass Lid|Grey</t>
+          <t>Hawkins Futura 5 Pieces Cookware Set 4 - Non Stick Kadhai, Two Frying Pans, Saucepan, Saute Pan and Two Glass Lids, Black (NSET4)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71NSco75mOL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61T0Fe6un2S._SX679_.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0BZYDWLMV</t>
+          <t>https://www.amazon.in/dp/B00EVR0CRY?th=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 22 cm Fry Pan, 22 cm Kadai, 1 Glass Lid</t>
+          <t>PFOA Free Non-stick coating locked into tough Hard Anodised Aluminium - lasts longer | The cookware set consists two Frying Pans, Deep-Fry Pan (Stir-Fry Pan), Saucepan with glass lid and Curry Pan (Sauté Pan) with glass lid to cater to most of your cooking needs | There is attractive saving on the purchase of the Set when compared with buying individual items separately | Each item included in the Set is accompanied by its own Instruction Manual / Cookbook and its own Guarantee Card | Suitable for use on domestic gas, electric, ceramic and halogen stoves</t>
         </is>
       </c>
     </row>
@@ -1072,346 +1072,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Crystal Classic Series 7-pc Non-Stick Induction Bottom Cookware Set, PFOA Free, Tawa, Fry-Pan, Kadhai with Glass Lid, Sauce Pan with 2 Serving Spoons, Red</t>
+          <t>Crystal Aluminum 11 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 3 Containers | 4 Layer Non Stick Coating | PFOA Free | White</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71-v9RBpQfL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71VFfXMdmeL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B09313HZ8B?th=1</t>
+          <t>https://www.amazon.in/dp/B0H41FL5NG?th=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | All items induction base except Sauce pan | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Pigeon Aluminium Nonstick Duo Pack Flat Tawa 250 and Fry Pan 200 Gift Set (Red)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/510yXR4GoNL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B07KYPZHJ9</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>5 Layer Durable Nonstick Coating. Broiler :Safe | Made with High End Italian Technology | Oil Free Cooking | Ergonomic Bakelite Handle | Free from Peel-Off</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Impex Non-Stick Cookware Set of 4 Pcs | Tawa Pan, Fry Pan &amp; Kadai with Glass Lid | PFOA-Free Triple Layer Coated Aluminium Kitchen Cookware Set | Bakelite Handle, Gas Stove Compatible | 1 Yr Warranty</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/717khrN3Z0L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CH1B2M1S</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟒-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐊𝐈𝐓𝐂𝐇𝐄𝐍: Includes a 24cm Kadai with Glass Lid, 24cm Tawa Pan and 24cm Fry Pan – a versatile non-stick cookware set for frying, roasting, sautéing, tadka and everyday Indian cooking needs at home. | 🥘 𝐓𝐑𝐈𝐏𝐋𝐄-𝐋𝐀𝐘𝐄𝐑 𝐍𝐎𝐍-𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐀𝐓𝐈𝐍𝐆 𝐅𝐎𝐑 𝐇𝐄𝐀𝐋𝐓𝐇𝐈𝐄𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free non-stick coated aluminium cookware ensures healthier low-oil cooking, effortless food release and quick, easy cleanup after every single meal you prepare. | 🔥 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐀𝐋𝐔𝐌𝐈𝐍𝐈𝐔𝐌 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝐄𝐕𝐄𝐍 𝐇𝐄𝐀𝐓 𝐃𝐈𝐒𝐓𝐑𝐈𝐁𝐔𝐓𝐈𝐎𝐍: Superior aluminium construction with heat-resistant exterior paint delivers fast, even heating and long-lasting performance for your everyday cooking in the kitchen. | ✋ 𝐂𝐎𝐌𝐅𝐎𝐑𝐓𝐀𝐁𝐋𝐄, 𝐒𝐄𝐂𝐔𝐑𝐄 𝐁𝐀𝐊𝐄𝐋𝐈𝐓𝐄 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy, heat-resistant bakelite handles are designed for a comfortable, secure grip while cooking, reducing the risk of burns and slips during daily kitchen use at home. | 🔍 𝐓𝐄𝐌𝐏𝐄𝐑𝐄𝐃 𝐆𝐋𝐀𝐒𝐒 𝐋𝐈𝐃 𝐅𝐎𝐑 𝐄𝐀𝐒𝐘 𝐌𝐎𝐍𝐈𝐓𝐎𝐑𝐈𝐍𝐆: The toughened glass lid on the Kadai lets you monitor food while it cooks, while retaining heat and moisture for evenly cooked, flavourful, delicious home-style dishes. | ⚡ 𝐆𝐀𝐒 𝐒𝐓𝐎𝐕𝐄 𝐅𝐑𝐈𝐄𝐍𝐃𝐋𝐘 𝐍𝐎𝐍-𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Designed with a non-induction bottom, this non-stick cookware set is ideal for gas stove kitchens, delivering consistent, reliable everyday cooking performance every time. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍, 𝐋𝐎𝐖 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: The smooth non-stick coated surface allows quick, effortless cleaning after cooking, saving valuable time on daily kitchen chores with no heavy scrubbing ever required. | 🎁 𝐈𝐃𝐄𝐀𝐋 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐍𝐄𝐖 𝐇𝐎𝐌𝐄𝐒: This multicolor 4-piece cookware set makes a thoughtful gift for weddings, housewarmings, anniversaries, or new homemakers setting up their very first kitchen space. | ✅ 𝐈𝐒𝐎 𝐂𝐄𝐑𝐓𝐈𝐅𝐈𝐄𝐃 𝐅𝐎𝐑 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Manufactured under ISO certification standards, this cookware set ensures premium quality, safety, and consistent performance you can rely on across every single piece. | 🛡️ 𝐖𝐎𝐑𝐑𝐘-𝐅𝐑𝐄𝐄 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 𝐀𝐒𝐒𝐔𝐑𝐀𝐍𝐂𝐄: Backed by Impex's 1-year manufacturer warranty, this cookware set gives you complete peace of mind and confidence in your everyday kitchen investment for years to come.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>DOZY 5-Piece Non-Stick Cookware Combo Set with Kadhai, Tawa &amp; Tadka Pan Induction Bottom Non-Stick Coated Cookware Set (Iron-Rich Nonstick Cookware Combo)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61c2sc0TNjL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H1WBB126?th=1</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>COMPLETE 5-PIECE SET: Includes a Kadhai, Tawa, Tadka Pan, and additional cookware pieces to cover all your everyday Indian cooking needs. | PREMIUM NON-STICK COATING: Superior non-stick surface ensures food slides off effortlessly, making cooking and cleaning quick and hassle-free. | INDUCTION COMPATIBLE: Specially designed with an induction-friendly bottom, making this cookware set compatible with all types of cooktops. | ERGONOMIC HANDLES: Fitted with sturdy, heat-resistant handles for a secure and comfortable grip while cooking, ensuring safe handling at all times. | DURABLE CONSTRUCTION: Handcrafted from high-quality materials with even heat distribution for consistent, perfectly cooked results every time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Amazon Solimo Aluminium 4 Piece Non-Stick Cookware Set | Granite Finish | Induction Base | PFOA Free | HTR Exterior Coating | 25 Cm Tawa, 22 Cm Kadai, 22 Cm Fry Pan, 1 Glass Lid | Grey</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71g3Y8X9hQL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BZY9PTHF?th=1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>HEAT CONDUCTIVITY: with die-cast aluminium, the fry pan provides high conductivity which enables quick heat distribution and even cooking | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | ELEGANT FINISH: It has a granite finish on the interior and the exterior which gives it an elegant look</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Hawkins Futura 5 Pieces Cookware Set 4 - Non Stick Kadhai, Two Frying Pans, Saucepan, Saute Pan and Two Glass Lids, Black (NSET4)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61T0Fe6un2S._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B00EVR0CRY?th=1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>PFOA Free Non-stick coating locked into tough Hard Anodised Aluminium - lasts longer | The cookware set consists two Frying Pans, Deep-Fry Pan (Stir-Fry Pan), Saucepan with glass lid and Curry Pan (Sauté Pan) with glass lid to cater to most of your cooking needs | There is attractive saving on the purchase of the Set when compared with buying individual items separately | Each item included in the Set is accompanied by its own Instruction Manual / Cookbook and its own Guarantee Card | Suitable for use on domestic gas, electric, ceramic and halogen stoves</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Crystal Aluminum 11 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 3 Containers | 4 Layer Non Stick Coating | PFOA Free | White</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71VFfXMdmeL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H41FL5NG?th=1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
           <t>Complete cookware set for versatile cooking requirements | Induction and gas stove compatible base | Elegant white marble nonstick interior and exterior | Even heat distribution for faster cooking | Heat resistant handles for safe and easy use</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Crystal 11 Pcs Non Stick Cookware Set with Storage Containers | Gas Stove Friendly | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 2 Containers &amp; Grater Set | PFOA Free Coating</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71q-5-ENFCL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H41FFYYF?th=1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Attractive white marble coated cookware combo | Gas stove compatible design for convenient cooking | Nonstick coating supports healthy cooking with less oil | Durable body for long-lasting usage | Elegant appearance suitable for every kitchen</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Amazon Basics Granite Finish Non Stick 5 Pcs Induction Base Cookware Set-Granito Grey (24cm Fry Pan, 24 cm Kadai, 28cm Tawa and 2 Nylon Spatulas)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71fcuPgHEBL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C2J76WPF?th=1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>DURABLE IMPORTED COATING: It comes with water-based coating imported from Japan which is compliant with US FDA and European Food Safety Authority (EFSA) standards. This cookware features three granite-finished coats each on its interior and exterior. It has been tested to last for more than 10,000 cycles. | HEALTHIER CHOICE: Its granite coating is free from PFOA, PTFE, lead, cadmiumm nickel and arsenic. This makes it safer and healthier to use than traditional non-stick cookware, which may contain harmful chemicals. | FAST, EVEN COOKING: Made from pressed aluminium, this cookware is ultra-conductive and corrosion-resistant. Its granite coating and flat, thick skillet bottom offer exceptional heat distribution to ensure even cooking and prevent hot spots. Overall, this cookware offers quick heating, thus using less energy. | REQUIRES LESS OIL: Cook a variety of healthy, delicious recipes for Indian households using this non-stick cookware set from Amazon Basics. It requires very little oil and cooks evenly and quickly without using much power. | CONDUCTIVE BASE: Its base is made from Aluminium and is highly magnetic and conductive. It features grooves that help retain heat. | COMPATIBLE WITH ALL COOKTOPS: The induction base with small perforation boosts faster cooking while helping you consume less electricity. This cookware is compatible with both gas-stove and induction cooktops. | COMFORTABLE TO HANDLE: The coookware is 3.5 MM thick with ideal weight distribution throughout the material for comfortable handling. | EASY TO CLEAN: Food particles are less likely to stick to the surface of the non-stick coating, making this cookware easy to clean. | CLEANING AND TEMPERATURE: We recommend hand-washing this cookware. Alternatively, you may clean it in a dishwasher with liquid detergent. It may be safely even at temperatures up to (200° and (260° C. | COLOUR: Granito Grey; PACKAGE CONTENTS: 1 tawa (28 cm), 1 fry pan (24 cm), 1 kadai (24 cm), 1 glass lid and 2 nylon spatulas; Thickness: 3.5 mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Amazon Brand - Solimo 3-Piece Aluminium Cookware Set - Fry Pan,Kadhai&amp;Tawa|2-Way 3 Layer Non-Stick Coating|Induction Friendly Design|Pfoa Free|High Temperature Resistant Exterior Coating,Maroon</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71bwxsfTaeL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B08637F7W2?th=1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>3 piece non-stick cookware set; frypan, kadhai with glass lid and tawa for convenient everyday cooking | Made using virgin aluminium for even heat distribution | Durable and long lasting with 3 layers of food grade non-stick coating facilitating minimal oil use while preventing stickiness and mess | Premium metallic finish with High Temperature Resistance (HTR) and a sleek shiny appeal | Bakelite handles provide a safe and firm ergonomic grip | Prepare rotis, chapatis, dosa, stir-fries, pulao, korma, sauteed vegetables as well as sear meats and fish, and fry eggs with this 3 piece cookware set | Can be used on gas stove and induction cooktops | Easy to clean and maintain; dishwasher safe | Warranty: 1 year warranty against manufacturing defects | Dimensions- Fry Pan:- Diameter: 220 mm (22 cm); Thickness: 3 mm; Depth: 45 mm (4.5 cm); Capacity: 1650 ml; Weight: 610 gm; Tawa:- Diameter: 265 mm (26.5 cm); Thickness: 3 mm; Depth: 13 mm (1.3 cm); Weight 615 gm; Kadhai:- Diameter: 220 mm (22 cm); Thickness: 3mm; Depth: 73 mm (7.3 cm); Capacity: 2500 ml; Weight: 1125 gm;Package Contents:- 1 Fry Pan, 1 Flat Tawa &amp; 1 Kadhai with 1 Glass Lid</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Wonderchef Valencia Plus Non-Stick Cookware 3 Piece Set | Kadhai, Glass Lid, Dosa Tawa | Cool Touch Bakelite Handles | Pure Grade Aluminium| PFOA Free| 1 Year Warranty | Purple</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51i43QAE0UL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GNT31PLH?th=1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>VERSATILE 3-PIECE SET - Kadhai, Glass Lid, Dosa Tawa let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | HEALTHY COOKING MADE EASY: MetaTuff 5-layer non-stick coating ensures minimal oil use, excellent abrasion resistance and is 00% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | VERSATILE: Cook delicious cutlets, stir-fry veggies, curries, dosas, uttapams, sandwiches, omelets, and parathas with the fry pan, kadhai, and tawa. Complete your cookware needs with Valencia set! | ENERGY-EFFICIENT: Pure grade virgin aluminium offers 9-times better heat conduction, cooking your meals faster while saving energy and time. | COMPATIBLE WITH ALL COOKING SURFACES - Use on gas cooktops, hot plates, infrared cooktops, and ceramic cooktops for maximum flexibility in your kitchen. | COMFORTABLE &amp; STYLISH - Cool touch Bakelite handles provide a firm grip and utmost convenience. Enjoy cooking with comfort and ease. | CONVENIENT: Easy to clean and dishwasher safe. Lightweight for daily use. | IDEAL FOR GIFTING - Loaded with features and beautiful looks, the Valencia cookware set is an ideal choice for gifting. Surprise your loved ones with a perfect addition to their kitchen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Crystal Classic Series 7-pc Non-Stick Cookware Set, PFOA Free, Red</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71bYDdKns5L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BD1JHYS7?th=1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart. | Soft touch bakelite handle</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Crystal Eco Plus 8-pc Non-Stick Cookware Set, PFOA Free, Tawa, Kadhai with SS Lid, Fry Pan, Vagariya, Mini Grill Pan, 2 Spatulas, Multicolor</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71oGMB2shTL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BD1JLNKM?th=1</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart. | Soft touch bakelite handle</t>
         </is>
       </c>
     </row>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,6 +1091,466 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AUSK Men's Retro Cable-Knit Quarter-Zip Polo | Premium Textured Self-Design Half Sleeve T-Shirt for Men</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51o3uMcvGSL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GJDMLG33?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Lymio Polo T Shirt for Men || T Shirt for Man || Collar T Shirt Style Men (Packs Also Available) (Polo-40-43)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61xTfKaqUlL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DP7PQX5Y?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AUSK Baggy Hip-Hop T-Shirt for Men - Graphic Printed T Shirts || Oversized Men Tshirt || T-Shirts</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51kJ2ga3xUL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GKV18R4N?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AUSK Men Printed Polo Neck Cotton Blend T-Shirt (Regular Fit, Half Sleeve) || Tshirts for Mens</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51uzisX1fyL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GKV3BNWF?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BULLMER Trendy Printed Cotton Blend Crew Neck/Round Neck Half Sleeve Tshirt for Men - Pack of 3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61D2GVIp-RL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DJYKXCSP?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Lux Cozi Men's Half Sleeve Soild Casual Regular Fit T-Shirt with Chest Pocket | Polo Tshirt for Men</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61Qrj5J9F-L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CVXQ9SKB?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KAJARU Men's Polyester Blend T Shirt with Spread Collar Neck Line Zipper Closure Full Sleeves Solid Pattern Regular Fit and Standard Length</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81l69obPixL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FFMJKFK4?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Symbol Men's Cotton Rich Solid Polo Tshirt | Collar Tshirts | Half Sleeves | Plain-Regular Fit (Available in Plus Sizes and Combo Pack of 2)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/713n+TxyfCL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07MZM26XG?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AUSK Men's Cotton Blend Rib Knit Textured Full Sleeve Polo T-Shirt | Regular Fit Zip Polo Neck Smart Casual T Shirt for Men | Stylish Fashion &amp; Casual Wear Tshirt for Men</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41vtYsBbRdL._SX342_SY445_QL70_FMwebp_.jpg</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H9LQZZQW?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AUSK Men's Zip Collar Polo Tshirt | Cotton Rich Material | Half Sleeves | Modern Knit Panel Work | Regular Fit</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61DCbAmebML._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GZPTV35B?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lux Cozi Men Cotton Half Sleeves Round Neck Regular Fit Casual T-Shirt</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61MJ6BrekXL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D39544VM?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FTX Men Polyester Regular Fit T-Shirt</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71+RZzHylcL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BPSWKRWV?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Peter England Men's Regular Fit Insignia Half Sleeve Polo T-Shirt | Cotton Rich | Premium Pique Weave</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61D2tQq2tJL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09XMV4T3Q?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Men's Premium Waffle Knit Henley Tshirt for Men</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41yKXwNNzAL.jpg</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H74X4CCD?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Allen Solly Men’s Polo T‑Shirt | Comfortable Rich Cotton Blend, Band Collar, Regular Fit | Stylish &amp; Premium All Day Wear</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61lNvbdEtiL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B06Y2BZJN6?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Noble Monk Men T-Shirt</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81I400aM+8L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GRWFS3WD?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>INKKR Men's Polo Neck Half Sleeve Solid T-Shirts</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71f0cHk7vML._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08MFL782K?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LEOTUDE Men's Half Sleeve Round Neck Cottonblend Graphic Print Oversized</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61WYx598KKL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FHDL7JY8?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Max Men's Polycotton Half Sleeves Regular Fit Solid Polo T-Shirt</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51415tyNDEL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09KCJNKBX?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Van Heusen Men's Cotton Solid Regular Fit Collar Polo T-Shirt</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51IeycKBNkL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B076CJHDGZ?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AUSK Men's Retro Cable-Knit Quarter-Zip Polo | Premium Textured Self-Design Half Sleeve T-Shirt for Men</t>
+          <t>Lymio Polo T Shirt for Men || T Shirt for Man || Collar T Shirt Style Men (Packs Also Available) (Polo-40-43)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51o3uMcvGSL._SX569_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61xTfKaqUlL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GJDMLG33?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0DP7PQX5Y?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lymio Polo T Shirt for Men || T Shirt for Man || Collar T Shirt Style Men (Packs Also Available) (Polo-40-43)</t>
+          <t>AUSK Baggy Hip-Hop T-Shirt for Men - Graphic Printed T Shirts || Oversized Men Tshirt || T-Shirts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61xTfKaqUlL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51kJ2ga3xUL._SX569_.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0DP7PQX5Y?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0GKV18R4N?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AUSK Baggy Hip-Hop T-Shirt for Men - Graphic Printed T Shirts || Oversized Men Tshirt || T-Shirts</t>
+          <t>BULLMER Trendy Printed Cotton Blend Crew Neck/Round Neck Half Sleeve Tshirt for Men - Pack of 3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51kJ2ga3xUL._SX569_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61D2GVIp-RL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GKV18R4N?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0DJYKXCSP?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1168,388 +1168,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AUSK Men Printed Polo Neck Cotton Blend T-Shirt (Regular Fit, Half Sleeve) || Tshirts for Mens</t>
+          <t>Lux Cozi Men's Half Sleeve Soild Casual Regular Fit T-Shirt with Chest Pocket | Polo Tshirt for Men</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51uzisX1fyL._SX569_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61Qrj5J9F-L._SY741_.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GKV3BNWF?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0CVXQ9SKB?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BULLMER Trendy Printed Cotton Blend Crew Neck/Round Neck Half Sleeve Tshirt for Men - Pack of 3</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61D2GVIp-RL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DJYKXCSP?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Lux Cozi Men's Half Sleeve Soild Casual Regular Fit T-Shirt with Chest Pocket | Polo Tshirt for Men</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61Qrj5J9F-L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CVXQ9SKB?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>KAJARU Men's Polyester Blend T Shirt with Spread Collar Neck Line Zipper Closure Full Sleeves Solid Pattern Regular Fit and Standard Length</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81l69obPixL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FFMJKFK4?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Amazon Brand - Symbol Men's Cotton Rich Solid Polo Tshirt | Collar Tshirts | Half Sleeves | Plain-Regular Fit (Available in Plus Sizes and Combo Pack of 2)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/713n+TxyfCL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B07MZM26XG?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>AUSK Men's Cotton Blend Rib Knit Textured Full Sleeve Polo T-Shirt | Regular Fit Zip Polo Neck Smart Casual T Shirt for Men | Stylish Fashion &amp; Casual Wear Tshirt for Men</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41vtYsBbRdL._SX342_SY445_QL70_FMwebp_.jpg</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H9LQZZQW?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>AUSK Men's Zip Collar Polo Tshirt | Cotton Rich Material | Half Sleeves | Modern Knit Panel Work | Regular Fit</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61DCbAmebML._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GZPTV35B?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Lux Cozi Men Cotton Half Sleeves Round Neck Regular Fit Casual T-Shirt</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61MJ6BrekXL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D39544VM?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>FTX Men Polyester Regular Fit T-Shirt</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71+RZzHylcL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BPSWKRWV?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Peter England Men's Regular Fit Insignia Half Sleeve Polo T-Shirt | Cotton Rich | Premium Pique Weave</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61D2tQq2tJL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09XMV4T3Q?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Men's Premium Waffle Knit Henley Tshirt for Men</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41yKXwNNzAL.jpg</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H74X4CCD?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Allen Solly Men’s Polo T‑Shirt | Comfortable Rich Cotton Blend, Band Collar, Regular Fit | Stylish &amp; Premium All Day Wear</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61lNvbdEtiL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B06Y2BZJN6?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Noble Monk Men T-Shirt</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81I400aM+8L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GRWFS3WD?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>INKKR Men's Polo Neck Half Sleeve Solid T-Shirts</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71f0cHk7vML._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B08MFL782K?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>LEOTUDE Men's Half Sleeve Round Neck Cottonblend Graphic Print Oversized</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61WYx598KKL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FHDL7JY8?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Max Men's Polycotton Half Sleeves Regular Fit Solid Polo T-Shirt</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51415tyNDEL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09KCJNKBX?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Van Heusen Men's Cotton Solid Regular Fit Collar Polo T-Shirt</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51IeycKBNkL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B076CJHDGZ?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1183,6 +1183,466 @@
       </c>
       <c r="E29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2-Piece Multifunctional Vegetable Peeler with Ergonomic Wooden Handle, Heavy Duty Stainless Steel 2-in-1 &amp; 3-in-1 Kitchen Tool with Scallion Shredder &amp; Built-in Bottle Opener for Home Cooking</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/614ZeFf98-L._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H7JWZNQP</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VERSATILE 2-PIECE MULTIFUNCTIONAL SET – Streamline your kitchen preparation with this premium 2-pack tool set. Includes a highly efficient 2-in-1 and 3-in-1 multi-tool peeler designed to replace multiple bulky kitchen gadgets, saving you precious drawer space while conquering daily culinary tasks. | ULTRA-SHARP, ODORLESS STAINLESS STEEL – Engineered with professional-grade, rust-resistant stainless steel blades that glide smoothly through tough skins. The odorless material ensures no metallic or leftover food odors transfer between ingredients, keeping your potatoes, carrots, and apples tasting completely fresh. | ERGONOMIC REAL WOODEN HANDLE – Experience ultimate comfort and superior control. The classic, beautifully crafted wooden handle provides a secure, non-slip grip that conforms naturally to your hand, reducing wrist fatigue during extended meal prep or holiday cooking sessions. | INTEGRATED SCALLION SHREDDER &amp; BOTTLE OPENER – Do more with less. The innovative 3-in-1 peeler features an integrated precision scallion shredder for uniform veggie ribbons and garnishes, alongside a heavy-duty, built-in bottle opener to conveniently open refreshments while hosting or cooking. | THE ULTIMATE HOME COOKING COMPANION – Perfect for julienning, shredding, peeling, and grating. This highly durable set makes an exceptional gift for home chefs, newlyweds, or culinary enthusiasts looking to elevate their food styling, veggie prep, and everyday home cooking efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dry Fruit Cutter &amp; Slicer Gadgets (3 in 1, Mix Colour) Kitchen Tools Kitchen Gadgets Dryfruit Choppers for Kitchen, Stainless Steel Blade, Green, Blue, Red</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71MbwrhpzlL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B853XRLJ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>UNMATCHED QUALITY – Chop, Dice, Slice or Grate with our newest Multi Chopper and Slicer by Mueller! This functional kitchen gadget will alleviate your prep time to just a couple of minutes. Made with premium materials like steel blades and food-grade BPA-free materials, it's the perfect tool to make home-cooked meals easier and faster. | SAFER: The unique design kitchen tool prevents your hands from ever going near the built-in blades, making this mandoline the safest option for an expert slice. | INNOVATIVE DESIGN - Don't need more space in your kitchen free up countertop space with this kitchen gadgets. Use the Dry Fruits Slicer while cutting Dry fruits. This prevents Dry fruits from slipping while slicing them. It also makes it clean, safe, and easy to work with. No more hassles of washing and wiping. | RUST RESISTANT - Heavy-duty 420 stainless steel blades razor sharpness for crisp, smooth slicing &amp; cutting. Blades snap in and out with ease. | IMPROVES YOUR HEALTH &amp; SAVE TIME – Busy lifestyles make us fall into the fast-food trap. It can take a lot of time and effort to dice, chop and slice the ingredients of the desired dish. Do not despair. Our multi-functional kitchen tool makes this process less time-consuming making it easier to slice dry fruits. That being said, you’re less likely to reach for unhealthy options. From now on, enjoy having more time for your family without missing out on any of the important nutrition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2-Piece Vegetable Peeler Set, Multifunctional Stainless Steel Vegetable &amp; Fruit Peeler with Ergonomic Wooden Handle, 2-in-1 &amp; 3-in-1 Kitchen Tool with Scallion Shredder &amp; Bottle Opener</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612Sbd4GeDL._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HGMCSZ7V</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MULTIFUNCTIONAL KITCHEN TOOL: Peel vegetables and fruits, shred scallions, and open bottles with this versatile kitchen peeler set. Designed to handle everyday food-preparation tasks with fewer tools cluttering your kitchen drawer. | SHARP STAINLESS STEEL BLADE: Made with a durable stainless steel peeling blade for smooth, efficient peeling of potatoes, carrots, cucumbers, apples and other fruits and vegetables. The practical design helps make daily meal preparation faster and easier. | COMFORTABLE WOODEN HANDLE: Ergonomic wooden handles provide a comfortable, natural grip and easy control while peeling and preparing ingredients. The lightweight design is convenient for everyday cooking at home. | 2-PIECE VALUE SET: Includes two multifunctional peelers so you can keep one handy at your main prep area and another available for different ingredients or kitchen tasks. A practical addition to everyday cooking and meal preparation. | IDEAL FOR EVERYDAY COOKING: A useful kitchen accessory for home cooks, food preparation, meal prep and everyday kitchen tasks. Compact and multifunctional, it also makes a practical gift for cooking enthusiasts, new homeowners and anyone who enjoys convenient kitchen tools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ganesh Round Masher Kitchen Gadget with Non-Slip Handle, Masher Utensil for Mashed Potato, Vegetables</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61ECYzDsEsL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C818Z214</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>This potato masher is made of stainless steel, so you don't need to worry about safety of your baby and families. Also it possess higher durability and comfort and long time use is guaranteed. It is not easy to rust | Easy In Use and Clean – There are different kitchen essentials in the market but our potato ricer masher is extremely easy to use and can be cleaned under the tap water, after that it is ready for next use. | Perfect use in mashing potatoes, vegetables, sweet potatoes, boiled eggs, cheese etc. You don’t need any mixer for your kitchen as our masher can be use in different ways to save the time and money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Samta Stainless Steel Garlic Press Crusher Manual Garlic &amp; Ginger Presser for Kitchen | Garlic Crusher Chopper Tool | Dishwasher Safe Curved Garlic Grinding Slicer | Multipurpose Cooking Gadget</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71RPI68L-qL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FZK9LFW3</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>🧄 Effortless Garlic &amp; Ginger Crushing: Easily crush and press garlic or ginger with minimal effort using this strong stainless steel kitchen tool. | 🔪 Curved Ergonomic Design: Features a comfortable curved handle for better grip and efficient pressing—perfect for daily cooking use. | 💪 Durable Stainless Steel Build: Made from high-quality rust-resistant stainless steel for long-lasting performance and strength. | 🧼 Dishwasher Safe &amp; Easy to Clean: Simply rinse under running water or toss in the dishwasher for quick cleanup—no mess, no hassle! | 🧂 Multi-Function Kitchen Tool: Use it as a garlic presser, ginger crusher, or even for soft veggies—an all-in-one prep tool for your kitchen. | 👌 Compact &amp; Handy Design: Small yet powerful, the compact design makes it easy to store and perfect for small or busy kitchens. | 🎁 Ideal Cooking Gadget Gift: A practical and thoughtful gift for home cooks, chefs, or kitchen lovers who appreciate time-saving tools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ganesh 14 in 1 Multipurpose Chopper, Fruits &amp; Vegetable Cutters, Grater Peeler Chipser, Unbreakable Food Grade Body, Easy Push to Clean Button Slicer Dicer, Chopper for Kitchen (Green, Plastic)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71SSpHadzXL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B01BVDS1BE?th=1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Large break resistant container with rubber grip base which holds the device firmly in place | Fastest, safest and easiest way to chop or dice fruits and vegetables ; Not Dishwasher Safe ; Other Features: Easy To Use, Clean and Store, Hand Operated, No Electricity Needed, The Container Is Break Resistant, Extra Sharp Stainless Steel Blades | Advanced push to clean button which ensures easy and hygienic cleaning | High-quality stainless steel blades for easy chopping, Sharp pyramid-shaped cutting blade for efficient and smooth cutting | Large detachable container which can also be used to store vegetable and fruits in refrigerator | Colour: Green, Material: Plastic and Stainless Steel, Shape: Rectangle | Package Contents: 1 Plastic Container, 1 peeler with grater, 1 safety holder, 1 masher &amp; 1 handle with cleaning press | Blades: 1 dual, 2 slicer, 2 grater, 1 Juliane, blade die attachment</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Solitude Dry Fruit Cutter, Slicer, Grinder, Chocolate Cutter and Butter Slicer with 3 in 1 Blade Kitchen Tools, Gadgets for Almonds, Cashews etc (Stainless Steel, 1 Piece)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/715ytJXxIXL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BR5RJHZR?th=1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>❖ 𝐒𝐭𝐫𝐮𝐠𝐠𝐥𝐢𝐧𝐠 𝐖𝐢𝐭𝐡 𝐓𝐨𝐮𝐠𝐡 𝐃𝐫𝐲 𝐅𝐫𝐮𝐢𝐭𝐬? The Solitude dry fruit cutter comes with a non-detachable stainless steel blade that can slice dry fruit so easily. | ❖ 𝐏𝐫𝐞𝐜𝐢𝐬𝐢𝐨𝐧 𝐂𝐮𝐭𝐭𝐢𝐧𝐠 𝐌𝐚𝐝𝐞 𝐄𝐚𝐬𝐲: With sharp stainless steel blades, the Solitude Dry Fruit Cutter effortlessly slices through dry fruits, providing precise cuts and uniform slices every time. | ❖ 𝐄𝐟𝐟𝐞𝐜𝐭𝐢𝐯𝐞 𝐆𝐫𝐢𝐧𝐝𝐢𝐧𝐠: Transforms tough dry fruits into fine powder or coarse grind to suit your preferences, and it is perfect for preparing garnishes, salads, and baking ingredients. | ❖ 𝐔𝐬𝐞𝐫-𝐅𝐫𝐢𝐞𝐧𝐝𝐥𝐲 &amp; 𝐒𝐚𝐟𝐞: Ergonomically designed with a comfortable grip, the Solitude Dry Fruit Cutter promises smooth slicing while prioritising safety with a secure locking mechanism and non-slip base. | ❖ 𝐇𝐚𝐬𝐬𝐥𝐞-𝐅𝐫𝐞𝐞 𝐂𝐥𝐞𝐚𝐧 𝐚𝐧𝐝 𝐌𝐚𝐢𝐧𝐭𝐞𝐧𝐚𝐧𝐜𝐞: Our easy disassembly design ensures effortless cleanup. Detachable parts allow for thorough washing, and it's also dishwasher safe, streamlining your post-cooking cleanup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EXQ HOME Glass Basting Set Silicone Oil Dispenser Pastry Brush Docking Bowl Set for Cooking, BBQ, Baking and Grilling, Innovative Kitchen Gadget</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41uTsM041TL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DDT7VX7M</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Product material: The oil brush is made of food-grade organic silicone, which is thick, soft, and elastic. The oil bottle is hand-made of plastic, which can withstand 450 degrees of high temperature. | Easy to use: The bottleneck is large, it is easy to fill the liquid, and will not overflow, Our unique design lightly pinchs the hose to easily obtain the required amount of oil, and the oil brush can be used to remove the remaining oil, and it can be used repeatedly after cleaning without odor It is convenient to observe the distribution | Reasonable design: The large-head brush has a wider audience and makes it easier to apply oil. The round bottle design is more stable, the lid has a good seal, and the liquid will not overflow and make the bottle greasy. | Use occasion: The oil bottle brush is used for outdoor BBQ or kitchen cooking, home barbecue, baking, fried eggs, and pizza, and can also add vinegar, egg liquid, honey, and other different liquids. You can microwave butter in the plastic jar to brush onto marinades or salad dressing on your meats or vegetables | Easy to use and easy to clean: The newly designed silicone basting brush is dishwasher safe, which makes cleaning so easy! The individual parts come apart for a hassle-free cleaning experience. Focus more on enjoying the food and less on doing the dishes! | Package Includes: Silicone Oil Brush + Plastic Docking Bowl Set | Color: Multi, Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ekaarav ® Stainless Steel Corn Peeler – Heavy Duty Cob Stripper Tool for Kitchen, Removes Kernels in Seconds, Sharp Serrated Blade, Comfortable Grip (Pack of 1)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/615R4eFnoLL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DRV5NJNF?th=1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Heavy Duty Stainless Steel – Made from solid 304 stainless steel; rustproof, durable, and built to last. | Sharp Serrated Blade – Quickly removes corn kernels with ease; a perfect corn peeler and corn remover tool. | Comfortable Grip – Smooth handle for a secure hold while peeling and cutting corn effortlessly. | Multi-Use Kitchen Tool – Ideal as a corn cutter, sweet corn peeler, and general kitchen tool for home or commercial use. | Quick &amp; Easy – Strips kernels in seconds, saving time whether prepping salads, soups, or desserts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TrendPlain 16oz/470ml Olive Oil Sprayer for Cooking - 2 in 1 Olive Oil Dispenser for Kitchen Gadgets, Air Fryer, Salad, and BBQ - Green, Glass</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612-b6FTtbL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CNK6BPTV?th=1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Dual Dosing Convenience: These Kitchen Oil Bottles Offer Both Pouring And Spraying Options, Allowing You To Easily Switch Between The Two. It'S A Space-Saving Solution That Keeps Your Kitchen Clean And Organized. | ?Exceptional Spray Nozzle Design?Our Olive Oil Bottle Features A Unique Spray Nozzle That Delivers A Wide-Angle, Fine Mist When Pressed Quickly And A Steady Stream Of Oil When Pressed Slowly. This Precise Design Ensures Even Coverage And Control Over Your Oil Consumption. | Precise Oil Control: Each Spray Dispenses Approximately 0.15G Of Oil, Making It Easy To Monitor And Measure Your Daily Oil Intake. With A Daily Recommended Oil Consumption Of Up To 30G, You Can Effortlessly Manage Your Dietary Preferences. | Safe And Odorless Materials: Made Of Glass, Our Olive Oil Spray Is Both Safe And Non-Toxic. It Can Withstand High Temperatures And Is Completely Odorless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Stainless Steel Coconut Slicer Cutter Tool for Kitchen | Coconut Opener, Grater, Scraper, White Remover | Heavy Duty Thengai Thuruvi | Manual Kitchen Accessories Items for Home Use (Pack of 1)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61uOzEkFBQL._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F92QK9NZ</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Heavy Duty Coconut Slicer &amp; Cutter 🥥🔪 – Made with premium stainless steel, this manual Thengai Thuruvi is perfect for grating, scraping, and cutting coconuts easily and safely at home. | Multi-Use Kitchen Tool 🍽️✨ – Functions as a Coconut Opener, Grater, Scraper, and White Remover; ideal for traditional Indian cooking, chutneys, and sweets. | Rustproof &amp; Long-Lasting 🛡️✔️ – Crafted for durability with corrosion-resistant stainless steel, ensuring years of hassle-free use without losing sharpness or quality. | Ergonomic &amp; Easy to Use 🤲👌 – Designed for smooth handling, lightweight construction, and effortless cleaning, making it a must-have kitchen accessory. | Perfect for Home Cooking &amp; Festive Recipes 🎉🍛 – Essential for preparing authentic South Indian dishes, coconut chutney, laddoos, and other delicacies with ease. | Compact &amp; Space Saving 📦🏠 – Convenient size fits easily in kitchen drawers or shelves, making storage simple without cluttering your cooking space. | Trusted Kitchen Accessories for Every Household 🏡❤️ – Ideal for daily use or gifting; enhances your kitchen experience with efficiency, safety, and superior performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Stainless Steel 6-Piece Kitchen Gadgets Set, Kitchen Scissors, Kitchen Utensils Set with Holder, Paring Knife, Whisk, Bottle Opener, Peeler- Anti-Slip Handle, Decorative Base,</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61R-5RNwl0L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F3JQXP8V</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>VERSATILE SET: Includes paring knife, whisk, bottle opener, peeler and other kitchen gadgets for essential cooking tasks | HIGH-QUALITY MATERIALS: Knives are made of strong stainless steel blades with plastic handles for comfort and durability | ASSORTED SIZES: Variety of tools from a 3-inch paring knife to 8-inch chef's knife for fruits, veggies and more | KITCHEN ESSENTIALS: All the basic appliances needed for preparing, mixing and opening to make cooking easy and efficient | DURABLE AND SAFE: Stainless steel won't rust or stain and smooth edges on tools help prevent cuts for safe daily use</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pigeon Polypropylene Mini Handy and Compact Chopper with 3 Blades for Effortlessly Chopping Vegetables and Fruits for Your Kitchen (12420, Green, 400 ml)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51RXzjrUmkL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B01LWYDEQ7?th=1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Unique string function to chop vegetables and fruits with ease;Package Contents: 1-Piece Handy Chopper.Blade Length: 3 centimeters | Eco-friendly design, no electricity required;Warranty: 30 Days Warranty, Only On Manufacturing Defects | Made from unbreakable ABS plastic for long-lasting use, Material: Polypropylene (PP);Sturdy 3-blade design made from Stainless Steel, As this chopper by Pigeon can be opened and detached easily, cleaning is an easy task using lukewarm water, mild detergent and a soft cloth.Power Requirement: Manual | Colour: Green, Material: Plastic | Size Name: Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Clazkit Stainless Steel Coconut Opener Tool, Coconut Driller, Coconut Opener Machine, Coconut Opener Knife, Coconut Water Opener- (Pack- 1)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/6159Kc-wHpL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CG68ZK2G</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Simply Pop off the top of the coconut, the tool will crack an opening you can remove to either pour out the water or simply insert a straw. | Constructed of Durable FOOD GRADE Stainless Steel.This is the safest way to open green coconut. | Comfortable Rubber Handle for easy opening every time.No Knives, No Machete, No Power Drills, No Hammers!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RERANT Plastic 3 in 1 Soap Pump Dispenser Dish Soap Liquid Dispenser Sponge Holder Dish Soap Pump Dispenser for Kitchen Sink Countertop Kitchen Bathroom (Multi-Color) (Multicolour)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/618xrswsstL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F84892TQ</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RERANT Compact Design: This 3-in-1 dispenser measures 19.50 cm in length, 10.25 cm in height, and 9 cm in width, making it a space-saving solution for your kitchen or bathroom countertop. | RERANT Multi-Purpose: It combines a liquid soap pump dispenser, a sponge holder, and a detachable dish for added convenience. | RERANT Durable Construction: Crafted from high-quality plastic, this dispenser is built to withstand daily use and retain its vibrant colours. | RERANT Easy to Refill: The pump mechanism allows for effortless refilling of your preferred liquid soap or detergent. | RERANT Versatile Placement: Its sleek design complements various kitchen and bathroom decors, allowing you to place it wherever it's most accessible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vegetable Chopper Mandoline Slicer Home Kitchen Appliance Essential Gadget</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81RvBMCJ4NL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G6Z4TVJG?th=1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Unmatched Quality - The blades is made of 420 stainless steel using Dewpeton unique punching blade technology, razor sharp for crisp, smooth cuts and grating. Can create perfectly chopped onions, tomatoes, and peppers for salsa, or shred an entire cabbage for coleslaw in no time. The main body of the vegetable chopper is made from food-grade ABS plastic to guarante healthy meals for your family. | Meet Various Needs - Contains 2 different sized chopper blades and 5 interchangeable blades, offer the functionality of multiple kitchen tools in just one, highly versatile, kitchen gadget, meet all your slicing, shredding, grating needs. There is an egg white separator include,to easily separate egg whites from yolks. Can cut most types of vegetables and fruits as potato, tomato, cucumber, carrot and cheese. Can make WAFFLE FRIES OR RUFFLED POTATO CHIPS. | Improves Your Health And Saves Time - With our functional kitchen gadget, you can free your hand on chopping, slicing and cutting, help you cook like a pro, making it easier to add vegetables to your meals. With faster prep &amp; faster cleanup you can live your best, healthiest life every day. Allows you to spend less time preparing food and enjoying more time for your family without missing out on any of the important nutrition. | 1.5L Large Container - Built-in chop lid lets you cut foods directly into the 1.5L collection tray without the mess of a knife and cutting board. Storage container lets you hold prepared vegetables in the Dewpeton Vegetable Cutter until you are ready to begin cooking. Free-up countertop space with the Food Container. And Dewpeton mandoline slicer can be fully disassembled with ease and stored in the container. Its compact size allows you to store it almost anywhere. | Safety &amp; Easy to Use - Blades snap in and out with ease, no need to touch the blade. Comes with a fingerguard to keep you safe whilst using and a cleaning brush + blade organizer thorough and convenient cleaning when aren’t. Soft grip handle with rubberized tpu enhances leverage while the non-skid base ensures stability during use. It can be fully disassembled for easy cleaning on the top shelf of your dishwasher. After rinsing and drying, please collect them into the container.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Garlic Press Rocker Stainless Steel | Premium Garlic Crusher &amp; Mincer with Silicone Peeler | Heavy Duty Manual Garlic Masher for Ginger, Garlic &amp; Herbs | Easy Clean Kitchen Tool New 2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/7151bZo8kTL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H6TZHSN7</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>🧄 CRUSH GARLIC IN SECONDS Effortlessly mince garlic cloves with a simple rocking motion. Creates finely crushed garlic quickly without complicated mechanisms, making meal preparation faster and easier. | 💪 HEAVY-DUTY STAINLESS STEEL BUILD Made from premium food-grade stainless steel for strength, durability, rust resistance, and long-lasting performance. Designed for everyday kitchen use. | ✨ ERGONOMIC COMFORT GRIP Curved ergonomic handle provides a comfortable grip and reduces hand strain while pressing. Suitable for regular cooking, meal prep, and everyday kitchen tasks. | 🧽 EASY TO CLEAN DESIGN Open structure allows garlic residue to rinse away easily under running water. Dishwasher safe design helps save cleaning time after cooking. | 🌿 MULTIPURPOSE KITCHEN TOOL Perfect for garlic, ginger, herbs, small vegetables, and seasoning preparation. A practical kitchen accessory for Indian cooking, curries, gravies, marinades, and sauces. | 🏠 COMPACT &amp; SPACE SAVING Lightweight and compact design fits easily inside kitchen drawers, cabinets, utensil holders, and kitchen organizers without occupying extra space. | 🎁 PERFECT GIFT FOR HOME CHEFS An ideal kitchen gadget for home cooks, food lovers, newly married couples, housewarming gifts, and anyone who enjoys convenient cooking tools. | garlic press garlic crusher garlic mincer garlic press rocker stainless steel garlic press garlic chopper garlic crusher stainless steel manual garlic press garlic rocker garlic ginger crusher garlic mincer stainless steel garlic press tool garlic mashing tool garlic pressing tool garlic press stainless steel garlic crusher and mincer best garlic press garlic press for kitchen garlic press manual easy clean garlic press heavy duty garlic press professional garlic press kitchen garlic crusher garlic cutter tool garlic grinding tool garlic press for ginger garlic mincer tool | garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker garlic crusher stainless steel garlic ginger crusher manual garlic press garlic chopper garlic mincer tool best garlic press easy clean garlic press heavy duty garlic press professional garlic press garlic press for kitchen garlic crusher tool garlic press stainless steel heavy duty garlic rocker stainless steel ginger garlic crusher garlic mincing tool garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CRIYALE Silicone Baking Mat Sheet | Roti Making Mat | Table Placemat Pad | Silicon Fondant Rolling Mat | BPA-Free Non-Stick Pastry Board Matt | Dough Making Kitchen Gadgets Cooking Tools (Pink)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Iqs+xTutL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C1G82FKF?th=1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Roti Mat for Kneading, Rolling, and Shaping Breads, Pizza Dough's, Pastas, Pastries, Pie Crusts and fondants. Provides a Clean Extra-Large Baking or Cooking Preparation Surface. Makes the Perfect Gift! | Light weight, easy to clean and use. | Will keep your worktop clean. No more scrapping dough or fondant off the worktop | Mat with pre-marked circles helps you get the perfect amount of fondant or dough and the easy-glide material allows you to rotate the mat as you roll | Great surface for kneading dough or rolling out dough and pastries</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GwernKB 4-in-1 Manual Knife Sharpener Tool for Kitchen, Kitchen Knife Sharpener for Home with Tungsten Steel &amp; Ceramic Slots, Scissor Slot, Non-Slip Base &amp; Ergonomic Handle</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51IlMlDyvbL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H86ZG11G?th=1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1️⃣ 4-IN-1 MANUAL KNIFE SHARPENER TOOL🔪 Restore dull kitchen blades with 4 precision sharpening slots designed for scissor sharpening, coarse repair, fine sharpening and polishing. A practical knife sharpener tool for everyday home kitchens. | 2️⃣ TUNGSTEN STEEL &amp; CERAMIC SHARPENING SYSTEM✨ Built with strong sharpening slots to help improve blade edges smoothly and consistently. Ideal for maintaining chef knives, utility knives, paring knives, slicing knives and cleavers. | 3️⃣ SAFE, STABLE &amp; COMFORTABLE GRIP🖐️ The ergonomic handle gives steady control for left and right-hand use, while the non-slip base helps keep the sharpener stable on your kitchen counter during sharpening. | 4️⃣ DETACHABLE SHARPENING UNIT FOR EASY CLEANING🧼 Designed for convenient maintenance, the sharpening unit can be removed and cleaned easily after use, helping keep your kitchen knife sharpener hygienic and ready for daily use. | 5️⃣ COMPACT KITCHEN SIZE FOR HOME USE🏡 With its space-saving design, this kitchen knife sharpener for home fits easily on most countertops and drawers. Suitable for straight-edge kitchen knives and scissors. Not suitable for serrated or wavy-edge knives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unify Stainless Steel Phulka Grill Jali for Gas Stove with Free Oil Brush | Roti Grill, Papad Roaster, Baingan Bharta Roaster | Heavy Gauge Steel Mesh Griller | Multi-Purpose Kitchen Cooking Tool</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71aw2TLRtQL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FWZSJ3BN</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MULTI-PURPOSE PHULKA GRILL FOR KITCHEN COOKING:-Enjoy perfectly roasted phulkas, rotis, papads, and baingan bharta with the Unify Stainless Steel Phulka Grill Jali for Gas Stove. This multi-purpose kitchen tool is ideal for every Indian home. Use it as a papad roaster, roti grill, or brinjal roaster — designed for fast, even roasting that delivers authentic flavor and aroma to your dishes | HEAVY-DUTY STAINLESS STEEL JALI - STRONG, DURABLE &amp; RUST-PROOF:- Crafted from premium heavy-gauge stainless steel, this phulka jali for gas stove ensures long-lasting performance, heat resistance, and uniform flame distribution. Unlike cheap iron or tin jalis, it won’t rust or deform even with daily high-heat cooking. Perfect for baingan roasting, papad crisping, or roti puffing with consistent results every time. | UNIFORM FLAME DISTRIBUTION FOR PERFECT ROASTING &amp; CRISPING:- The fine mesh design allows for even flame spread, ensuring your rotis puff evenly and papads roast without burning. Ideal for gas stove roasting, it gives that perfect homemade taste — whether you’re preparing baingan bharta, roasted papad, or phulka rotis. Trusted by Indian households for its high heat efficiency and durability. | FITS ALL GAS STOVES – EASY TO USE &amp; CLEAN:- The Unify Grill Jali is compatible with all types of gas stoves, making it perfect for every kitchen setup. Its universal size fits comfortably over any burner. Simply place it on the gas stove, roast your phulka or papad, and wipe clean after use. The stainless steel surface prevents sticking and allows easy cleaning. Lightweight, compact, and portable, it’s ideal for daily use at home or even for outdoor cooking. | HEALTHY, SMOKE-FREE &amp; ENERGY-EFFICIENT COOKING:- Enjoy healthy, oil-free, and smoke-free cooking every day with the Unify Phulka Grill Jali. Its advanced mesh pattern ensures even flame spread and faster roasting, saving both time and gas. Prepare crispy rotis, roasted papads, or smoky veggies without deep frying promoting a healthier lifestyle for your family. The food cooks evenly without burning, locking in authentic roasted flavor while reducing smoke and odor. Perfect for homes that value taste and wellness together.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1210,22 +1210,22 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dry Fruit Cutter &amp; Slicer Gadgets (3 in 1, Mix Colour) Kitchen Tools Kitchen Gadgets Dryfruit Choppers for Kitchen, Stainless Steel Blade, Green, Blue, Red</t>
+          <t>Solitude Dry Fruit Cutter, Slicer, Grinder, Chocolate Cutter and Butter Slicer with 3 in 1 Blade Kitchen Tools, Gadgets for Almonds, Cashews etc (Stainless Steel, 1 Piece)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71MbwrhpzlL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/715ytJXxIXL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0B853XRLJ</t>
+          <t>https://www.amazon.in/dp/B0BR5RJHZR?th=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UNMATCHED QUALITY – Chop, Dice, Slice or Grate with our newest Multi Chopper and Slicer by Mueller! This functional kitchen gadget will alleviate your prep time to just a couple of minutes. Made with premium materials like steel blades and food-grade BPA-free materials, it's the perfect tool to make home-cooked meals easier and faster. | SAFER: The unique design kitchen tool prevents your hands from ever going near the built-in blades, making this mandoline the safest option for an expert slice. | INNOVATIVE DESIGN - Don't need more space in your kitchen free up countertop space with this kitchen gadgets. Use the Dry Fruits Slicer while cutting Dry fruits. This prevents Dry fruits from slipping while slicing them. It also makes it clean, safe, and easy to work with. No more hassles of washing and wiping. | RUST RESISTANT - Heavy-duty 420 stainless steel blades razor sharpness for crisp, smooth slicing &amp; cutting. Blades snap in and out with ease. | IMPROVES YOUR HEALTH &amp; SAVE TIME – Busy lifestyles make us fall into the fast-food trap. It can take a lot of time and effort to dice, chop and slice the ingredients of the desired dish. Do not despair. Our multi-functional kitchen tool makes this process less time-consuming making it easier to slice dry fruits. That being said, you’re less likely to reach for unhealthy options. From now on, enjoy having more time for your family without missing out on any of the important nutrition.</t>
+          <t>❖ 𝐒𝐭𝐫𝐮𝐠𝐠𝐥𝐢𝐧𝐠 𝐖𝐢𝐭𝐡 𝐓𝐨𝐮𝐠𝐡 𝐃𝐫𝐲 𝐅𝐫𝐮𝐢𝐭𝐬? The Solitude dry fruit cutter comes with a non-detachable stainless steel blade that can slice dry fruit so easily. | ❖ 𝐏𝐫𝐞𝐜𝐢𝐬𝐢𝐨𝐧 𝐂𝐮𝐭𝐭𝐢𝐧𝐠 𝐌𝐚𝐝𝐞 𝐄𝐚𝐬𝐲: With sharp stainless steel blades, the Solitude Dry Fruit Cutter effortlessly slices through dry fruits, providing precise cuts and uniform slices every time. | ❖ 𝐄𝐟𝐟𝐞𝐜𝐭𝐢𝐯𝐞 𝐆𝐫𝐢𝐧𝐝𝐢𝐧𝐠: Transforms tough dry fruits into fine powder or coarse grind to suit your preferences, and it is perfect for preparing garnishes, salads, and baking ingredients. | ❖ 𝐔𝐬𝐞𝐫-𝐅𝐫𝐢𝐞𝐧𝐝𝐥𝐲 &amp; 𝐒𝐚𝐟𝐞: Ergonomically designed with a comfortable grip, the Solitude Dry Fruit Cutter promises smooth slicing while prioritising safety with a secure locking mechanism and non-slip base. | ❖ 𝐇𝐚𝐬𝐬𝐥𝐞-𝐅𝐫𝐞𝐞 𝐂𝐥𝐞𝐚𝐧 𝐚𝐧𝐝 𝐌𝐚𝐢𝐧𝐭𝐞𝐧𝐚𝐧𝐜𝐞: Our easy disassembly design ensures effortless cleanup. Detachable parts allow for thorough washing, and it's also dishwasher safe, streamlining your post-cooking cleanup.</t>
         </is>
       </c>
     </row>
@@ -1233,22 +1233,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2-Piece Vegetable Peeler Set, Multifunctional Stainless Steel Vegetable &amp; Fruit Peeler with Ergonomic Wooden Handle, 2-in-1 &amp; 3-in-1 Kitchen Tool with Scallion Shredder &amp; Bottle Opener</t>
+          <t>Pigeon Polypropylene Mini Handy and Compact Chopper with 3 Blades for Effortlessly Chopping Vegetables and Fruits for Your Kitchen (12420, Green, 400 ml)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612Sbd4GeDL._SY879_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51RXzjrUmkL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0HGMCSZ7V</t>
+          <t>https://www.amazon.in/dp/B01LWYDEQ7?th=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MULTIFUNCTIONAL KITCHEN TOOL: Peel vegetables and fruits, shred scallions, and open bottles with this versatile kitchen peeler set. Designed to handle everyday food-preparation tasks with fewer tools cluttering your kitchen drawer. | SHARP STAINLESS STEEL BLADE: Made with a durable stainless steel peeling blade for smooth, efficient peeling of potatoes, carrots, cucumbers, apples and other fruits and vegetables. The practical design helps make daily meal preparation faster and easier. | COMFORTABLE WOODEN HANDLE: Ergonomic wooden handles provide a comfortable, natural grip and easy control while peeling and preparing ingredients. The lightweight design is convenient for everyday cooking at home. | 2-PIECE VALUE SET: Includes two multifunctional peelers so you can keep one handy at your main prep area and another available for different ingredients or kitchen tasks. A practical addition to everyday cooking and meal preparation. | IDEAL FOR EVERYDAY COOKING: A useful kitchen accessory for home cooks, food preparation, meal prep and everyday kitchen tasks. Compact and multifunctional, it also makes a practical gift for cooking enthusiasts, new homeowners and anyone who enjoys convenient kitchen tools.</t>
+          <t>Unique string function to chop vegetables and fruits with ease;Package Contents: 1-Piece Handy Chopper.Blade Length: 3 centimeters | Eco-friendly design, no electricity required;Warranty: 30 Days Warranty, Only On Manufacturing Defects | Made from unbreakable ABS plastic for long-lasting use, Material: Polypropylene (PP);Sturdy 3-blade design made from Stainless Steel, As this chopper by Pigeon can be opened and detached easily, cleaning is an easy task using lukewarm water, mild detergent and a soft cloth.Power Requirement: Manual | Colour: Green, Material: Plastic | Size Name: Standard</t>
         </is>
       </c>
     </row>
@@ -1256,390 +1256,22 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ganesh Round Masher Kitchen Gadget with Non-Slip Handle, Masher Utensil for Mashed Potato, Vegetables</t>
+          <t>RERANT Plastic 3 in 1 Soap Pump Dispenser Dish Soap Liquid Dispenser Sponge Holder Dish Soap Pump Dispenser for Kitchen Sink Countertop Kitchen Bathroom (Multi-Color) (Multicolour)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61ECYzDsEsL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/618xrswsstL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0C818Z214</t>
+          <t>https://www.amazon.in/dp/B0F84892TQ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>This potato masher is made of stainless steel, so you don't need to worry about safety of your baby and families. Also it possess higher durability and comfort and long time use is guaranteed. It is not easy to rust | Easy In Use and Clean – There are different kitchen essentials in the market but our potato ricer masher is extremely easy to use and can be cleaned under the tap water, after that it is ready for next use. | Perfect use in mashing potatoes, vegetables, sweet potatoes, boiled eggs, cheese etc. You don’t need any mixer for your kitchen as our masher can be use in different ways to save the time and money.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Samta Stainless Steel Garlic Press Crusher Manual Garlic &amp; Ginger Presser for Kitchen | Garlic Crusher Chopper Tool | Dishwasher Safe Curved Garlic Grinding Slicer | Multipurpose Cooking Gadget</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71RPI68L-qL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FZK9LFW3</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>🧄 Effortless Garlic &amp; Ginger Crushing: Easily crush and press garlic or ginger with minimal effort using this strong stainless steel kitchen tool. | 🔪 Curved Ergonomic Design: Features a comfortable curved handle for better grip and efficient pressing—perfect for daily cooking use. | 💪 Durable Stainless Steel Build: Made from high-quality rust-resistant stainless steel for long-lasting performance and strength. | 🧼 Dishwasher Safe &amp; Easy to Clean: Simply rinse under running water or toss in the dishwasher for quick cleanup—no mess, no hassle! | 🧂 Multi-Function Kitchen Tool: Use it as a garlic presser, ginger crusher, or even for soft veggies—an all-in-one prep tool for your kitchen. | 👌 Compact &amp; Handy Design: Small yet powerful, the compact design makes it easy to store and perfect for small or busy kitchens. | 🎁 Ideal Cooking Gadget Gift: A practical and thoughtful gift for home cooks, chefs, or kitchen lovers who appreciate time-saving tools.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Ganesh 14 in 1 Multipurpose Chopper, Fruits &amp; Vegetable Cutters, Grater Peeler Chipser, Unbreakable Food Grade Body, Easy Push to Clean Button Slicer Dicer, Chopper for Kitchen (Green, Plastic)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71SSpHadzXL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B01BVDS1BE?th=1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Large break resistant container with rubber grip base which holds the device firmly in place | Fastest, safest and easiest way to chop or dice fruits and vegetables ; Not Dishwasher Safe ; Other Features: Easy To Use, Clean and Store, Hand Operated, No Electricity Needed, The Container Is Break Resistant, Extra Sharp Stainless Steel Blades | Advanced push to clean button which ensures easy and hygienic cleaning | High-quality stainless steel blades for easy chopping, Sharp pyramid-shaped cutting blade for efficient and smooth cutting | Large detachable container which can also be used to store vegetable and fruits in refrigerator | Colour: Green, Material: Plastic and Stainless Steel, Shape: Rectangle | Package Contents: 1 Plastic Container, 1 peeler with grater, 1 safety holder, 1 masher &amp; 1 handle with cleaning press | Blades: 1 dual, 2 slicer, 2 grater, 1 Juliane, blade die attachment</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Solitude Dry Fruit Cutter, Slicer, Grinder, Chocolate Cutter and Butter Slicer with 3 in 1 Blade Kitchen Tools, Gadgets for Almonds, Cashews etc (Stainless Steel, 1 Piece)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/715ytJXxIXL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BR5RJHZR?th=1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>❖ 𝐒𝐭𝐫𝐮𝐠𝐠𝐥𝐢𝐧𝐠 𝐖𝐢𝐭𝐡 𝐓𝐨𝐮𝐠𝐡 𝐃𝐫𝐲 𝐅𝐫𝐮𝐢𝐭𝐬? The Solitude dry fruit cutter comes with a non-detachable stainless steel blade that can slice dry fruit so easily. | ❖ 𝐏𝐫𝐞𝐜𝐢𝐬𝐢𝐨𝐧 𝐂𝐮𝐭𝐭𝐢𝐧𝐠 𝐌𝐚𝐝𝐞 𝐄𝐚𝐬𝐲: With sharp stainless steel blades, the Solitude Dry Fruit Cutter effortlessly slices through dry fruits, providing precise cuts and uniform slices every time. | ❖ 𝐄𝐟𝐟𝐞𝐜𝐭𝐢𝐯𝐞 𝐆𝐫𝐢𝐧𝐝𝐢𝐧𝐠: Transforms tough dry fruits into fine powder or coarse grind to suit your preferences, and it is perfect for preparing garnishes, salads, and baking ingredients. | ❖ 𝐔𝐬𝐞𝐫-𝐅𝐫𝐢𝐞𝐧𝐝𝐥𝐲 &amp; 𝐒𝐚𝐟𝐞: Ergonomically designed with a comfortable grip, the Solitude Dry Fruit Cutter promises smooth slicing while prioritising safety with a secure locking mechanism and non-slip base. | ❖ 𝐇𝐚𝐬𝐬𝐥𝐞-𝐅𝐫𝐞𝐞 𝐂𝐥𝐞𝐚𝐧 𝐚𝐧𝐝 𝐌𝐚𝐢𝐧𝐭𝐞𝐧𝐚𝐧𝐜𝐞: Our easy disassembly design ensures effortless cleanup. Detachable parts allow for thorough washing, and it's also dishwasher safe, streamlining your post-cooking cleanup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>EXQ HOME Glass Basting Set Silicone Oil Dispenser Pastry Brush Docking Bowl Set for Cooking, BBQ, Baking and Grilling, Innovative Kitchen Gadget</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41uTsM041TL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DDT7VX7M</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Product material: The oil brush is made of food-grade organic silicone, which is thick, soft, and elastic. The oil bottle is hand-made of plastic, which can withstand 450 degrees of high temperature. | Easy to use: The bottleneck is large, it is easy to fill the liquid, and will not overflow, Our unique design lightly pinchs the hose to easily obtain the required amount of oil, and the oil brush can be used to remove the remaining oil, and it can be used repeatedly after cleaning without odor It is convenient to observe the distribution | Reasonable design: The large-head brush has a wider audience and makes it easier to apply oil. The round bottle design is more stable, the lid has a good seal, and the liquid will not overflow and make the bottle greasy. | Use occasion: The oil bottle brush is used for outdoor BBQ or kitchen cooking, home barbecue, baking, fried eggs, and pizza, and can also add vinegar, egg liquid, honey, and other different liquids. You can microwave butter in the plastic jar to brush onto marinades or salad dressing on your meats or vegetables | Easy to use and easy to clean: The newly designed silicone basting brush is dishwasher safe, which makes cleaning so easy! The individual parts come apart for a hassle-free cleaning experience. Focus more on enjoying the food and less on doing the dishes! | Package Includes: Silicone Oil Brush + Plastic Docking Bowl Set | Color: Multi, Random</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Ekaarav ® Stainless Steel Corn Peeler – Heavy Duty Cob Stripper Tool for Kitchen, Removes Kernels in Seconds, Sharp Serrated Blade, Comfortable Grip (Pack of 1)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/615R4eFnoLL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DRV5NJNF?th=1</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Heavy Duty Stainless Steel – Made from solid 304 stainless steel; rustproof, durable, and built to last. | Sharp Serrated Blade – Quickly removes corn kernels with ease; a perfect corn peeler and corn remover tool. | Comfortable Grip – Smooth handle for a secure hold while peeling and cutting corn effortlessly. | Multi-Use Kitchen Tool – Ideal as a corn cutter, sweet corn peeler, and general kitchen tool for home or commercial use. | Quick &amp; Easy – Strips kernels in seconds, saving time whether prepping salads, soups, or desserts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>TrendPlain 16oz/470ml Olive Oil Sprayer for Cooking - 2 in 1 Olive Oil Dispenser for Kitchen Gadgets, Air Fryer, Salad, and BBQ - Green, Glass</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612-b6FTtbL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CNK6BPTV?th=1</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Dual Dosing Convenience: These Kitchen Oil Bottles Offer Both Pouring And Spraying Options, Allowing You To Easily Switch Between The Two. It'S A Space-Saving Solution That Keeps Your Kitchen Clean And Organized. | ?Exceptional Spray Nozzle Design?Our Olive Oil Bottle Features A Unique Spray Nozzle That Delivers A Wide-Angle, Fine Mist When Pressed Quickly And A Steady Stream Of Oil When Pressed Slowly. This Precise Design Ensures Even Coverage And Control Over Your Oil Consumption. | Precise Oil Control: Each Spray Dispenses Approximately 0.15G Of Oil, Making It Easy To Monitor And Measure Your Daily Oil Intake. With A Daily Recommended Oil Consumption Of Up To 30G, You Can Effortlessly Manage Your Dietary Preferences. | Safe And Odorless Materials: Made Of Glass, Our Olive Oil Spray Is Both Safe And Non-Toxic. It Can Withstand High Temperatures And Is Completely Odorless.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Stainless Steel Coconut Slicer Cutter Tool for Kitchen | Coconut Opener, Grater, Scraper, White Remover | Heavy Duty Thengai Thuruvi | Manual Kitchen Accessories Items for Home Use (Pack of 1)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61uOzEkFBQL._SY879_.jpg</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F92QK9NZ</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Heavy Duty Coconut Slicer &amp; Cutter 🥥🔪 – Made with premium stainless steel, this manual Thengai Thuruvi is perfect for grating, scraping, and cutting coconuts easily and safely at home. | Multi-Use Kitchen Tool 🍽️✨ – Functions as a Coconut Opener, Grater, Scraper, and White Remover; ideal for traditional Indian cooking, chutneys, and sweets. | Rustproof &amp; Long-Lasting 🛡️✔️ – Crafted for durability with corrosion-resistant stainless steel, ensuring years of hassle-free use without losing sharpness or quality. | Ergonomic &amp; Easy to Use 🤲👌 – Designed for smooth handling, lightweight construction, and effortless cleaning, making it a must-have kitchen accessory. | Perfect for Home Cooking &amp; Festive Recipes 🎉🍛 – Essential for preparing authentic South Indian dishes, coconut chutney, laddoos, and other delicacies with ease. | Compact &amp; Space Saving 📦🏠 – Convenient size fits easily in kitchen drawers or shelves, making storage simple without cluttering your cooking space. | Trusted Kitchen Accessories for Every Household 🏡❤️ – Ideal for daily use or gifting; enhances your kitchen experience with efficiency, safety, and superior performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Stainless Steel 6-Piece Kitchen Gadgets Set, Kitchen Scissors, Kitchen Utensils Set with Holder, Paring Knife, Whisk, Bottle Opener, Peeler- Anti-Slip Handle, Decorative Base,</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61R-5RNwl0L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F3JQXP8V</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>VERSATILE SET: Includes paring knife, whisk, bottle opener, peeler and other kitchen gadgets for essential cooking tasks | HIGH-QUALITY MATERIALS: Knives are made of strong stainless steel blades with plastic handles for comfort and durability | ASSORTED SIZES: Variety of tools from a 3-inch paring knife to 8-inch chef's knife for fruits, veggies and more | KITCHEN ESSENTIALS: All the basic appliances needed for preparing, mixing and opening to make cooking easy and efficient | DURABLE AND SAFE: Stainless steel won't rust or stain and smooth edges on tools help prevent cuts for safe daily use</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Pigeon Polypropylene Mini Handy and Compact Chopper with 3 Blades for Effortlessly Chopping Vegetables and Fruits for Your Kitchen (12420, Green, 400 ml)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51RXzjrUmkL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B01LWYDEQ7?th=1</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Unique string function to chop vegetables and fruits with ease;Package Contents: 1-Piece Handy Chopper.Blade Length: 3 centimeters | Eco-friendly design, no electricity required;Warranty: 30 Days Warranty, Only On Manufacturing Defects | Made from unbreakable ABS plastic for long-lasting use, Material: Polypropylene (PP);Sturdy 3-blade design made from Stainless Steel, As this chopper by Pigeon can be opened and detached easily, cleaning is an easy task using lukewarm water, mild detergent and a soft cloth.Power Requirement: Manual | Colour: Green, Material: Plastic | Size Name: Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Clazkit Stainless Steel Coconut Opener Tool, Coconut Driller, Coconut Opener Machine, Coconut Opener Knife, Coconut Water Opener- (Pack- 1)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/6159Kc-wHpL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CG68ZK2G</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Simply Pop off the top of the coconut, the tool will crack an opening you can remove to either pour out the water or simply insert a straw. | Constructed of Durable FOOD GRADE Stainless Steel.This is the safest way to open green coconut. | Comfortable Rubber Handle for easy opening every time.No Knives, No Machete, No Power Drills, No Hammers!!</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>RERANT Plastic 3 in 1 Soap Pump Dispenser Dish Soap Liquid Dispenser Sponge Holder Dish Soap Pump Dispenser for Kitchen Sink Countertop Kitchen Bathroom (Multi-Color) (Multicolour)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/618xrswsstL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F84892TQ</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
           <t>RERANT Compact Design: This 3-in-1 dispenser measures 19.50 cm in length, 10.25 cm in height, and 9 cm in width, making it a space-saving solution for your kitchen or bathroom countertop. | RERANT Multi-Purpose: It combines a liquid soap pump dispenser, a sponge holder, and a detachable dish for added convenience. | RERANT Durable Construction: Crafted from high-quality plastic, this dispenser is built to withstand daily use and retain its vibrant colours. | RERANT Easy to Refill: The pump mechanism allows for effortless refilling of your preferred liquid soap or detergent. | RERANT Versatile Placement: Its sleek design complements various kitchen and bathroom decors, allowing you to place it wherever it's most accessible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Vegetable Chopper Mandoline Slicer Home Kitchen Appliance Essential Gadget</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81RvBMCJ4NL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G6Z4TVJG?th=1</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Unmatched Quality - The blades is made of 420 stainless steel using Dewpeton unique punching blade technology, razor sharp for crisp, smooth cuts and grating. Can create perfectly chopped onions, tomatoes, and peppers for salsa, or shred an entire cabbage for coleslaw in no time. The main body of the vegetable chopper is made from food-grade ABS plastic to guarante healthy meals for your family. | Meet Various Needs - Contains 2 different sized chopper blades and 5 interchangeable blades, offer the functionality of multiple kitchen tools in just one, highly versatile, kitchen gadget, meet all your slicing, shredding, grating needs. There is an egg white separator include,to easily separate egg whites from yolks. Can cut most types of vegetables and fruits as potato, tomato, cucumber, carrot and cheese. Can make WAFFLE FRIES OR RUFFLED POTATO CHIPS. | Improves Your Health And Saves Time - With our functional kitchen gadget, you can free your hand on chopping, slicing and cutting, help you cook like a pro, making it easier to add vegetables to your meals. With faster prep &amp; faster cleanup you can live your best, healthiest life every day. Allows you to spend less time preparing food and enjoying more time for your family without missing out on any of the important nutrition. | 1.5L Large Container - Built-in chop lid lets you cut foods directly into the 1.5L collection tray without the mess of a knife and cutting board. Storage container lets you hold prepared vegetables in the Dewpeton Vegetable Cutter until you are ready to begin cooking. Free-up countertop space with the Food Container. And Dewpeton mandoline slicer can be fully disassembled with ease and stored in the container. Its compact size allows you to store it almost anywhere. | Safety &amp; Easy to Use - Blades snap in and out with ease, no need to touch the blade. Comes with a fingerguard to keep you safe whilst using and a cleaning brush + blade organizer thorough and convenient cleaning when aren’t. Soft grip handle with rubberized tpu enhances leverage while the non-skid base ensures stability during use. It can be fully disassembled for easy cleaning on the top shelf of your dishwasher. After rinsing and drying, please collect them into the container.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Garlic Press Rocker Stainless Steel | Premium Garlic Crusher &amp; Mincer with Silicone Peeler | Heavy Duty Manual Garlic Masher for Ginger, Garlic &amp; Herbs | Easy Clean Kitchen Tool New 2026</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/7151bZo8kTL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H6TZHSN7</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>🧄 CRUSH GARLIC IN SECONDS Effortlessly mince garlic cloves with a simple rocking motion. Creates finely crushed garlic quickly without complicated mechanisms, making meal preparation faster and easier. | 💪 HEAVY-DUTY STAINLESS STEEL BUILD Made from premium food-grade stainless steel for strength, durability, rust resistance, and long-lasting performance. Designed for everyday kitchen use. | ✨ ERGONOMIC COMFORT GRIP Curved ergonomic handle provides a comfortable grip and reduces hand strain while pressing. Suitable for regular cooking, meal prep, and everyday kitchen tasks. | 🧽 EASY TO CLEAN DESIGN Open structure allows garlic residue to rinse away easily under running water. Dishwasher safe design helps save cleaning time after cooking. | 🌿 MULTIPURPOSE KITCHEN TOOL Perfect for garlic, ginger, herbs, small vegetables, and seasoning preparation. A practical kitchen accessory for Indian cooking, curries, gravies, marinades, and sauces. | 🏠 COMPACT &amp; SPACE SAVING Lightweight and compact design fits easily inside kitchen drawers, cabinets, utensil holders, and kitchen organizers without occupying extra space. | 🎁 PERFECT GIFT FOR HOME CHEFS An ideal kitchen gadget for home cooks, food lovers, newly married couples, housewarming gifts, and anyone who enjoys convenient cooking tools. | garlic press garlic crusher garlic mincer garlic press rocker stainless steel garlic press garlic chopper garlic crusher stainless steel manual garlic press garlic rocker garlic ginger crusher garlic mincer stainless steel garlic press tool garlic mashing tool garlic pressing tool garlic press stainless steel garlic crusher and mincer best garlic press garlic press for kitchen garlic press manual easy clean garlic press heavy duty garlic press professional garlic press kitchen garlic crusher garlic cutter tool garlic grinding tool garlic press for ginger garlic mincer tool | garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker garlic crusher stainless steel garlic ginger crusher manual garlic press garlic chopper garlic mincer tool best garlic press easy clean garlic press heavy duty garlic press professional garlic press garlic press for kitchen garlic crusher tool garlic press stainless steel heavy duty garlic rocker stainless steel ginger garlic crusher garlic mincing tool garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CRIYALE Silicone Baking Mat Sheet | Roti Making Mat | Table Placemat Pad | Silicon Fondant Rolling Mat | BPA-Free Non-Stick Pastry Board Matt | Dough Making Kitchen Gadgets Cooking Tools (Pink)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Iqs+xTutL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C1G82FKF?th=1</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Roti Mat for Kneading, Rolling, and Shaping Breads, Pizza Dough's, Pastas, Pastries, Pie Crusts and fondants. Provides a Clean Extra-Large Baking or Cooking Preparation Surface. Makes the Perfect Gift! | Light weight, easy to clean and use. | Will keep your worktop clean. No more scrapping dough or fondant off the worktop | Mat with pre-marked circles helps you get the perfect amount of fondant or dough and the easy-glide material allows you to rotate the mat as you roll | Great surface for kneading dough or rolling out dough and pastries</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>GwernKB 4-in-1 Manual Knife Sharpener Tool for Kitchen, Kitchen Knife Sharpener for Home with Tungsten Steel &amp; Ceramic Slots, Scissor Slot, Non-Slip Base &amp; Ergonomic Handle</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51IlMlDyvbL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H86ZG11G?th=1</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>1️⃣ 4-IN-1 MANUAL KNIFE SHARPENER TOOL🔪 Restore dull kitchen blades with 4 precision sharpening slots designed for scissor sharpening, coarse repair, fine sharpening and polishing. A practical knife sharpener tool for everyday home kitchens. | 2️⃣ TUNGSTEN STEEL &amp; CERAMIC SHARPENING SYSTEM✨ Built with strong sharpening slots to help improve blade edges smoothly and consistently. Ideal for maintaining chef knives, utility knives, paring knives, slicing knives and cleavers. | 3️⃣ SAFE, STABLE &amp; COMFORTABLE GRIP🖐️ The ergonomic handle gives steady control for left and right-hand use, while the non-slip base helps keep the sharpener stable on your kitchen counter during sharpening. | 4️⃣ DETACHABLE SHARPENING UNIT FOR EASY CLEANING🧼 Designed for convenient maintenance, the sharpening unit can be removed and cleaned easily after use, helping keep your kitchen knife sharpener hygienic and ready for daily use. | 5️⃣ COMPACT KITCHEN SIZE FOR HOME USE🏡 With its space-saving design, this kitchen knife sharpener for home fits easily on most countertops and drawers. Suitable for straight-edge kitchen knives and scissors. Not suitable for serrated or wavy-edge knives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Unify Stainless Steel Phulka Grill Jali for Gas Stove with Free Oil Brush | Roti Grill, Papad Roaster, Baingan Bharta Roaster | Heavy Gauge Steel Mesh Griller | Multi-Purpose Kitchen Cooking Tool</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71aw2TLRtQL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FWZSJ3BN</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>MULTI-PURPOSE PHULKA GRILL FOR KITCHEN COOKING:-Enjoy perfectly roasted phulkas, rotis, papads, and baingan bharta with the Unify Stainless Steel Phulka Grill Jali for Gas Stove. This multi-purpose kitchen tool is ideal for every Indian home. Use it as a papad roaster, roti grill, or brinjal roaster — designed for fast, even roasting that delivers authentic flavor and aroma to your dishes | HEAVY-DUTY STAINLESS STEEL JALI - STRONG, DURABLE &amp; RUST-PROOF:- Crafted from premium heavy-gauge stainless steel, this phulka jali for gas stove ensures long-lasting performance, heat resistance, and uniform flame distribution. Unlike cheap iron or tin jalis, it won’t rust or deform even with daily high-heat cooking. Perfect for baingan roasting, papad crisping, or roti puffing with consistent results every time. | UNIFORM FLAME DISTRIBUTION FOR PERFECT ROASTING &amp; CRISPING:- The fine mesh design allows for even flame spread, ensuring your rotis puff evenly and papads roast without burning. Ideal for gas stove roasting, it gives that perfect homemade taste — whether you’re preparing baingan bharta, roasted papad, or phulka rotis. Trusted by Indian households for its high heat efficiency and durability. | FITS ALL GAS STOVES – EASY TO USE &amp; CLEAN:- The Unify Grill Jali is compatible with all types of gas stoves, making it perfect for every kitchen setup. Its universal size fits comfortably over any burner. Simply place it on the gas stove, roast your phulka or papad, and wipe clean after use. The stainless steel surface prevents sticking and allows easy cleaning. Lightweight, compact, and portable, it’s ideal for daily use at home or even for outdoor cooking. | HEALTHY, SMOKE-FREE &amp; ENERGY-EFFICIENT COOKING:- Enjoy healthy, oil-free, and smoke-free cooking every day with the Unify Phulka Grill Jali. Its advanced mesh pattern ensures even flame spread and faster roasting, saving both time and gas. Prepare crispy rotis, roasted papads, or smoky veggies without deep frying promoting a healthier lifestyle for your family. The food cooks evenly without burning, locking in authentic roasted flavor while reducing smoke and odor. Perfect for homes that value taste and wellness together.</t>
         </is>
       </c>
     </row>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1275,6 +1275,466 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2-Piece Vegetable Peeler Set, Multifunctional Stainless Steel Vegetable &amp; Fruit Peeler with Ergonomic Wooden Handle, 2-in-1 &amp; 3-in-1 Kitchen Tool with Scallion Shredder &amp; Bottle Opener</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612Sbd4GeDL._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HGMCSZ7V</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MULTIFUNCTIONAL KITCHEN TOOL: Peel vegetables and fruits, shred scallions, and open bottles with this versatile kitchen peeler set. Designed to handle everyday food-preparation tasks with fewer tools cluttering your kitchen drawer. | SHARP STAINLESS STEEL BLADE: Made with a durable stainless steel peeling blade for smooth, efficient peeling of potatoes, carrots, cucumbers, apples and other fruits and vegetables. The practical design helps make daily meal preparation faster and easier. | COMFORTABLE WOODEN HANDLE: Ergonomic wooden handles provide a comfortable, natural grip and easy control while peeling and preparing ingredients. The lightweight design is convenient for everyday cooking at home. | 2-PIECE VALUE SET: Includes two multifunctional peelers so you can keep one handy at your main prep area and another available for different ingredients or kitchen tasks. A practical addition to everyday cooking and meal preparation. | IDEAL FOR EVERYDAY COOKING: A useful kitchen accessory for home cooks, food preparation, meal prep and everyday kitchen tasks. Compact and multifunctional, it also makes a practical gift for cooking enthusiasts, new homeowners and anyone who enjoys convenient kitchen tools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ekaarav ® Stainless Steel Corn Peeler – Heavy Duty Cob Stripper Tool for Kitchen, Removes Kernels in Seconds, Sharp Serrated Blade, Comfortable Grip (Pack of 1)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/615R4eFnoLL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DRV5NJNF?th=1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Heavy Duty Stainless Steel – Made from solid 304 stainless steel; rustproof, durable, and built to last. | Sharp Serrated Blade – Quickly removes corn kernels with ease; a perfect corn peeler and corn remover tool. | Comfortable Grip – Smooth handle for a secure hold while peeling and cutting corn effortlessly. | Multi-Use Kitchen Tool – Ideal as a corn cutter, sweet corn peeler, and general kitchen tool for home or commercial use. | Quick &amp; Easy – Strips kernels in seconds, saving time whether prepping salads, soups, or desserts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1 Pack Multifunctional Vegetable Peeler for Kitchen 3 in 1 Stainless Steel Fruit &amp; Vegetable Peeler with Wooden Handle, Built-in Grater &amp; Bottle Opener for Potato, Carrot, Apple &amp; Cucumber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51ZLcJEiRwL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H2QKZYF7?th=1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>🥕 3 IN 1 MULTIFUNCTIONAL KITCHEN TOOL Peel, grate, and open bottles with one compact kitchen tool. This multifunctional vegetable peeler is designed to simplify daily cooking and food preparation tasks." | 🍎 PREMIUM STAINLESS STEEL BLADE Made with sharp rust-resistant stainless steel for smooth and effortless peeling of potatoes, carrots, apples, cucumbers, and other fruits &amp; vegetables." | 🌿 COMFORTABLE WOODEN HANDLE Ergonomic wooden handle provides a strong, non-slip, and comfortable grip for better control while peeling, slicing, or grating." | 🧀 BUILT-IN GRATER &amp; BOTTLE OPENER Integrated grater helps shred vegetables and cheese easily, while the bottle opener adds extra convenience for multipurpose kitchen use." | 🧼 EASY TO CLEAN &amp; DURABLE Lightweight yet sturdy design ensures long-lasting performance. Easy to wash and maintain, making it a practical addition to every kitchen."</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dry Fruit Cutter &amp; Slicer Gadgets (3 in 1, Mix Colour) Kitchen Tools Kitchen Gadgets Dryfruit Choppers for Kitchen, Stainless Steel Blade, Green, Blue, Red</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71MbwrhpzlL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B853XRLJ</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>UNMATCHED QUALITY – Chop, Dice, Slice or Grate with our newest Multi Chopper and Slicer by Mueller! This functional kitchen gadget will alleviate your prep time to just a couple of minutes. Made with premium materials like steel blades and food-grade BPA-free materials, it's the perfect tool to make home-cooked meals easier and faster. | SAFER: The unique design kitchen tool prevents your hands from ever going near the built-in blades, making this mandoline the safest option for an expert slice. | INNOVATIVE DESIGN - Don't need more space in your kitchen free up countertop space with this kitchen gadgets. Use the Dry Fruits Slicer while cutting Dry fruits. This prevents Dry fruits from slipping while slicing them. It also makes it clean, safe, and easy to work with. No more hassles of washing and wiping. | RUST RESISTANT - Heavy-duty 420 stainless steel blades razor sharpness for crisp, smooth slicing &amp; cutting. Blades snap in and out with ease. | IMPROVES YOUR HEALTH &amp; SAVE TIME – Busy lifestyles make us fall into the fast-food trap. It can take a lot of time and effort to dice, chop and slice the ingredients of the desired dish. Do not despair. Our multi-functional kitchen tool makes this process less time-consuming making it easier to slice dry fruits. That being said, you’re less likely to reach for unhealthy options. From now on, enjoy having more time for your family without missing out on any of the important nutrition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Samta Stainless Steel Garlic Press Crusher Manual Garlic &amp; Ginger Presser for Kitchen | Garlic Crusher Chopper Tool | Dishwasher Safe Curved Garlic Grinding Slicer | Multipurpose Cooking Gadget</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71RPI68L-qL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FZK9LFW3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>🧄 Effortless Garlic &amp; Ginger Crushing: Easily crush and press garlic or ginger with minimal effort using this strong stainless steel kitchen tool. | 🔪 Curved Ergonomic Design: Features a comfortable curved handle for better grip and efficient pressing—perfect for daily cooking use. | 💪 Durable Stainless Steel Build: Made from high-quality rust-resistant stainless steel for long-lasting performance and strength. | 🧼 Dishwasher Safe &amp; Easy to Clean: Simply rinse under running water or toss in the dishwasher for quick cleanup—no mess, no hassle! | 🧂 Multi-Function Kitchen Tool: Use it as a garlic presser, ginger crusher, or even for soft veggies—an all-in-one prep tool for your kitchen. | 👌 Compact &amp; Handy Design: Small yet powerful, the compact design makes it easy to store and perfect for small or busy kitchens. | 🎁 Ideal Cooking Gadget Gift: A practical and thoughtful gift for home cooks, chefs, or kitchen lovers who appreciate time-saving tools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ganesh Round Masher Kitchen Gadget with Non-Slip Handle, Masher Utensil for Mashed Potato, Vegetables</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61ECYzDsEsL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C818Z214</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>This potato masher is made of stainless steel, so you don't need to worry about safety of your baby and families. Also it possess higher durability and comfort and long time use is guaranteed. It is not easy to rust | Easy In Use and Clean – There are different kitchen essentials in the market but our potato ricer masher is extremely easy to use and can be cleaned under the tap water, after that it is ready for next use. | Perfect use in mashing potatoes, vegetables, sweet potatoes, boiled eggs, cheese etc. You don’t need any mixer for your kitchen as our masher can be use in different ways to save the time and money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ganesh 14 in 1 Multipurpose Chopper, Fruits &amp; Vegetable Cutters, Grater Peeler Chipser, Unbreakable Food Grade Body, Easy Push to Clean Button Slicer Dicer, Chopper for Kitchen (Green, Plastic)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71SSpHadzXL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B01BVDS1BE?th=1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Large break resistant container with rubber grip base which holds the device firmly in place | Fastest, safest and easiest way to chop or dice fruits and vegetables ; Not Dishwasher Safe ; Other Features: Easy To Use, Clean and Store, Hand Operated, No Electricity Needed, The Container Is Break Resistant, Extra Sharp Stainless Steel Blades | Advanced push to clean button which ensures easy and hygienic cleaning | High-quality stainless steel blades for easy chopping, Sharp pyramid-shaped cutting blade for efficient and smooth cutting | Large detachable container which can also be used to store vegetable and fruits in refrigerator | Colour: Green, Material: Plastic and Stainless Steel, Shape: Rectangle | Package Contents: 1 Plastic Container, 1 peeler with grater, 1 safety holder, 1 masher &amp; 1 handle with cleaning press | Blades: 1 dual, 2 slicer, 2 grater, 1 Juliane, blade die attachment</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2-Piece 3-in-1 Multifunctional Vegetable Peeler Set, Stainless Steel Blade with Ergonomic Wooden Handle, Potato &amp; Fruit Peeler, Scallion Shredder and Built-in Bottle Opener Kitchen Tool</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61RdTHmXUvL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HHJKS3JR?th=1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3-in-1 design combines a stainless steel double‑blade peeler, a julienne cutter for fine vegetable strips, and a built‑in bottle opener. | Premium stainless steel blades stay sharp for smooth, effortless peeling of fruits and vegetables. | Comfortable wooden handle provides a secure grip and a natural look that complements any kitchen décor. | Sleek silver finish adds a modern appearance while the standard size fits comfortably in any hand. | High‑capacity 200 ml design handles large vegetables and fruits without frequent refilling. | Powerful 150 W rating ensures consistent performance for heavy‑duty kitchen tasks. | Comes in a single‑count pack – ready to use right out of the box. | Easy to clean – dishwasher‑safe stainless steel and removable wooden handle for quick maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stainless Steel Coconut Slicer Cutter Tool for Kitchen | Coconut Opener, Grater, Scraper, White Remover | Heavy Duty Thengai Thuruvi | Manual Kitchen Accessories Items for Home Use (Pack of 1)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61uOzEkFBQL._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F92QK9NZ</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Heavy Duty Coconut Slicer &amp; Cutter 🥥🔪 – Made with premium stainless steel, this manual Thengai Thuruvi is perfect for grating, scraping, and cutting coconuts easily and safely at home. | Multi-Use Kitchen Tool 🍽️✨ – Functions as a Coconut Opener, Grater, Scraper, and White Remover; ideal for traditional Indian cooking, chutneys, and sweets. | Rustproof &amp; Long-Lasting 🛡️✔️ – Crafted for durability with corrosion-resistant stainless steel, ensuring years of hassle-free use without losing sharpness or quality. | Ergonomic &amp; Easy to Use 🤲👌 – Designed for smooth handling, lightweight construction, and effortless cleaning, making it a must-have kitchen accessory. | Perfect for Home Cooking &amp; Festive Recipes 🎉🍛 – Essential for preparing authentic South Indian dishes, coconut chutney, laddoos, and other delicacies with ease. | Compact &amp; Space Saving 📦🏠 – Convenient size fits easily in kitchen drawers or shelves, making storage simple without cluttering your cooking space. | Trusted Kitchen Accessories for Every Household 🏡❤️ – Ideal for daily use or gifting; enhances your kitchen experience with efficiency, safety, and superior performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Clazkit Stainless Steel Coconut Opener Tool, Coconut Driller, Coconut Opener Machine, Coconut Opener Knife, Coconut Water Opener- (Pack- 1)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/6159Kc-wHpL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CG68ZK2G</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Simply Pop off the top of the coconut, the tool will crack an opening you can remove to either pour out the water or simply insert a straw. | Constructed of Durable FOOD GRADE Stainless Steel.This is the safest way to open green coconut. | Comfortable Rubber Handle for easy opening every time.No Knives, No Machete, No Power Drills, No Hammers!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>GwernKB 4-in-1 Manual Knife Sharpener Tool for Kitchen, Kitchen Knife Sharpener for Home with Tungsten Steel &amp; Ceramic Slots, Scissor Slot, Non-Slip Base &amp; Ergonomic Handle</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51IlMlDyvbL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H86ZG11G?th=1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1️⃣ 4-IN-1 MANUAL KNIFE SHARPENER TOOL🔪 Restore dull kitchen blades with 4 precision sharpening slots designed for scissor sharpening, coarse repair, fine sharpening and polishing. A practical knife sharpener tool for everyday home kitchens. | 2️⃣ TUNGSTEN STEEL &amp; CERAMIC SHARPENING SYSTEM✨ Built with strong sharpening slots to help improve blade edges smoothly and consistently. Ideal for maintaining chef knives, utility knives, paring knives, slicing knives and cleavers. | 3️⃣ SAFE, STABLE &amp; COMFORTABLE GRIP🖐️ The ergonomic handle gives steady control for left and right-hand use, while the non-slip base helps keep the sharpener stable on your kitchen counter during sharpening. | 4️⃣ DETACHABLE SHARPENING UNIT FOR EASY CLEANING🧼 Designed for convenient maintenance, the sharpening unit can be removed and cleaned easily after use, helping keep your kitchen knife sharpener hygienic and ready for daily use. | 5️⃣ COMPACT KITCHEN SIZE FOR HOME USE🏡 With its space-saving design, this kitchen knife sharpener for home fits easily on most countertops and drawers. Suitable for straight-edge kitchen knives and scissors. Not suitable for serrated or wavy-edge knives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Clazkit Multi-Purpose Strainer or Washer Bowl for Rice Fruits &amp; Vegetable Rice Bowl Color May Vary, Plastic - 10.2 x 17.5 x 24.3 Centimeters</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61H0t3PWOXL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C7V8RC3J</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>**Multi-Functional Design:** - Versatile bowl designed for washing fruits, vegetables, straining rice, pasta, lentils, and more. | **Built-in Handle:** - Sturdy handle for easy grip and control during washing or straining, ensuring user comfort. | **Efficient Draining:** - Precision-drilled holes allow for efficient drainage while keeping food secure in the bowl. | **Durable Material:**- Made from durable, food-grade materials for long-lasting use and safety in food preparation. | **Easy to Clean:** - Smooth surface and non-stick design make cleaning a breeze, saving time and effort. | **Space-Saving Design:**- Compact and stackable design for convenient storage, saving cabinet or pantry space. | **Enhanced Stability:**- Stable base prevents tipping or slipping, ensuring a secure and steady operation. | **Sleek Aesthetic:** - Modern and sleek design to complement any kitchen decor, adding a touch of style to your cooking routine. | **Large Capacity:** - Ample space to accommodate a variety of fruits, vegetables, or a generous portion of rice or pasta. | **Versatile Colors:** - Available in a range of appealing colors to match your kitchen aesthetics or personal preference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Vegetable Peeler with Wooden Handle &amp; Bottle Opener, 2 in 1&amp; 3in 1 Stainless Steel Sharp Blade Potato Peeler, Ergonomic Handheld Kitchen Gadget for Fruits &amp; Vegetables</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Vec9DN2JL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H5JVSP92</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2 in 1 Multi-Functional Design: Vegetable peeler with wooden handle and built-in bottle opener for added convenience in daily kitchen tasks. | Premium Stainless Steel Blade: Rust resistant sharp blade ensures smooth, fast, and effortless peeling of fruits and vegetables. | Ergonomic Wooden Handle: Comfortable wooden grip provides better control and reduces hand strain during extended use. | Versatile Kitchen Tool: Ideal for peeling potatoes, carrots, cucumbers, and other fruits and vegetables with ease. | Durable &amp; Eco-Friendly Design: Strong construction with a vintage wooden finish makes it a long-lasting and sustainable kitchen gadget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Garlic Press Rocker Stainless Steel | Premium Garlic Crusher &amp; Mincer with Silicone Peeler | Heavy Duty Manual Garlic Masher for Ginger, Garlic &amp; Herbs | Easy Clean Kitchen Tool New 2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/7151bZo8kTL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H6TZHSN7</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>🧄 CRUSH GARLIC IN SECONDS Effortlessly mince garlic cloves with a simple rocking motion. Creates finely crushed garlic quickly without complicated mechanisms, making meal preparation faster and easier. | 💪 HEAVY-DUTY STAINLESS STEEL BUILD Made from premium food-grade stainless steel for strength, durability, rust resistance, and long-lasting performance. Designed for everyday kitchen use. | ✨ ERGONOMIC COMFORT GRIP Curved ergonomic handle provides a comfortable grip and reduces hand strain while pressing. Suitable for regular cooking, meal prep, and everyday kitchen tasks. | 🧽 EASY TO CLEAN DESIGN Open structure allows garlic residue to rinse away easily under running water. Dishwasher safe design helps save cleaning time after cooking. | 🌿 MULTIPURPOSE KITCHEN TOOL Perfect for garlic, ginger, herbs, small vegetables, and seasoning preparation. A practical kitchen accessory for Indian cooking, curries, gravies, marinades, and sauces. | 🏠 COMPACT &amp; SPACE SAVING Lightweight and compact design fits easily inside kitchen drawers, cabinets, utensil holders, and kitchen organizers without occupying extra space. | 🎁 PERFECT GIFT FOR HOME CHEFS An ideal kitchen gadget for home cooks, food lovers, newly married couples, housewarming gifts, and anyone who enjoys convenient cooking tools. | garlic press garlic crusher garlic mincer garlic press rocker stainless steel garlic press garlic chopper garlic crusher stainless steel manual garlic press garlic rocker garlic ginger crusher garlic mincer stainless steel garlic press tool garlic mashing tool garlic pressing tool garlic press stainless steel garlic crusher and mincer best garlic press garlic press for kitchen garlic press manual easy clean garlic press heavy duty garlic press professional garlic press kitchen garlic crusher garlic cutter tool garlic grinding tool garlic press for ginger garlic mincer tool | garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker garlic crusher stainless steel garlic ginger crusher manual garlic press garlic chopper garlic mincer tool best garlic press easy clean garlic press heavy duty garlic press professional garlic press garlic press for kitchen garlic crusher tool garlic press stainless steel heavy duty garlic rocker stainless steel ginger garlic crusher garlic mincing tool garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>EXQ HOME Glass Basting Set Silicone Oil Dispenser Pastry Brush Docking Bowl Set for Cooking, BBQ, Baking and Grilling, Innovative Kitchen Gadget</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41uTsM041TL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DDT7VX7M</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Product material: The oil brush is made of food-grade organic silicone, which is thick, soft, and elastic. The oil bottle is hand-made of plastic, which can withstand 450 degrees of high temperature. | Easy to use: The bottleneck is large, it is easy to fill the liquid, and will not overflow, Our unique design lightly pinchs the hose to easily obtain the required amount of oil, and the oil brush can be used to remove the remaining oil, and it can be used repeatedly after cleaning without odor It is convenient to observe the distribution | Reasonable design: The large-head brush has a wider audience and makes it easier to apply oil. The round bottle design is more stable, the lid has a good seal, and the liquid will not overflow and make the bottle greasy. | Use occasion: The oil bottle brush is used for outdoor BBQ or kitchen cooking, home barbecue, baking, fried eggs, and pizza, and can also add vinegar, egg liquid, honey, and other different liquids. You can microwave butter in the plastic jar to brush onto marinades or salad dressing on your meats or vegetables | Easy to use and easy to clean: The newly designed silicone basting brush is dishwasher safe, which makes cleaning so easy! The individual parts come apart for a hassle-free cleaning experience. Focus more on enjoying the food and less on doing the dishes! | Package Includes: Silicone Oil Brush + Plastic Docking Bowl Set | Color: Multi, Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TrendPlain 16oz/470ml Olive Oil Sprayer for Cooking - 2 in 1 Olive Oil Dispenser for Kitchen Gadgets, Air Fryer, Salad, and BBQ - Green, Glass</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612-b6FTtbL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CNK6BPTV?th=1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Dual Dosing Convenience: These Kitchen Oil Bottles Offer Both Pouring And Spraying Options, Allowing You To Easily Switch Between The Two. It'S A Space-Saving Solution That Keeps Your Kitchen Clean And Organized. | ?Exceptional Spray Nozzle Design?Our Olive Oil Bottle Features A Unique Spray Nozzle That Delivers A Wide-Angle, Fine Mist When Pressed Quickly And A Steady Stream Of Oil When Pressed Slowly. This Precise Design Ensures Even Coverage And Control Over Your Oil Consumption. | Precise Oil Control: Each Spray Dispenses Approximately 0.15G Of Oil, Making It Easy To Monitor And Measure Your Daily Oil Intake. With A Daily Recommended Oil Consumption Of Up To 30G, You Can Effortlessly Manage Your Dietary Preferences. | Safe And Odorless Materials: Made Of Glass, Our Olive Oil Spray Is Both Safe And Non-Toxic. It Can Withstand High Temperatures And Is Completely Odorless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Clazkit Corn Cutter Unbreakable Corn Cob Stripping Kernels Remover Stainless Steel Blades and Hand Protector Mini Circular Shaving Thresher, Kitchen Gadgets</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612IBP9i7gL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CW1NFRMJ</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High quality - Made of stainless steel, mirror polished,strong corrosion resistance,environmental protection and health.Durable and solid enough,it doesn't rust even if it is not used for a long time and won't bend,break too. | User Friendly Design - Upgrade Design Corn Stripper Ellipse Triangle Design Increases the Force Points to Prevent Hand Slipping; Rationally Use the Space and Increase the Corn Kernel Passage to Make the Corn Kernels Pass Smoothly. | Perfect for all Types or Sizes Corn - The Corn Cob Cutter can Fit for Small and Large Corn, with a Simple Twist the Corn Peeler Easily Strips Kernels off Corn Cobs. | Easy to Use - Just Insert Cob and Then Press or Twist, Easy to Remove Corn from the Cob Effortlessly and Efficiently. Perfectly Contoured Cob Peeler Saves You Time. | Ergonomic Grip - It is easy and comfortable to hold, lets you remove kernels off the cob easier and faster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2 Pack Multi-Functional Vegetable Peeler, 3 in 1 Multi Functional Wooden Handle Peeler and Bottle Opener, Kitchen Gadgets Tool for Fruit Pumpkin Peeling Potato Carrot Veggie Peeler</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61sQNK2coeL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GWGY16WQ?th=1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3-in-1 Multi-Functional Vegetable Peeler: This product cleverly integrates 3 essential tools into a simple design, allowing for efficient peeling and shredding of vegetables and fruits, as well as serving as a bottle opener | Solid Hand Held Wood Handle: Crafted from quality solid wood with a non slip grip, the handle fits comfortably in most hands, even during extended use | Easy to Storage: Multi-functional veggie peeler easy to clean,Compact size, Space-efficient design, ideal for drawer storage | Durable Stainless Steel Construction: Crafted from high-quality stainless steel, this kitchen peeler maintains its ultra-sharp blade over time and is easy to clean. Its robust construction ensures longevity, making it suitable for regular use in both home and professional kitchens | Easy to Use:This peeler features a wooden handle and a built-in bottle opener, efficiently peeling thick-skinned fruits and vegetables such as potatoes, sweet potatoes, pumpkins, taro, apples, sugarcane, winter melons, lettuce, and cantaloupes. It can also shred vegetables</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CRIYALE Silicone Baking Mat Sheet | Roti Making Mat | Table Placemat Pad | Silicon Fondant Rolling Mat | BPA-Free Non-Stick Pastry Board Matt | Dough Making Kitchen Gadgets Cooking Tools (Pink)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Iqs+xTutL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C1G82FKF?th=1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Roti Mat for Kneading, Rolling, and Shaping Breads, Pizza Dough's, Pastas, Pastries, Pie Crusts and fondants. Provides a Clean Extra-Large Baking or Cooking Preparation Surface. Makes the Perfect Gift! | Light weight, easy to clean and use. | Will keep your worktop clean. No more scrapping dough or fondant off the worktop | Mat with pre-marked circles helps you get the perfect amount of fondant or dough and the easy-glide material allows you to rotate the mat as you roll | Great surface for kneading dough or rolling out dough and pastries</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Go Store 2 in 1 Stainless Steel Julienne Vegetable Peeler Multi-Functional Fruit &amp; Veggie Shredder Slicer and Grater for Potatoes, Carrots, Cucumbers (Silver, 18 x 8.2 x 2.3 cm)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/717nGHcgNPL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DY51ZQTN?th=1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>✅ 𝟐-𝐢𝐧-𝟏 𝐌𝐮𝐥𝐭𝐢𝐟𝐮𝐧𝐜𝐭𝐢𝐨𝐧𝐚𝐥 𝐃𝐞𝐬𝐢𝐠𝐧: Effortlessly peels and juliennes fruits and vegetables with dual blades. One blade peels smoothly, while the other creates uniform strips for salads and garnishes. | ✅ 𝐔𝐥𝐭𝐫𝐚 𝐒𝐡𝐚𝐫𝐩: Made from the highest quality stainless steel with razor-sharp blades and an anti-cut design. Peel smoothly, quickly, and safely. | ✅ 𝐕𝐞𝐫𝐬𝐚𝐭𝐢𝐥𝐞 𝐊𝐢𝐭𝐜𝐡𝐞𝐧 𝐄𝐬𝐬𝐞𝐧𝐭𝐢𝐚𝐥: Perfect for peeling potatoes, carrots, cucumbers, sweet potatoes, and more. A must-have tool for professional chefs and home cooks to create delicious, visually appealing meals. | ✅ 𝐄𝐫𝐠𝐨𝐧𝐨𝐦𝐢𝐜 &amp; 𝐂𝐨𝐧𝐯𝐞𝐧𝐢𝐞𝐧𝐭: Designed with an easy-grip handle and a hanging hole for simple storage. Built-in scoop holes make it easy to remove spots from fruits and vegetables. | ✅ 𝐄𝐚𝐬𝐲 𝐭𝐨 𝐂𝐥𝐞𝐚𝐧 &amp; 𝐌𝐚𝐢𝐧𝐭𝐚𝐢𝐧: Simply rinse it under running water or place in the dishwasher for hassle-free cleaning. Shake it in water to clear any food clogs quickly. | ✅ 𝐒𝐩𝐚𝐜𝐞-𝐒𝐚𝐯𝐢𝐧𝐠 &amp; 𝐏𝐫𝐚𝐜𝐭𝐢𝐜𝐚𝐥: Compact design replaces bulky kitchen tools. Store it in a drawer or hang it using the handle loop to keep your kitchen organized. | ✅ 𝐖𝐚𝐫𝐧𝐢𝐧𝐠: This tool has a very sharp blade; handle it carefully and keep out of reach of children.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1325,22 +1325,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1 Pack Multifunctional Vegetable Peeler for Kitchen 3 in 1 Stainless Steel Fruit &amp; Vegetable Peeler with Wooden Handle, Built-in Grater &amp; Bottle Opener for Potato, Carrot, Apple &amp; Cucumber</t>
+          <t>Dry Fruit Cutter &amp; Slicer Gadgets (3 in 1, Mix Colour) Kitchen Tools Kitchen Gadgets Dryfruit Choppers for Kitchen, Stainless Steel Blade, Green, Blue, Red</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51ZLcJEiRwL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71MbwrhpzlL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H2QKZYF7?th=1</t>
+          <t>https://www.amazon.in/dp/B0B853XRLJ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>🥕 3 IN 1 MULTIFUNCTIONAL KITCHEN TOOL Peel, grate, and open bottles with one compact kitchen tool. This multifunctional vegetable peeler is designed to simplify daily cooking and food preparation tasks." | 🍎 PREMIUM STAINLESS STEEL BLADE Made with sharp rust-resistant stainless steel for smooth and effortless peeling of potatoes, carrots, apples, cucumbers, and other fruits &amp; vegetables." | 🌿 COMFORTABLE WOODEN HANDLE Ergonomic wooden handle provides a strong, non-slip, and comfortable grip for better control while peeling, slicing, or grating." | 🧀 BUILT-IN GRATER &amp; BOTTLE OPENER Integrated grater helps shred vegetables and cheese easily, while the bottle opener adds extra convenience for multipurpose kitchen use." | 🧼 EASY TO CLEAN &amp; DURABLE Lightweight yet sturdy design ensures long-lasting performance. Easy to wash and maintain, making it a practical addition to every kitchen."</t>
+          <t>UNMATCHED QUALITY – Chop, Dice, Slice or Grate with our newest Multi Chopper and Slicer by Mueller! This functional kitchen gadget will alleviate your prep time to just a couple of minutes. Made with premium materials like steel blades and food-grade BPA-free materials, it's the perfect tool to make home-cooked meals easier and faster. | SAFER: The unique design kitchen tool prevents your hands from ever going near the built-in blades, making this mandoline the safest option for an expert slice. | INNOVATIVE DESIGN - Don't need more space in your kitchen free up countertop space with this kitchen gadgets. Use the Dry Fruits Slicer while cutting Dry fruits. This prevents Dry fruits from slipping while slicing them. It also makes it clean, safe, and easy to work with. No more hassles of washing and wiping. | RUST RESISTANT - Heavy-duty 420 stainless steel blades razor sharpness for crisp, smooth slicing &amp; cutting. Blades snap in and out with ease. | IMPROVES YOUR HEALTH &amp; SAVE TIME – Busy lifestyles make us fall into the fast-food trap. It can take a lot of time and effort to dice, chop and slice the ingredients of the desired dish. Do not despair. Our multi-functional kitchen tool makes this process less time-consuming making it easier to slice dry fruits. That being said, you’re less likely to reach for unhealthy options. From now on, enjoy having more time for your family without missing out on any of the important nutrition.</t>
         </is>
       </c>
     </row>
@@ -1348,22 +1348,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dry Fruit Cutter &amp; Slicer Gadgets (3 in 1, Mix Colour) Kitchen Tools Kitchen Gadgets Dryfruit Choppers for Kitchen, Stainless Steel Blade, Green, Blue, Red</t>
+          <t>Samta Stainless Steel Garlic Press Crusher Manual Garlic &amp; Ginger Presser for Kitchen | Garlic Crusher Chopper Tool | Dishwasher Safe Curved Garlic Grinding Slicer | Multipurpose Cooking Gadget</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71MbwrhpzlL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71RPI68L-qL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0B853XRLJ</t>
+          <t>https://www.amazon.in/dp/B0FZK9LFW3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UNMATCHED QUALITY – Chop, Dice, Slice or Grate with our newest Multi Chopper and Slicer by Mueller! This functional kitchen gadget will alleviate your prep time to just a couple of minutes. Made with premium materials like steel blades and food-grade BPA-free materials, it's the perfect tool to make home-cooked meals easier and faster. | SAFER: The unique design kitchen tool prevents your hands from ever going near the built-in blades, making this mandoline the safest option for an expert slice. | INNOVATIVE DESIGN - Don't need more space in your kitchen free up countertop space with this kitchen gadgets. Use the Dry Fruits Slicer while cutting Dry fruits. This prevents Dry fruits from slipping while slicing them. It also makes it clean, safe, and easy to work with. No more hassles of washing and wiping. | RUST RESISTANT - Heavy-duty 420 stainless steel blades razor sharpness for crisp, smooth slicing &amp; cutting. Blades snap in and out with ease. | IMPROVES YOUR HEALTH &amp; SAVE TIME – Busy lifestyles make us fall into the fast-food trap. It can take a lot of time and effort to dice, chop and slice the ingredients of the desired dish. Do not despair. Our multi-functional kitchen tool makes this process less time-consuming making it easier to slice dry fruits. That being said, you’re less likely to reach for unhealthy options. From now on, enjoy having more time for your family without missing out on any of the important nutrition.</t>
+          <t>🧄 Effortless Garlic &amp; Ginger Crushing: Easily crush and press garlic or ginger with minimal effort using this strong stainless steel kitchen tool. | 🔪 Curved Ergonomic Design: Features a comfortable curved handle for better grip and efficient pressing—perfect for daily cooking use. | 💪 Durable Stainless Steel Build: Made from high-quality rust-resistant stainless steel for long-lasting performance and strength. | 🧼 Dishwasher Safe &amp; Easy to Clean: Simply rinse under running water or toss in the dishwasher for quick cleanup—no mess, no hassle! | 🧂 Multi-Function Kitchen Tool: Use it as a garlic presser, ginger crusher, or even for soft veggies—an all-in-one prep tool for your kitchen. | 👌 Compact &amp; Handy Design: Small yet powerful, the compact design makes it easy to store and perfect for small or busy kitchens. | 🎁 Ideal Cooking Gadget Gift: A practical and thoughtful gift for home cooks, chefs, or kitchen lovers who appreciate time-saving tools.</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1371,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Samta Stainless Steel Garlic Press Crusher Manual Garlic &amp; Ginger Presser for Kitchen | Garlic Crusher Chopper Tool | Dishwasher Safe Curved Garlic Grinding Slicer | Multipurpose Cooking Gadget</t>
+          <t>Ganesh Round Masher Kitchen Gadget with Non-Slip Handle, Masher Utensil for Mashed Potato, Vegetables</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71RPI68L-qL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61ECYzDsEsL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0FZK9LFW3</t>
+          <t>https://www.amazon.in/dp/B0C818Z214</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>🧄 Effortless Garlic &amp; Ginger Crushing: Easily crush and press garlic or ginger with minimal effort using this strong stainless steel kitchen tool. | 🔪 Curved Ergonomic Design: Features a comfortable curved handle for better grip and efficient pressing—perfect for daily cooking use. | 💪 Durable Stainless Steel Build: Made from high-quality rust-resistant stainless steel for long-lasting performance and strength. | 🧼 Dishwasher Safe &amp; Easy to Clean: Simply rinse under running water or toss in the dishwasher for quick cleanup—no mess, no hassle! | 🧂 Multi-Function Kitchen Tool: Use it as a garlic presser, ginger crusher, or even for soft veggies—an all-in-one prep tool for your kitchen. | 👌 Compact &amp; Handy Design: Small yet powerful, the compact design makes it easy to store and perfect for small or busy kitchens. | 🎁 Ideal Cooking Gadget Gift: A practical and thoughtful gift for home cooks, chefs, or kitchen lovers who appreciate time-saving tools.</t>
+          <t>This potato masher is made of stainless steel, so you don't need to worry about safety of your baby and families. Also it possess higher durability and comfort and long time use is guaranteed. It is not easy to rust | Easy In Use and Clean – There are different kitchen essentials in the market but our potato ricer masher is extremely easy to use and can be cleaned under the tap water, after that it is ready for next use. | Perfect use in mashing potatoes, vegetables, sweet potatoes, boiled eggs, cheese etc. You don’t need any mixer for your kitchen as our masher can be use in different ways to save the time and money.</t>
         </is>
       </c>
     </row>
@@ -1394,22 +1394,22 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ganesh Round Masher Kitchen Gadget with Non-Slip Handle, Masher Utensil for Mashed Potato, Vegetables</t>
+          <t>Ganesh 14 in 1 Multipurpose Chopper, Fruits &amp; Vegetable Cutters, Grater Peeler Chipser, Unbreakable Food Grade Body, Easy Push to Clean Button Slicer Dicer, Chopper for Kitchen (Green, Plastic)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61ECYzDsEsL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71SSpHadzXL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0C818Z214</t>
+          <t>https://www.amazon.in/dp/B01BVDS1BE?th=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>This potato masher is made of stainless steel, so you don't need to worry about safety of your baby and families. Also it possess higher durability and comfort and long time use is guaranteed. It is not easy to rust | Easy In Use and Clean – There are different kitchen essentials in the market but our potato ricer masher is extremely easy to use and can be cleaned under the tap water, after that it is ready for next use. | Perfect use in mashing potatoes, vegetables, sweet potatoes, boiled eggs, cheese etc. You don’t need any mixer for your kitchen as our masher can be use in different ways to save the time and money.</t>
+          <t>Large break resistant container with rubber grip base which holds the device firmly in place | Fastest, safest and easiest way to chop or dice fruits and vegetables ; Not Dishwasher Safe ; Other Features: Easy To Use, Clean and Store, Hand Operated, No Electricity Needed, The Container Is Break Resistant, Extra Sharp Stainless Steel Blades | Advanced push to clean button which ensures easy and hygienic cleaning | High-quality stainless steel blades for easy chopping, Sharp pyramid-shaped cutting blade for efficient and smooth cutting | Large detachable container which can also be used to store vegetable and fruits in refrigerator | Colour: Green, Material: Plastic and Stainless Steel, Shape: Rectangle | Package Contents: 1 Plastic Container, 1 peeler with grater, 1 safety holder, 1 masher &amp; 1 handle with cleaning press | Blades: 1 dual, 2 slicer, 2 grater, 1 Juliane, blade die attachment</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ganesh 14 in 1 Multipurpose Chopper, Fruits &amp; Vegetable Cutters, Grater Peeler Chipser, Unbreakable Food Grade Body, Easy Push to Clean Button Slicer Dicer, Chopper for Kitchen (Green, Plastic)</t>
+          <t>Stainless Steel Coconut Slicer Cutter Tool for Kitchen | Coconut Opener, Grater, Scraper, White Remover | Heavy Duty Thengai Thuruvi | Manual Kitchen Accessories Items for Home Use (Pack of 1)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71SSpHadzXL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61uOzEkFBQL._SY879_.jpg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B01BVDS1BE?th=1</t>
+          <t>https://www.amazon.in/dp/B0F92QK9NZ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Large break resistant container with rubber grip base which holds the device firmly in place | Fastest, safest and easiest way to chop or dice fruits and vegetables ; Not Dishwasher Safe ; Other Features: Easy To Use, Clean and Store, Hand Operated, No Electricity Needed, The Container Is Break Resistant, Extra Sharp Stainless Steel Blades | Advanced push to clean button which ensures easy and hygienic cleaning | High-quality stainless steel blades for easy chopping, Sharp pyramid-shaped cutting blade for efficient and smooth cutting | Large detachable container which can also be used to store vegetable and fruits in refrigerator | Colour: Green, Material: Plastic and Stainless Steel, Shape: Rectangle | Package Contents: 1 Plastic Container, 1 peeler with grater, 1 safety holder, 1 masher &amp; 1 handle with cleaning press | Blades: 1 dual, 2 slicer, 2 grater, 1 Juliane, blade die attachment</t>
+          <t>Heavy Duty Coconut Slicer &amp; Cutter 🥥🔪 – Made with premium stainless steel, this manual Thengai Thuruvi is perfect for grating, scraping, and cutting coconuts easily and safely at home. | Multi-Use Kitchen Tool 🍽️✨ – Functions as a Coconut Opener, Grater, Scraper, and White Remover; ideal for traditional Indian cooking, chutneys, and sweets. | Rustproof &amp; Long-Lasting 🛡️✔️ – Crafted for durability with corrosion-resistant stainless steel, ensuring years of hassle-free use without losing sharpness or quality. | Ergonomic &amp; Easy to Use 🤲👌 – Designed for smooth handling, lightweight construction, and effortless cleaning, making it a must-have kitchen accessory. | Perfect for Home Cooking &amp; Festive Recipes 🎉🍛 – Essential for preparing authentic South Indian dishes, coconut chutney, laddoos, and other delicacies with ease. | Compact &amp; Space Saving 📦🏠 – Convenient size fits easily in kitchen drawers or shelves, making storage simple without cluttering your cooking space. | Trusted Kitchen Accessories for Every Household 🏡❤️ – Ideal for daily use or gifting; enhances your kitchen experience with efficiency, safety, and superior performance.</t>
         </is>
       </c>
     </row>
@@ -1440,22 +1440,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2-Piece 3-in-1 Multifunctional Vegetable Peeler Set, Stainless Steel Blade with Ergonomic Wooden Handle, Potato &amp; Fruit Peeler, Scallion Shredder and Built-in Bottle Opener Kitchen Tool</t>
+          <t>Clazkit Stainless Steel Coconut Opener Tool, Coconut Driller, Coconut Opener Machine, Coconut Opener Knife, Coconut Water Opener- (Pack- 1)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61RdTHmXUvL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/6159Kc-wHpL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0HHJKS3JR?th=1</t>
+          <t>https://www.amazon.in/dp/B0CG68ZK2G</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3-in-1 design combines a stainless steel double‑blade peeler, a julienne cutter for fine vegetable strips, and a built‑in bottle opener. | Premium stainless steel blades stay sharp for smooth, effortless peeling of fruits and vegetables. | Comfortable wooden handle provides a secure grip and a natural look that complements any kitchen décor. | Sleek silver finish adds a modern appearance while the standard size fits comfortably in any hand. | High‑capacity 200 ml design handles large vegetables and fruits without frequent refilling. | Powerful 150 W rating ensures consistent performance for heavy‑duty kitchen tasks. | Comes in a single‑count pack – ready to use right out of the box. | Easy to clean – dishwasher‑safe stainless steel and removable wooden handle for quick maintenance.</t>
+          <t>Simply Pop off the top of the coconut, the tool will crack an opening you can remove to either pour out the water or simply insert a straw. | Constructed of Durable FOOD GRADE Stainless Steel.This is the safest way to open green coconut. | Comfortable Rubber Handle for easy opening every time.No Knives, No Machete, No Power Drills, No Hammers!!</t>
         </is>
       </c>
     </row>
@@ -1463,22 +1463,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stainless Steel Coconut Slicer Cutter Tool for Kitchen | Coconut Opener, Grater, Scraper, White Remover | Heavy Duty Thengai Thuruvi | Manual Kitchen Accessories Items for Home Use (Pack of 1)</t>
+          <t>GwernKB 4-in-1 Manual Knife Sharpener Tool for Kitchen, Kitchen Knife Sharpener for Home with Tungsten Steel &amp; Ceramic Slots, Scissor Slot, Non-Slip Base &amp; Ergonomic Handle</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61uOzEkFBQL._SY879_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51IlMlDyvbL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0F92QK9NZ</t>
+          <t>https://www.amazon.in/dp/B0H86ZG11G?th=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Heavy Duty Coconut Slicer &amp; Cutter 🥥🔪 – Made with premium stainless steel, this manual Thengai Thuruvi is perfect for grating, scraping, and cutting coconuts easily and safely at home. | Multi-Use Kitchen Tool 🍽️✨ – Functions as a Coconut Opener, Grater, Scraper, and White Remover; ideal for traditional Indian cooking, chutneys, and sweets. | Rustproof &amp; Long-Lasting 🛡️✔️ – Crafted for durability with corrosion-resistant stainless steel, ensuring years of hassle-free use without losing sharpness or quality. | Ergonomic &amp; Easy to Use 🤲👌 – Designed for smooth handling, lightweight construction, and effortless cleaning, making it a must-have kitchen accessory. | Perfect for Home Cooking &amp; Festive Recipes 🎉🍛 – Essential for preparing authentic South Indian dishes, coconut chutney, laddoos, and other delicacies with ease. | Compact &amp; Space Saving 📦🏠 – Convenient size fits easily in kitchen drawers or shelves, making storage simple without cluttering your cooking space. | Trusted Kitchen Accessories for Every Household 🏡❤️ – Ideal for daily use or gifting; enhances your kitchen experience with efficiency, safety, and superior performance.</t>
+          <t>1️⃣ 4-IN-1 MANUAL KNIFE SHARPENER TOOL🔪 Restore dull kitchen blades with 4 precision sharpening slots designed for scissor sharpening, coarse repair, fine sharpening and polishing. A practical knife sharpener tool for everyday home kitchens. | 2️⃣ TUNGSTEN STEEL &amp; CERAMIC SHARPENING SYSTEM✨ Built with strong sharpening slots to help improve blade edges smoothly and consistently. Ideal for maintaining chef knives, utility knives, paring knives, slicing knives and cleavers. | 3️⃣ SAFE, STABLE &amp; COMFORTABLE GRIP🖐️ The ergonomic handle gives steady control for left and right-hand use, while the non-slip base helps keep the sharpener stable on your kitchen counter during sharpening. | 4️⃣ DETACHABLE SHARPENING UNIT FOR EASY CLEANING🧼 Designed for convenient maintenance, the sharpening unit can be removed and cleaned easily after use, helping keep your kitchen knife sharpener hygienic and ready for daily use. | 5️⃣ COMPACT KITCHEN SIZE FOR HOME USE🏡 With its space-saving design, this kitchen knife sharpener for home fits easily on most countertops and drawers. Suitable for straight-edge kitchen knives and scissors. Not suitable for serrated or wavy-edge knives.</t>
         </is>
       </c>
     </row>
@@ -1486,22 +1486,22 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Clazkit Stainless Steel Coconut Opener Tool, Coconut Driller, Coconut Opener Machine, Coconut Opener Knife, Coconut Water Opener- (Pack- 1)</t>
+          <t>Clazkit Multi-Purpose Strainer or Washer Bowl for Rice Fruits &amp; Vegetable Rice Bowl Color May Vary, Plastic - 10.2 x 17.5 x 24.3 Centimeters</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/6159Kc-wHpL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61H0t3PWOXL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CG68ZK2G</t>
+          <t>https://www.amazon.in/dp/B0C7V8RC3J</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Simply Pop off the top of the coconut, the tool will crack an opening you can remove to either pour out the water or simply insert a straw. | Constructed of Durable FOOD GRADE Stainless Steel.This is the safest way to open green coconut. | Comfortable Rubber Handle for easy opening every time.No Knives, No Machete, No Power Drills, No Hammers!!</t>
+          <t>**Multi-Functional Design:** - Versatile bowl designed for washing fruits, vegetables, straining rice, pasta, lentils, and more. | **Built-in Handle:** - Sturdy handle for easy grip and control during washing or straining, ensuring user comfort. | **Efficient Draining:** - Precision-drilled holes allow for efficient drainage while keeping food secure in the bowl. | **Durable Material:**- Made from durable, food-grade materials for long-lasting use and safety in food preparation. | **Easy to Clean:** - Smooth surface and non-stick design make cleaning a breeze, saving time and effort. | **Space-Saving Design:**- Compact and stackable design for convenient storage, saving cabinet or pantry space. | **Enhanced Stability:**- Stable base prevents tipping or slipping, ensuring a secure and steady operation. | **Sleek Aesthetic:** - Modern and sleek design to complement any kitchen decor, adding a touch of style to your cooking routine. | **Large Capacity:** - Ample space to accommodate a variety of fruits, vegetables, or a generous portion of rice or pasta. | **Versatile Colors:** - Available in a range of appealing colors to match your kitchen aesthetics or personal preference.</t>
         </is>
       </c>
     </row>
@@ -1509,22 +1509,22 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GwernKB 4-in-1 Manual Knife Sharpener Tool for Kitchen, Kitchen Knife Sharpener for Home with Tungsten Steel &amp; Ceramic Slots, Scissor Slot, Non-Slip Base &amp; Ergonomic Handle</t>
+          <t>Garlic Press Rocker Stainless Steel | Premium Garlic Crusher &amp; Mincer with Silicone Peeler | Heavy Duty Manual Garlic Masher for Ginger, Garlic &amp; Herbs | Easy Clean Kitchen Tool New 2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51IlMlDyvbL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/7151bZo8kTL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H86ZG11G?th=1</t>
+          <t>https://www.amazon.in/dp/B0H6TZHSN7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1️⃣ 4-IN-1 MANUAL KNIFE SHARPENER TOOL🔪 Restore dull kitchen blades with 4 precision sharpening slots designed for scissor sharpening, coarse repair, fine sharpening and polishing. A practical knife sharpener tool for everyday home kitchens. | 2️⃣ TUNGSTEN STEEL &amp; CERAMIC SHARPENING SYSTEM✨ Built with strong sharpening slots to help improve blade edges smoothly and consistently. Ideal for maintaining chef knives, utility knives, paring knives, slicing knives and cleavers. | 3️⃣ SAFE, STABLE &amp; COMFORTABLE GRIP🖐️ The ergonomic handle gives steady control for left and right-hand use, while the non-slip base helps keep the sharpener stable on your kitchen counter during sharpening. | 4️⃣ DETACHABLE SHARPENING UNIT FOR EASY CLEANING🧼 Designed for convenient maintenance, the sharpening unit can be removed and cleaned easily after use, helping keep your kitchen knife sharpener hygienic and ready for daily use. | 5️⃣ COMPACT KITCHEN SIZE FOR HOME USE🏡 With its space-saving design, this kitchen knife sharpener for home fits easily on most countertops and drawers. Suitable for straight-edge kitchen knives and scissors. Not suitable for serrated or wavy-edge knives.</t>
+          <t>🧄 CRUSH GARLIC IN SECONDS Effortlessly mince garlic cloves with a simple rocking motion. Creates finely crushed garlic quickly without complicated mechanisms, making meal preparation faster and easier. | 💪 HEAVY-DUTY STAINLESS STEEL BUILD Made from premium food-grade stainless steel for strength, durability, rust resistance, and long-lasting performance. Designed for everyday kitchen use. | ✨ ERGONOMIC COMFORT GRIP Curved ergonomic handle provides a comfortable grip and reduces hand strain while pressing. Suitable for regular cooking, meal prep, and everyday kitchen tasks. | 🧽 EASY TO CLEAN DESIGN Open structure allows garlic residue to rinse away easily under running water. Dishwasher safe design helps save cleaning time after cooking. | 🌿 MULTIPURPOSE KITCHEN TOOL Perfect for garlic, ginger, herbs, small vegetables, and seasoning preparation. A practical kitchen accessory for Indian cooking, curries, gravies, marinades, and sauces. | 🏠 COMPACT &amp; SPACE SAVING Lightweight and compact design fits easily inside kitchen drawers, cabinets, utensil holders, and kitchen organizers without occupying extra space. | 🎁 PERFECT GIFT FOR HOME CHEFS An ideal kitchen gadget for home cooks, food lovers, newly married couples, housewarming gifts, and anyone who enjoys convenient cooking tools. | garlic press garlic crusher garlic mincer garlic press rocker stainless steel garlic press garlic chopper garlic crusher stainless steel manual garlic press garlic rocker garlic ginger crusher garlic mincer stainless steel garlic press tool garlic mashing tool garlic pressing tool garlic press stainless steel garlic crusher and mincer best garlic press garlic press for kitchen garlic press manual easy clean garlic press heavy duty garlic press professional garlic press kitchen garlic crusher garlic cutter tool garlic grinding tool garlic press for ginger garlic mincer tool | garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker garlic crusher stainless steel garlic ginger crusher manual garlic press garlic chopper garlic mincer tool best garlic press easy clean garlic press heavy duty garlic press professional garlic press garlic press for kitchen garlic crusher tool garlic press stainless steel heavy duty garlic rocker stainless steel ginger garlic crusher garlic mincing tool garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker</t>
         </is>
       </c>
     </row>
@@ -1532,22 +1532,22 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Clazkit Multi-Purpose Strainer or Washer Bowl for Rice Fruits &amp; Vegetable Rice Bowl Color May Vary, Plastic - 10.2 x 17.5 x 24.3 Centimeters</t>
+          <t>EXQ HOME Glass Basting Set Silicone Oil Dispenser Pastry Brush Docking Bowl Set for Cooking, BBQ, Baking and Grilling, Innovative Kitchen Gadget</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61H0t3PWOXL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41uTsM041TL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0C7V8RC3J</t>
+          <t>https://www.amazon.in/dp/B0DDT7VX7M</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>**Multi-Functional Design:** - Versatile bowl designed for washing fruits, vegetables, straining rice, pasta, lentils, and more. | **Built-in Handle:** - Sturdy handle for easy grip and control during washing or straining, ensuring user comfort. | **Efficient Draining:** - Precision-drilled holes allow for efficient drainage while keeping food secure in the bowl. | **Durable Material:**- Made from durable, food-grade materials for long-lasting use and safety in food preparation. | **Easy to Clean:** - Smooth surface and non-stick design make cleaning a breeze, saving time and effort. | **Space-Saving Design:**- Compact and stackable design for convenient storage, saving cabinet or pantry space. | **Enhanced Stability:**- Stable base prevents tipping or slipping, ensuring a secure and steady operation. | **Sleek Aesthetic:** - Modern and sleek design to complement any kitchen decor, adding a touch of style to your cooking routine. | **Large Capacity:** - Ample space to accommodate a variety of fruits, vegetables, or a generous portion of rice or pasta. | **Versatile Colors:** - Available in a range of appealing colors to match your kitchen aesthetics or personal preference.</t>
+          <t>Product material: The oil brush is made of food-grade organic silicone, which is thick, soft, and elastic. The oil bottle is hand-made of plastic, which can withstand 450 degrees of high temperature. | Easy to use: The bottleneck is large, it is easy to fill the liquid, and will not overflow, Our unique design lightly pinchs the hose to easily obtain the required amount of oil, and the oil brush can be used to remove the remaining oil, and it can be used repeatedly after cleaning without odor It is convenient to observe the distribution | Reasonable design: The large-head brush has a wider audience and makes it easier to apply oil. The round bottle design is more stable, the lid has a good seal, and the liquid will not overflow and make the bottle greasy. | Use occasion: The oil bottle brush is used for outdoor BBQ or kitchen cooking, home barbecue, baking, fried eggs, and pizza, and can also add vinegar, egg liquid, honey, and other different liquids. You can microwave butter in the plastic jar to brush onto marinades or salad dressing on your meats or vegetables | Easy to use and easy to clean: The newly designed silicone basting brush is dishwasher safe, which makes cleaning so easy! The individual parts come apart for a hassle-free cleaning experience. Focus more on enjoying the food and less on doing the dishes! | Package Includes: Silicone Oil Brush + Plastic Docking Bowl Set | Color: Multi, Random</t>
         </is>
       </c>
     </row>
@@ -1555,22 +1555,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vegetable Peeler with Wooden Handle &amp; Bottle Opener, 2 in 1&amp; 3in 1 Stainless Steel Sharp Blade Potato Peeler, Ergonomic Handheld Kitchen Gadget for Fruits &amp; Vegetables</t>
+          <t>TrendPlain 16oz/470ml Olive Oil Sprayer for Cooking - 2 in 1 Olive Oil Dispenser for Kitchen Gadgets, Air Fryer, Salad, and BBQ - Green, Glass</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Vec9DN2JL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612-b6FTtbL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H5JVSP92</t>
+          <t>https://www.amazon.in/dp/B0CNK6BPTV?th=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2 in 1 Multi-Functional Design: Vegetable peeler with wooden handle and built-in bottle opener for added convenience in daily kitchen tasks. | Premium Stainless Steel Blade: Rust resistant sharp blade ensures smooth, fast, and effortless peeling of fruits and vegetables. | Ergonomic Wooden Handle: Comfortable wooden grip provides better control and reduces hand strain during extended use. | Versatile Kitchen Tool: Ideal for peeling potatoes, carrots, cucumbers, and other fruits and vegetables with ease. | Durable &amp; Eco-Friendly Design: Strong construction with a vintage wooden finish makes it a long-lasting and sustainable kitchen gadget.</t>
+          <t>Dual Dosing Convenience: These Kitchen Oil Bottles Offer Both Pouring And Spraying Options, Allowing You To Easily Switch Between The Two. It'S A Space-Saving Solution That Keeps Your Kitchen Clean And Organized. | ?Exceptional Spray Nozzle Design?Our Olive Oil Bottle Features A Unique Spray Nozzle That Delivers A Wide-Angle, Fine Mist When Pressed Quickly And A Steady Stream Of Oil When Pressed Slowly. This Precise Design Ensures Even Coverage And Control Over Your Oil Consumption. | Precise Oil Control: Each Spray Dispenses Approximately 0.15G Of Oil, Making It Easy To Monitor And Measure Your Daily Oil Intake. With A Daily Recommended Oil Consumption Of Up To 30G, You Can Effortlessly Manage Your Dietary Preferences. | Safe And Odorless Materials: Made Of Glass, Our Olive Oil Spray Is Both Safe And Non-Toxic. It Can Withstand High Temperatures And Is Completely Odorless.</t>
         </is>
       </c>
     </row>
@@ -1578,160 +1578,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Garlic Press Rocker Stainless Steel | Premium Garlic Crusher &amp; Mincer with Silicone Peeler | Heavy Duty Manual Garlic Masher for Ginger, Garlic &amp; Herbs | Easy Clean Kitchen Tool New 2026</t>
+          <t>CRIYALE Silicone Baking Mat Sheet | Roti Making Mat | Table Placemat Pad | Silicon Fondant Rolling Mat | BPA-Free Non-Stick Pastry Board Matt | Dough Making Kitchen Gadgets Cooking Tools (Pink)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/7151bZo8kTL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Iqs+xTutL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H6TZHSN7</t>
+          <t>https://www.amazon.in/dp/B0C1G82FKF?th=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>🧄 CRUSH GARLIC IN SECONDS Effortlessly mince garlic cloves with a simple rocking motion. Creates finely crushed garlic quickly without complicated mechanisms, making meal preparation faster and easier. | 💪 HEAVY-DUTY STAINLESS STEEL BUILD Made from premium food-grade stainless steel for strength, durability, rust resistance, and long-lasting performance. Designed for everyday kitchen use. | ✨ ERGONOMIC COMFORT GRIP Curved ergonomic handle provides a comfortable grip and reduces hand strain while pressing. Suitable for regular cooking, meal prep, and everyday kitchen tasks. | 🧽 EASY TO CLEAN DESIGN Open structure allows garlic residue to rinse away easily under running water. Dishwasher safe design helps save cleaning time after cooking. | 🌿 MULTIPURPOSE KITCHEN TOOL Perfect for garlic, ginger, herbs, small vegetables, and seasoning preparation. A practical kitchen accessory for Indian cooking, curries, gravies, marinades, and sauces. | 🏠 COMPACT &amp; SPACE SAVING Lightweight and compact design fits easily inside kitchen drawers, cabinets, utensil holders, and kitchen organizers without occupying extra space. | 🎁 PERFECT GIFT FOR HOME CHEFS An ideal kitchen gadget for home cooks, food lovers, newly married couples, housewarming gifts, and anyone who enjoys convenient cooking tools. | garlic press garlic crusher garlic mincer garlic press rocker stainless steel garlic press garlic chopper garlic crusher stainless steel manual garlic press garlic rocker garlic ginger crusher garlic mincer stainless steel garlic press tool garlic mashing tool garlic pressing tool garlic press stainless steel garlic crusher and mincer best garlic press garlic press for kitchen garlic press manual easy clean garlic press heavy duty garlic press professional garlic press kitchen garlic crusher garlic cutter tool garlic grinding tool garlic press for ginger garlic mincer tool | garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker garlic crusher stainless steel garlic ginger crusher manual garlic press garlic chopper garlic mincer tool best garlic press easy clean garlic press heavy duty garlic press professional garlic press garlic press for kitchen garlic crusher tool garlic press stainless steel heavy duty garlic rocker stainless steel ginger garlic crusher garlic mincing tool garlic press garlic crusher garlic mincer stainless steel garlic press garlic press rocker</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>EXQ HOME Glass Basting Set Silicone Oil Dispenser Pastry Brush Docking Bowl Set for Cooking, BBQ, Baking and Grilling, Innovative Kitchen Gadget</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41uTsM041TL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DDT7VX7M</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Product material: The oil brush is made of food-grade organic silicone, which is thick, soft, and elastic. The oil bottle is hand-made of plastic, which can withstand 450 degrees of high temperature. | Easy to use: The bottleneck is large, it is easy to fill the liquid, and will not overflow, Our unique design lightly pinchs the hose to easily obtain the required amount of oil, and the oil brush can be used to remove the remaining oil, and it can be used repeatedly after cleaning without odor It is convenient to observe the distribution | Reasonable design: The large-head brush has a wider audience and makes it easier to apply oil. The round bottle design is more stable, the lid has a good seal, and the liquid will not overflow and make the bottle greasy. | Use occasion: The oil bottle brush is used for outdoor BBQ or kitchen cooking, home barbecue, baking, fried eggs, and pizza, and can also add vinegar, egg liquid, honey, and other different liquids. You can microwave butter in the plastic jar to brush onto marinades or salad dressing on your meats or vegetables | Easy to use and easy to clean: The newly designed silicone basting brush is dishwasher safe, which makes cleaning so easy! The individual parts come apart for a hassle-free cleaning experience. Focus more on enjoying the food and less on doing the dishes! | Package Includes: Silicone Oil Brush + Plastic Docking Bowl Set | Color: Multi, Random</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>TrendPlain 16oz/470ml Olive Oil Sprayer for Cooking - 2 in 1 Olive Oil Dispenser for Kitchen Gadgets, Air Fryer, Salad, and BBQ - Green, Glass</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612-b6FTtbL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CNK6BPTV?th=1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Dual Dosing Convenience: These Kitchen Oil Bottles Offer Both Pouring And Spraying Options, Allowing You To Easily Switch Between The Two. It'S A Space-Saving Solution That Keeps Your Kitchen Clean And Organized. | ?Exceptional Spray Nozzle Design?Our Olive Oil Bottle Features A Unique Spray Nozzle That Delivers A Wide-Angle, Fine Mist When Pressed Quickly And A Steady Stream Of Oil When Pressed Slowly. This Precise Design Ensures Even Coverage And Control Over Your Oil Consumption. | Precise Oil Control: Each Spray Dispenses Approximately 0.15G Of Oil, Making It Easy To Monitor And Measure Your Daily Oil Intake. With A Daily Recommended Oil Consumption Of Up To 30G, You Can Effortlessly Manage Your Dietary Preferences. | Safe And Odorless Materials: Made Of Glass, Our Olive Oil Spray Is Both Safe And Non-Toxic. It Can Withstand High Temperatures And Is Completely Odorless.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Clazkit Corn Cutter Unbreakable Corn Cob Stripping Kernels Remover Stainless Steel Blades and Hand Protector Mini Circular Shaving Thresher, Kitchen Gadgets</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612IBP9i7gL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CW1NFRMJ</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>High quality - Made of stainless steel, mirror polished,strong corrosion resistance,environmental protection and health.Durable and solid enough,it doesn't rust even if it is not used for a long time and won't bend,break too. | User Friendly Design - Upgrade Design Corn Stripper Ellipse Triangle Design Increases the Force Points to Prevent Hand Slipping; Rationally Use the Space and Increase the Corn Kernel Passage to Make the Corn Kernels Pass Smoothly. | Perfect for all Types or Sizes Corn - The Corn Cob Cutter can Fit for Small and Large Corn, with a Simple Twist the Corn Peeler Easily Strips Kernels off Corn Cobs. | Easy to Use - Just Insert Cob and Then Press or Twist, Easy to Remove Corn from the Cob Effortlessly and Efficiently. Perfectly Contoured Cob Peeler Saves You Time. | Ergonomic Grip - It is easy and comfortable to hold, lets you remove kernels off the cob easier and faster.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2 Pack Multi-Functional Vegetable Peeler, 3 in 1 Multi Functional Wooden Handle Peeler and Bottle Opener, Kitchen Gadgets Tool for Fruit Pumpkin Peeling Potato Carrot Veggie Peeler</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61sQNK2coeL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GWGY16WQ?th=1</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>3-in-1 Multi-Functional Vegetable Peeler: This product cleverly integrates 3 essential tools into a simple design, allowing for efficient peeling and shredding of vegetables and fruits, as well as serving as a bottle opener | Solid Hand Held Wood Handle: Crafted from quality solid wood with a non slip grip, the handle fits comfortably in most hands, even during extended use | Easy to Storage: Multi-functional veggie peeler easy to clean,Compact size, Space-efficient design, ideal for drawer storage | Durable Stainless Steel Construction: Crafted from high-quality stainless steel, this kitchen peeler maintains its ultra-sharp blade over time and is easy to clean. Its robust construction ensures longevity, making it suitable for regular use in both home and professional kitchens | Easy to Use:This peeler features a wooden handle and a built-in bottle opener, efficiently peeling thick-skinned fruits and vegetables such as potatoes, sweet potatoes, pumpkins, taro, apples, sugarcane, winter melons, lettuce, and cantaloupes. It can also shred vegetables</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>CRIYALE Silicone Baking Mat Sheet | Roti Making Mat | Table Placemat Pad | Silicon Fondant Rolling Mat | BPA-Free Non-Stick Pastry Board Matt | Dough Making Kitchen Gadgets Cooking Tools (Pink)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Iqs+xTutL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C1G82FKF?th=1</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
           <t>Roti Mat for Kneading, Rolling, and Shaping Breads, Pizza Dough's, Pastas, Pastries, Pie Crusts and fondants. Provides a Clean Extra-Large Baking or Cooking Preparation Surface. Makes the Perfect Gift! | Light weight, easy to clean and use. | Will keep your worktop clean. No more scrapping dough or fondant off the worktop | Mat with pre-marked circles helps you get the perfect amount of fondant or dough and the easy-glide material allows you to rotate the mat as you roll | Great surface for kneading dough or rolling out dough and pastries</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Go Store 2 in 1 Stainless Steel Julienne Vegetable Peeler Multi-Functional Fruit &amp; Veggie Shredder Slicer and Grater for Potatoes, Carrots, Cucumbers (Silver, 18 x 8.2 x 2.3 cm)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/717nGHcgNPL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DY51ZQTN?th=1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>✅ 𝟐-𝐢𝐧-𝟏 𝐌𝐮𝐥𝐭𝐢𝐟𝐮𝐧𝐜𝐭𝐢𝐨𝐧𝐚𝐥 𝐃𝐞𝐬𝐢𝐠𝐧: Effortlessly peels and juliennes fruits and vegetables with dual blades. One blade peels smoothly, while the other creates uniform strips for salads and garnishes. | ✅ 𝐔𝐥𝐭𝐫𝐚 𝐒𝐡𝐚𝐫𝐩: Made from the highest quality stainless steel with razor-sharp blades and an anti-cut design. Peel smoothly, quickly, and safely. | ✅ 𝐕𝐞𝐫𝐬𝐚𝐭𝐢𝐥𝐞 𝐊𝐢𝐭𝐜𝐡𝐞𝐧 𝐄𝐬𝐬𝐞𝐧𝐭𝐢𝐚𝐥: Perfect for peeling potatoes, carrots, cucumbers, sweet potatoes, and more. A must-have tool for professional chefs and home cooks to create delicious, visually appealing meals. | ✅ 𝐄𝐫𝐠𝐨𝐧𝐨𝐦𝐢𝐜 &amp; 𝐂𝐨𝐧𝐯𝐞𝐧𝐢𝐞𝐧𝐭: Designed with an easy-grip handle and a hanging hole for simple storage. Built-in scoop holes make it easy to remove spots from fruits and vegetables. | ✅ 𝐄𝐚𝐬𝐲 𝐭𝐨 𝐂𝐥𝐞𝐚𝐧 &amp; 𝐌𝐚𝐢𝐧𝐭𝐚𝐢𝐧: Simply rinse it under running water or place in the dishwasher for hassle-free cleaning. Shake it in water to clear any food clogs quickly. | ✅ 𝐒𝐩𝐚𝐜𝐞-𝐒𝐚𝐯𝐢𝐧𝐠 &amp; 𝐏𝐫𝐚𝐜𝐭𝐢𝐜𝐚𝐥: Compact design replaces bulky kitchen tools. Store it in a drawer or hang it using the handle loop to keep your kitchen organized. | ✅ 𝐖𝐚𝐫𝐧𝐢𝐧𝐠: This tool has a very sharp blade; handle it carefully and keep out of reach of children.</t>
         </is>
       </c>
     </row>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,6 +1597,386 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-02</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51ivBuhty9L._SX695_.jpg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G9MQKMRR</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ROSS BROWN Satchel Bag for women | Handbags for women</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81k+zgTW2jL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H6FXGFVX?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Carrylux Large Capacity Croco Pattern Tote Bags For Womens Big Purses And Handbags Ladies Big Shoulder Bag</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71M7n4XqWCL._SX625_.jpg</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CP9GGP5X?th=1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Self Design PU Handbag for Women Ladies Casual Travel Shopping Office Shoulder Carry Bag</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/316PYKeuNUL.jpg</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H1D6H38J?th=1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BLUE WORLD PU Women Handbag</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61LOeB-ug0L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FYZ13169?th=1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Storite Women's Tote Bag with Leather Handles &amp; Embroidery Printed Handbag with Zip Pockets, Shoulder Tote Bag and Handbag for Office and College</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81+cwVciz+L._SY625_.jpg</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DGXX72D3?th=1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LEGAL BRIBE Women Textured Tote bag</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81D8fFPF+IL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CP829WXM?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LEGAL BRIBE Textured Tote Bag Combo Of 4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71OW7nY-JdL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CQP1QYBW?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Large Capacity Stylish Textured Tote Handbag for Women | Spacious Leather Shoulder Bag Purse Ideal for Office, College, Shopping &amp; Everyday Carry</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41Yy1jJZPOL.jpg</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H3638HD9?th=1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>EXOTIC® Women's Striped Line Handbag for Women| Ladies purse | Stylish Shoulder Bag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71oW9ddfGsL._SY625_.jpg</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09RW3DK6W?th=1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Carrylux Spacious Tote Bag For Womens Handbag Ladies Purses, With Zip Closure Shining Synthetic Leather</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/616tYPi6LZL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DSQ61B9C?th=1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>women's pu leather handbag shoulder bag hand held bag with long strap queen collection simple sober and stylish (HB5)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51v7ZuVmwfL._SY625_.jpg</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H334GPP7?th=1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lavie Women's Betula Tote Handbag | Ladies Purse Handbag | Bag for Women | Rakhi Gift for Sister</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51B5i8VXffL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08HWFWGNX?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>DAISY STAR Women Fashion Tote Purses Stylish Ladies Women and Girls Zip Pocket Canvas Handbag for Office Bag Ladies Travel Shoulder Bag Tote for College Girls</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Ik29fSIGL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CK4HDMX5?th=1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Carrylux Dual Tone Large Capacity Croco Pattern Tote Handbags Purses Shoulder Bag For Womens</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71xfJBW1WLL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CPYRNV8G?th=1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HaveGlam Floral Embossed Crossbody Sling Bag Small Shoulder Handbag for Daily Use Travel &amp; Shopping Phone Purse with Adjustable Strap Lightweight Trendy Bag for Ladies &amp; Girls</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61wxgP4SadL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GPWQQG52?th=1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Lavie Women's Ushawu Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81SRDNUx+kL._SY625_.jpg</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B3JBRB6J?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-06</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51gcz3ppyJL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G9KZ8YV7</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Lavie Ushawu Small Satchel Bag</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/91+bYunDJuL._SY625_.jpg</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B3JBV7Y5</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Storite Women's Tote Bag With Leather Handles &amp; Embroidery Printed bag With Zip Pockets, Shoulder Tote Bag And Handbag For Office And College</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81CMb5BZyVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D2KDCVZQ?th=1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,386 +1597,6 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-02</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51ivBuhty9L._SX695_.jpg</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G9MQKMRR</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ROSS BROWN Satchel Bag for women | Handbags for women</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81k+zgTW2jL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H6FXGFVX?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Carrylux Large Capacity Croco Pattern Tote Bags For Womens Big Purses And Handbags Ladies Big Shoulder Bag</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71M7n4XqWCL._SX625_.jpg</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CP9GGP5X?th=1</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Self Design PU Handbag for Women Ladies Casual Travel Shopping Office Shoulder Carry Bag</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/316PYKeuNUL.jpg</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H1D6H38J?th=1</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>BLUE WORLD PU Women Handbag</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61LOeB-ug0L._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FYZ13169?th=1</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Storite Women's Tote Bag with Leather Handles &amp; Embroidery Printed Handbag with Zip Pockets, Shoulder Tote Bag and Handbag for Office and College</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81+cwVciz+L._SY625_.jpg</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DGXX72D3?th=1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LEGAL BRIBE Women Textured Tote bag</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81D8fFPF+IL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CP829WXM?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>LEGAL BRIBE Textured Tote Bag Combo Of 4</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71OW7nY-JdL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CQP1QYBW?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Large Capacity Stylish Textured Tote Handbag for Women | Spacious Leather Shoulder Bag Purse Ideal for Office, College, Shopping &amp; Everyday Carry</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41Yy1jJZPOL.jpg</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H3638HD9?th=1</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>EXOTIC® Women's Striped Line Handbag for Women| Ladies purse | Stylish Shoulder Bag | Gift for Women</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71oW9ddfGsL._SY625_.jpg</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09RW3DK6W?th=1</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Carrylux Spacious Tote Bag For Womens Handbag Ladies Purses, With Zip Closure Shining Synthetic Leather</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/616tYPi6LZL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DSQ61B9C?th=1</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>women's pu leather handbag shoulder bag hand held bag with long strap queen collection simple sober and stylish (HB5)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51v7ZuVmwfL._SY625_.jpg</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H334GPP7?th=1</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Lavie Women's Betula Tote Handbag | Ladies Purse Handbag | Bag for Women | Rakhi Gift for Sister</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51B5i8VXffL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B08HWFWGNX?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>DAISY STAR Women Fashion Tote Purses Stylish Ladies Women and Girls Zip Pocket Canvas Handbag for Office Bag Ladies Travel Shoulder Bag Tote for College Girls</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Ik29fSIGL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CK4HDMX5?th=1</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Carrylux Dual Tone Large Capacity Croco Pattern Tote Handbags Purses Shoulder Bag For Womens</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71xfJBW1WLL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CPYRNV8G?th=1</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>HaveGlam Floral Embossed Crossbody Sling Bag Small Shoulder Handbag for Daily Use Travel &amp; Shopping Phone Purse with Adjustable Strap Lightweight Trendy Bag for Ladies &amp; Girls</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61wxgP4SadL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GPWQQG52?th=1</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Lavie Women's Ushawu Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81SRDNUx+kL._SY625_.jpg</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0B3JBRB6J?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-06</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51gcz3ppyJL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G9KZ8YV7</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Lavie Ushawu Small Satchel Bag</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/91+bYunDJuL._SY625_.jpg</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0B3JBV7Y5</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Storite Women's Tote Bag With Leather Handles &amp; Embroidery Printed bag With Zip Pockets, Shoulder Tote Bag And Handbag For Office And College</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81CMb5BZyVL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D2KDCVZQ?th=1</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,6 +1597,466 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CR18 COLLECTION Heavy Big Size 2-Layer Stainless Steel Spice Rack | Modular kitchen Storage Organizer | Multipurpose Space Saver Rack for Efficient kitchen Organization</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71-Fb1WV0bL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BHNMMGZM?th=1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Efficient Kitchen Organization: Maximize your kitchen space with the CR18 COLLECTION Heavy Big Size Stainless Steel 2-Layer Kitchen Spice Rack, offering a sleek and organized solution for your culinary essentials. | Durable Stainless Steel Construction: Crafted from high-quality stainless steel, this spice rack ensures durability, corrosion resistance, and a contemporary look that complements any kitchen decor. | Versatile Modular Design: The two-layer design allows for easy customization, adapting to your unique storage needs. Keep spices, condiments, and essentials neatly organized for quick and convenient access. | Space-Saving Solution: Optimize your kitchen layout with this space-saving rack, suitable for both small and large kitchens. Clear up cluttered countertops and create a more functional cooking environment. | Premium Multipurpose Organizer: Upgrade your kitchen with a premium stainless steel organizer that not only enhances efficiency but also adds a touch of sophistication to your cooking space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Dillard's Plastic Multipurpose 4-Tier Floor Mount Corner Shelf Kitchen Organizer Rack/Storage Shelf/Dish Rack/Storage Rack For Kitchen</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61m039qSy2L._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FGJYFV3L</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>VERSATILE DESIGN: 3-tier rolling cart with mesh sides perfect for organizing and storing items in any room, featuring a modern black finish | MOBILE SOLUTION: Smooth-rolling casters allow easy movement between rooms, making it ideal for home, office, or craft room use | STURDY CONSTRUCTION: Durable metal frame with mesh side panels provides stability and ventilation while keeping items secure | SPACE-SAVING: Compact vertical design maximises storage in minimal floor space, with three spacious tiers for efficient organisation | PRACTICAL DIMENSIONS: Each tier offers ample storage space with mesh sides for visibility and easy access to stored items</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TEX-RO 3-Layer Kitchen Rack Stand | Multipurpose Rack for Storage | Vegetable Stand for Kitchen Storage Rack | Durable Kitchen Racks for Storage (Grey)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71fF87VT4BL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FLKBTVPM?th=1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Versatile Storage Solution – Durable rack for kitchen storage designed as an onion potato rack for kitchen with a convenient onion basket for kitchen. This multi-layer shelf for kitchen offers ample space for vegetables, groceries, and utensils, while its sturdy plastic racks for storage multipurpose design keeps your kitchen organized and clutter-free. | Multi-Functional &amp; Space-Saving – Sturdy multipurpose storage rack that works as a kitchen storage rack for home, complete with a removable vegetable basket. Designed with a durable plastic rack frame, this vegetable basket stand doubles as a stylish kitchen basket to keep your vegetables, fruits, and essentials organized in one place. | Durable &amp; Organized Storage – Keep your kitchen neat with this vegetable rack for kitchen that also works as a sturdy onion stand for kitchen. Featuring a spacious 3 tier rack kitchen storage design, this plastic rack for kitchen includes a removable plastic basket for kitchen essentials. The versatile organiser rack doubles as a plastic shelf rack for storage, perfect for vegetables, fruits, and pantry items. | Spacious &amp; Multi-Purpose Design – Stylish fruit basket for kitchen combined with a practical kitchen vegetable storage rack for everyday use. This versatile organiser for kitchen also serves as an onion potato storage for kitchen, featuring sturdy plastic racks for shelf placement. With its smooth-rolling vegetable trolley function, it doubles as one of the best kitchen shelf organisers to keep your vegetables, fruits, and groceries neatly arranged. | Strong &amp; Versatile Storage – Durable vegetable rack with a sturdy plastic stand for kitchen that doubles as a stylish kitchen storage stand. This spacious vegetables stand for kitchen works as a multi purpose storage organiser with a convenient 3 layer storage organizer rack design. Made from high-quality plastic storage material, it is ideal for vegetable storage, fruits, and other kitchen essentials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Plastic Multipurpose 4-Tier Floor Mount Corner Shelf Kitchen Organizer Rack/Storage Shelf/Dish Rack/Storage Rack for Kitchen</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Po+suxtkL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H2W22D8X</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ERSATILE STORAGE: 4-tier multipurpose trolley perfect for organising kitchen items, fruits, vegetables, snacks, toys and kitchenware in a space-saving vertical design | PRACTICAL DESIGN: Features a dedicated dish rack layer along with multiple storage baskets for efficient organisation and easy access to items | MOBILE CONVENIENCE: Equipped with smooth-rolling wheels for effortless movement, making it easy to relocate as needed | DURABLE CONSTRUCTION: Made from sturdy plastic material that ensures long-lasting performance and stability during daily use | COMPACT DIMENSIONS: Space-efficient design with multiple tiers helps maximise storage in small kitchen areas while maintaining a sleek appearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cri8Hub 3 Tier Stainless Steel Kitchen Rack Basket Stand Storage Organizer Wall-Mounted Shelf for Spice Boxes Utensils Large(3-Tier Wall &amp; Floor Mounted Rack)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Xf--Nt1NL._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H6Q96S5X</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3-TIER STORAGE DESIGN: Features three spacious basket shelves to neatly organise spice boxes, utensils, jars, mugs, and other kitchen essentials in one place. | STURDY STAINLESS STEEL CONSTRUCTION: Built with high-quality stainless steel wire for long-lasting durability, resistance to rust, and a polished chrome finish that complements any kitchen décor. | WALL-MOUNTED SPACE SAVER: Mounts securely on the wall to keep your countertops clutter-free, making it ideal for small kitchens where every centimetre of space matters. | VERSATILE USE: Suitable for storing spice boxes, condiment bottles, cups, canisters, and more, helping you maintain a tidy and well-organised kitchen at all times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Zepdos 2 Tier Kitchen Storage Rack Organizer | Multipurpose Metal Storage Shelf, Spice Rack for kitchen, Bathroom &amp; Dish Rack | Space Saving Countertop Rack, Black (40 x 20 x 33 CM)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/712uGFvJhJL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41V678R?th=1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>💪 HEAVY-DUTY METAL CONSTRUCTION : Crafted from premium-quality powder-coated metal for superior durability, corrosion resistance, and long-lasting performance. Strong frame construction provides excellent stability for everyday use in kitchens, bathrooms, and utility areas. | 🏠 MAXIMIZE COUNTER SPACE WITH 2-TIER STORAGE : Designed with two spacious shelves to efficiently organize spice jars, seasoning bottles, cooking oils, sauces, tea, coffee containers, and kitchen essentials. Helps keep countertops clutter-free while maximizing vertical storage space. | ✨ MODERN MINIMALIST DESIGN : Elegant matte black finish complements modern, contemporary, industrial, and traditional home décor styles. Stylish appearance enhances kitchen countertops while offering practical organization solutions. | 🍳 MULTIPURPOSE ORGANIZER FOR EVERY ROOM : Perfect for organizing spices, condiments, cooking ingredients, toiletries, cosmetics, skincare products, office supplies, coffee station accessories, pantry items, and more. Suitable for kitchens, bathrooms, bedrooms, offices, and laundry rooms. | 🛡️ STABLE &amp; SAFE DESIGN : Features raised side rails to prevent items from slipping and anti-slip foot caps for enhanced stability on countertops, shelves, cabinets, and tabletops. Keeps stored items secure and easily accessible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tabletop Spice Rack For Your Kitchen_Countertop Spice s And Masala Rack 2 -Tiered Shelf And 2 Layer Stainless Steel And Special Countertop Spice Rack-(Pack Of One) (Nhsp)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81W+6KEwa-L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CLGK218X</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>The 2 Shelves Can Fit Jars, Bottles, And Cans Up To 2.5 Inches In Diameter And The Top And Middle Shelves Can Fit Jars The Top Shelf Can Accommodate Taller Items | Multipurpose Use - Organize &amp; Display Spices, Spice Jars, Shakers, Snacks, Grinders, Dry Goods, Condiments, Nail Polishes, Vitamin Bottles, Medicine Bottles, Jars, Nail Polish, And Other Smaller Items. | the Craftland 2 Tier Rack offers organized space compatible with the majority of glass or plastic bottles, shakers, jars, and smaller canisters. Perfect for starter spice sets or personal everyday collections. | Elegant Scroll Design Can Be Utilized In Any Room Of The House, Including The Kitchen, Bath Room, Living Room, Bedroom, Craft Room, Playroom, Kids Rooms, Guest Rooms &amp; More | 2 Tier Rack An Essential Item To Keep Smaller Kitchen, Home, And Health Storage Jars, Bottles, And Canisters Organized And Accessible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kitchen Organizer Rack – Multi-Purpose Kitchen Stand for Countertop &amp; Cabinet Storage | Heavy-Duty Kitchen Rack Organizer for Spices, Utensils, Dishes &amp; Pantry Items (2 Tier Z shape Rack)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61X2seYu4zL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GHZN7B1R?th=1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>✔ MULTI-PURPOSE KITCHEN ORGANIZER Keep your kitchen neat and clutter-free. Perfect for organizing spices, jars, utensils, plates, bowls, cleaning supplies, and pantry essentials. | ✔ STRONG &amp; STABLE DESIGN Made from durable, heavy-duty material for long-lasting use. Sturdy construction ensures stability even when fully loaded. | ✔ SPACE-SAVING KITCHEN STAND Maximize countertop, cabinet, or pantry space. Ideal for small kitchens, apartments, and modern homes. | ✔ EASY TO ASSEMBLE &amp; CLEAN Quick and simple installation with minimal tools required. Smooth surface makes cleaning fast and hassle-free. | ✔ MODERN &amp; ELEGANT LOOK Sleek design complements any kitchen décor — perfect for countertops, cabinets, shelves, or under-sink storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CR18 COLLLECTION Stainless Steel 2 Layer Kitchen Spice Rack| Modular Storage Rack | Kitchen Organizer Multipurpose Storage Shelf/Rack, Silver</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51W5lotUOKL.jpg</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C1BYQN7Y</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | SMART STORAGE: Use anywhere you need to keep food, pantry and kitchen items organized; Perfect for organizing pasta, packets, extra supplies of salt, dressing and vinegar, macaroni and cheese boxes, baking supplies, condiments and more; These bins also work in any room of your home! | Stainless Steel Kitchen Rack Stand Container Organizer Organiser Storage Shelf Shelves Holder Trolley Basket for Spice Boxes Dabba Bartan Utensils Dishes for Home, 2-Tier, Large, Silver Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | FUNCTIONAL &amp; VERSATILE: The perfect solution for organizing a multitude of items - such as video games, bath soaps, shampoos, conditioners, linens, towels, laundry needs, craft supplies and more; Use in bathroom, bedroom, closet, laundry room, utility room, garage, hobby and craft room, home office, mudroom and entryways; Perfect for homes, apartments, condos, college dorm rooms, RVs and campers | 2 SHELVES : This trolley has 2 shelves, which makes it large enough to store many things at a time. | Multipurpose - apart from using as mixer &amp; jar rack, it can be used as a general purpose storage rack too</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RILION 6 fridge storage boxes multipurpose containers for storage Space-saving Refrigerator Side Door Organizer for fridge kitchen Fruits, Vegetables Storage Containers- transparent</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71KVlyVtG3L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DC5MJQYZ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Perfect Size: The kitchen organizer container box bins are meticulously designed to fit seamlessly into the refrigerator side door, maximizing space utilization and saving valuable fridge space. By storing vegetables separately in these containers, freshness is preserved, spoilage is minimized, and healthier storage habits are encouraged. Plus, their convenient design ensures easy access with just a simple open of the fridge door. | High Quality: Crafted from premium PP Transparent material, plastic storage boxes guarantee durability and strength. Their transparent bodies offer clear visibility of the contents stored inside, enhancing their functionality as top-notch kitchen organizer tools. | Multipurpose Use: Made from robust, high-quality plastic, these kitchen storage containers are versatile and built to last. From storing utensils, cutlery, and chopsticks in the kitchen to organizing toiletries in the bathroom or stationery on the desktop, these containers serve multiple purposes throughout the home. | Freezer-Friendly Containers: Engineered to withstand freezing temperatures, freezer storage containers are ideal for keeping items safely stored in the freezer. Their durable construction ensures long-lasting performance, even in challenging conditions, making them essential additions to any kitchen. | Efficient Fridge Organizer: fridge containers offer an efficient solution for organizing your fridge. With these containers, finding what you need is a breeze, eliminating the hassle of rummaging through cluttered shelves. Sized at 11.8cm in length, 9.8cm in width, and 12.5cm in height, these containers are optimally designed for effective fridge organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2-Tier Stainless Steel Kitchen Storage Spice Rack and Container Organizer Counter top Pantry Stand Multipurpose Masala Kitchen Rack Stand Space Saver Rack (Pack of 1) (NHSP)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71xcENEGMyL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CH6M5MXX</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Two-Tiered Storage: This rack offers two spacious tiers, allowing you to efficiently store a wide range of kitchen items. Keep your spices, condiments, and cooking utensils neatly organized within easy reach. | Stainless Steel Durability: Crafted from high-quality stainless steel, this kitchen rack is not only stylish but also built to withstand daily use. It resists corrosion, stains, and wear, ensuring long-lasting performance. | Space-Saving Design: Maximize your kitchen's available space with this compact yet roomy shelf. Its two tiers make excellent use of vertical space, freeing up your countertops and cabinets. | Multi-Purpose Functionality: This versatile rack is not limited to just spices and utensils. It can also be used for storing kitchen gadgets, small appliances, or even as a display shelf for your favorite cookbooks or decorative items. | Sleek and Modern Design: Its minimalist stainless steel design complements any kitchen decor, adding a touch of contemporary elegance to your culinary space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Privesh Stainless Steel Modern Kitchen Storage Rack, Folding Perforated Design Trolley for Spice, Fruits, Vegetable, Onion, Potato, Organizer Stand with Wheel, 4 Layer Trolley</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/611g96ubcaL._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BRVDXZ28?th=1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Product Material: 100% Stainless Steel Grade 202. | Uses: Can Store Fruits, Vegetables and Other Kitchen Accessories like Spice Jars, Containers etc. | This Product Is Rust Resistance and Strong Body Material. | It's Made Of Premium Grade Stainless Steel And It Is Highly Durable And Rust-Proof. | Attractive Design Strong Material, Durable and Rust Proof and Finishing Look Enhance Kitchen Beauty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>StainlessSteel Under Cabinet Kitchen DishRack Expandable Storage FloatingShelves For Kitchen Multipurpose Organizer Extend Up To 580 Mm With Anti-Rust Nano Coating(Pack of 2)(Nhsp) Silver</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61IW6o2oPDL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CH6MD3LV?th=1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Stainless Steel Durability: Crafted from premium stainless steel, these racks are built to withstand the rigors of daily use while maintaining a sleek and modern appearance. They resist corrosion, ensuring they'll stand the test of time. | Multi-Purpose Functionality: These racks are not just for dishes; they're designed for versatility. Use them to store utensils, pots, or even as a mini stand to organize your kitchen essentials. | Space-Saving Design: The cleverly designed racks are space-saving champions. They help you make the most of your kitchen space, keeping it clutter-free and well-organized. | Fridge-Friendly: These racks are fridge-friendly, allowing you to create extra storage space within your refrigerator. Keep your favorite snacks, condiments, and beverages within easy reach. | Stylish and Functional: The minimalist stainless steel design adds a touch of sophistication to your kitchen while enhancing its functionality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cri8Hub Metal 2 Tier Standing Spice Rack, Bathroom Countertop Storage Shelf Organizer, Kitchen Organizer, Cabinet Tray for Dresser, Multipurpose Stand, (2 Tier Standing Multipurpose Rack)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/413na2K-HnL.jpg</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C5RJ822T</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>:-Premium Quality :- Under cabinet organizers is made with premium ABS and Mild steel, We have passed a lot of use and load-bearing tests, It is stable and durable . So you don’t have to worry about the shelf wobbly to cause the items in the pallet to overturn . | :-Modern and simple Nordic style design, this storage rack can be matched well with most household style; perfect for organizing kitchen, living room, bathrooms, office, desk, balcony, also can using as small plant stand, makeup organizer rack. | :-Spray painting and thickening body, good rust prevention and no need to install. Free-standing, solid build that will not tip over or fall. | :-A Wide Range of Usages: The shelf can serve itself for different purposes, holding small items in your kitchen, bathroom, bedroom, living room, reading room, balcony and office, etc. You can try to place as many small-sized household and office items as you can imagine. | :-Durable Material: Made of premium iron and sprayed with eco-grade paint, the shelf is sturdy to use and easy to clean, rust-proof and water-proof, no need to install and free standing. Each evenly well-polished corner can keep you from being scratched, safe and unharmed. | :-Easy To Clean - Simply wipe the surface with a damp cloth to clean the shelf, keep dry and do not submerge. The under bathroom sink storage adopts hollow design, which has a good draining effect and prevents moldy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HomeWiz 360° Rotating Kitchen Organiser | Lazy Susan Smooth Turntable Organiser | Spice Rack Organizer | Cosmetic Holder Organizer | Multipurpose Use for Kitchen Counter, Dining Table | Dark Blue</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71c26Zr37WL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CX1YPXW5?th=1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>THE SHELF THAT HIDES THINGS AT THE BACK IS NOT AN ORGANISATION PROBLEM — IT IS A ROTATION PROBLEM: Bottles at the back jars you cannot reach without moving three things first condiments nobody uses because they are always behind something else. A spinning tray means there is no back. One gentle spin brings everything forward. The HomeWiz Dark Blue Rotating Tray at makes every item on a shelf equally accessible in under one second. | SMOOTH 360° ROTATION — EVERYTHING COMES TO YOU: Give it a spin. Whatever was at the back comes to the front. No more reaching across the shelf no more knocking things over trying to get to the item behind another. | DIAMETER — FITS COUNTERS SHELVES AND INSIDE CABINETS: The round base fits on kitchen counters near the stove inside cabinets on dining tables and on bathroom shelves. A versatile size for most surfaces. | RAISED RIM KEEPS ITEMS FROM FALLING OFF: The curved edge around the base keeps bottles jars and containers from sliding off when the tray spins. Everything stays on the tray even with a fast spin. | FOOD-GRADE BPA-FREE — SAFE FOR KITCHEN CONTACT: Made from food-grade plastic with no BPA. Safe for direct contact with food containers oil bottles and kitchen items. | SMOOTH 360° ROTATION — EVERYTHING COMES TO YOU: Give it a spin. Whatever was at the back comes to the front. No more reaching across the shelf no more knocking things over trying to get to the item behind another. | LIGHTWEIGHT — EASY TO MOVE AND CLEAN: The light weight means you can pick up the entire tray and wipe the shelf underneath easily. Keep both the tray and the shelf clean. | WHY 10 LAKH INDIAN FAMILIES COOK WITH HOMEWIZ: HomeWiz was not built in a boardroom. It was built around the reality of Indian kitchens — the morning chai the Sunday biryani the daily dal that feeds a family. We started with one belief: that the tools in your kitchen should be as honest as the food you cook with them. Today over 10 lakh families across India trust HomeWiz in their homes. Not because of flashy marketing — but because when a HomeWiz product lands in your kitchen it simply works. Every single day. That is the only promise we make — and the only one we need to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Organizer Tray Office Drawer Dividers Storage Bins Multipurpose Desk for Makeup, Kitchen, Office, Bathroom, Bedroom Dreassing, Basket Rack MultiColor(23*8*5 CM) Pack Of 6 (Multi 6pcs)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71UDWR9wrBL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CR374476</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Combo of 6pcs multipurpose storage baskets set which is useful for one's daily activity. | Color : Available in assorted colors, Color will be shipped as pe availability, Material : Plastic | Portable, light weight stack-able. Can be kept in drawers, almirahs, kitchen cabinets, refrigerator, shelves etc. | The desk drawer organizer trays can be used for desk, drawers, kitchen, office and living room as well as for other applications. help you to create your own mix and match organizational system to fit in any drawers, cabinets, lockers and wardrobe closets</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>COMFYHOME Kitchen Organizer Rack with Wheels - Adjustable 4 Tier Microwave Stand with 3 Wire Baskets, Oven Stand with Storage Cabinet, Metal Kitchen Storage Cart for Pantry （80x32x108cm）</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/717u0QDFKVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GX1P63MY?th=1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>【Large Capacity 4-Tier Kitchen Organizer Rack】Designed with a four-tier structure and an extra-wide countertop, this microwave stand for kitchen​easily supports large appliances like microwaves and air fryers. The combination of adjustable shelves and deep, pull-out mesh baskets significantly boosts your storage capacity. The open-mesh design ensures optimal airflow, keeping fruits and vegetables fresh and preventing moisture buildup. | 【Heavy-Duty Metal Frame &amp; Stable Structure】 This upgraded carbon steel 4 tier kitchen rack stand​features thickened shelves, reinforced tubing, and deepened baskets—increasing basket volume by 37.5%. Engineered for superior load-bearing, the tight joints and robust frame resist bending or wobbling, even under heavy weight. It offers a comprehensive upgrade in durability, ensuring your kitchen racks for storage remain stable and secure for years to come. | 【Mobile &amp; Stationary Dual Mode】Equipped with 360° silent swivel casters, this oven stand with wheels 4 tier heavy duty​glides smoothly for easy cleaning underneath. Two locking brakes keep the unit firmly in place to prevent accidental sliding. We also include non-slip stationary feet, allowing you to freely switch between a mobile cart and a fixed stand for kitchen storage rack based on your needs. | 【Multipurpose Storage Solution】More than just a rack for storage multipurpose, this oven stand​adapts to any room. Use it in the kitchen for appliances, in the office for printers and files, or on the balcony for plants. Whether used as a coffee bar cart, bathroom shelf, or pantry organizer, one unit fulfills all your organizational needs. | 【Premium Finish &amp; Easy Assembly】Featuring a classic matte black finish, this microwave stand for kitchen platform​ is scratch-resistant and easy to clean—just wipe it down to maintain its premium look. Overall dimensions: 12.5" D x 31.5" W x 42.5" H. The minimalist design complements any decor. Assembly is quick and tool-friendly with clear instructions included, combining open shelving for display with hidden baskets for a clutter-free home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SAFAK 3 Tier Wooden Kitchen Organizer Rack for Countertop | Wooden Spice Rack Stand for Kitchen Counter | Kitchen Shelf Organizer &amp; Cabinet Shelf Riser | Decorative Masala Rack Storage Stand | Dark</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71swzxPftnL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GRVMYVQH?th=1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>A wooden kitchen organizer is essential for any kitchen since it is both stylish and practical. The purpose of these organizers is to improve the efficiency and organization of your kitchen. To accommodate different storage needs, they are available in a range of sizes and forms. | Jars, cans, bottles, sugar, tea, spices, sauces, and other kitchen supplies can all be stored in these useful step organizers. Additionally, they are a great method to store things for your pooja room. | Because it doesn't require any additional building or equipment, this freestanding organizer is easy to use. | Because it makes room in cramped cabinets and pantries, this three-tiered organizer is a great tool for kitchen and pantry organization. | When necessary, a moist towel can be used to clean the step shelf organizer's nonslip shelf lining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TEX-RO Kitchen Trolley with Wheels | 3-Layer Metal Vegetable Basket Stand &amp; Kitchen Storage Rack | Multipurpose Kitchen Organizer for Onion Potato Storage (Black)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81zSFh5uwdL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B3JST2F4?th=1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Maximize Kitchen Storage with Tex Ro Kitchen Trolley: Versatile Kitchen Shelf and Storage Organizer for Kitchen, Vegetable Rack for Kitchen, Ideal for Efficient Kitchen Storage Solutions. | Efficient Home Organization with Kitchen Trolley Organizer and kitchen Stand : Store and Organize Home Organizer Items and Storage with a Stylish Basket for Kitchen, Perfect for Kitchen Essentials for Home Organization. | Versatile Kitchen Organization with Multipurpose Storage Solutions: Organize and Store Onions with Onion Baskets for Storage and Utilize the Onion Potato Rack for Kitchen. Enhance Storage Efficiency with a Vegetable Basket for Kitchen and Versatile Multipurpose Storage Trolley. Keep Your Kitchen Clutter-Free with a Functional Kitchen Cabinet Organizer. | Enhance Your Kitchen Organization with a Modern vegetable stand for kitchen and kitchen storage rack : Utilize the Versatile Trolley for Kitchen Storage, Ideal for Showcasing Vegetables and Providing Ample Space, and Discover the Latest Modern Kitchen Accessories for Stylish and Efficient Storage Solutions. | Convenient and Space-Saving Kitchen Storage: Maximize Efficiency with a Variety of Storage Solutions, including Onion Stand for Kitchen, Onion Storage Container for kitchen , Potato Onion Storage Container, Corner Rack, Rotating Kitchen Rack, and corner Shelf for Kitchen Organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GOLWYN Air Tight Containers For Kitchen Storage Set, Bpa Container For Kitchen Storage Set, Kitchen Organizer And Kitchen Accessories Items &amp; Storage(1200 Ml Set Of 8)(Plastic)Transparent</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71auAIxh1PL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B2SBK18B?th=1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Airtight kitchen storage containers set Keep Food Fresh----The lids with silicone gasket make these storage containers airtight, and the top flips open easily. Airtight storage system will always keep your food dry and fresh. All have the same lids make it easy to wash dry and reuse with ease. We can also use for spice containers for kitchen storage . Perfect ! plastic containers for kitchen storage . | Package Content: 8Pcs Container Jar Set With Cap | Material: Premium Quality Plastic | Airtight / 100% Leak Proof. | Capacity: 1100 ml | Color: transparent | BPA Free and Food Grade Material Plastic Boxes For Storage ---- pantry storage containers for kitchen airtight are made of durable plastic, BPA free, which have a longer life than many other brands plastic containers. Clear containers make it convenient to see what’s inside, you can easily get what you want without opening every container. Space saving storage box for kitchen .</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1601,459 +1601,22 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CR18 COLLECTION Heavy Big Size 2-Layer Stainless Steel Spice Rack | Modular kitchen Storage Organizer | Multipurpose Space Saver Rack for Efficient kitchen Organization</t>
+          <t>RILION 6 fridge storage boxes multipurpose containers for storage Space-saving Refrigerator Side Door Organizer for fridge kitchen Fruits, Vegetables Storage Containers- transparent</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71-Fb1WV0bL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71KVlyVtG3L._SX679_.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0BHNMMGZM?th=1</t>
+          <t>https://www.amazon.in/dp/B0DC5MJQYZ</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Efficient Kitchen Organization: Maximize your kitchen space with the CR18 COLLECTION Heavy Big Size Stainless Steel 2-Layer Kitchen Spice Rack, offering a sleek and organized solution for your culinary essentials. | Durable Stainless Steel Construction: Crafted from high-quality stainless steel, this spice rack ensures durability, corrosion resistance, and a contemporary look that complements any kitchen decor. | Versatile Modular Design: The two-layer design allows for easy customization, adapting to your unique storage needs. Keep spices, condiments, and essentials neatly organized for quick and convenient access. | Space-Saving Solution: Optimize your kitchen layout with this space-saving rack, suitable for both small and large kitchens. Clear up cluttered countertops and create a more functional cooking environment. | Premium Multipurpose Organizer: Upgrade your kitchen with a premium stainless steel organizer that not only enhances efficiency but also adds a touch of sophistication to your cooking space.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Dillard's Plastic Multipurpose 4-Tier Floor Mount Corner Shelf Kitchen Organizer Rack/Storage Shelf/Dish Rack/Storage Rack For Kitchen</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61m039qSy2L._SY879_.jpg</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FGJYFV3L</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>VERSATILE DESIGN: 3-tier rolling cart with mesh sides perfect for organizing and storing items in any room, featuring a modern black finish | MOBILE SOLUTION: Smooth-rolling casters allow easy movement between rooms, making it ideal for home, office, or craft room use | STURDY CONSTRUCTION: Durable metal frame with mesh side panels provides stability and ventilation while keeping items secure | SPACE-SAVING: Compact vertical design maximises storage in minimal floor space, with three spacious tiers for efficient organisation | PRACTICAL DIMENSIONS: Each tier offers ample storage space with mesh sides for visibility and easy access to stored items</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>TEX-RO 3-Layer Kitchen Rack Stand | Multipurpose Rack for Storage | Vegetable Stand for Kitchen Storage Rack | Durable Kitchen Racks for Storage (Grey)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71fF87VT4BL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FLKBTVPM?th=1</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Versatile Storage Solution – Durable rack for kitchen storage designed as an onion potato rack for kitchen with a convenient onion basket for kitchen. This multi-layer shelf for kitchen offers ample space for vegetables, groceries, and utensils, while its sturdy plastic racks for storage multipurpose design keeps your kitchen organized and clutter-free. | Multi-Functional &amp; Space-Saving – Sturdy multipurpose storage rack that works as a kitchen storage rack for home, complete with a removable vegetable basket. Designed with a durable plastic rack frame, this vegetable basket stand doubles as a stylish kitchen basket to keep your vegetables, fruits, and essentials organized in one place. | Durable &amp; Organized Storage – Keep your kitchen neat with this vegetable rack for kitchen that also works as a sturdy onion stand for kitchen. Featuring a spacious 3 tier rack kitchen storage design, this plastic rack for kitchen includes a removable plastic basket for kitchen essentials. The versatile organiser rack doubles as a plastic shelf rack for storage, perfect for vegetables, fruits, and pantry items. | Spacious &amp; Multi-Purpose Design – Stylish fruit basket for kitchen combined with a practical kitchen vegetable storage rack for everyday use. This versatile organiser for kitchen also serves as an onion potato storage for kitchen, featuring sturdy plastic racks for shelf placement. With its smooth-rolling vegetable trolley function, it doubles as one of the best kitchen shelf organisers to keep your vegetables, fruits, and groceries neatly arranged. | Strong &amp; Versatile Storage – Durable vegetable rack with a sturdy plastic stand for kitchen that doubles as a stylish kitchen storage stand. This spacious vegetables stand for kitchen works as a multi purpose storage organiser with a convenient 3 layer storage organizer rack design. Made from high-quality plastic storage material, it is ideal for vegetable storage, fruits, and other kitchen essentials.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Plastic Multipurpose 4-Tier Floor Mount Corner Shelf Kitchen Organizer Rack/Storage Shelf/Dish Rack/Storage Rack for Kitchen</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61Po+suxtkL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H2W22D8X</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ERSATILE STORAGE: 4-tier multipurpose trolley perfect for organising kitchen items, fruits, vegetables, snacks, toys and kitchenware in a space-saving vertical design | PRACTICAL DESIGN: Features a dedicated dish rack layer along with multiple storage baskets for efficient organisation and easy access to items | MOBILE CONVENIENCE: Equipped with smooth-rolling wheels for effortless movement, making it easy to relocate as needed | DURABLE CONSTRUCTION: Made from sturdy plastic material that ensures long-lasting performance and stability during daily use | COMPACT DIMENSIONS: Space-efficient design with multiple tiers helps maximise storage in small kitchen areas while maintaining a sleek appearance</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Cri8Hub 3 Tier Stainless Steel Kitchen Rack Basket Stand Storage Organizer Wall-Mounted Shelf for Spice Boxes Utensils Large(3-Tier Wall &amp; Floor Mounted Rack)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71Xf--Nt1NL._SY879_.jpg</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H6Q96S5X</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3-TIER STORAGE DESIGN: Features three spacious basket shelves to neatly organise spice boxes, utensils, jars, mugs, and other kitchen essentials in one place. | STURDY STAINLESS STEEL CONSTRUCTION: Built with high-quality stainless steel wire for long-lasting durability, resistance to rust, and a polished chrome finish that complements any kitchen décor. | WALL-MOUNTED SPACE SAVER: Mounts securely on the wall to keep your countertops clutter-free, making it ideal for small kitchens where every centimetre of space matters. | VERSATILE USE: Suitable for storing spice boxes, condiment bottles, cups, canisters, and more, helping you maintain a tidy and well-organised kitchen at all times.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Zepdos 2 Tier Kitchen Storage Rack Organizer | Multipurpose Metal Storage Shelf, Spice Rack for kitchen, Bathroom &amp; Dish Rack | Space Saving Countertop Rack, Black (40 x 20 x 33 CM)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/712uGFvJhJL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H41V678R?th=1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>💪 HEAVY-DUTY METAL CONSTRUCTION : Crafted from premium-quality powder-coated metal for superior durability, corrosion resistance, and long-lasting performance. Strong frame construction provides excellent stability for everyday use in kitchens, bathrooms, and utility areas. | 🏠 MAXIMIZE COUNTER SPACE WITH 2-TIER STORAGE : Designed with two spacious shelves to efficiently organize spice jars, seasoning bottles, cooking oils, sauces, tea, coffee containers, and kitchen essentials. Helps keep countertops clutter-free while maximizing vertical storage space. | ✨ MODERN MINIMALIST DESIGN : Elegant matte black finish complements modern, contemporary, industrial, and traditional home décor styles. Stylish appearance enhances kitchen countertops while offering practical organization solutions. | 🍳 MULTIPURPOSE ORGANIZER FOR EVERY ROOM : Perfect for organizing spices, condiments, cooking ingredients, toiletries, cosmetics, skincare products, office supplies, coffee station accessories, pantry items, and more. Suitable for kitchens, bathrooms, bedrooms, offices, and laundry rooms. | 🛡️ STABLE &amp; SAFE DESIGN : Features raised side rails to prevent items from slipping and anti-slip foot caps for enhanced stability on countertops, shelves, cabinets, and tabletops. Keeps stored items secure and easily accessible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Tabletop Spice Rack For Your Kitchen_Countertop Spice s And Masala Rack 2 -Tiered Shelf And 2 Layer Stainless Steel And Special Countertop Spice Rack-(Pack Of One) (Nhsp)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81W+6KEwa-L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CLGK218X</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>The 2 Shelves Can Fit Jars, Bottles, And Cans Up To 2.5 Inches In Diameter And The Top And Middle Shelves Can Fit Jars The Top Shelf Can Accommodate Taller Items | Multipurpose Use - Organize &amp; Display Spices, Spice Jars, Shakers, Snacks, Grinders, Dry Goods, Condiments, Nail Polishes, Vitamin Bottles, Medicine Bottles, Jars, Nail Polish, And Other Smaller Items. | the Craftland 2 Tier Rack offers organized space compatible with the majority of glass or plastic bottles, shakers, jars, and smaller canisters. Perfect for starter spice sets or personal everyday collections. | Elegant Scroll Design Can Be Utilized In Any Room Of The House, Including The Kitchen, Bath Room, Living Room, Bedroom, Craft Room, Playroom, Kids Rooms, Guest Rooms &amp; More | 2 Tier Rack An Essential Item To Keep Smaller Kitchen, Home, And Health Storage Jars, Bottles, And Canisters Organized And Accessible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Kitchen Organizer Rack – Multi-Purpose Kitchen Stand for Countertop &amp; Cabinet Storage | Heavy-Duty Kitchen Rack Organizer for Spices, Utensils, Dishes &amp; Pantry Items (2 Tier Z shape Rack)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61X2seYu4zL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GHZN7B1R?th=1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>✔ MULTI-PURPOSE KITCHEN ORGANIZER Keep your kitchen neat and clutter-free. Perfect for organizing spices, jars, utensils, plates, bowls, cleaning supplies, and pantry essentials. | ✔ STRONG &amp; STABLE DESIGN Made from durable, heavy-duty material for long-lasting use. Sturdy construction ensures stability even when fully loaded. | ✔ SPACE-SAVING KITCHEN STAND Maximize countertop, cabinet, or pantry space. Ideal for small kitchens, apartments, and modern homes. | ✔ EASY TO ASSEMBLE &amp; CLEAN Quick and simple installation with minimal tools required. Smooth surface makes cleaning fast and hassle-free. | ✔ MODERN &amp; ELEGANT LOOK Sleek design complements any kitchen décor — perfect for countertops, cabinets, shelves, or under-sink storage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>CR18 COLLLECTION Stainless Steel 2 Layer Kitchen Spice Rack| Modular Storage Rack | Kitchen Organizer Multipurpose Storage Shelf/Rack, Silver</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51W5lotUOKL.jpg</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C1BYQN7Y</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | SMART STORAGE: Use anywhere you need to keep food, pantry and kitchen items organized; Perfect for organizing pasta, packets, extra supplies of salt, dressing and vinegar, macaroni and cheese boxes, baking supplies, condiments and more; These bins also work in any room of your home! | Stainless Steel Kitchen Rack Stand Container Organizer Organiser Storage Shelf Shelves Holder Trolley Basket for Spice Boxes Dabba Bartan Utensils Dishes for Home, 2-Tier, Large, Silver Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | FUNCTIONAL &amp; VERSATILE: The perfect solution for organizing a multitude of items - such as video games, bath soaps, shampoos, conditioners, linens, towels, laundry needs, craft supplies and more; Use in bathroom, bedroom, closet, laundry room, utility room, garage, hobby and craft room, home office, mudroom and entryways; Perfect for homes, apartments, condos, college dorm rooms, RVs and campers | 2 SHELVES : This trolley has 2 shelves, which makes it large enough to store many things at a time. | Multipurpose - apart from using as mixer &amp; jar rack, it can be used as a general purpose storage rack too</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>RILION 6 fridge storage boxes multipurpose containers for storage Space-saving Refrigerator Side Door Organizer for fridge kitchen Fruits, Vegetables Storage Containers- transparent</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71KVlyVtG3L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DC5MJQYZ</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
           <t>Perfect Size: The kitchen organizer container box bins are meticulously designed to fit seamlessly into the refrigerator side door, maximizing space utilization and saving valuable fridge space. By storing vegetables separately in these containers, freshness is preserved, spoilage is minimized, and healthier storage habits are encouraged. Plus, their convenient design ensures easy access with just a simple open of the fridge door. | High Quality: Crafted from premium PP Transparent material, plastic storage boxes guarantee durability and strength. Their transparent bodies offer clear visibility of the contents stored inside, enhancing their functionality as top-notch kitchen organizer tools. | Multipurpose Use: Made from robust, high-quality plastic, these kitchen storage containers are versatile and built to last. From storing utensils, cutlery, and chopsticks in the kitchen to organizing toiletries in the bathroom or stationery on the desktop, these containers serve multiple purposes throughout the home. | Freezer-Friendly Containers: Engineered to withstand freezing temperatures, freezer storage containers are ideal for keeping items safely stored in the freezer. Their durable construction ensures long-lasting performance, even in challenging conditions, making them essential additions to any kitchen. | Efficient Fridge Organizer: fridge containers offer an efficient solution for organizing your fridge. With these containers, finding what you need is a breeze, eliminating the hassle of rummaging through cluttered shelves. Sized at 11.8cm in length, 9.8cm in width, and 12.5cm in height, these containers are optimally designed for effective fridge organizer</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2-Tier Stainless Steel Kitchen Storage Spice Rack and Container Organizer Counter top Pantry Stand Multipurpose Masala Kitchen Rack Stand Space Saver Rack (Pack of 1) (NHSP)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71xcENEGMyL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CH6M5MXX</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Two-Tiered Storage: This rack offers two spacious tiers, allowing you to efficiently store a wide range of kitchen items. Keep your spices, condiments, and cooking utensils neatly organized within easy reach. | Stainless Steel Durability: Crafted from high-quality stainless steel, this kitchen rack is not only stylish but also built to withstand daily use. It resists corrosion, stains, and wear, ensuring long-lasting performance. | Space-Saving Design: Maximize your kitchen's available space with this compact yet roomy shelf. Its two tiers make excellent use of vertical space, freeing up your countertops and cabinets. | Multi-Purpose Functionality: This versatile rack is not limited to just spices and utensils. It can also be used for storing kitchen gadgets, small appliances, or even as a display shelf for your favorite cookbooks or decorative items. | Sleek and Modern Design: Its minimalist stainless steel design complements any kitchen decor, adding a touch of contemporary elegance to your culinary space.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Privesh Stainless Steel Modern Kitchen Storage Rack, Folding Perforated Design Trolley for Spice, Fruits, Vegetable, Onion, Potato, Organizer Stand with Wheel, 4 Layer Trolley</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/611g96ubcaL._SY879_.jpg</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BRVDXZ28?th=1</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Product Material: 100% Stainless Steel Grade 202. | Uses: Can Store Fruits, Vegetables and Other Kitchen Accessories like Spice Jars, Containers etc. | This Product Is Rust Resistance and Strong Body Material. | It's Made Of Premium Grade Stainless Steel And It Is Highly Durable And Rust-Proof. | Attractive Design Strong Material, Durable and Rust Proof and Finishing Look Enhance Kitchen Beauty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>StainlessSteel Under Cabinet Kitchen DishRack Expandable Storage FloatingShelves For Kitchen Multipurpose Organizer Extend Up To 580 Mm With Anti-Rust Nano Coating(Pack of 2)(Nhsp) Silver</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61IW6o2oPDL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CH6MD3LV?th=1</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Stainless Steel Durability: Crafted from premium stainless steel, these racks are built to withstand the rigors of daily use while maintaining a sleek and modern appearance. They resist corrosion, ensuring they'll stand the test of time. | Multi-Purpose Functionality: These racks are not just for dishes; they're designed for versatility. Use them to store utensils, pots, or even as a mini stand to organize your kitchen essentials. | Space-Saving Design: The cleverly designed racks are space-saving champions. They help you make the most of your kitchen space, keeping it clutter-free and well-organized. | Fridge-Friendly: These racks are fridge-friendly, allowing you to create extra storage space within your refrigerator. Keep your favorite snacks, condiments, and beverages within easy reach. | Stylish and Functional: The minimalist stainless steel design adds a touch of sophistication to your kitchen while enhancing its functionality.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Cri8Hub Metal 2 Tier Standing Spice Rack, Bathroom Countertop Storage Shelf Organizer, Kitchen Organizer, Cabinet Tray for Dresser, Multipurpose Stand, (2 Tier Standing Multipurpose Rack)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/413na2K-HnL.jpg</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C5RJ822T</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>:-Premium Quality :- Under cabinet organizers is made with premium ABS and Mild steel, We have passed a lot of use and load-bearing tests, It is stable and durable . So you don’t have to worry about the shelf wobbly to cause the items in the pallet to overturn . | :-Modern and simple Nordic style design, this storage rack can be matched well with most household style; perfect for organizing kitchen, living room, bathrooms, office, desk, balcony, also can using as small plant stand, makeup organizer rack. | :-Spray painting and thickening body, good rust prevention and no need to install. Free-standing, solid build that will not tip over or fall. | :-A Wide Range of Usages: The shelf can serve itself for different purposes, holding small items in your kitchen, bathroom, bedroom, living room, reading room, balcony and office, etc. You can try to place as many small-sized household and office items as you can imagine. | :-Durable Material: Made of premium iron and sprayed with eco-grade paint, the shelf is sturdy to use and easy to clean, rust-proof and water-proof, no need to install and free standing. Each evenly well-polished corner can keep you from being scratched, safe and unharmed. | :-Easy To Clean - Simply wipe the surface with a damp cloth to clean the shelf, keep dry and do not submerge. The under bathroom sink storage adopts hollow design, which has a good draining effect and prevents moldy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>HomeWiz 360° Rotating Kitchen Organiser | Lazy Susan Smooth Turntable Organiser | Spice Rack Organizer | Cosmetic Holder Organizer | Multipurpose Use for Kitchen Counter, Dining Table | Dark Blue</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71c26Zr37WL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CX1YPXW5?th=1</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>THE SHELF THAT HIDES THINGS AT THE BACK IS NOT AN ORGANISATION PROBLEM — IT IS A ROTATION PROBLEM: Bottles at the back jars you cannot reach without moving three things first condiments nobody uses because they are always behind something else. A spinning tray means there is no back. One gentle spin brings everything forward. The HomeWiz Dark Blue Rotating Tray at makes every item on a shelf equally accessible in under one second. | SMOOTH 360° ROTATION — EVERYTHING COMES TO YOU: Give it a spin. Whatever was at the back comes to the front. No more reaching across the shelf no more knocking things over trying to get to the item behind another. | DIAMETER — FITS COUNTERS SHELVES AND INSIDE CABINETS: The round base fits on kitchen counters near the stove inside cabinets on dining tables and on bathroom shelves. A versatile size for most surfaces. | RAISED RIM KEEPS ITEMS FROM FALLING OFF: The curved edge around the base keeps bottles jars and containers from sliding off when the tray spins. Everything stays on the tray even with a fast spin. | FOOD-GRADE BPA-FREE — SAFE FOR KITCHEN CONTACT: Made from food-grade plastic with no BPA. Safe for direct contact with food containers oil bottles and kitchen items. | SMOOTH 360° ROTATION — EVERYTHING COMES TO YOU: Give it a spin. Whatever was at the back comes to the front. No more reaching across the shelf no more knocking things over trying to get to the item behind another. | LIGHTWEIGHT — EASY TO MOVE AND CLEAN: The light weight means you can pick up the entire tray and wipe the shelf underneath easily. Keep both the tray and the shelf clean. | WHY 10 LAKH INDIAN FAMILIES COOK WITH HOMEWIZ: HomeWiz was not built in a boardroom. It was built around the reality of Indian kitchens — the morning chai the Sunday biryani the daily dal that feeds a family. We started with one belief: that the tools in your kitchen should be as honest as the food you cook with them. Today over 10 lakh families across India trust HomeWiz in their homes. Not because of flashy marketing — but because when a HomeWiz product lands in your kitchen it simply works. Every single day. That is the only promise we make — and the only one we need to.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Organizer Tray Office Drawer Dividers Storage Bins Multipurpose Desk for Makeup, Kitchen, Office, Bathroom, Bedroom Dreassing, Basket Rack MultiColor(23*8*5 CM) Pack Of 6 (Multi 6pcs)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71UDWR9wrBL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CR374476</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Combo of 6pcs multipurpose storage baskets set which is useful for one's daily activity. | Color : Available in assorted colors, Color will be shipped as pe availability, Material : Plastic | Portable, light weight stack-able. Can be kept in drawers, almirahs, kitchen cabinets, refrigerator, shelves etc. | The desk drawer organizer trays can be used for desk, drawers, kitchen, office and living room as well as for other applications. help you to create your own mix and match organizational system to fit in any drawers, cabinets, lockers and wardrobe closets</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>COMFYHOME Kitchen Organizer Rack with Wheels - Adjustable 4 Tier Microwave Stand with 3 Wire Baskets, Oven Stand with Storage Cabinet, Metal Kitchen Storage Cart for Pantry （80x32x108cm）</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/717u0QDFKVL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GX1P63MY?th=1</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>【Large Capacity 4-Tier Kitchen Organizer Rack】Designed with a four-tier structure and an extra-wide countertop, this microwave stand for kitchen​easily supports large appliances like microwaves and air fryers. The combination of adjustable shelves and deep, pull-out mesh baskets significantly boosts your storage capacity. The open-mesh design ensures optimal airflow, keeping fruits and vegetables fresh and preventing moisture buildup. | 【Heavy-Duty Metal Frame &amp; Stable Structure】 This upgraded carbon steel 4 tier kitchen rack stand​features thickened shelves, reinforced tubing, and deepened baskets—increasing basket volume by 37.5%. Engineered for superior load-bearing, the tight joints and robust frame resist bending or wobbling, even under heavy weight. It offers a comprehensive upgrade in durability, ensuring your kitchen racks for storage remain stable and secure for years to come. | 【Mobile &amp; Stationary Dual Mode】Equipped with 360° silent swivel casters, this oven stand with wheels 4 tier heavy duty​glides smoothly for easy cleaning underneath. Two locking brakes keep the unit firmly in place to prevent accidental sliding. We also include non-slip stationary feet, allowing you to freely switch between a mobile cart and a fixed stand for kitchen storage rack based on your needs. | 【Multipurpose Storage Solution】More than just a rack for storage multipurpose, this oven stand​adapts to any room. Use it in the kitchen for appliances, in the office for printers and files, or on the balcony for plants. Whether used as a coffee bar cart, bathroom shelf, or pantry organizer, one unit fulfills all your organizational needs. | 【Premium Finish &amp; Easy Assembly】Featuring a classic matte black finish, this microwave stand for kitchen platform​ is scratch-resistant and easy to clean—just wipe it down to maintain its premium look. Overall dimensions: 12.5" D x 31.5" W x 42.5" H. The minimalist design complements any decor. Assembly is quick and tool-friendly with clear instructions included, combining open shelving for display with hidden baskets for a clutter-free home.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>SAFAK 3 Tier Wooden Kitchen Organizer Rack for Countertop | Wooden Spice Rack Stand for Kitchen Counter | Kitchen Shelf Organizer &amp; Cabinet Shelf Riser | Decorative Masala Rack Storage Stand | Dark</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71swzxPftnL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GRVMYVQH?th=1</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>A wooden kitchen organizer is essential for any kitchen since it is both stylish and practical. The purpose of these organizers is to improve the efficiency and organization of your kitchen. To accommodate different storage needs, they are available in a range of sizes and forms. | Jars, cans, bottles, sugar, tea, spices, sauces, and other kitchen supplies can all be stored in these useful step organizers. Additionally, they are a great method to store things for your pooja room. | Because it doesn't require any additional building or equipment, this freestanding organizer is easy to use. | Because it makes room in cramped cabinets and pantries, this three-tiered organizer is a great tool for kitchen and pantry organization. | When necessary, a moist towel can be used to clean the step shelf organizer's nonslip shelf lining.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>TEX-RO Kitchen Trolley with Wheels | 3-Layer Metal Vegetable Basket Stand &amp; Kitchen Storage Rack | Multipurpose Kitchen Organizer for Onion Potato Storage (Black)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81zSFh5uwdL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0B3JST2F4?th=1</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Maximize Kitchen Storage with Tex Ro Kitchen Trolley: Versatile Kitchen Shelf and Storage Organizer for Kitchen, Vegetable Rack for Kitchen, Ideal for Efficient Kitchen Storage Solutions. | Efficient Home Organization with Kitchen Trolley Organizer and kitchen Stand : Store and Organize Home Organizer Items and Storage with a Stylish Basket for Kitchen, Perfect for Kitchen Essentials for Home Organization. | Versatile Kitchen Organization with Multipurpose Storage Solutions: Organize and Store Onions with Onion Baskets for Storage and Utilize the Onion Potato Rack for Kitchen. Enhance Storage Efficiency with a Vegetable Basket for Kitchen and Versatile Multipurpose Storage Trolley. Keep Your Kitchen Clutter-Free with a Functional Kitchen Cabinet Organizer. | Enhance Your Kitchen Organization with a Modern vegetable stand for kitchen and kitchen storage rack : Utilize the Versatile Trolley for Kitchen Storage, Ideal for Showcasing Vegetables and Providing Ample Space, and Discover the Latest Modern Kitchen Accessories for Stylish and Efficient Storage Solutions. | Convenient and Space-Saving Kitchen Storage: Maximize Efficiency with a Variety of Storage Solutions, including Onion Stand for Kitchen, Onion Storage Container for kitchen , Potato Onion Storage Container, Corner Rack, Rotating Kitchen Rack, and corner Shelf for Kitchen Organization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>GOLWYN Air Tight Containers For Kitchen Storage Set, Bpa Container For Kitchen Storage Set, Kitchen Organizer And Kitchen Accessories Items &amp; Storage(1200 Ml Set Of 8)(Plastic)Transparent</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71auAIxh1PL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0B2SBK18B?th=1</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Airtight kitchen storage containers set Keep Food Fresh----The lids with silicone gasket make these storage containers airtight, and the top flips open easily. Airtight storage system will always keep your food dry and fresh. All have the same lids make it easy to wash dry and reuse with ease. We can also use for spice containers for kitchen storage . Perfect ! plastic containers for kitchen storage . | Package Content: 8Pcs Container Jar Set With Cap | Material: Premium Quality Plastic | Airtight / 100% Leak Proof. | Capacity: 1100 ml | Color: transparent | BPA Free and Food Grade Material Plastic Boxes For Storage ---- pantry storage containers for kitchen airtight are made of durable plastic, BPA free, which have a longer life than many other brands plastic containers. Clear containers make it convenient to see what’s inside, you can easily get what you want without opening every container. Space saving storage box for kitchen .</t>
         </is>
       </c>
     </row>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1620,6 +1620,386 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Carrylux Large Capacity Croco Pattern Tote Bags For Womens Big Purses And Handbags Ladies Big Shoulder Bag</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71M7n4XqWCL._SX695_.jpg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CP9GGP5X?th=1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ROSS BROWN Satchel Bag for women | Handbags for women</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81k+zgTW2jL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H6FXGFVX?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BLUE WORLD PU Women Handbag</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61LOeB-ug0L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FYZ13169?th=1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LEGAL BRIBE Textured Tote Bag Combo Of 4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71OW7nY-JdL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CQP1QYBW?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LEGAL BRIBE Women Textured Tote bag</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81D8fFPF+IL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CP829WXM?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Storite Women's Tote Bag With PU Leather Handles &amp; Embroidery Printed bag With Zip Pockets, Shoulder Tote Bag And Handbag For Office And College</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81CMb5BZyVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D2KDCVZQ?th=1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Storite Women's Embroidery Printed Tote Bag, Multicolour</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81+cwVciz+L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DGXX72D3?th=1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-02</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51ivBuhty9L._SX695_.jpg</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G9MQKMRR</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Carrylux Dual Tone Large Capacity Croco Pattern Tote Handbags Purses Shoulder Bag For Womens</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71xfJBW1WLL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CPYRNV8G?th=1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Self Design PU Handbag for Women Ladies Casual Travel Shopping Office Shoulder Carry Bag</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/316PYKeuNUL.jpg</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H1D6H38J?th=1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DAISY STAR Women Fashion Tote Purses Stylish Ladies Women and Girls Zip Pocket Canvas Handbag for Office Bag Ladies Travel Shoulder Bag Tote for College Girls</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Ik29fSIGL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CK4HDMX5?th=1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Carrylux Spacious Tote Bag For Womens Handbag Ladies Purses, With Zip Closure Shining Synthetic Leather</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/616tYPi6LZL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DSQ61B9C?th=1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Large Capacity Stylish Textured Tote Handbag for Women | Spacious Leather Shoulder Bag Purse Ideal for Office, College, Shopping &amp; Everyday Carry</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41Yy1jJZPOL.jpg</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H3638HD9?th=1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>women's pu leather handbag shoulder bag hand held bag with long strap queen collection simple sober and stylish (HB5)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51v7ZuVmwfL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H334GPP7?th=1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-06</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51gcz3ppyJL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G9KZ8YV7</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>HaveGlam Floral Embossed Crossbody Sling Bag Small Shoulder Handbag for Daily Use Travel &amp; Shopping Phone Purse with Adjustable Strap Lightweight Trendy Bag for Ladies &amp; Girls</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61wxgP4SadL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GPWQQG52?th=1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EXOTIC® Women's Striped Line Handbag for Women| Ladies purse | Stylish Shoulder Bag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71oW9ddfGsL._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09RW3DK6W?th=1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pure Vegan Leather Tote Bag for Women, Fully Embossed, Handbag, Shoulder Bag, Black</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61KxXAzmWKL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F185ZY65?th=1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SIJJEEL Women's Handbag Synthetic Leather Shoulder Bag with Bear Charm Tote One Size Women's Shoulder Bag Faux Leather Tote</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51Dyn+hZz5L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GH23KQ4K?th=1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Carrylux Women's Soft PU Tote Bag | Large Single Compartment Shoulder Handbag | Office, College &amp; Casual</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61FfZyulIZL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GK34HKMN?th=1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1719,17 +1719,17 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Storite Women's Tote Bag With PU Leather Handles &amp; Embroidery Printed bag With Zip Pockets, Shoulder Tote Bag And Handbag For Office And College</t>
+          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-02</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81CMb5BZyVL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51ivBuhty9L._SX695_.jpg</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0D2KDCVZQ?th=1</t>
+          <t>https://www.amazon.in/dp/B0G9MQKMRR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1738,17 +1738,17 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Storite Women's Embroidery Printed Tote Bag, Multicolour</t>
+          <t>Carrylux Dual Tone Large Capacity Croco Pattern Tote Handbags Purses Shoulder Bag For Womens</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81+cwVciz+L._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71xfJBW1WLL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0DGXX72D3?th=1</t>
+          <t>https://www.amazon.in/dp/B0CPYRNV8G?th=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1757,17 +1757,17 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-02</t>
+          <t>Self Design PU Handbag for Women Ladies Casual Travel Shopping Office Shoulder Carry Bag</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51ivBuhty9L._SX695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/316PYKeuNUL.jpg</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0G9MQKMRR</t>
+          <t>https://www.amazon.in/dp/B0H1D6H38J?th=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -1776,17 +1776,17 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Carrylux Dual Tone Large Capacity Croco Pattern Tote Handbags Purses Shoulder Bag For Womens</t>
+          <t>DAISY STAR Women Fashion Tote Purses Stylish Ladies Women and Girls Zip Pocket Canvas Handbag for Office Bag Ladies Travel Shoulder Bag Tote for College Girls</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71xfJBW1WLL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71Ik29fSIGL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CPYRNV8G?th=1</t>
+          <t>https://www.amazon.in/dp/B0CK4HDMX5?th=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -1795,17 +1795,17 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Self Design PU Handbag for Women Ladies Casual Travel Shopping Office Shoulder Carry Bag</t>
+          <t>Carrylux Spacious Tote Bag For Womens Handbag Ladies Purses, With Zip Closure Shining Synthetic Leather</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/316PYKeuNUL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/616tYPi6LZL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H1D6H38J?th=1</t>
+          <t>https://www.amazon.in/dp/B0DSQ61B9C?th=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -1814,17 +1814,17 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DAISY STAR Women Fashion Tote Purses Stylish Ladies Women and Girls Zip Pocket Canvas Handbag for Office Bag Ladies Travel Shoulder Bag Tote for College Girls</t>
+          <t>Large Capacity Stylish Textured Tote Handbag for Women | Spacious Leather Shoulder Bag Purse Ideal for Office, College, Shopping &amp; Everyday Carry</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71Ik29fSIGL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41Yy1jJZPOL.jpg</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CK4HDMX5?th=1</t>
+          <t>https://www.amazon.in/dp/B0H3638HD9?th=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -1833,17 +1833,17 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Carrylux Spacious Tote Bag For Womens Handbag Ladies Purses, With Zip Closure Shining Synthetic Leather</t>
+          <t>women's pu leather handbag shoulder bag hand held bag with long strap queen collection simple sober and stylish (HB5)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/616tYPi6LZL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51v7ZuVmwfL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0DSQ61B9C?th=1</t>
+          <t>https://www.amazon.in/dp/B0H334GPP7?th=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -1852,17 +1852,17 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Large Capacity Stylish Textured Tote Handbag for Women | Spacious Leather Shoulder Bag Purse Ideal for Office, College, Shopping &amp; Everyday Carry</t>
+          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-06</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41Yy1jJZPOL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51gcz3ppyJL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H3638HD9?th=1</t>
+          <t>https://www.amazon.in/dp/B0G9KZ8YV7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -1871,17 +1871,17 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>women's pu leather handbag shoulder bag hand held bag with long strap queen collection simple sober and stylish (HB5)</t>
+          <t>HaveGlam Floral Embossed Crossbody Sling Bag Small Shoulder Handbag for Daily Use Travel &amp; Shopping Phone Purse with Adjustable Strap Lightweight Trendy Bag for Ladies &amp; Girls</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51v7ZuVmwfL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61wxgP4SadL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H334GPP7?th=1</t>
+          <t>https://www.amazon.in/dp/B0GPWQQG52?th=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -1890,115 +1890,20 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AESTHETIC Women’s Shoulder Handbag | Elegant PU Leather Tote with Chain Strap | Stylish Daily Use Purse for Office, College &amp; Casual Outings-T-06</t>
+          <t>EXOTIC® Women's Striped Line Handbag for Women| Ladies purse | Stylish Shoulder Bag | Gift for Women</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51gcz3ppyJL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71oW9ddfGsL._SY575_.jpg</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0G9KZ8YV7</t>
+          <t>https://www.amazon.in/dp/B09RW3DK6W?th=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>HaveGlam Floral Embossed Crossbody Sling Bag Small Shoulder Handbag for Daily Use Travel &amp; Shopping Phone Purse with Adjustable Strap Lightweight Trendy Bag for Ladies &amp; Girls</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61wxgP4SadL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GPWQQG52?th=1</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>EXOTIC® Women's Striped Line Handbag for Women| Ladies purse | Stylish Shoulder Bag | Gift for Women</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71oW9ddfGsL._SY575_.jpg</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09RW3DK6W?th=1</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Pure Vegan Leather Tote Bag for Women, Fully Embossed, Handbag, Shoulder Bag, Black</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61KxXAzmWKL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F185ZY65?th=1</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>SIJJEEL Women's Handbag Synthetic Leather Shoulder Bag with Bear Charm Tote One Size Women's Shoulder Bag Faux Leather Tote</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51Dyn+hZz5L._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GH23KQ4K?th=1</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Carrylux Women's Soft PU Tote Bag | Large Single Compartment Shoulder Handbag | Office, College &amp; Casual</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61FfZyulIZL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GK34HKMN?th=1</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1905,6 +1905,466 @@
       </c>
       <c r="E63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pigeon Aluminium Non Stick Tawa-Fry Pan Gift Set (Red) - Duo Pack</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/510yXR4GoNL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07KYPZHJ9</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>5 Layer Durable Nonstick Coating | Made with High End Italian Technology | Oil Free Cooking | Ergonomic Bakelite Handle | Free from Peel-Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Amazon Basics Granite Finish Non Stick 5 Pcs Induction Base Cookware Set-Granito Grey (24cm Fry Pan, 24 cm Kadai, 28cm Tawa and 2 Nylon Spatulas)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71fcuPgHEBL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C2J76WPF?th=1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DURABLE IMPORTED COATING: It comes with water-based coating imported from Japan which is compliant with US FDA and European Food Safety Authority (EFSA) standards. This cookware features three granite-finished coats each on its interior and exterior. It has been tested to last for more than 10,000 cycles. | HEALTHIER CHOICE: Its granite coating is free from PFOA, PTFE, lead, cadmiumm nickel and arsenic. This makes it safer and healthier to use than traditional non-stick cookware, which may contain harmful chemicals. | FAST, EVEN COOKING: Made from pressed aluminium, this cookware is ultra-conductive and corrosion-resistant. Its granite coating and flat, thick skillet bottom offer exceptional heat distribution to ensure even cooking and prevent hot spots. Overall, this cookware offers quick heating, thus using less energy. | REQUIRES LESS OIL: Cook a variety of healthy, delicious recipes for Indian households using this non-stick cookware set from Amazon Basics. It requires very little oil and cooks evenly and quickly without using much power. | CONDUCTIVE BASE: Its base is made from Aluminium and is highly magnetic and conductive. It features grooves that help retain heat. | COMPATIBLE WITH ALL COOKTOPS: The induction base with small perforation boosts faster cooking while helping you consume less electricity. This cookware is compatible with both gas-stove and induction cooktops. | COMFORTABLE TO HANDLE: The coookware is 3.5 MM thick with ideal weight distribution throughout the material for comfortable handling. | EASY TO CLEAN: Food particles are less likely to stick to the surface of the non-stick coating, making this cookware easy to clean. | CLEANING AND TEMPERATURE: We recommend hand-washing this cookware. Alternatively, you may clean it in a dishwasher with liquid detergent. It may be safely even at temperatures up to (200° and (260° C. | COLOUR: Granito Grey; PACKAGE CONTENTS: 1 tawa (28 cm), 1 fry pan (24 cm), 1 kadai (24 cm), 1 glass lid and 2 nylon spatulas; Thickness: 3.5 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Crystal Classic Series 7-pc Non-Stick Induction Bottom Cookware Set, PFOA Free, Tawa, Fry-Pan, Kadhai with Glass Lid, Sauce Pan with 2 Serving Spoons, Red</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71-v9RBpQfL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09313HZ8B</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | All items induction base except Sauce pan | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|25 Cm Tawa,22 Cm Kadai,1 Glass Lid|Grey</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71bHYFW1TmL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYDJ892?th=1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Kadai, 1 Glass Lid</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ceramic Coated Cast Iron Non Stick Induction Cookware Set 6 Piece Kadai Fry Pan Tawa Saucepan Milk Pan Kitchen Set Black Free Size</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/310fMyOkioL.jpg</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GXDS58PG</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Multi Purpose Cookware: Includes kadai sauce pan fry pan tawa and tadka pan for diverse cooking needs | Non Stick Surface: Ensures easy cooking with less oil and prevents food from sticking | Even Heat Distribution: Designed to cook food evenly for better taste and texture | Easy Maintenance: Simple to clean and maintain for regular kitchen use | Suitable for All Kitchens: Ideal for home restaurants hotels and professional cooking setups</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Judge by Prestige Ace Aluminium Non-Stick Cookware Set - Kadai 20 cm, Fry Pan 20 cm, Omni Tawa 25 cm - 1 Unit Each, Black</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/515a2mz5TOL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DG8M74Z8</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Durable Body | Low Oil Cooking | Easy to Maintain | Cool Touch Handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Hawkins 6-Piece Triply with Shielded Nonstick Gift Set | Induction &amp; Gas Compatible | Metal Spoon Friendly | Long-Lasting | with Lid | Silver (SNSGP1)|Induction and Gas Stove Compatible</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/812pw-1SxyL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FT8GJKDB</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>High quality German PFOA-free Nonstick | Nonstick locked firmly into the tough Hard Anodised surface with a unique patented process | Extra-thick, Tri-Ply metal spreads heat evenly, is more durable | Lasts longer than ordinary nonstick | Stay-cool, sturdy riveted handles - will not loosen</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>6 Pcs Pots and Pans Non Stick Cookware Combo Set Induction Ready, with Detachable Handle, Stackable Kitchen Cooking Set Removable Handles, Oven Safe, frypan Tea pan Utensils (Cream White)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Gi7O-fTbL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GP8M15MC?th=1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DETACHABLE HANDLE SYSTEM FOR FLEXIBLE COOKING – Designed for convenience and everyday kitchen efficiency, the removable handle system allows easy attachment and detachment for cooking, serving, storage, and kitchen organization. Ideal for modern cookware setups. | SPACE SAVING &amp; STACKABLE KITCHEN SOLUTION – The detachable design helps create a compact and organized kitchen experience. Perfect for apartments, small kitchens, RVs, camping, and homes where storage space matters. | STRONG LOCKING MECHANISM &amp; COMFORTABLE GRIP – Built with a secure locking design that helps provide stability during cooking and handling. The ergonomic grip offers comfort and control for daily kitchen use. | INDUCTION READY COOKWARE COMPATIBILITY – Designed to support modern cooking needs and compatible cookware systems. Suitable for everyday meal preparation while helping maintain a clean and organized cooking space. | EASY TO CLEAN &amp; STORE – The detachable configuration simplifies cleaning and helps reduce kitchen clutter. Convenient for storing cookware and kitchen accessories in cabinets, drawers, and shelves. | VERSATILE KITCHEN ESSENTIAL FOR DAILY USE – A practical cookware solution for home chefs, students, families, and travel cooking setups. Designed for convenience, durability, and efficient kitchen organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hawkins Ceramic Nonstick 3-Piece Kitchen Gift Set - 1.75 L Deep Kadhai, 16 cm Frying Pan and 24 cm Tava, Grey (24ICGP)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Dx2YMMrZL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DPB512KB</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>New Hawkins Ceramic Nonstick Inside: Excellent release properties - Uses 36% less oil for Tasty but Healthy Dishes | Can cook crisper, tastier | No PTFE, PFOA, PFAS or Heavy Metals - Ceramic based revolutionary nonstick. More hygienic, more healthy | German Ceramic - High quality, lasts longer | 3.25 mm Extra-Thick - heats fast and evenly</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Prestige Omega Granite Aluminium Kitchen Set, 4-Pieces, Black</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Q5O9edctL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B01684OHYQ</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Material: Non-stick Aluminium; Size: Tawa Dia (280 Mm), Fry Pan Dia (240 Mm), Kadai (240 Mm), Milk Pan (160 Mm); Base type: Induction Base; Base thickness (in mm): 2.8; Included components: 4 Kitchen Set With Milk Pan; Colour: Black | Warranty: 2 Years; Included in warranty: Manufacturing defects will be covered in the warranty. Remaining things have been mentioned in the user manual; Not included in warranty: Mentioned in the manual | Durable Granite finish | Superior Non stick surface | Dishwasher safe | Metal spoon friendly | 5-layer non-stick cookware with German technology, Lid Included: Yes | Coating type: Non-Stick; No. of layers: 5 Layer; Finish: Granite Finish | Country of Origin: India.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Impex Non-Stick Cookware Set of 4 Pcs | Tawa Pan, Fry Pan &amp; Kadai with Glass Lid | PFOA-Free Triple Layer Coated Aluminium Kitchen Cookware Set | Bakelite Handle, Gas Stove Compatible | 1 Yr Warranty</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/717khrN3Z0L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CH1B2M1S</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟒-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐊𝐈𝐓𝐂𝐇𝐄𝐍: Includes a 24cm Kadai with Glass Lid, 24cm Tawa Pan and 24cm Fry Pan – a versatile non-stick cookware set for frying, roasting, sautéing, tadka and everyday Indian cooking needs at home. | 🥘 𝐓𝐑𝐈𝐏𝐋𝐄-𝐋𝐀𝐘𝐄𝐑 𝐍𝐎𝐍-𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐀𝐓𝐈𝐍𝐆 𝐅𝐎𝐑 𝐇𝐄𝐀𝐋𝐓𝐇𝐈𝐄𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free non-stick coated aluminium cookware ensures healthier low-oil cooking, effortless food release and quick, easy cleanup after every single meal you prepare. | 🔥 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐀𝐋𝐔𝐌𝐈𝐍𝐈𝐔𝐌 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝐄𝐕𝐄𝐍 𝐇𝐄𝐀𝐓 𝐃𝐈𝐒𝐓𝐑𝐈𝐁𝐔𝐓𝐈𝐎𝐍: Superior aluminium construction with heat-resistant exterior paint delivers fast, even heating and long-lasting performance for your everyday cooking in the kitchen. | ✋ 𝐂𝐎𝐌𝐅𝐎𝐑𝐓𝐀𝐁𝐋𝐄, 𝐒𝐄𝐂𝐔𝐑𝐄 𝐁𝐀𝐊𝐄𝐋𝐈𝐓𝐄 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy, heat-resistant bakelite handles are designed for a comfortable, secure grip while cooking, reducing the risk of burns and slips during daily kitchen use at home. | 🔍 𝐓𝐄𝐌𝐏𝐄𝐑𝐄𝐃 𝐆𝐋𝐀𝐒𝐒 𝐋𝐈𝐃 𝐅𝐎𝐑 𝐄𝐀𝐒𝐘 𝐌𝐎𝐍𝐈𝐓𝐎𝐑𝐈𝐍𝐆: The toughened glass lid on the Kadai lets you monitor food while it cooks, while retaining heat and moisture for evenly cooked, flavourful, delicious home-style dishes. | ⚡ 𝐆𝐀𝐒 𝐒𝐓𝐎𝐕𝐄 𝐅𝐑𝐈𝐄𝐍𝐃𝐋𝐘 𝐍𝐎𝐍-𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Designed with a non-induction bottom, this non-stick cookware set is ideal for gas stove kitchens, delivering consistent, reliable everyday cooking performance every time. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍, 𝐋𝐎𝐖 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: The smooth non-stick coated surface allows quick, effortless cleaning after cooking, saving valuable time on daily kitchen chores with no heavy scrubbing ever required. | 🎁 𝐈𝐃𝐄𝐀𝐋 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐍𝐄𝐖 𝐇𝐎𝐌𝐄𝐒: This multicolor 4-piece cookware set makes a thoughtful gift for weddings, housewarmings, anniversaries, or new homemakers setting up their very first kitchen space. | ✅ 𝐈𝐒𝐎 𝐂𝐄𝐑𝐓𝐈𝐅𝐈𝐄𝐃 𝐅𝐎𝐑 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Manufactured under ISO certification standards, this cookware set ensures premium quality, safety, and consistent performance you can rely on across every single piece. | 🛡️ 𝐖𝐎𝐑𝐑𝐘-𝐅𝐑𝐄𝐄 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 𝐀𝐒𝐒𝐔𝐑𝐀𝐍𝐂𝐄: Backed by Impex's 1-year manufacturer warranty, this cookware set gives you complete peace of mind and confidence in your everyday kitchen investment for years to come.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Impex Cook &amp; Serve Casserole Set 6 Pcs, Nonstick Granite Coated Cookware Set with Glass Lid, Induction &amp; Gas Compatible Aluminium Saucepan Combo 4.6L+2.7L+1.9L, PFOA Free Cookware for Kitchen</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/813UmqBf0IL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CW2YQC49?th=1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>🍳 5-LAYER SUPER GRANITE COATING: Premium granite-finish nonstick coating is 10X tougher than standard nonstick cookware, resisting scratches and wear from daily use while keeping food from sticking, so meals release effortlessly every time. | 🛡️ 100% PFOA FREE &amp; NON-TOXIC: Built with safe, food-grade PFOA-free construction, this cookware set ensures no harmful chemicals leach into your food, giving your family healthy, worry-free everyday cooking on every casserole in the set. | 🔥 INDUCTION &amp; GAS COMPATIBLE: Featuring an induction-bottom base, this Impex casserole set works seamlessly on induction cooktops, gas stoves and other cooking surfaces, making it a versatile addition to any modern or traditional kitchen. | 👀 TRANSPARENT GLASS LID: Each casserole comes with a toughened glass lid so you can monitor food while it cooks without lifting the lid, locking in heat, moisture and flavor for perfectly cooked curries, rice, soups and gravies every time. | 🍽️ COOK AND SERVE CONVENIENCE: Go straight from stovetop to dining table with this elegant cook-and-serve casserole set, saving time on transferring food to separate serving bowls while keeping meals warm for longer during family dinners. | 📦 6-PIECE COMBO SET FOR EVERY NEED: Includes 3 nonstick granite casseroles with glass lids in 4.6L, 2.7L and 1.9L capacities, perfect for cooking and serving everything from small side dishes to large family-size curries and biryanis. | ⚡ LIGHTWEIGHT ALUMINIUM BODY: Crafted from durable, heat-conductive aluminium, this cookware set heats up quickly and evenly while remaining lightweight and easy to lift, pour and handle, even when fully loaded with hot food. | 🥗 HEALTHY LOW-OIL COOKING: The super granite nonstick surface allows you to cook flavorful, healthy meals using minimal oil and butter, making this saucepan combo ideal for health-conscious families and everyday nutritious cooking. | 🧼 EASY TO CLEAN NONSTICK SURFACE: The smooth granite-coated interior wipes clean in seconds and resists stubborn stains and food residue, cutting down kitchen cleanup time and keeping your cookware looking new for longer. | 🎁 IDEAL KITCHEN &amp; GIFTING ESSENTIAL: A must-have cookware set for new homes, daily cooking or gifting on weddings, housewarmings and anniversaries, this Impex casserole combo makes a practical and elegant addition to any kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Wonderchef Valencia Plus Non-Stick Cookware 3 Piece Set | Kadhai, Glass Lid, Dosa Tawa | Cool Touch Bakelite Handles | Pure Grade Aluminium| PFOA Free| 1 Year Warranty | Purple</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51i43QAE0UL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GNT31PLH?th=1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>VERSATILE 3-PIECE SET - Kadhai, Glass Lid, Dosa Tawa let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | HEALTHY COOKING MADE EASY: MetaTuff 5-layer non-stick coating ensures minimal oil use, excellent abrasion resistance and is 00% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | VERSATILE: Cook delicious cutlets, stir-fry veggies, curries, dosas, uttapams, sandwiches, omelets, and parathas with the fry pan, kadhai, and tawa. Complete your cookware needs with Valencia set! | ENERGY-EFFICIENT: Pure grade virgin aluminium offers 9-times better heat conduction, cooking your meals faster while saving energy and time. | COMPATIBLE WITH ALL COOKING SURFACES - Use on gas cooktops, hot plates, infrared cooktops, and ceramic cooktops for maximum flexibility in your kitchen. | COMFORTABLE &amp; STYLISH - Cool touch Bakelite handles provide a firm grip and utmost convenience. Enjoy cooking with comfort and ease. | CONVENIENT: Easy to clean and dishwasher safe. Lightweight for daily use. | IDEAL FOR GIFTING - Loaded with features and beautiful looks, the Valencia cookware set is an ideal choice for gifting. Surprise your loved ones with a perfect addition to their kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Crystal Eco Plus 8-pc Non-Stick Cookware Set, PFOA Free, Tawa, Kadhai with SS Lid, Fry Pan, Vagariya, Mini Grill Pan, 2 Spatulas, Multicolor</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71oGMB2shTL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BD1JLNKM?th=1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart. | Soft touch bakelite handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Vinod Di Casa Signature Ceramic Non Stick Cookware Set - 4 pcs | 24 cm Kadai and Frying Pan, 27 cm Dosa Tawa | Soft Touch Wooden Handle | Less Oil Healthy Cooking | Induction Compatible | Toxin Free</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61bbjGbh6dL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GGC33JCG?th=1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>𝐒𝐈𝐆𝐍𝐀𝐓𝐔𝐑𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 = Crafted with advanced ceramic coating, this ceramic cookware set is designed as a complete kitchen essential. It delivers smooth heat flow and dependable performance, elevating everyday Indian cooking with confidence and elegance. | 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Engineered using toxin-free ceramic layers, this ceramic non stick cookware allows food to release effortlessly with minimal oil. Enjoy healthier meals that preserve taste, texture, and tradition without compromising safety. | 𝐕𝐄𝐑𝐒𝐀𝐓𝐈𝐋𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Thoughtfully curated as a nonstick cookware set combo, it includes a ceramic kadai, frying pan, and Dosa tawa. This balanced cookware set combo supports daily sabzi, roti, dosa, and gravy cooking with ease. | 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐊𝐀𝐃𝐀𝐈 𝐅𝐎𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆 = Built for Indian kitchens, the ceramic kadai for cooking offers depth, stability, and strength. Ideal for curries, stir-fries, and tadka, it blends modern durability with classic cooking needs. | 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐏𝐀𝐍 𝐒𝐄𝐓 = This refined non stick pan set brings together functionality and form. The balanced weight and ergonomic handles make everyday cooking comfortable, supporting long hours at the stove without strain or fatigue. | 𝐄𝐀𝐒𝐘 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = The smooth ceramic surface of this non stick cookware resists staining and food buildup. Gentle hand washing keeps the shine intact, making daily maintenance effortless and preserving long-term performance. | 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐑𝐄𝐀𝐃𝐘 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Designed for modern homes, this cookware set is compatible with induction and gas stoves. The sturdy base ensures stability and efficient heating, adapting seamlessly to evolving kitchen technologies. | 𝐑𝐄𝐋𝐈𝐀𝐁𝐋𝐄 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Backed by quality assurance, this non stick cookware set combo offer reflects lasting value. With dependable construction and 1 year warranty support, this kadai set for cooking brings peace of mind to every meal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>The Better Home Non Stick Cookware Set (Tawa - 26cm, Fry Pan - 24cm, Kadai with Lid - 24cm) | Non Stick Pan Set | Induction Cookware | Cookware Set Combo | 2.8mm Thickness (Blue)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51+f68YcPhL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DS2N3XJM?th=1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ENHANCED USABILITY : Effortless meal prep with easy-to-clean non-stick cookware designed for family versatility and convenience. | IDEAL FOR ALL HEAT SOURCES : Compatible with gas and induction stoves, this set meets all your cooking needs, from roti to dosa. | VERSATILE USE CASES : Perfect for home cooking or BBQs, this set boosts your culinary skills, suitable for both beginners and pros. | PERFECT CAPACITY : Includes tawa (700ml), frypan (1750ml), and kadai (2500ml) with comfortable riveted soft-touch handles. | DESIGN CONSIDERATIONS : Thoughtfully designed for ease of use and maintenance, ensuring a user-friendly cooking experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tramontina Aura 4-Pc Cookware Set : 24cm Kadhai + Lid, 24cm Frypan, 28cm Dosa Tawa | Reinforced Ceramic Non-Stick | Quick &amp; Even Heat | Low-Oil Cooking | Gas &amp; Induction | Sea Green</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/612po7oNfOL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FL85J8KY?th=1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Effortless Food Release &amp; Healthier Cooking – Ceramic-reinforced interior ensures smooth food release, allowing you to cook with less oil for healthier meals and quicker cleanup. | Quick &amp; Even Heating – Cold-forged body delivers fast, consistent heat distribution, eliminating hotspots for perfectly cooked results every time. | All Cooktop Compatible – Designed for versatility, this cookware works flawlessly on gas, induction, ceramic, and glass cooktops | Easy to Clean &amp; Dishwasher Safe – Cleanup is a breeze with the dishwasher-safe design, saving you time and effort after every meal. | Stylish &amp; Functional Design – Available in vibrant Blue and Green finishes, this cookware adds a splash of color and charm to any modern kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Crystal Classic Series 7-pc Non-Stick Cookware Set, PFOA Free, Red</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71bYDdKns5L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BD1JHYS7?th=1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart. | Soft touch bakelite handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Dozy Iron-Rich Nonstick Cookware Combo: 20cm Deep Pan &amp; 23cm Frypan Set Induction Bottom Non-Stick Coated Cookware Set</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/718DJ7gzFtL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H1QP34G8?th=1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PREMIUM COMBO SET: Includes a 28cm Kadhai and an 11cm Tadka Pan, designed to handle everyday Indian cooking with ease and efficiency. | IRON-RICH CONSTRUCTION: Made from durable iron material that ensures even heat distribution and long-lasting performance for daily use. | NON-STICK COATING: Features a high-quality non-stick coated interior that prevents food from sticking and makes cooking and serving effortless. | INDUCTION COMPATIBLE: Both the Kadhai and Tadka Pan come with an induction-compatible bottom, making them suitable for all cooktops including gas and induction. | EASY TO CLEAN: The smooth non-stick surface allows for quick and hassle-free cleaning with just a sponge and water after every use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NAVRANG Non Stick Cookware Set of 3 Pcs | Nonstick Dosa Tawa 26 cm &amp; Frypan 22cm with Glass Lid | Non-Induction - Purple</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/319XgXOcfML._SX300_SY300_QL70_FMwebp_.jpg</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D4VL9M95?th=1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DURABLE NONSTICK: Navrang tawa and frypan feature a reinforced nonstick coating that is PFOA free and durable enough to withstand years of regular use. | EVEN HEATING: An aluminum body construction provides quick and even heat distribution across the entire cooking surface. | NONSTICK COATING: Both the tawa and frypan (shallow frying pan) come with a nonstick coating, which prevents food from sticking to the surface. This feature makes cooking and cleaning easier. | VERSATILE COOKING: The tawa measures 26 cm for making crispy dosas and uttapams, while the 22 cm frypan is perfect for scrambling eggs or pan frying meats and vegetables. | DISHWASHER SAFE: For easy cleanup, both pans are fully immersible and dishwasher safe for carefree maintenance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1909,22 +1909,22 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pigeon Aluminium Non Stick Tawa-Fry Pan Gift Set (Red) - Duo Pack</t>
+          <t>Amazon Basics Granite Finish Non Stick 5 Pcs Induction Base Cookware Set-Granito Grey (24cm Fry Pan, 24 cm Kadai, 28cm Tawa and 2 Nylon Spatulas)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/510yXR4GoNL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71fcuPgHEBL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B07KYPZHJ9</t>
+          <t>https://www.amazon.in/dp/B0C2J76WPF?th=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>5 Layer Durable Nonstick Coating | Made with High End Italian Technology | Oil Free Cooking | Ergonomic Bakelite Handle | Free from Peel-Off</t>
+          <t>DURABLE IMPORTED COATING: It comes with water-based coating imported from Japan which is compliant with US FDA and European Food Safety Authority (EFSA) standards. This cookware features three granite-finished coats each on its interior and exterior. It has been tested to last for more than 10,000 cycles. | HEALTHIER CHOICE: Its granite coating is free from PFOA, PTFE, lead, cadmiumm nickel and arsenic. This makes it safer and healthier to use than traditional non-stick cookware, which may contain harmful chemicals. | FAST, EVEN COOKING: Made from pressed aluminium, this cookware is ultra-conductive and corrosion-resistant. Its granite coating and flat, thick skillet bottom offer exceptional heat distribution to ensure even cooking and prevent hot spots. Overall, this cookware offers quick heating, thus using less energy. | REQUIRES LESS OIL: Cook a variety of healthy, delicious recipes for Indian households using this non-stick cookware set from Amazon Basics. It requires very little oil and cooks evenly and quickly without using much power. | CONDUCTIVE BASE: Its base is made from Aluminium and is highly magnetic and conductive. It features grooves that help retain heat. | COMPATIBLE WITH ALL COOKTOPS: The induction base with small perforation boosts faster cooking while helping you consume less electricity. This cookware is compatible with both gas-stove and induction cooktops. | COMFORTABLE TO HANDLE: The coookware is 3.5 MM thick with ideal weight distribution throughout the material for comfortable handling. | EASY TO CLEAN: Food particles are less likely to stick to the surface of the non-stick coating, making this cookware easy to clean. | CLEANING AND TEMPERATURE: We recommend hand-washing this cookware. Alternatively, you may clean it in a dishwasher with liquid detergent. It may be safely even at temperatures up to (200° and (260° C. | COLOUR: Granito Grey; PACKAGE CONTENTS: 1 tawa (28 cm), 1 fry pan (24 cm), 1 kadai (24 cm), 1 glass lid and 2 nylon spatulas; Thickness: 3.5 mm</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Amazon Basics Granite Finish Non Stick 5 Pcs Induction Base Cookware Set-Granito Grey (24cm Fry Pan, 24 cm Kadai, 28cm Tawa and 2 Nylon Spatulas)</t>
+          <t>Crystal Classic Series 7-pc Non-Stick Induction Bottom Cookware Set, PFOA Free, Tawa, Fry-Pan, Kadhai with Glass Lid, Sauce Pan with 2 Serving Spoons, Red</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71fcuPgHEBL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71-v9RBpQfL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0C2J76WPF?th=1</t>
+          <t>https://www.amazon.in/dp/B09313HZ8B</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DURABLE IMPORTED COATING: It comes with water-based coating imported from Japan which is compliant with US FDA and European Food Safety Authority (EFSA) standards. This cookware features three granite-finished coats each on its interior and exterior. It has been tested to last for more than 10,000 cycles. | HEALTHIER CHOICE: Its granite coating is free from PFOA, PTFE, lead, cadmiumm nickel and arsenic. This makes it safer and healthier to use than traditional non-stick cookware, which may contain harmful chemicals. | FAST, EVEN COOKING: Made from pressed aluminium, this cookware is ultra-conductive and corrosion-resistant. Its granite coating and flat, thick skillet bottom offer exceptional heat distribution to ensure even cooking and prevent hot spots. Overall, this cookware offers quick heating, thus using less energy. | REQUIRES LESS OIL: Cook a variety of healthy, delicious recipes for Indian households using this non-stick cookware set from Amazon Basics. It requires very little oil and cooks evenly and quickly without using much power. | CONDUCTIVE BASE: Its base is made from Aluminium and is highly magnetic and conductive. It features grooves that help retain heat. | COMPATIBLE WITH ALL COOKTOPS: The induction base with small perforation boosts faster cooking while helping you consume less electricity. This cookware is compatible with both gas-stove and induction cooktops. | COMFORTABLE TO HANDLE: The coookware is 3.5 MM thick with ideal weight distribution throughout the material for comfortable handling. | EASY TO CLEAN: Food particles are less likely to stick to the surface of the non-stick coating, making this cookware easy to clean. | CLEANING AND TEMPERATURE: We recommend hand-washing this cookware. Alternatively, you may clean it in a dishwasher with liquid detergent. It may be safely even at temperatures up to (200° and (260° C. | COLOUR: Granito Grey; PACKAGE CONTENTS: 1 tawa (28 cm), 1 fry pan (24 cm), 1 kadai (24 cm), 1 glass lid and 2 nylon spatulas; Thickness: 3.5 mm</t>
+          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | All items induction base except Sauce pan | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart.</t>
         </is>
       </c>
     </row>
@@ -1955,22 +1955,22 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Crystal Classic Series 7-pc Non-Stick Induction Bottom Cookware Set, PFOA Free, Tawa, Fry-Pan, Kadhai with Glass Lid, Sauce Pan with 2 Serving Spoons, Red</t>
+          <t>Judge by Prestige Ace Aluminium Non-Stick Cookware Set - Kadai 20 cm, Fry Pan 20 cm, Omni Tawa 25 cm - 1 Unit Each, Black</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71-v9RBpQfL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/515a2mz5TOL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B09313HZ8B</t>
+          <t>https://www.amazon.in/dp/B0DG8M74Z8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | All items induction base except Sauce pan | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart.</t>
+          <t>Durable Body | Low Oil Cooking | Easy to Maintain | Cool Touch Handle</t>
         </is>
       </c>
     </row>
@@ -1978,22 +1978,22 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|25 Cm Tawa,22 Cm Kadai,1 Glass Lid|Grey</t>
+          <t>Impex Non-Stick Cookware Set of 4 Pcs | Tawa Pan, Fry Pan &amp; Kadai with Glass Lid | PFOA-Free Triple Layer Coated Aluminium Kitchen Cookware Set | Bakelite Handle, Gas Stove Compatible | 1 Yr Warranty</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71bHYFW1TmL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/717khrN3Z0L._SX679_.jpg</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0BZYDJ892?th=1</t>
+          <t>https://www.amazon.in/dp/B0CH1B2M1S</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Kadai, 1 Glass Lid</t>
+          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟒-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐊𝐈𝐓𝐂𝐇𝐄𝐍: Includes a 24cm Kadai with Glass Lid, 24cm Tawa Pan and 24cm Fry Pan – a versatile non-stick cookware set for frying, roasting, sautéing, tadka and everyday Indian cooking needs at home. | 🥘 𝐓𝐑𝐈𝐏𝐋𝐄-𝐋𝐀𝐘𝐄𝐑 𝐍𝐎𝐍-𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐀𝐓𝐈𝐍𝐆 𝐅𝐎𝐑 𝐇𝐄𝐀𝐋𝐓𝐇𝐈𝐄𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free non-stick coated aluminium cookware ensures healthier low-oil cooking, effortless food release and quick, easy cleanup after every single meal you prepare. | 🔥 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐀𝐋𝐔𝐌𝐈𝐍𝐈𝐔𝐌 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝐄𝐕𝐄𝐍 𝐇𝐄𝐀𝐓 𝐃𝐈𝐒𝐓𝐑𝐈𝐁𝐔𝐓𝐈𝐎𝐍: Superior aluminium construction with heat-resistant exterior paint delivers fast, even heating and long-lasting performance for your everyday cooking in the kitchen. | ✋ 𝐂𝐎𝐌𝐅𝐎𝐑𝐓𝐀𝐁𝐋𝐄, 𝐒𝐄𝐂𝐔𝐑𝐄 𝐁𝐀𝐊𝐄𝐋𝐈𝐓𝐄 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy, heat-resistant bakelite handles are designed for a comfortable, secure grip while cooking, reducing the risk of burns and slips during daily kitchen use at home. | 🔍 𝐓𝐄𝐌𝐏𝐄𝐑𝐄𝐃 𝐆𝐋𝐀𝐒𝐒 𝐋𝐈𝐃 𝐅𝐎𝐑 𝐄𝐀𝐒𝐘 𝐌𝐎𝐍𝐈𝐓𝐎𝐑𝐈𝐍𝐆: The toughened glass lid on the Kadai lets you monitor food while it cooks, while retaining heat and moisture for evenly cooked, flavourful, delicious home-style dishes. | ⚡ 𝐆𝐀𝐒 𝐒𝐓𝐎𝐕𝐄 𝐅𝐑𝐈𝐄𝐍𝐃𝐋𝐘 𝐍𝐎𝐍-𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Designed with a non-induction bottom, this non-stick cookware set is ideal for gas stove kitchens, delivering consistent, reliable everyday cooking performance every time. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍, 𝐋𝐎𝐖 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: The smooth non-stick coated surface allows quick, effortless cleaning after cooking, saving valuable time on daily kitchen chores with no heavy scrubbing ever required. | 🎁 𝐈𝐃𝐄𝐀𝐋 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐍𝐄𝐖 𝐇𝐎𝐌𝐄𝐒: This multicolor 4-piece cookware set makes a thoughtful gift for weddings, housewarmings, anniversaries, or new homemakers setting up their very first kitchen space. | ✅ 𝐈𝐒𝐎 𝐂𝐄𝐑𝐓𝐈𝐅𝐈𝐄𝐃 𝐅𝐎𝐑 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Manufactured under ISO certification standards, this cookware set ensures premium quality, safety, and consistent performance you can rely on across every single piece. | 🛡️ 𝐖𝐎𝐑𝐑𝐘-𝐅𝐑𝐄𝐄 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 𝐀𝐒𝐒𝐔𝐑𝐀𝐍𝐂𝐄: Backed by Impex's 1-year manufacturer warranty, this cookware set gives you complete peace of mind and confidence in your everyday kitchen investment for years to come.</t>
         </is>
       </c>
     </row>
@@ -2001,22 +2001,22 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ceramic Coated Cast Iron Non Stick Induction Cookware Set 6 Piece Kadai Fry Pan Tawa Saucepan Milk Pan Kitchen Set Black Free Size</t>
+          <t>Wonderchef Valencia Plus Non-Stick Cookware 3 Piece Set | Kadhai, Glass Lid, Dosa Tawa | Cool Touch Bakelite Handles | Pure Grade Aluminium| PFOA Free| 1 Year Warranty | Purple</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/310fMyOkioL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51i43QAE0UL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GXDS58PG</t>
+          <t>https://www.amazon.in/dp/B0GNT31PLH?th=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Multi Purpose Cookware: Includes kadai sauce pan fry pan tawa and tadka pan for diverse cooking needs | Non Stick Surface: Ensures easy cooking with less oil and prevents food from sticking | Even Heat Distribution: Designed to cook food evenly for better taste and texture | Easy Maintenance: Simple to clean and maintain for regular kitchen use | Suitable for All Kitchens: Ideal for home restaurants hotels and professional cooking setups</t>
+          <t>VERSATILE 3-PIECE SET - Kadhai, Glass Lid, Dosa Tawa let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | HEALTHY COOKING MADE EASY: MetaTuff 5-layer non-stick coating ensures minimal oil use, excellent abrasion resistance and is 00% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | VERSATILE: Cook delicious cutlets, stir-fry veggies, curries, dosas, uttapams, sandwiches, omelets, and parathas with the fry pan, kadhai, and tawa. Complete your cookware needs with Valencia set! | ENERGY-EFFICIENT: Pure grade virgin aluminium offers 9-times better heat conduction, cooking your meals faster while saving energy and time. | COMPATIBLE WITH ALL COOKING SURFACES - Use on gas cooktops, hot plates, infrared cooktops, and ceramic cooktops for maximum flexibility in your kitchen. | COMFORTABLE &amp; STYLISH - Cool touch Bakelite handles provide a firm grip and utmost convenience. Enjoy cooking with comfort and ease. | CONVENIENT: Easy to clean and dishwasher safe. Lightweight for daily use. | IDEAL FOR GIFTING - Loaded with features and beautiful looks, the Valencia cookware set is an ideal choice for gifting. Surprise your loved ones with a perfect addition to their kitchen.</t>
         </is>
       </c>
     </row>
@@ -2024,22 +2024,22 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Judge by Prestige Ace Aluminium Non-Stick Cookware Set - Kadai 20 cm, Fry Pan 20 cm, Omni Tawa 25 cm - 1 Unit Each, Black</t>
+          <t>Crystal Eco Plus 8-pc Non-Stick Cookware Set, PFOA Free, Tawa, Kadhai with SS Lid, Fry Pan, Vagariya, Mini Grill Pan, 2 Spatulas, Multicolor</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/515a2mz5TOL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71oGMB2shTL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0DG8M74Z8</t>
+          <t>https://www.amazon.in/dp/B0BD1JLNKM?th=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Durable Body | Low Oil Cooking | Easy to Maintain | Cool Touch Handle</t>
+          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart. | Soft touch bakelite handle</t>
         </is>
       </c>
     </row>
@@ -2047,321 +2047,22 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hawkins 6-Piece Triply with Shielded Nonstick Gift Set | Induction &amp; Gas Compatible | Metal Spoon Friendly | Long-Lasting | with Lid | Silver (SNSGP1)|Induction and Gas Stove Compatible</t>
+          <t>Crystal Classic Series 7-pc Non-Stick Cookware Set, PFOA Free, Red</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/812pw-1SxyL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71bYDdKns5L._SX679_.jpg</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0FT8GJKDB</t>
+          <t>https://www.amazon.in/dp/B0BD1JHYS7?th=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>High quality German PFOA-free Nonstick | Nonstick locked firmly into the tough Hard Anodised surface with a unique patented process | Extra-thick, Tri-Ply metal spreads heat evenly, is more durable | Lasts longer than ordinary nonstick | Stay-cool, sturdy riveted handles - will not loosen</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>6 Pcs Pots and Pans Non Stick Cookware Combo Set Induction Ready, with Detachable Handle, Stackable Kitchen Cooking Set Removable Handles, Oven Safe, frypan Tea pan Utensils (Cream White)</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71Gi7O-fTbL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GP8M15MC?th=1</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>DETACHABLE HANDLE SYSTEM FOR FLEXIBLE COOKING – Designed for convenience and everyday kitchen efficiency, the removable handle system allows easy attachment and detachment for cooking, serving, storage, and kitchen organization. Ideal for modern cookware setups. | SPACE SAVING &amp; STACKABLE KITCHEN SOLUTION – The detachable design helps create a compact and organized kitchen experience. Perfect for apartments, small kitchens, RVs, camping, and homes where storage space matters. | STRONG LOCKING MECHANISM &amp; COMFORTABLE GRIP – Built with a secure locking design that helps provide stability during cooking and handling. The ergonomic grip offers comfort and control for daily kitchen use. | INDUCTION READY COOKWARE COMPATIBILITY – Designed to support modern cooking needs and compatible cookware systems. Suitable for everyday meal preparation while helping maintain a clean and organized cooking space. | EASY TO CLEAN &amp; STORE – The detachable configuration simplifies cleaning and helps reduce kitchen clutter. Convenient for storing cookware and kitchen accessories in cabinets, drawers, and shelves. | VERSATILE KITCHEN ESSENTIAL FOR DAILY USE – A practical cookware solution for home chefs, students, families, and travel cooking setups. Designed for convenience, durability, and efficient kitchen organization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Hawkins Ceramic Nonstick 3-Piece Kitchen Gift Set - 1.75 L Deep Kadhai, 16 cm Frying Pan and 24 cm Tava, Grey (24ICGP)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61Dx2YMMrZL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DPB512KB</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>New Hawkins Ceramic Nonstick Inside: Excellent release properties - Uses 36% less oil for Tasty but Healthy Dishes | Can cook crisper, tastier | No PTFE, PFOA, PFAS or Heavy Metals - Ceramic based revolutionary nonstick. More hygienic, more healthy | German Ceramic - High quality, lasts longer | 3.25 mm Extra-Thick - heats fast and evenly</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Prestige Omega Granite Aluminium Kitchen Set, 4-Pieces, Black</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61Q5O9edctL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B01684OHYQ</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Material: Non-stick Aluminium; Size: Tawa Dia (280 Mm), Fry Pan Dia (240 Mm), Kadai (240 Mm), Milk Pan (160 Mm); Base type: Induction Base; Base thickness (in mm): 2.8; Included components: 4 Kitchen Set With Milk Pan; Colour: Black | Warranty: 2 Years; Included in warranty: Manufacturing defects will be covered in the warranty. Remaining things have been mentioned in the user manual; Not included in warranty: Mentioned in the manual | Durable Granite finish | Superior Non stick surface | Dishwasher safe | Metal spoon friendly | 5-layer non-stick cookware with German technology, Lid Included: Yes | Coating type: Non-Stick; No. of layers: 5 Layer; Finish: Granite Finish | Country of Origin: India.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Impex Non-Stick Cookware Set of 4 Pcs | Tawa Pan, Fry Pan &amp; Kadai with Glass Lid | PFOA-Free Triple Layer Coated Aluminium Kitchen Cookware Set | Bakelite Handle, Gas Stove Compatible | 1 Yr Warranty</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/717khrN3Z0L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CH1B2M1S</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟒-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐊𝐈𝐓𝐂𝐇𝐄𝐍: Includes a 24cm Kadai with Glass Lid, 24cm Tawa Pan and 24cm Fry Pan – a versatile non-stick cookware set for frying, roasting, sautéing, tadka and everyday Indian cooking needs at home. | 🥘 𝐓𝐑𝐈𝐏𝐋𝐄-𝐋𝐀𝐘𝐄𝐑 𝐍𝐎𝐍-𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐀𝐓𝐈𝐍𝐆 𝐅𝐎𝐑 𝐇𝐄𝐀𝐋𝐓𝐇𝐈𝐄𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free non-stick coated aluminium cookware ensures healthier low-oil cooking, effortless food release and quick, easy cleanup after every single meal you prepare. | 🔥 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐀𝐋𝐔𝐌𝐈𝐍𝐈𝐔𝐌 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝐄𝐕𝐄𝐍 𝐇𝐄𝐀𝐓 𝐃𝐈𝐒𝐓𝐑𝐈𝐁𝐔𝐓𝐈𝐎𝐍: Superior aluminium construction with heat-resistant exterior paint delivers fast, even heating and long-lasting performance for your everyday cooking in the kitchen. | ✋ 𝐂𝐎𝐌𝐅𝐎𝐑𝐓𝐀𝐁𝐋𝐄, 𝐒𝐄𝐂𝐔𝐑𝐄 𝐁𝐀𝐊𝐄𝐋𝐈𝐓𝐄 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy, heat-resistant bakelite handles are designed for a comfortable, secure grip while cooking, reducing the risk of burns and slips during daily kitchen use at home. | 🔍 𝐓𝐄𝐌𝐏𝐄𝐑𝐄𝐃 𝐆𝐋𝐀𝐒𝐒 𝐋𝐈𝐃 𝐅𝐎𝐑 𝐄𝐀𝐒𝐘 𝐌𝐎𝐍𝐈𝐓𝐎𝐑𝐈𝐍𝐆: The toughened glass lid on the Kadai lets you monitor food while it cooks, while retaining heat and moisture for evenly cooked, flavourful, delicious home-style dishes. | ⚡ 𝐆𝐀𝐒 𝐒𝐓𝐎𝐕𝐄 𝐅𝐑𝐈𝐄𝐍𝐃𝐋𝐘 𝐍𝐎𝐍-𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Designed with a non-induction bottom, this non-stick cookware set is ideal for gas stove kitchens, delivering consistent, reliable everyday cooking performance every time. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍, 𝐋𝐎𝐖 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: The smooth non-stick coated surface allows quick, effortless cleaning after cooking, saving valuable time on daily kitchen chores with no heavy scrubbing ever required. | 🎁 𝐈𝐃𝐄𝐀𝐋 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐍𝐄𝐖 𝐇𝐎𝐌𝐄𝐒: This multicolor 4-piece cookware set makes a thoughtful gift for weddings, housewarmings, anniversaries, or new homemakers setting up their very first kitchen space. | ✅ 𝐈𝐒𝐎 𝐂𝐄𝐑𝐓𝐈𝐅𝐈𝐄𝐃 𝐅𝐎𝐑 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Manufactured under ISO certification standards, this cookware set ensures premium quality, safety, and consistent performance you can rely on across every single piece. | 🛡️ 𝐖𝐎𝐑𝐑𝐘-𝐅𝐑𝐄𝐄 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 𝐀𝐒𝐒𝐔𝐑𝐀𝐍𝐂𝐄: Backed by Impex's 1-year manufacturer warranty, this cookware set gives you complete peace of mind and confidence in your everyday kitchen investment for years to come.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Impex Cook &amp; Serve Casserole Set 6 Pcs, Nonstick Granite Coated Cookware Set with Glass Lid, Induction &amp; Gas Compatible Aluminium Saucepan Combo 4.6L+2.7L+1.9L, PFOA Free Cookware for Kitchen</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/813UmqBf0IL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CW2YQC49?th=1</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>🍳 5-LAYER SUPER GRANITE COATING: Premium granite-finish nonstick coating is 10X tougher than standard nonstick cookware, resisting scratches and wear from daily use while keeping food from sticking, so meals release effortlessly every time. | 🛡️ 100% PFOA FREE &amp; NON-TOXIC: Built with safe, food-grade PFOA-free construction, this cookware set ensures no harmful chemicals leach into your food, giving your family healthy, worry-free everyday cooking on every casserole in the set. | 🔥 INDUCTION &amp; GAS COMPATIBLE: Featuring an induction-bottom base, this Impex casserole set works seamlessly on induction cooktops, gas stoves and other cooking surfaces, making it a versatile addition to any modern or traditional kitchen. | 👀 TRANSPARENT GLASS LID: Each casserole comes with a toughened glass lid so you can monitor food while it cooks without lifting the lid, locking in heat, moisture and flavor for perfectly cooked curries, rice, soups and gravies every time. | 🍽️ COOK AND SERVE CONVENIENCE: Go straight from stovetop to dining table with this elegant cook-and-serve casserole set, saving time on transferring food to separate serving bowls while keeping meals warm for longer during family dinners. | 📦 6-PIECE COMBO SET FOR EVERY NEED: Includes 3 nonstick granite casseroles with glass lids in 4.6L, 2.7L and 1.9L capacities, perfect for cooking and serving everything from small side dishes to large family-size curries and biryanis. | ⚡ LIGHTWEIGHT ALUMINIUM BODY: Crafted from durable, heat-conductive aluminium, this cookware set heats up quickly and evenly while remaining lightweight and easy to lift, pour and handle, even when fully loaded with hot food. | 🥗 HEALTHY LOW-OIL COOKING: The super granite nonstick surface allows you to cook flavorful, healthy meals using minimal oil and butter, making this saucepan combo ideal for health-conscious families and everyday nutritious cooking. | 🧼 EASY TO CLEAN NONSTICK SURFACE: The smooth granite-coated interior wipes clean in seconds and resists stubborn stains and food residue, cutting down kitchen cleanup time and keeping your cookware looking new for longer. | 🎁 IDEAL KITCHEN &amp; GIFTING ESSENTIAL: A must-have cookware set for new homes, daily cooking or gifting on weddings, housewarmings and anniversaries, this Impex casserole combo makes a practical and elegant addition to any kitchen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Wonderchef Valencia Plus Non-Stick Cookware 3 Piece Set | Kadhai, Glass Lid, Dosa Tawa | Cool Touch Bakelite Handles | Pure Grade Aluminium| PFOA Free| 1 Year Warranty | Purple</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51i43QAE0UL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GNT31PLH?th=1</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>VERSATILE 3-PIECE SET - Kadhai, Glass Lid, Dosa Tawa let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | HEALTHY COOKING MADE EASY: MetaTuff 5-layer non-stick coating ensures minimal oil use, excellent abrasion resistance and is 00% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | VERSATILE: Cook delicious cutlets, stir-fry veggies, curries, dosas, uttapams, sandwiches, omelets, and parathas with the fry pan, kadhai, and tawa. Complete your cookware needs with Valencia set! | ENERGY-EFFICIENT: Pure grade virgin aluminium offers 9-times better heat conduction, cooking your meals faster while saving energy and time. | COMPATIBLE WITH ALL COOKING SURFACES - Use on gas cooktops, hot plates, infrared cooktops, and ceramic cooktops for maximum flexibility in your kitchen. | COMFORTABLE &amp; STYLISH - Cool touch Bakelite handles provide a firm grip and utmost convenience. Enjoy cooking with comfort and ease. | CONVENIENT: Easy to clean and dishwasher safe. Lightweight for daily use. | IDEAL FOR GIFTING - Loaded with features and beautiful looks, the Valencia cookware set is an ideal choice for gifting. Surprise your loved ones with a perfect addition to their kitchen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Crystal Eco Plus 8-pc Non-Stick Cookware Set, PFOA Free, Tawa, Kadhai with SS Lid, Fry Pan, Vagariya, Mini Grill Pan, 2 Spatulas, Multicolor</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71oGMB2shTL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BD1JLNKM?th=1</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
           <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart. | Soft touch bakelite handle</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Vinod Di Casa Signature Ceramic Non Stick Cookware Set - 4 pcs | 24 cm Kadai and Frying Pan, 27 cm Dosa Tawa | Soft Touch Wooden Handle | Less Oil Healthy Cooking | Induction Compatible | Toxin Free</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61bbjGbh6dL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GGC33JCG?th=1</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>𝐒𝐈𝐆𝐍𝐀𝐓𝐔𝐑𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 = Crafted with advanced ceramic coating, this ceramic cookware set is designed as a complete kitchen essential. It delivers smooth heat flow and dependable performance, elevating everyday Indian cooking with confidence and elegance. | 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Engineered using toxin-free ceramic layers, this ceramic non stick cookware allows food to release effortlessly with minimal oil. Enjoy healthier meals that preserve taste, texture, and tradition without compromising safety. | 𝐕𝐄𝐑𝐒𝐀𝐓𝐈𝐋𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Thoughtfully curated as a nonstick cookware set combo, it includes a ceramic kadai, frying pan, and Dosa tawa. This balanced cookware set combo supports daily sabzi, roti, dosa, and gravy cooking with ease. | 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐊𝐀𝐃𝐀𝐈 𝐅𝐎𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆 = Built for Indian kitchens, the ceramic kadai for cooking offers depth, stability, and strength. Ideal for curries, stir-fries, and tadka, it blends modern durability with classic cooking needs. | 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐏𝐀𝐍 𝐒𝐄𝐓 = This refined non stick pan set brings together functionality and form. The balanced weight and ergonomic handles make everyday cooking comfortable, supporting long hours at the stove without strain or fatigue. | 𝐄𝐀𝐒𝐘 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = The smooth ceramic surface of this non stick cookware resists staining and food buildup. Gentle hand washing keeps the shine intact, making daily maintenance effortless and preserving long-term performance. | 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐑𝐄𝐀𝐃𝐘 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Designed for modern homes, this cookware set is compatible with induction and gas stoves. The sturdy base ensures stability and efficient heating, adapting seamlessly to evolving kitchen technologies. | 𝐑𝐄𝐋𝐈𝐀𝐁𝐋𝐄 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Backed by quality assurance, this non stick cookware set combo offer reflects lasting value. With dependable construction and 1 year warranty support, this kadai set for cooking brings peace of mind to every meal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>The Better Home Non Stick Cookware Set (Tawa - 26cm, Fry Pan - 24cm, Kadai with Lid - 24cm) | Non Stick Pan Set | Induction Cookware | Cookware Set Combo | 2.8mm Thickness (Blue)</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51+f68YcPhL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DS2N3XJM?th=1</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>ENHANCED USABILITY : Effortless meal prep with easy-to-clean non-stick cookware designed for family versatility and convenience. | IDEAL FOR ALL HEAT SOURCES : Compatible with gas and induction stoves, this set meets all your cooking needs, from roti to dosa. | VERSATILE USE CASES : Perfect for home cooking or BBQs, this set boosts your culinary skills, suitable for both beginners and pros. | PERFECT CAPACITY : Includes tawa (700ml), frypan (1750ml), and kadai (2500ml) with comfortable riveted soft-touch handles. | DESIGN CONSIDERATIONS : Thoughtfully designed for ease of use and maintenance, ensuring a user-friendly cooking experience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Tramontina Aura 4-Pc Cookware Set : 24cm Kadhai + Lid, 24cm Frypan, 28cm Dosa Tawa | Reinforced Ceramic Non-Stick | Quick &amp; Even Heat | Low-Oil Cooking | Gas &amp; Induction | Sea Green</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/612po7oNfOL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FL85J8KY?th=1</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Effortless Food Release &amp; Healthier Cooking – Ceramic-reinforced interior ensures smooth food release, allowing you to cook with less oil for healthier meals and quicker cleanup. | Quick &amp; Even Heating – Cold-forged body delivers fast, consistent heat distribution, eliminating hotspots for perfectly cooked results every time. | All Cooktop Compatible – Designed for versatility, this cookware works flawlessly on gas, induction, ceramic, and glass cooktops | Easy to Clean &amp; Dishwasher Safe – Cleanup is a breeze with the dishwasher-safe design, saving you time and effort after every meal. | Stylish &amp; Functional Design – Available in vibrant Blue and Green finishes, this cookware adds a splash of color and charm to any modern kitchen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Crystal Classic Series 7-pc Non-Stick Cookware Set, PFOA Free, Red</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71bYDdKns5L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BD1JHYS7?th=1</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Made from High quality aluminium | PFOA Free Non Stick Coating. | Heavy Guage, Very Durable. | Uses Little Oil - Healthy For Heart. | Soft touch bakelite handle</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Dozy Iron-Rich Nonstick Cookware Combo: 20cm Deep Pan &amp; 23cm Frypan Set Induction Bottom Non-Stick Coated Cookware Set</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/718DJ7gzFtL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H1QP34G8?th=1</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>PREMIUM COMBO SET: Includes a 28cm Kadhai and an 11cm Tadka Pan, designed to handle everyday Indian cooking with ease and efficiency. | IRON-RICH CONSTRUCTION: Made from durable iron material that ensures even heat distribution and long-lasting performance for daily use. | NON-STICK COATING: Features a high-quality non-stick coated interior that prevents food from sticking and makes cooking and serving effortless. | INDUCTION COMPATIBLE: Both the Kadhai and Tadka Pan come with an induction-compatible bottom, making them suitable for all cooktops including gas and induction. | EASY TO CLEAN: The smooth non-stick surface allows for quick and hassle-free cleaning with just a sponge and water after every use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>NAVRANG Non Stick Cookware Set of 3 Pcs | Nonstick Dosa Tawa 26 cm &amp; Frypan 22cm with Glass Lid | Non-Induction - Purple</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/319XgXOcfML._SX300_SY300_QL70_FMwebp_.jpg</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D4VL9M95?th=1</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>DURABLE NONSTICK: Navrang tawa and frypan feature a reinforced nonstick coating that is PFOA free and durable enough to withstand years of regular use. | EVEN HEATING: An aluminum body construction provides quick and even heat distribution across the entire cooking surface. | NONSTICK COATING: Both the tawa and frypan (shallow frying pan) come with a nonstick coating, which prevents food from sticking to the surface. This feature makes cooking and cleaning easier. | VERSATILE COOKING: The tawa measures 26 cm for making crispy dosas and uttapams, while the 22 cm frypan is perfect for scrambling eggs or pan frying meats and vegetables. | DISHWASHER SAFE: For easy cleanup, both pans are fully immersible and dishwasher safe for carefree maintenance.</t>
         </is>
       </c>
     </row>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2066,6 +2066,466 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Privesh Stainless Steel Modern Kitchen Storage Rack, Folding Perforated Design Trolley for Spice, Fruits, Vegetable, Onion, Potato, Organizer Stand with Wheel, 4 Layer Trolley</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/611g96ubcaL._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BRVDXZ28?th=1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Product Material: 100% Stainless Steel Grade 202. | Uses: Can Store Fruits, Vegetables and Other Kitchen Accessories like Spice Jars, Containers etc. | This Product Is Rust Resistance and Strong Body Material. | It's Made Of Premium Grade Stainless Steel And It Is Highly Durable And Rust-Proof. | Attractive Design Strong Material, Durable and Rust Proof and Finishing Look Enhance Kitchen Beauty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>COMFYHOME Kitchen Organizer Rack with Wheels - Adjustable 4 Tier Microwave Stand with 3 Wire Baskets, Oven Stand with Storage Cabinet, Metal Kitchen Storage Cart for Pantry （80x32x108cm）</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/717u0QDFKVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GX1P63MY?th=1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>【Large Capacity 4-Tier Kitchen Organizer Rack】Designed with a four-tier structure and an extra-wide countertop, this microwave stand for kitchen​easily supports large appliances like microwaves and air fryers. The combination of adjustable shelves and deep, pull-out mesh baskets significantly boosts your storage capacity. The open-mesh design ensures optimal airflow, keeping fruits and vegetables fresh and preventing moisture buildup. | 【Heavy-Duty Metal Frame &amp; Stable Structure】 This upgraded carbon steel 4 tier kitchen rack stand​features thickened shelves, reinforced tubing, and deepened baskets—increasing basket volume by 37.5%. Engineered for superior load-bearing, the tight joints and robust frame resist bending or wobbling, even under heavy weight. It offers a comprehensive upgrade in durability, ensuring your kitchen racks for storage remain stable and secure for years to come. | 【Mobile &amp; Stationary Dual Mode】Equipped with 360° silent swivel casters, this oven stand with wheels 4 tier heavy duty​glides smoothly for easy cleaning underneath. Two locking brakes keep the unit firmly in place to prevent accidental sliding. We also include non-slip stationary feet, allowing you to freely switch between a mobile cart and a fixed stand for kitchen storage rack based on your needs. | 【Multipurpose Storage Solution】More than just a rack for storage multipurpose, this oven stand​adapts to any room. Use it in the kitchen for appliances, in the office for printers and files, or on the balcony for plants. Whether used as a coffee bar cart, bathroom shelf, or pantry organizer, one unit fulfills all your organizational needs. | 【Premium Finish &amp; Easy Assembly】Featuring a classic matte black finish, this microwave stand for kitchen platform​ is scratch-resistant and easy to clean—just wipe it down to maintain its premium look. Overall dimensions: 12.5" D x 31.5" W x 42.5" H. The minimalist design complements any decor. Assembly is quick and tool-friendly with clear instructions included, combining open shelving for display with hidden baskets for a clutter-free home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TEX-RO Kitchen Trolley with Wheels | 3-Layer Metal Vegetable Basket Stand &amp; Kitchen Storage Rack | Multipurpose Kitchen Organizer for Onion Potato Storage (Black)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81zSFh5uwdL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B3JST2F4?th=1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Maximize Kitchen Storage with Tex Ro Kitchen Trolley: Versatile Kitchen Shelf and Storage Organizer for Kitchen, Vegetable Rack for Kitchen, Ideal for Efficient Kitchen Storage Solutions. | Efficient Home Organization with Kitchen Trolley Organizer and kitchen Stand : Store and Organize Home Organizer Items and Storage with a Stylish Basket for Kitchen, Perfect for Kitchen Essentials for Home Organization. | Versatile Kitchen Organization with Multipurpose Storage Solutions: Organize and Store Onions with Onion Baskets for Storage and Utilize the Onion Potato Rack for Kitchen. Enhance Storage Efficiency with a Vegetable Basket for Kitchen and Versatile Multipurpose Storage Trolley. Keep Your Kitchen Clutter-Free with a Functional Kitchen Cabinet Organizer. | Enhance Your Kitchen Organization with a Modern vegetable stand for kitchen and kitchen storage rack : Utilize the Versatile Trolley for Kitchen Storage, Ideal for Showcasing Vegetables and Providing Ample Space, and Discover the Latest Modern Kitchen Accessories for Stylish and Efficient Storage Solutions. | Convenient and Space-Saving Kitchen Storage: Maximize Efficiency with a Variety of Storage Solutions, including Onion Stand for Kitchen, Onion Storage Container for kitchen , Potato Onion Storage Container, Corner Rack, Rotating Kitchen Rack, and corner Shelf for Kitchen Organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Dillard's Plastic Multipurpose 4-Tier Floor Mount Corner Shelf Kitchen Organizer Rack/Storage Shelf/Dish Rack/Storage Rack For Kitchen</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61m039qSy2L._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FGJYFV3L</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>VERSATILE DESIGN: 3-tier rolling cart with mesh sides perfect for organizing and storing items in any room, featuring a modern black finish | MOBILE SOLUTION: Smooth-rolling casters allow easy movement between rooms, making it ideal for home, office, or craft room use | STURDY CONSTRUCTION: Durable metal frame with mesh side panels provides stability and ventilation while keeping items secure | SPACE-SAVING: Compact vertical design maximises storage in minimal floor space, with three spacious tiers for efficient organisation | PRACTICAL DIMENSIONS: Each tier offers ample storage space with mesh sides for visibility and easy access to stored items</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CR18 COLLECTION Heavy Big Size 2-Layer Stainless Steel Spice Rack | Modular kitchen Storage Organizer | Multipurpose Space Saver Rack for Efficient kitchen Organization</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71-Fb1WV0bL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BHNMMGZM?th=1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Efficient Kitchen Organization: Maximize your kitchen space with the CR18 COLLECTION Heavy Big Size Stainless Steel 2-Layer Kitchen Spice Rack, offering a sleek and organized solution for your culinary essentials. | Durable Stainless Steel Construction: Crafted from high-quality stainless steel, this spice rack ensures durability, corrosion resistance, and a contemporary look that complements any kitchen decor. | Versatile Modular Design: The two-layer design allows for easy customization, adapting to your unique storage needs. Keep spices, condiments, and essentials neatly organized for quick and convenient access. | Space-Saving Solution: Optimize your kitchen layout with this space-saving rack, suitable for both small and large kitchens. Clear up cluttered countertops and create a more functional cooking environment. | Premium Multipurpose Organizer: Upgrade your kitchen with a premium stainless steel organizer that not only enhances efficiency but also adds a touch of sophistication to your cooking space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Plastic Multipurpose 4-Tier Floor Mount Corner Shelf Kitchen Organizer Rack/Storage Shelf/Dish Rack/Storage Rack for Kitchen</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Po+suxtkL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H2W22D8X</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ERSATILE STORAGE: 4-tier multipurpose trolley perfect for organising kitchen items, fruits, vegetables, snacks, toys and kitchenware in a space-saving vertical design | PRACTICAL DESIGN: Features a dedicated dish rack layer along with multiple storage baskets for efficient organisation and easy access to items | MOBILE CONVENIENCE: Equipped with smooth-rolling wheels for effortless movement, making it easy to relocate as needed | DURABLE CONSTRUCTION: Made from sturdy plastic material that ensures long-lasting performance and stability during daily use | COMPACT DIMENSIONS: Space-efficient design with multiple tiers helps maximise storage in small kitchen areas while maintaining a sleek appearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Zepdos 2 Tier Kitchen Storage Rack Organizer | Multipurpose Metal Storage Shelf, Spice Rack for kitchen, Bathroom &amp; Dish Rack | Space Saving Countertop Rack, Black (40 x 20 x 33 CM)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/712uGFvJhJL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41V678R?th=1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>💪 HEAVY-DUTY METAL CONSTRUCTION : Crafted from premium-quality powder-coated metal for superior durability, corrosion resistance, and long-lasting performance. Strong frame construction provides excellent stability for everyday use in kitchens, bathrooms, and utility areas. | 🏠 MAXIMIZE COUNTER SPACE WITH 2-TIER STORAGE : Designed with two spacious shelves to efficiently organize spice jars, seasoning bottles, cooking oils, sauces, tea, coffee containers, and kitchen essentials. Helps keep countertops clutter-free while maximizing vertical storage space. | ✨ MODERN MINIMALIST DESIGN : Elegant matte black finish complements modern, contemporary, industrial, and traditional home décor styles. Stylish appearance enhances kitchen countertops while offering practical organization solutions. | 🍳 MULTIPURPOSE ORGANIZER FOR EVERY ROOM : Perfect for organizing spices, condiments, cooking ingredients, toiletries, cosmetics, skincare products, office supplies, coffee station accessories, pantry items, and more. Suitable for kitchens, bathrooms, bedrooms, offices, and laundry rooms. | 🛡️ STABLE &amp; SAFE DESIGN : Features raised side rails to prevent items from slipping and anti-slip foot caps for enhanced stability on countertops, shelves, cabinets, and tabletops. Keeps stored items secure and easily accessible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TEX-RO 3-Layer Kitchen Rack Stand | Multipurpose Rack for Storage | Vegetable Stand for Kitchen Storage Rack | Durable Kitchen Racks for Storage (Grey)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71fF87VT4BL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FLKBTVPM?th=1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Versatile Storage Solution – Durable rack for kitchen storage designed as an onion potato rack for kitchen with a convenient onion basket for kitchen. This multi-layer shelf for kitchen offers ample space for vegetables, groceries, and utensils, while its sturdy plastic racks for storage multipurpose design keeps your kitchen organized and clutter-free. | Multi-Functional &amp; Space-Saving – Sturdy multipurpose storage rack that works as a kitchen storage rack for home, complete with a removable vegetable basket. Designed with a durable plastic rack frame, this vegetable basket stand doubles as a stylish kitchen basket to keep your vegetables, fruits, and essentials organized in one place. | Durable &amp; Organized Storage – Keep your kitchen neat with this vegetable rack for kitchen that also works as a sturdy onion stand for kitchen. Featuring a spacious 3 tier rack kitchen storage design, this plastic rack for kitchen includes a removable plastic basket for kitchen essentials. The versatile organiser rack doubles as a plastic shelf rack for storage, perfect for vegetables, fruits, and pantry items. | Spacious &amp; Multi-Purpose Design – Stylish fruit basket for kitchen combined with a practical kitchen vegetable storage rack for everyday use. This versatile organiser for kitchen also serves as an onion potato storage for kitchen, featuring sturdy plastic racks for shelf placement. With its smooth-rolling vegetable trolley function, it doubles as one of the best kitchen shelf organisers to keep your vegetables, fruits, and groceries neatly arranged. | Strong &amp; Versatile Storage – Durable vegetable rack with a sturdy plastic stand for kitchen that doubles as a stylish kitchen storage stand. This spacious vegetables stand for kitchen works as a multi purpose storage organiser with a convenient 3 layer storage organizer rack design. Made from high-quality plastic storage material, it is ideal for vegetable storage, fruits, and other kitchen essentials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Rasvesh Multi-Purpose Trolley Storage Organizer and Kitchen Accessories Items for Kitchen Storage Rack Square Design Fruits &amp; Vegetable Onion Cutler (5 Tier)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61DCMZUkMtL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C3MCBSDD?th=1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Multipurpose Kitchen Shelf: It is a great choice to be your kitchen storage shelf, microwave stand, baker's rack, spice rack organizer, kitchen workstation shelf, It is perfect for kitchen, living room, bedroom, bathroom. | STURDY &amp; STABLE The fruit and vegetable storage rack is made of high quality metal, which is anti-corrosion, waterproof and anti-rust, durable for long-term reliability. | The trolley rotates freely 360° with lockable universal rollers at the bottom, which help the cart can move freely and turn effortlessly stop the cart in small spaces. Easy to clean, just wipe it with a wet towel. | Rolling carts with multiple baskets provide enough space for your daily storage. Fully enveloping the guardrail, encrypted wire mesh ventilation basket, allowing airflow to keep the freshness of fruits and vegetables. | Multipurpose Put the sitting room, beautiful and easy practical, Fruit snacks are easily stored and neatly placed. Put the bathroom, Products not messy, you dont't need to clean the bathroom. Set the kitchen, cooking good food without fuss. | Package Included: 1 Pc Rotating Vegetable Storage Rack.Material:Metal.Color:Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Cri8Hub 3 Tier Stainless Steel Kitchen Rack Basket Stand Storage Organizer Wall-Mounted Shelf for Spice Boxes Utensils Large(3-Tier Wall &amp; Floor Mounted Rack)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Xf--Nt1NL._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H6Q96S5X</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>3-TIER STORAGE DESIGN: Features three spacious basket shelves to neatly organise spice boxes, utensils, jars, mugs, and other kitchen essentials in one place. | STURDY STAINLESS STEEL CONSTRUCTION: Built with high-quality stainless steel wire for long-lasting durability, resistance to rust, and a polished chrome finish that complements any kitchen décor. | WALL-MOUNTED SPACE SAVER: Mounts securely on the wall to keep your countertops clutter-free, making it ideal for small kitchens where every centimetre of space matters. | VERSATILE USE: Suitable for storing spice boxes, condiment bottles, cups, canisters, and more, helping you maintain a tidy and well-organised kitchen at all times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo 4-Tier Ventilated Storage with Swivel Wheels| Multipurpose Storage Organizer for Kitchen, Bathroom &amp; Laundry | High Quality Stainless Steel Trolly (Steel)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71H96x3scmL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F79HBCFQ?th=1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Durable Stainless Steel Build – Made with premium stainless steel, this 4-tier kitchen storage rack ensures long-lasting strength, rust resistance, and heavy-duty support. | Multi-Purpose Organizer – Ideal for storing onions, potatoes, fruits, vegetables, spices, condiments, and everyday kitchen essentials in one compact unit. | Portable with Wheels – Equipped with smooth-rolling wheels, this kitchen trolley rack allows effortless mobility and easy access across different spaces. | Space-Saving Design – Compact dimensions (39 x 22 x 74 cm) make it perfect for small kitchens, apartments, and tight corners without occupying much floor space. | Open Wire Shelves for Freshness – The ventilated basket design promotes air circulation, keeping fruits and vegetables fresh while ensuring everything remains visible and accessible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>JD FRESH Metal Rotating Kitchen Trolley Storage Rack with 360-Degree Rotatable Wheels/Fruits, Vegetable &amp; Spices 6 Layer Trolly for Kitchen Organizer/Space Saving and Multipurpose Basket for Kitchen</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/8151BfsRhzL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GYRKTJZM?th=1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>𝐌𝐮𝐥𝐭𝐢𝐩𝐮𝐫𝐩𝐨𝐬𝐞 𝐊𝐢𝐭𝐜𝐡𝐞𝐧 𝐒𝐡𝐞𝐥𝐟: versatile and stable storage solution, perfect as a kitchen organizer, microwave stand, baker's rack, spice rack, or workstation shelf. Ideal for any room in your home, it combines functionality and design. | 𝐈𝐧𝐧𝐨𝐯𝐚𝐭𝐢𝐯𝐞 𝐑𝐨𝐭𝐚𝐭𝐢𝐧𝐠 𝐃𝐞𝐬𝐢𝐠𝐧: This 4-layer rotating fruit basket ensures easy access from all directions, promotes airflow with a hollow mesh design, and keeps fruits and vegetables fresh and odour-free. | 𝐇𝐢𝐠𝐡-𝐐𝐮𝐚𝐥𝐢𝐭𝐲 𝐂𝐨𝐧𝐬𝐭𝐫𝐮𝐜𝐭𝐢𝐨𝐧: from durable carbon steel, this rotating vegetable rack is waterproof, rust-proof, and built to last. Its sturdy design ensures stability, making it perfect for organizing kitchen essentials in a clutter-free way. | 𝐌𝐨𝐛𝐢𝐥𝐢𝐭𝐲 𝐚𝐧𝐝 𝐂𝐨𝐧𝐯𝐞𝐧𝐢𝐞𝐧𝐜𝐞: Equipped with 360-degree rotating casters, this storage rack moves effortlessly, ensuring easy access to items and hassle-free cleaning of your space. | 𝐒𝐩𝐚𝐜𝐢𝐨𝐮𝐬 𝐚𝐧𝐝 𝐕𝐞𝐫𝐬𝐚𝐭𝐢𝐥𝐞: This rotating basket trolley, measuring 26.5cm x 26.5cm x 58.5cm, provides ample storage for fruits, vegetables, utensils, and more. Its adaptable design fits perfectly in the kitchen, living room, bathroom, or bedroom, meeting all your home storage needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Stainless Steel Kitchen Dish Rack Expandable Storage Shelves, Multipurpose Organizer Extend Up to 580 mm with Anti-Rust Nano Coating (Pack of 4) (NHSP), Countertop, Floating Shelves</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61rmL5QqxSL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CLVJDS6F?th=1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>This Stainless Steel Shelf Can Be Of Best Use For Making Partitions Or Dividing The Space To Keep Maximum Products. This One-Piece Will Satisfy All Your Basic Needs For Purchasing Different Products For Separate Uses. | The Best Bathroom/Kitchen Accessories Which Is Totally Rust-Proof And Corrosion-Free Because Of Additional Layers Of Nickel-Chrome Mirror Finishing. We Recommend Using Wet &amp; Dry Clothes For Cleaning The Product Periodically To Maintain Its Shine And Keep It Durable. | This Rack Comes With Anti-Skid Rubber Fittings In Its Legs, Ensuring That Your Floor Stays Scratch-Free And Prevents The Rack From Slipping. You Can Start Using This Rack/Shelf As Soon As Your Receive The Product. It Can Be Placed On Kitchen/Bathroom/Cabinet/Office Floor/Platform. | It Has Simply The Best Design As It Has Spaces Between The Wires To Keep The Stored Products Ventilated. It Can Easily Store Products Above And Below The Stand. This Allows Users To Make Partitions And Get The Best Out Of Small Places In An Organized Way. | :-Smart Storage: Use Anywhere You Need To Keep Food, Pantry And Kitchen Items Organized; Perfect For Organizing Pasta, Packets, Extra Supplies Of Salt, Dressing And Vinegar, Macaroni And Cheese Boxes, Baking Supplies, Condiments And More; These Bins Also Work In Any Room Of Your Home!</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tabletop Spice Rack For Your Kitchen_Countertop Spice s And Masala Rack 2 -Tiered Shelf And 2 Layer Stainless Steel And Special Countertop Spice Rack-(Pack Of One) (Nhsp)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81W+6KEwa-L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CLGK218X</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>The 2 Shelves Can Fit Jars, Bottles, And Cans Up To 2.5 Inches In Diameter And The Top And Middle Shelves Can Fit Jars The Top Shelf Can Accommodate Taller Items | Multipurpose Use - Organize &amp; Display Spices, Spice Jars, Shakers, Snacks, Grinders, Dry Goods, Condiments, Nail Polishes, Vitamin Bottles, Medicine Bottles, Jars, Nail Polish, And Other Smaller Items. | the Craftland 2 Tier Rack offers organized space compatible with the majority of glass or plastic bottles, shakers, jars, and smaller canisters. Perfect for starter spice sets or personal everyday collections. | Elegant Scroll Design Can Be Utilized In Any Room Of The House, Including The Kitchen, Bath Room, Living Room, Bedroom, Craft Room, Playroom, Kids Rooms, Guest Rooms &amp; More | 2 Tier Rack An Essential Item To Keep Smaller Kitchen, Home, And Health Storage Jars, Bottles, And Canisters Organized And Accessible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Kitchen Organizer Rack – Multi-Purpose Kitchen Stand for Countertop &amp; Cabinet Storage | Heavy-Duty Kitchen Rack Organizer for Spices, Utensils, Dishes &amp; Pantry Items (2 Tier Z shape Rack)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61X2seYu4zL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GHZN7B1R?th=1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>✔ MULTI-PURPOSE KITCHEN ORGANIZER Keep your kitchen neat and clutter-free. Perfect for organizing spices, jars, utensils, plates, bowls, cleaning supplies, and pantry essentials. | ✔ STRONG &amp; STABLE DESIGN Made from durable, heavy-duty material for long-lasting use. Sturdy construction ensures stability even when fully loaded. | ✔ SPACE-SAVING KITCHEN STAND Maximize countertop, cabinet, or pantry space. Ideal for small kitchens, apartments, and modern homes. | ✔ EASY TO ASSEMBLE &amp; CLEAN Quick and simple installation with minimal tools required. Smooth surface makes cleaning fast and hassle-free. | ✔ MODERN &amp; ELEGANT LOOK Sleek design complements any kitchen décor — perfect for countertops, cabinets, shelves, or under-sink storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Kitchenwell Multi-Purpose Trolley Storage Organizer and Kitchen Accessories Items for Kitchen Storage Rack Square Design Fruits &amp; Vegetable Onion Cutlery Matt Black 4 Layer Drawer</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71LEjn++-EL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BVBXSC11?th=1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Country of Origin: Proudly manufactured in India with quality craftsmanship and attention to detail | Complete Package Contents: Includes 1 set of 4-layer drawer organizer for comprehensive kitchen storage solutions | Easy Organization and Management: Simplifies kitchen organization with accessible compartments for efficient storage of various items | Simple Maintenance and Cleaning: Features smooth surfaces that can be easily wiped clean with a wet towel for hassle-free upkeep | User-Friendly Design: Designed for convenient daily use with straightforward assembly and intuitive storage configuration | Stylish Matt Black Finish: Features an attractive matt black color that complements modern kitchen decor while providing durable protection | Versatile Storage Solution: Multi-purpose design accommodates fruits, vegetables, onions, cutlery, and various kitchen accessories in a space-saving square configuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Amazon Basics Multi-Purpose Large Organizer | Modular Storage Box for Clothes, Kitchen, Bedroom &amp; Living Room | Stackable Rack, Space-Saving Wardrobe Cabinet (Off White), 4 Piece, 37.5LX44.7WX27H cm</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51gHimftlML._SY300_SX300_QL70_FMwebp_.jpg</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FXXVN5V3?th=1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>BUILT WITH ULTRA-STURDY PLASTIC: Crafted from high-strength PPCP plastic to withstand daily wear, ensuring long-lasting use. SAFE PACKAGING: Packaged with care to prevent damage during transit, so your Chester arrives in pristine condition. | LAB TESTED DURABILITY: Tested by an internationally accredited lab, Chester’s resilience meets global quality standards. | COLLAPSIBLE &amp; PORTABLE: Chester's collapsible design makes it easy to dismantle, store, or relocate as needed. | SECURE MAGNETIC DOOR LOCK: Protect items from dust and keeps contents securely in place preventing them from shifting or falling out. | VERSATILE &amp; ADAPTABLE DESIGN: Perfect for organizing toys, clothes, books, and more—Chester fits seamlessly in the kitchen, living room, bathroom, or garden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CR18 COLLLECTION Stainless Steel 2 Layer Kitchen Spice Rack| Modular Storage Rack | Kitchen Organizer Multipurpose Storage Shelf/Rack, Silver</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51W5lotUOKL.jpg</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C1BYQN7Y</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | SMART STORAGE: Use anywhere you need to keep food, pantry and kitchen items organized; Perfect for organizing pasta, packets, extra supplies of salt, dressing and vinegar, macaroni and cheese boxes, baking supplies, condiments and more; These bins also work in any room of your home! | Stainless Steel Kitchen Rack Stand Container Organizer Organiser Storage Shelf Shelves Holder Trolley Basket for Spice Boxes Dabba Bartan Utensils Dishes for Home, 2-Tier, Large, Silver Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | FUNCTIONAL &amp; VERSATILE: The perfect solution for organizing a multitude of items - such as video games, bath soaps, shampoos, conditioners, linens, towels, laundry needs, craft supplies and more; Use in bathroom, bedroom, closet, laundry room, utility room, garage, hobby and craft room, home office, mudroom and entryways; Perfect for homes, apartments, condos, college dorm rooms, RVs and campers | 2 SHELVES : This trolley has 2 shelves, which makes it large enough to store many things at a time. | Multipurpose - apart from using as mixer &amp; jar rack, it can be used as a general purpose storage rack too</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Cri8Hub Metal 2 Tier Standing Spice Rack, Bathroom Countertop Storage Shelf Organizer, Kitchen Organizer, Cabinet Tray for Dresser, Multipurpose Stand, (2 Tier Standing Multipurpose Rack)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/413na2K-HnL.jpg</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C5RJ822T</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>:-Premium Quality :- Under cabinet organizers is made with premium ABS and Mild steel, We have passed a lot of use and load-bearing tests, It is stable and durable . So you don’t have to worry about the shelf wobbly to cause the items in the pallet to overturn . | :-Modern and simple Nordic style design, this storage rack can be matched well with most household style; perfect for organizing kitchen, living room, bathrooms, office, desk, balcony, also can using as small plant stand, makeup organizer rack. | :-Spray painting and thickening body, good rust prevention and no need to install. Free-standing, solid build that will not tip over or fall. | :-A Wide Range of Usages: The shelf can serve itself for different purposes, holding small items in your kitchen, bathroom, bedroom, living room, reading room, balcony and office, etc. You can try to place as many small-sized household and office items as you can imagine. | :-Durable Material: Made of premium iron and sprayed with eco-grade paint, the shelf is sturdy to use and easy to clean, rust-proof and water-proof, no need to install and free standing. Each evenly well-polished corner can keep you from being scratched, safe and unharmed. | :-Easy To Clean - Simply wipe the surface with a damp cloth to clean the shelf, keep dry and do not submerge. The under bathroom sink storage adopts hollow design, which has a good draining effect and prevents moldy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BonKaso 4-Layer Round Multipurpose Kitchen Trolley with Swivel Storage Basket &amp; 360° Rotating Wheels, Black Steel Frame, Easy Mobility, Space-Saving and Durable</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71wQ18TG9IL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GKPJ6LLV?th=1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Durable Construction: Built with a rust-resistant steel frame for long-lasting durability and protection against corrosion. | Effortless Mobility: Equipped with 360° rotating wheels for smooth, multi-directional movement, making it easy to move between rooms. | Spacious Storage: The 4-layer round design offers ample space to store kitchen essentials, office supplies, or bathroom toiletries. | Swivel Storage Baskets: Includes glide-out swivel baskets for easy access to frequently used items, enhancing organization and convenience. | No Assembly Required: Arrives fully assembled and ready for use, providing a hassle-free solution for home or office organization.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2254,22 +2254,22 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rasvesh Multi-Purpose Trolley Storage Organizer and Kitchen Accessories Items for Kitchen Storage Rack Square Design Fruits &amp; Vegetable Onion Cutler (5 Tier)</t>
+          <t>Cri8Hub 3 Tier Stainless Steel Kitchen Rack Basket Stand Storage Organizer Wall-Mounted Shelf for Spice Boxes Utensils Large(3-Tier Wall &amp; Floor Mounted Rack)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61DCMZUkMtL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71Xf--Nt1NL._SY879_.jpg</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0C3MCBSDD?th=1</t>
+          <t>https://www.amazon.in/dp/B0H6Q96S5X</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Multipurpose Kitchen Shelf: It is a great choice to be your kitchen storage shelf, microwave stand, baker's rack, spice rack organizer, kitchen workstation shelf, It is perfect for kitchen, living room, bedroom, bathroom. | STURDY &amp; STABLE The fruit and vegetable storage rack is made of high quality metal, which is anti-corrosion, waterproof and anti-rust, durable for long-term reliability. | The trolley rotates freely 360° with lockable universal rollers at the bottom, which help the cart can move freely and turn effortlessly stop the cart in small spaces. Easy to clean, just wipe it with a wet towel. | Rolling carts with multiple baskets provide enough space for your daily storage. Fully enveloping the guardrail, encrypted wire mesh ventilation basket, allowing airflow to keep the freshness of fruits and vegetables. | Multipurpose Put the sitting room, beautiful and easy practical, Fruit snacks are easily stored and neatly placed. Put the bathroom, Products not messy, you dont't need to clean the bathroom. Set the kitchen, cooking good food without fuss. | Package Included: 1 Pc Rotating Vegetable Storage Rack.Material:Metal.Color:Black</t>
+          <t>3-TIER STORAGE DESIGN: Features three spacious basket shelves to neatly organise spice boxes, utensils, jars, mugs, and other kitchen essentials in one place. | STURDY STAINLESS STEEL CONSTRUCTION: Built with high-quality stainless steel wire for long-lasting durability, resistance to rust, and a polished chrome finish that complements any kitchen décor. | WALL-MOUNTED SPACE SAVER: Mounts securely on the wall to keep your countertops clutter-free, making it ideal for small kitchens where every centimetre of space matters. | VERSATILE USE: Suitable for storing spice boxes, condiment bottles, cups, canisters, and more, helping you maintain a tidy and well-organised kitchen at all times.</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2277,22 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cri8Hub 3 Tier Stainless Steel Kitchen Rack Basket Stand Storage Organizer Wall-Mounted Shelf for Spice Boxes Utensils Large(3-Tier Wall &amp; Floor Mounted Rack)</t>
+          <t>Tabletop Spice Rack For Your Kitchen_Countertop Spice s And Masala Rack 2 -Tiered Shelf And 2 Layer Stainless Steel And Special Countertop Spice Rack-(Pack Of One) (Nhsp)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71Xf--Nt1NL._SY879_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81W+6KEwa-L._SX679_.jpg</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H6Q96S5X</t>
+          <t>https://www.amazon.in/dp/B0CLGK218X</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>3-TIER STORAGE DESIGN: Features three spacious basket shelves to neatly organise spice boxes, utensils, jars, mugs, and other kitchen essentials in one place. | STURDY STAINLESS STEEL CONSTRUCTION: Built with high-quality stainless steel wire for long-lasting durability, resistance to rust, and a polished chrome finish that complements any kitchen décor. | WALL-MOUNTED SPACE SAVER: Mounts securely on the wall to keep your countertops clutter-free, making it ideal for small kitchens where every centimetre of space matters. | VERSATILE USE: Suitable for storing spice boxes, condiment bottles, cups, canisters, and more, helping you maintain a tidy and well-organised kitchen at all times.</t>
+          <t>The 2 Shelves Can Fit Jars, Bottles, And Cans Up To 2.5 Inches In Diameter And The Top And Middle Shelves Can Fit Jars The Top Shelf Can Accommodate Taller Items | Multipurpose Use - Organize &amp; Display Spices, Spice Jars, Shakers, Snacks, Grinders, Dry Goods, Condiments, Nail Polishes, Vitamin Bottles, Medicine Bottles, Jars, Nail Polish, And Other Smaller Items. | the Craftland 2 Tier Rack offers organized space compatible with the majority of glass or plastic bottles, shakers, jars, and smaller canisters. Perfect for starter spice sets or personal everyday collections. | Elegant Scroll Design Can Be Utilized In Any Room Of The House, Including The Kitchen, Bath Room, Living Room, Bedroom, Craft Room, Playroom, Kids Rooms, Guest Rooms &amp; More | 2 Tier Rack An Essential Item To Keep Smaller Kitchen, Home, And Health Storage Jars, Bottles, And Canisters Organized And Accessible.</t>
         </is>
       </c>
     </row>
@@ -2300,22 +2300,22 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Amazon Brand - Solimo 4-Tier Ventilated Storage with Swivel Wheels| Multipurpose Storage Organizer for Kitchen, Bathroom &amp; Laundry | High Quality Stainless Steel Trolly (Steel)</t>
+          <t>Kitchen Organizer Rack – Multi-Purpose Kitchen Stand for Countertop &amp; Cabinet Storage | Heavy-Duty Kitchen Rack Organizer for Spices, Utensils, Dishes &amp; Pantry Items (2 Tier Z shape Rack)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71H96x3scmL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61X2seYu4zL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0F79HBCFQ?th=1</t>
+          <t>https://www.amazon.in/dp/B0GHZN7B1R?th=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Durable Stainless Steel Build – Made with premium stainless steel, this 4-tier kitchen storage rack ensures long-lasting strength, rust resistance, and heavy-duty support. | Multi-Purpose Organizer – Ideal for storing onions, potatoes, fruits, vegetables, spices, condiments, and everyday kitchen essentials in one compact unit. | Portable with Wheels – Equipped with smooth-rolling wheels, this kitchen trolley rack allows effortless mobility and easy access across different spaces. | Space-Saving Design – Compact dimensions (39 x 22 x 74 cm) make it perfect for small kitchens, apartments, and tight corners without occupying much floor space. | Open Wire Shelves for Freshness – The ventilated basket design promotes air circulation, keeping fruits and vegetables fresh while ensuring everything remains visible and accessible.</t>
+          <t>✔ MULTI-PURPOSE KITCHEN ORGANIZER Keep your kitchen neat and clutter-free. Perfect for organizing spices, jars, utensils, plates, bowls, cleaning supplies, and pantry essentials. | ✔ STRONG &amp; STABLE DESIGN Made from durable, heavy-duty material for long-lasting use. Sturdy construction ensures stability even when fully loaded. | ✔ SPACE-SAVING KITCHEN STAND Maximize countertop, cabinet, or pantry space. Ideal for small kitchens, apartments, and modern homes. | ✔ EASY TO ASSEMBLE &amp; CLEAN Quick and simple installation with minimal tools required. Smooth surface makes cleaning fast and hassle-free. | ✔ MODERN &amp; ELEGANT LOOK Sleek design complements any kitchen décor — perfect for countertops, cabinets, shelves, or under-sink storage.</t>
         </is>
       </c>
     </row>
@@ -2323,22 +2323,22 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JD FRESH Metal Rotating Kitchen Trolley Storage Rack with 360-Degree Rotatable Wheels/Fruits, Vegetable &amp; Spices 6 Layer Trolly for Kitchen Organizer/Space Saving and Multipurpose Basket for Kitchen</t>
+          <t>CR18 COLLLECTION Stainless Steel 2 Layer Kitchen Spice Rack| Modular Storage Rack | Kitchen Organizer Multipurpose Storage Shelf/Rack, Silver</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/8151BfsRhzL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51W5lotUOKL.jpg</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GYRKTJZM?th=1</t>
+          <t>https://www.amazon.in/dp/B0C1BYQN7Y</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>𝐌𝐮𝐥𝐭𝐢𝐩𝐮𝐫𝐩𝐨𝐬𝐞 𝐊𝐢𝐭𝐜𝐡𝐞𝐧 𝐒𝐡𝐞𝐥𝐟: versatile and stable storage solution, perfect as a kitchen organizer, microwave stand, baker's rack, spice rack, or workstation shelf. Ideal for any room in your home, it combines functionality and design. | 𝐈𝐧𝐧𝐨𝐯𝐚𝐭𝐢𝐯𝐞 𝐑𝐨𝐭𝐚𝐭𝐢𝐧𝐠 𝐃𝐞𝐬𝐢𝐠𝐧: This 4-layer rotating fruit basket ensures easy access from all directions, promotes airflow with a hollow mesh design, and keeps fruits and vegetables fresh and odour-free. | 𝐇𝐢𝐠𝐡-𝐐𝐮𝐚𝐥𝐢𝐭𝐲 𝐂𝐨𝐧𝐬𝐭𝐫𝐮𝐜𝐭𝐢𝐨𝐧: from durable carbon steel, this rotating vegetable rack is waterproof, rust-proof, and built to last. Its sturdy design ensures stability, making it perfect for organizing kitchen essentials in a clutter-free way. | 𝐌𝐨𝐛𝐢𝐥𝐢𝐭𝐲 𝐚𝐧𝐝 𝐂𝐨𝐧𝐯𝐞𝐧𝐢𝐞𝐧𝐜𝐞: Equipped with 360-degree rotating casters, this storage rack moves effortlessly, ensuring easy access to items and hassle-free cleaning of your space. | 𝐒𝐩𝐚𝐜𝐢𝐨𝐮𝐬 𝐚𝐧𝐝 𝐕𝐞𝐫𝐬𝐚𝐭𝐢𝐥𝐞: This rotating basket trolley, measuring 26.5cm x 26.5cm x 58.5cm, provides ample storage for fruits, vegetables, utensils, and more. Its adaptable design fits perfectly in the kitchen, living room, bathroom, or bedroom, meeting all your home storage needs.</t>
+          <t>Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | SMART STORAGE: Use anywhere you need to keep food, pantry and kitchen items organized; Perfect for organizing pasta, packets, extra supplies of salt, dressing and vinegar, macaroni and cheese boxes, baking supplies, condiments and more; These bins also work in any room of your home! | Stainless Steel Kitchen Rack Stand Container Organizer Organiser Storage Shelf Shelves Holder Trolley Basket for Spice Boxes Dabba Bartan Utensils Dishes for Home, 2-Tier, Large, Silver Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | FUNCTIONAL &amp; VERSATILE: The perfect solution for organizing a multitude of items - such as video games, bath soaps, shampoos, conditioners, linens, towels, laundry needs, craft supplies and more; Use in bathroom, bedroom, closet, laundry room, utility room, garage, hobby and craft room, home office, mudroom and entryways; Perfect for homes, apartments, condos, college dorm rooms, RVs and campers | 2 SHELVES : This trolley has 2 shelves, which makes it large enough to store many things at a time. | Multipurpose - apart from using as mixer &amp; jar rack, it can be used as a general purpose storage rack too</t>
         </is>
       </c>
     </row>
@@ -2346,183 +2346,22 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Stainless Steel Kitchen Dish Rack Expandable Storage Shelves, Multipurpose Organizer Extend Up to 580 mm with Anti-Rust Nano Coating (Pack of 4) (NHSP), Countertop, Floating Shelves</t>
+          <t>Cri8Hub Metal 2 Tier Standing Spice Rack, Bathroom Countertop Storage Shelf Organizer, Kitchen Organizer, Cabinet Tray for Dresser, Multipurpose Stand, (2 Tier Standing Multipurpose Rack)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61rmL5QqxSL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/413na2K-HnL.jpg</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CLVJDS6F?th=1</t>
+          <t>https://www.amazon.in/dp/B0C5RJ822T</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>This Stainless Steel Shelf Can Be Of Best Use For Making Partitions Or Dividing The Space To Keep Maximum Products. This One-Piece Will Satisfy All Your Basic Needs For Purchasing Different Products For Separate Uses. | The Best Bathroom/Kitchen Accessories Which Is Totally Rust-Proof And Corrosion-Free Because Of Additional Layers Of Nickel-Chrome Mirror Finishing. We Recommend Using Wet &amp; Dry Clothes For Cleaning The Product Periodically To Maintain Its Shine And Keep It Durable. | This Rack Comes With Anti-Skid Rubber Fittings In Its Legs, Ensuring That Your Floor Stays Scratch-Free And Prevents The Rack From Slipping. You Can Start Using This Rack/Shelf As Soon As Your Receive The Product. It Can Be Placed On Kitchen/Bathroom/Cabinet/Office Floor/Platform. | It Has Simply The Best Design As It Has Spaces Between The Wires To Keep The Stored Products Ventilated. It Can Easily Store Products Above And Below The Stand. This Allows Users To Make Partitions And Get The Best Out Of Small Places In An Organized Way. | :-Smart Storage: Use Anywhere You Need To Keep Food, Pantry And Kitchen Items Organized; Perfect For Organizing Pasta, Packets, Extra Supplies Of Salt, Dressing And Vinegar, Macaroni And Cheese Boxes, Baking Supplies, Condiments And More; These Bins Also Work In Any Room Of Your Home!</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Tabletop Spice Rack For Your Kitchen_Countertop Spice s And Masala Rack 2 -Tiered Shelf And 2 Layer Stainless Steel And Special Countertop Spice Rack-(Pack Of One) (Nhsp)</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81W+6KEwa-L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CLGK218X</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>The 2 Shelves Can Fit Jars, Bottles, And Cans Up To 2.5 Inches In Diameter And The Top And Middle Shelves Can Fit Jars The Top Shelf Can Accommodate Taller Items | Multipurpose Use - Organize &amp; Display Spices, Spice Jars, Shakers, Snacks, Grinders, Dry Goods, Condiments, Nail Polishes, Vitamin Bottles, Medicine Bottles, Jars, Nail Polish, And Other Smaller Items. | the Craftland 2 Tier Rack offers organized space compatible with the majority of glass or plastic bottles, shakers, jars, and smaller canisters. Perfect for starter spice sets or personal everyday collections. | Elegant Scroll Design Can Be Utilized In Any Room Of The House, Including The Kitchen, Bath Room, Living Room, Bedroom, Craft Room, Playroom, Kids Rooms, Guest Rooms &amp; More | 2 Tier Rack An Essential Item To Keep Smaller Kitchen, Home, And Health Storage Jars, Bottles, And Canisters Organized And Accessible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Kitchen Organizer Rack – Multi-Purpose Kitchen Stand for Countertop &amp; Cabinet Storage | Heavy-Duty Kitchen Rack Organizer for Spices, Utensils, Dishes &amp; Pantry Items (2 Tier Z shape Rack)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61X2seYu4zL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GHZN7B1R?th=1</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>✔ MULTI-PURPOSE KITCHEN ORGANIZER Keep your kitchen neat and clutter-free. Perfect for organizing spices, jars, utensils, plates, bowls, cleaning supplies, and pantry essentials. | ✔ STRONG &amp; STABLE DESIGN Made from durable, heavy-duty material for long-lasting use. Sturdy construction ensures stability even when fully loaded. | ✔ SPACE-SAVING KITCHEN STAND Maximize countertop, cabinet, or pantry space. Ideal for small kitchens, apartments, and modern homes. | ✔ EASY TO ASSEMBLE &amp; CLEAN Quick and simple installation with minimal tools required. Smooth surface makes cleaning fast and hassle-free. | ✔ MODERN &amp; ELEGANT LOOK Sleek design complements any kitchen décor — perfect for countertops, cabinets, shelves, or under-sink storage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Kitchenwell Multi-Purpose Trolley Storage Organizer and Kitchen Accessories Items for Kitchen Storage Rack Square Design Fruits &amp; Vegetable Onion Cutlery Matt Black 4 Layer Drawer</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71LEjn++-EL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BVBXSC11?th=1</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Country of Origin: Proudly manufactured in India with quality craftsmanship and attention to detail | Complete Package Contents: Includes 1 set of 4-layer drawer organizer for comprehensive kitchen storage solutions | Easy Organization and Management: Simplifies kitchen organization with accessible compartments for efficient storage of various items | Simple Maintenance and Cleaning: Features smooth surfaces that can be easily wiped clean with a wet towel for hassle-free upkeep | User-Friendly Design: Designed for convenient daily use with straightforward assembly and intuitive storage configuration | Stylish Matt Black Finish: Features an attractive matt black color that complements modern kitchen decor while providing durable protection | Versatile Storage Solution: Multi-purpose design accommodates fruits, vegetables, onions, cutlery, and various kitchen accessories in a space-saving square configuration</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Amazon Basics Multi-Purpose Large Organizer | Modular Storage Box for Clothes, Kitchen, Bedroom &amp; Living Room | Stackable Rack, Space-Saving Wardrobe Cabinet (Off White), 4 Piece, 37.5LX44.7WX27H cm</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51gHimftlML._SY300_SX300_QL70_FMwebp_.jpg</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FXXVN5V3?th=1</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>BUILT WITH ULTRA-STURDY PLASTIC: Crafted from high-strength PPCP plastic to withstand daily wear, ensuring long-lasting use. SAFE PACKAGING: Packaged with care to prevent damage during transit, so your Chester arrives in pristine condition. | LAB TESTED DURABILITY: Tested by an internationally accredited lab, Chester’s resilience meets global quality standards. | COLLAPSIBLE &amp; PORTABLE: Chester's collapsible design makes it easy to dismantle, store, or relocate as needed. | SECURE MAGNETIC DOOR LOCK: Protect items from dust and keeps contents securely in place preventing them from shifting or falling out. | VERSATILE &amp; ADAPTABLE DESIGN: Perfect for organizing toys, clothes, books, and more—Chester fits seamlessly in the kitchen, living room, bathroom, or garden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>CR18 COLLLECTION Stainless Steel 2 Layer Kitchen Spice Rack| Modular Storage Rack | Kitchen Organizer Multipurpose Storage Shelf/Rack, Silver</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51W5lotUOKL.jpg</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C1BYQN7Y</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | SMART STORAGE: Use anywhere you need to keep food, pantry and kitchen items organized; Perfect for organizing pasta, packets, extra supplies of salt, dressing and vinegar, macaroni and cheese boxes, baking supplies, condiments and more; These bins also work in any room of your home! | Stainless Steel Kitchen Rack Stand Container Organizer Organiser Storage Shelf Shelves Holder Trolley Basket for Spice Boxes Dabba Bartan Utensils Dishes for Home, 2-Tier, Large, Silver Material Type: Constructed of durable stainless steel with a gleaming chrome finish, the stylish two-shelf shelving unit offers the best of both rugged reliability and modern appeal | FUNCTIONAL &amp; VERSATILE: The perfect solution for organizing a multitude of items - such as video games, bath soaps, shampoos, conditioners, linens, towels, laundry needs, craft supplies and more; Use in bathroom, bedroom, closet, laundry room, utility room, garage, hobby and craft room, home office, mudroom and entryways; Perfect for homes, apartments, condos, college dorm rooms, RVs and campers | 2 SHELVES : This trolley has 2 shelves, which makes it large enough to store many things at a time. | Multipurpose - apart from using as mixer &amp; jar rack, it can be used as a general purpose storage rack too</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Cri8Hub Metal 2 Tier Standing Spice Rack, Bathroom Countertop Storage Shelf Organizer, Kitchen Organizer, Cabinet Tray for Dresser, Multipurpose Stand, (2 Tier Standing Multipurpose Rack)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/413na2K-HnL.jpg</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C5RJ822T</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
           <t>:-Premium Quality :- Under cabinet organizers is made with premium ABS and Mild steel, We have passed a lot of use and load-bearing tests, It is stable and durable . So you don’t have to worry about the shelf wobbly to cause the items in the pallet to overturn . | :-Modern and simple Nordic style design, this storage rack can be matched well with most household style; perfect for organizing kitchen, living room, bathrooms, office, desk, balcony, also can using as small plant stand, makeup organizer rack. | :-Spray painting and thickening body, good rust prevention and no need to install. Free-standing, solid build that will not tip over or fall. | :-A Wide Range of Usages: The shelf can serve itself for different purposes, holding small items in your kitchen, bathroom, bedroom, living room, reading room, balcony and office, etc. You can try to place as many small-sized household and office items as you can imagine. | :-Durable Material: Made of premium iron and sprayed with eco-grade paint, the shelf is sturdy to use and easy to clean, rust-proof and water-proof, no need to install and free standing. Each evenly well-polished corner can keep you from being scratched, safe and unharmed. | :-Easy To Clean - Simply wipe the surface with a damp cloth to clean the shelf, keep dry and do not submerge. The under bathroom sink storage adopts hollow design, which has a good draining effect and prevents moldy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>BonKaso 4-Layer Round Multipurpose Kitchen Trolley with Swivel Storage Basket &amp; 360° Rotating Wheels, Black Steel Frame, Easy Mobility, Space-Saving and Durable</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71wQ18TG9IL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GKPJ6LLV?th=1</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Durable Construction: Built with a rust-resistant steel frame for long-lasting durability and protection against corrosion. | Effortless Mobility: Equipped with 360° rotating wheels for smooth, multi-directional movement, making it easy to move between rooms. | Spacious Storage: The 4-layer round design offers ample space to store kitchen essentials, office supplies, or bathroom toiletries. | Swivel Storage Baskets: Includes glide-out swivel baskets for easy access to frequently used items, enhancing organization and convenience. | No Assembly Required: Arrives fully assembled and ready for use, providing a hassle-free solution for home or office organization.</t>
         </is>
       </c>
     </row>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2365,6 +2365,386 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>THE Indian Garage CO Men Polycotton Slim Fit Shirt</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71kc73X3djL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BXLMTCSW?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>U TURN Men's Casual Printed Striped Stylish Latest Formal Plus Size Shirt for Men | Cotton Mix 220 GSM</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71XRV+IU0mL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CBX4LNT9?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CB-COLEBROOK Men's Regular Fit Solid Soft Touch Cotton Casual Shirt with Pocket Design with Spread Collar &amp; Full Sleeves (Available in Plus Size)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71DU0wuXOSL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CGLLYV2D?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DEEMOON Men's Premium Cotton Blend Printed Checkered Shirt | Full Sleeve Plaid Casual Button-Down Shirt | Soft &amp; Comfortable Regular Fit | Office, Travel &amp; Everyday Wear</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81ochE-BbUL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HBR1BH9Z?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Indian Garage Men's Slim Fit Casual Striped Cotton Shirt Features Cutaway Collar, Full Sleeves, one Patch Pocket, Regular Length, Curved Hem and Button Closure.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71LOVcd6f3L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B087S62ZT1?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Men's Black Casual Shirt, Long Sleeve, Dual Chest Pockets, Button-Down Collar</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/514EKJ-5LXL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GQC17NPR?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>DEELMO Men’s Stylish Cotton Blend Casual Shirt || Full Sleeve Button-Down Shirt with Dual Flap Pockets || Comfortable Breathable Fabric || Perfect for Casual Office and Outing Wear</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61qMMGkDHfL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FXRSKQBK?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Afflatus Men’s Checked Casual Premium Cotton Blend Full Sleeve Regular Fit Check Shirt for Man | Stylish Checks Shirt for Casual Wear | Cotton Shirt for Men</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81IPkuriVKL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H2LQSGRC?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Majestic Man Men Small Checkered Slim Fit Cotton Casual Shirt</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61R8D3VtFVL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CLK9N126?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Men's Casual Full Sleeve Button-Down Shirt | Regular Fit Shirt for Smart Casual</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/612gL5H2dZL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H6Q91KB8?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Macsivo Cotton Blend Solid Casual Short Kurta for Men Long Sleeve Mandarin Collar Stylish Shirt Kurta for Men</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51LFE3SQg9L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D1G54YW7?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Youth First Men's Cotton Blend Casual Shirt for Men | Regular Fit Solid Full Sleeve | Soft Comfortable Button-Down Collared Shirt for Office, Casual, Party &amp; Formal Wear</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61M3fxTBM4L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H8DQJMJ6?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NexaFlair Men's Shirt Regular Fit Solid Pattern Linen Cotton with Long Sleeve Collared Neck Standard Length and Button Down Closure Type | Mens Casual Shirts | Man's Formal Shirts</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81-BeHIhglL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DXCZ8FCH?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Combo of Men’s Casual Cotton Blend Shirt || Long Sleeve Button Down with Spread Collar | Lightweight Breathable Fabric | Stylish Solid Shirt for Beach, Office &amp; Everyday Wear Pack of 2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51h6S4JFlNL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FMFH11PQ?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DEELMO Men's Casual Button Down Shirts Long Sleeve Linen Shirt Fashion Textured Beach Summer Shirt</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61s-ohqlfLL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F4NJ2445?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Highlander Cotton Men Shirt, Regular Fit</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61D0pD7uTOL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F47TMBNT?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DEELMO Men's Cotton Blend Printed Checkered Casual Shirt | Full Sleeve Button Down Regular Fit Collared Shirt | Soft &amp; Breathable Everyday Wear for Office (Available in Plus Size)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61hbSEpCh3L._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H9YV524M?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Majestic Man Men Classic Slim Fit Pure Cotton Casual Shirt</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71kh27MQabL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CK6LC8QR?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Amazon Brand - INKAST Men Washed Cotton Twill Denim Casual Button Down Shirt | Full Sleeves | Regular Fit | Stylish Summer - Everyday Wear</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41rA0xoRFNL.jpg</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GQP1XFHD?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>The Souled Store Cotton Linen: Men and Boys Regular Fit Full Sleeve Collared Neck Buttoned Spread Collar Casual Wear Breathable Lightweight Comfortable Easy to Style Office Wear Cotton Linen Shirts</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61BMM-N+3PL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D3F3GGY5?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2369,17 +2369,17 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>THE Indian Garage CO Men Polycotton Slim Fit Shirt</t>
+          <t>CB-COLEBROOK Men's Regular Fit Solid Soft Touch Cotton Casual Shirt with Pocket Design with Spread Collar &amp; Full Sleeves (Available in Plus Size)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71kc73X3djL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71DU0wuXOSL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0BXLMTCSW?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0CGLLYV2D?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2388,362 +2388,20 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>U TURN Men's Casual Printed Striped Stylish Latest Formal Plus Size Shirt for Men | Cotton Mix 220 GSM</t>
+          <t>DEELMO Men’s Stylish Cotton Blend Casual Shirt || Full Sleeve Button-Down Shirt with Dual Flap Pockets || Comfortable Breathable Fabric || Perfect for Casual Office and Outing Wear</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71XRV+IU0mL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61qMMGkDHfL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CBX4LNT9?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0FXRSKQBK?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>CB-COLEBROOK Men's Regular Fit Solid Soft Touch Cotton Casual Shirt with Pocket Design with Spread Collar &amp; Full Sleeves (Available in Plus Size)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71DU0wuXOSL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CGLLYV2D?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>DEEMOON Men's Premium Cotton Blend Printed Checkered Shirt | Full Sleeve Plaid Casual Button-Down Shirt | Soft &amp; Comfortable Regular Fit | Office, Travel &amp; Everyday Wear</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81ochE-BbUL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HBR1BH9Z?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Indian Garage Men's Slim Fit Casual Striped Cotton Shirt Features Cutaway Collar, Full Sleeves, one Patch Pocket, Regular Length, Curved Hem and Button Closure.</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71LOVcd6f3L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B087S62ZT1?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Men's Black Casual Shirt, Long Sleeve, Dual Chest Pockets, Button-Down Collar</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/514EKJ-5LXL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GQC17NPR?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>DEELMO Men’s Stylish Cotton Blend Casual Shirt || Full Sleeve Button-Down Shirt with Dual Flap Pockets || Comfortable Breathable Fabric || Perfect for Casual Office and Outing Wear</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61qMMGkDHfL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FXRSKQBK?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Afflatus Men’s Checked Casual Premium Cotton Blend Full Sleeve Regular Fit Check Shirt for Man | Stylish Checks Shirt for Casual Wear | Cotton Shirt for Men</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81IPkuriVKL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H2LQSGRC?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Majestic Man Men Small Checkered Slim Fit Cotton Casual Shirt</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61R8D3VtFVL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CLK9N126?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Men's Casual Full Sleeve Button-Down Shirt | Regular Fit Shirt for Smart Casual</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/612gL5H2dZL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H6Q91KB8?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Macsivo Cotton Blend Solid Casual Short Kurta for Men Long Sleeve Mandarin Collar Stylish Shirt Kurta for Men</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51LFE3SQg9L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D1G54YW7?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Youth First Men's Cotton Blend Casual Shirt for Men | Regular Fit Solid Full Sleeve | Soft Comfortable Button-Down Collared Shirt for Office, Casual, Party &amp; Formal Wear</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61M3fxTBM4L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H8DQJMJ6?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>NexaFlair Men's Shirt Regular Fit Solid Pattern Linen Cotton with Long Sleeve Collared Neck Standard Length and Button Down Closure Type | Mens Casual Shirts | Man's Formal Shirts</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81-BeHIhglL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DXCZ8FCH?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Combo of Men’s Casual Cotton Blend Shirt || Long Sleeve Button Down with Spread Collar | Lightweight Breathable Fabric | Stylish Solid Shirt for Beach, Office &amp; Everyday Wear Pack of 2</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51h6S4JFlNL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FMFH11PQ?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>DEELMO Men's Casual Button Down Shirts Long Sleeve Linen Shirt Fashion Textured Beach Summer Shirt</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61s-ohqlfLL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F4NJ2445?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Highlander Cotton Men Shirt, Regular Fit</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61D0pD7uTOL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F47TMBNT?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>DEELMO Men's Cotton Blend Printed Checkered Casual Shirt | Full Sleeve Button Down Regular Fit Collared Shirt | Soft &amp; Breathable Everyday Wear for Office (Available in Plus Size)</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61hbSEpCh3L._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H9YV524M?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Majestic Man Men Classic Slim Fit Pure Cotton Casual Shirt</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71kh27MQabL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CK6LC8QR?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Amazon Brand - INKAST Men Washed Cotton Twill Denim Casual Button Down Shirt | Full Sleeves | Regular Fit | Stylish Summer - Everyday Wear</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41rA0xoRFNL.jpg</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GQP1XFHD?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>The Souled Store Cotton Linen: Men and Boys Regular Fit Full Sleeve Collared Neck Buttoned Spread Collar Casual Wear Breathable Lightweight Comfortable Easy to Style Office Wear Cotton Linen Shirts</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61BMM-N+3PL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D3F3GGY5?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,6 +2403,386 @@
       </c>
       <c r="E85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AUSK Men's Retro Cable-Knit Quarter-Zip Polo | Premium Textured Self-Design Half Sleeve T-Shirt for Men</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51o3uMcvGSL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GJDMLG33?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>AUSK Men Printed Polo Neck Cotton Blend T-Shirt (Regular Fit, Half Sleeve) || Tshirts for Mens</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51uzisX1fyL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GKV3BNWF?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>London Hills Men’s Loose Fit Half Sleeve Vertical Striped Polo T-Shirt with Zip Collar | Premium Polyester Fabric | T Shirt for Man | Tshirt | Shirts Men | Tshirt for Man | Men T-Shirts</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Az1zs9r5L._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GMWYFLDD?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Men's Premium Waffle Knit Henley Tshirt for Men</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41yKXwNNzAL.jpg</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H74X4CCD?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GRECIILOOKS Textured Polo T-Shirt for Men | Premium Jacquard Collared Cotton Blend Polo | Smart Casual &amp; Formal t Shirt for Men | Stylish t Shirt for Mens for Office, Party &amp; Everyday</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71qxdLfZniL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GSW9QZHV?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Noble Monk Men T-Shirt</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81I400aM+8L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GRWFS3WD?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KAJARU Men's Polyester Blend T Shirt with Spread Collar Neck Line Zipper Closure Full Sleeves Solid Pattern Regular Fit and Standard Length</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81l69obPixL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FFMJKFK4?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>boffi ... 100% Cotton Oversized T-Shirt Unisex Drop Shoulder Dye Washed Street Look Black Pack of 1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61w6tzMVuRL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GSGXJX7Y?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Symbol Men's Cotton Rich Solid Polo Tshirt | Collar Tshirts | Half Sleeves | Plain-Regular Fit (Available in Plus Sizes and Combo Pack of 2)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/713n+TxyfCL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07MZM26XG?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Max Men's Polycotton Half Sleeves Regular Fit Solid Polo T-Shirt</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81vHlgI1+dL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08353R4CD?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>LEOTUDE Men's Half Sleeve Round Neck Cottonblend Graphic Print Oversized</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61WYx598KKL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FHDHB938?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Peter England Men's Regular Fit Insignia Half Sleeve Polo T-Shirt | Cotton Rich | Premium Pique Weave</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61D2tQq2tJL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09XMV4T3Q?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Allen Solly Men’s Polo T‑Shirt | Comfortable Rich Cotton Blend, Band Collar, Regular Fit | Stylish &amp; Premium All Day Wear</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61yAbOVbQ6L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B06Y2CH63N?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Peter England Men's Snug Fit Solid Polo T-Shirt with Coloured Collar Tipping| Cotton Rich| Premium Pique Weave</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61v2kpNMmVL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C1S3JMR6?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NETCLICK Men's Polycotton Round Neck T-Shirt</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61FBAoaEllL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HF8DY8RL?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Polo T Shirt for Man with Pocket, Polo T Shirts for Men, Summer Shirt with Collar, Half Sleeve, Cotton Blend, Light Weight, Comfotable Fit (Pack of 1) M to 3XL</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51QTTWHLa0L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GLQ5XT44?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>JVX Men Polo T Shirt || Waffle Polo T Shirt for Men || Regular Fit Knitted Tshirt for Man || Coller T-Shirt (Available in Plus Size, Also Available in Combo Packs) (MRT-224)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71mPrcATmcL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GRVQSJ21?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Men's Cotton Rich Polo T-Shirt with Crest Emblem</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61U4elwSUQL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H7CTXFVZ?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Lymio Polo T Shirt for Men || T Shirt for Man || Collar T Shirt Style Men (Packs Also Available) (Polo-59-62)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/712jxsGgZyL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DWSPTPMV?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Lymio Polo T Shirt for Men || T Shirt for Man || Collar T Shirt Style Men (Packs Also Available) (Polo-18-21)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71g2n6GtKvL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CZ498VSM?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2445,17 +2445,17 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>London Hills Men’s Loose Fit Half Sleeve Vertical Striped Polo T-Shirt with Zip Collar | Premium Polyester Fabric | T Shirt for Man | Tshirt | Shirts Men | Tshirt for Man | Men T-Shirts</t>
+          <t>Men's Premium Waffle Knit Henley Tshirt for Men</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71Az1zs9r5L._SX569_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41yKXwNNzAL.jpg</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GMWYFLDD?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0H74X4CCD?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2464,17 +2464,17 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Men's Premium Waffle Knit Henley Tshirt for Men</t>
+          <t>Noble Monk Men T-Shirt</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41yKXwNNzAL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81I400aM+8L._SY741_.jpg</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H74X4CCD?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0GRWFS3WD?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2483,17 +2483,17 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GRECIILOOKS Textured Polo T-Shirt for Men | Premium Jacquard Collared Cotton Blend Polo | Smart Casual &amp; Formal t Shirt for Men | Stylish t Shirt for Mens for Office, Party &amp; Everyday</t>
+          <t>KAJARU Men's Polyester Blend T Shirt with Spread Collar Neck Line Zipper Closure Full Sleeves Solid Pattern Regular Fit and Standard Length</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71qxdLfZniL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81l69obPixL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GSW9QZHV?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0FFMJKFK4?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2502,17 +2502,17 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Noble Monk Men T-Shirt</t>
+          <t>Amazon Brand - Symbol Men's Cotton Rich Solid Polo Tshirt | Collar Tshirts | Half Sleeves | Plain-Regular Fit (Available in Plus Sizes and Combo Pack of 2)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81I400aM+8L._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/713n+TxyfCL._SX569_.jpg</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GRWFS3WD?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B07MZM26XG?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2521,17 +2521,17 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KAJARU Men's Polyester Blend T Shirt with Spread Collar Neck Line Zipper Closure Full Sleeves Solid Pattern Regular Fit and Standard Length</t>
+          <t>Max Men's Polycotton Half Sleeves Regular Fit Solid Polo T-Shirt</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81l69obPixL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81vHlgI1+dL._SX569_.jpg</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0FFMJKFK4?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B08353R4CD?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -2540,17 +2540,17 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>boffi ... 100% Cotton Oversized T-Shirt Unisex Drop Shoulder Dye Washed Street Look Black Pack of 1</t>
+          <t>LEOTUDE Men's Half Sleeve Round Neck Cottonblend Graphic Print Oversized</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61w6tzMVuRL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61WYx598KKL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GSGXJX7Y?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0FHDHB938?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -2559,17 +2559,17 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Amazon Brand - Symbol Men's Cotton Rich Solid Polo Tshirt | Collar Tshirts | Half Sleeves | Plain-Regular Fit (Available in Plus Sizes and Combo Pack of 2)</t>
+          <t>Peter England Men's Regular Fit Insignia Half Sleeve Polo T-Shirt | Cotton Rich | Premium Pique Weave</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/713n+TxyfCL._SX569_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61D2tQq2tJL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B07MZM26XG?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B09XMV4T3Q?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -2578,210 +2578,20 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Max Men's Polycotton Half Sleeves Regular Fit Solid Polo T-Shirt</t>
+          <t>Allen Solly Men’s Polo T‑Shirt | Comfortable Rich Cotton Blend, Band Collar, Regular Fit | Stylish &amp; Premium All Day Wear</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81vHlgI1+dL._SX569_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61yAbOVbQ6L._SY741_.jpg</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B08353R4CD?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B06Y2CH63N?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>LEOTUDE Men's Half Sleeve Round Neck Cottonblend Graphic Print Oversized</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61WYx598KKL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FHDHB938?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Peter England Men's Regular Fit Insignia Half Sleeve Polo T-Shirt | Cotton Rich | Premium Pique Weave</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61D2tQq2tJL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09XMV4T3Q?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Allen Solly Men’s Polo T‑Shirt | Comfortable Rich Cotton Blend, Band Collar, Regular Fit | Stylish &amp; Premium All Day Wear</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61yAbOVbQ6L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B06Y2CH63N?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Peter England Men's Snug Fit Solid Polo T-Shirt with Coloured Collar Tipping| Cotton Rich| Premium Pique Weave</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61v2kpNMmVL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C1S3JMR6?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>NETCLICK Men's Polycotton Round Neck T-Shirt</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61FBAoaEllL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HF8DY8RL?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Polo T Shirt for Man with Pocket, Polo T Shirts for Men, Summer Shirt with Collar, Half Sleeve, Cotton Blend, Light Weight, Comfotable Fit (Pack of 1) M to 3XL</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51QTTWHLa0L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GLQ5XT44?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>JVX Men Polo T Shirt || Waffle Polo T Shirt for Men || Regular Fit Knitted Tshirt for Man || Coller T-Shirt (Available in Plus Size, Also Available in Combo Packs) (MRT-224)</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71mPrcATmcL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GRVQSJ21?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Men's Cotton Rich Polo T-Shirt with Crest Emblem</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61U4elwSUQL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H7CTXFVZ?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Lymio Polo T Shirt for Men || T Shirt for Man || Collar T Shirt Style Men (Packs Also Available) (Polo-59-62)</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/712jxsGgZyL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DWSPTPMV?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Lymio Polo T Shirt for Men || T Shirt for Man || Collar T Shirt Style Men (Packs Also Available) (Polo-18-21)</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71g2n6GtKvL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CZ498VSM?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2593,6 +2593,386 @@
       </c>
       <c r="E95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ROSS BROWN PU Synthetic Leather Women's Mini Satchel Bag | Ladies Purse Handbag- Mini</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81Fih1Bai-L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C97H56RF?th=1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Modern crescent sling handbag for women girls office daily travel use compact lightweight shoulder bag</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/413937Zk-XL.jpg</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H1DNM48Q?th=1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fargo PU Women's Sling Bag Handbag For Women</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71KDJYxxMJL._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D4DVRFYM?th=1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ADISA Women's Girls Large Bucket Crossbody Sling Bag - Stylish Handbag for Woman with Adjustable Belt</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51uCFgyZOFL._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D7739W64?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Lavie Women's Mono Salma Solid Satchel Bag for Women | Satchel Handbag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Ladies</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61jL7yTJObL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DY7XTTJ5?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Lavie Women's Betula Tote Handbag | Ladies Purse Handbag | Bag for Women | Rakhi Gift for Sister</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51B5i8VXffL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08HWFWGNX?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EXOTIC Studded hand bag for women</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/719oH9Lqh6L._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BQ37973M?th=1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Lavie Women's Ushawu Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71dGAHccJNL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D2DLBB37?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Women's Handmade Macrame Crossbody Sling Bag Tote Bags Beautiful &amp; Fancy Ladies Purse For Girls Women's Mobile Pouch Friends Gifts Birthday Marriage Party and Events,1- Piece</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/715mDmSA1vL._SX695_.jpg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HDDF7G1D?th=1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ZOUK Stylish Office Laptop Bag | Tote Bag For Women Fits Upto 15.6 inch |Purse for Women | Vegan Leather Handbag | Daily &amp; Travel Use</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/815GRnV4NsL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09L79TM6D?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Lyrovo Clutch Purse for Women Formal Dressy Evening Clutches Handbags Crossbody Bag for Wedding Cocktail Prom Elegance Charm</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Qn7SrsJJL.jpg</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F6TZ572V?th=1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Lavie Women's Faroe Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women | Rakhi Gift for Sister</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61r5jK+tMoL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07SMBCMGY?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>INOVERA (LABEL) Women Inovera Faux Leather Handbags Shoulder Hobo Bag Ladies Big Purse With Long Strap</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Raw8VUk5L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08CMQD4BC?th=1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ZOUK Printed Women's Jute Handcrafted Vegan Leather Everyday Tote</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61CGkDInV5L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C7VMFVDC?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Storite Women's Tote Bag With PU Leather Handles &amp; Embroidery Printed bag With Zip Pockets, Shoulder Tote Bag And Handbag For Office And College</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81CMb5BZyVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D2KDCVZQ?th=1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Storite Women's Embroidery Printed Tote Bag, Multicolour</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81+cwVciz+L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DGXX72D3?th=1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Lavie Women's Beech Flap Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61l0XOO0bHL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D2DMQXSY?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Lavie Women's Sparkle Framed Clutch | Ladies Purse Handbag</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81QX9Dat3JL._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B094J474T3?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Mochi Women Shoulder Bag</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51RMrnSZbHL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BS6Y8WC4?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ADISA Women's Crossbody Sling Bag - Stylish Cross Body Handbag for Girls &amp; Women - Adjustable Strap Shoulder Bag (SL5141)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71I4Yx1anzL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CZPJRDQN?th=1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2597,17 +2597,17 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ROSS BROWN PU Synthetic Leather Women's Mini Satchel Bag | Ladies Purse Handbag- Mini</t>
+          <t>Lavie Women's Betula Tote Handbag | Ladies Purse Handbag | Bag for Women | Rakhi Gift for Sister</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81Fih1Bai-L._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51B5i8VXffL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0C97H56RF?th=1</t>
+          <t>https://www.amazon.in/dp/B08HWFWGNX?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -2616,17 +2616,17 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Modern crescent sling handbag for women girls office daily travel use compact lightweight shoulder bag</t>
+          <t>Lavie Women's Ushawu Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/413937Zk-XL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71dGAHccJNL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H1DNM48Q?th=1</t>
+          <t>https://www.amazon.in/dp/B0D2DLBB37?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -2635,17 +2635,17 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Fargo PU Women's Sling Bag Handbag For Women</t>
+          <t>Storite Women's Tote Bag With PU Leather Handles &amp; Embroidery Printed bag With Zip Pockets, Shoulder Tote Bag And Handbag For Office And College</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71KDJYxxMJL._SY575_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81CMb5BZyVL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0D4DVRFYM?th=1</t>
+          <t>https://www.amazon.in/dp/B0D2KDCVZQ?th=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -2654,324 +2654,20 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ADISA Women's Girls Large Bucket Crossbody Sling Bag - Stylish Handbag for Woman with Adjustable Belt</t>
+          <t>Storite Women's Embroidery Printed Tote Bag, Multicolour</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51uCFgyZOFL._SY575_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81+cwVciz+L._SX679_.jpg</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0D7739W64?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0DGXX72D3?th=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Lavie Women's Mono Salma Solid Satchel Bag for Women | Satchel Handbag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Ladies</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61jL7yTJObL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DY7XTTJ5?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Lavie Women's Betula Tote Handbag | Ladies Purse Handbag | Bag for Women | Rakhi Gift for Sister</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51B5i8VXffL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B08HWFWGNX?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>EXOTIC Studded hand bag for women</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/719oH9Lqh6L._SY575_.jpg</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BQ37973M?th=1</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Lavie Women's Ushawu Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71dGAHccJNL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D2DLBB37?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Women's Handmade Macrame Crossbody Sling Bag Tote Bags Beautiful &amp; Fancy Ladies Purse For Girls Women's Mobile Pouch Friends Gifts Birthday Marriage Party and Events,1- Piece</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/715mDmSA1vL._SX695_.jpg</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HDDF7G1D?th=1</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>ZOUK Stylish Office Laptop Bag | Tote Bag For Women Fits Upto 15.6 inch |Purse for Women | Vegan Leather Handbag | Daily &amp; Travel Use</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/815GRnV4NsL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09L79TM6D?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Lyrovo Clutch Purse for Women Formal Dressy Evening Clutches Handbags Crossbody Bag for Wedding Cocktail Prom Elegance Charm</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61Qn7SrsJJL.jpg</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F6TZ572V?th=1</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Lavie Women's Faroe Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women | Rakhi Gift for Sister</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61r5jK+tMoL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B07SMBCMGY?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>INOVERA (LABEL) Women Inovera Faux Leather Handbags Shoulder Hobo Bag Ladies Big Purse With Long Strap</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71Raw8VUk5L._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B08CMQD4BC?th=1</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>ZOUK Printed Women's Jute Handcrafted Vegan Leather Everyday Tote</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61CGkDInV5L._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C7VMFVDC?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Storite Women's Tote Bag With PU Leather Handles &amp; Embroidery Printed bag With Zip Pockets, Shoulder Tote Bag And Handbag For Office And College</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81CMb5BZyVL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D2KDCVZQ?th=1</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Storite Women's Embroidery Printed Tote Bag, Multicolour</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81+cwVciz+L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DGXX72D3?th=1</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Lavie Women's Beech Flap Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61l0XOO0bHL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D2DMQXSY?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Lavie Women's Sparkle Framed Clutch | Ladies Purse Handbag</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81QX9Dat3JL._SY575_.jpg</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B094J474T3?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Mochi Women Shoulder Bag</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51RMrnSZbHL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BS6Y8WC4?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>ADISA Women's Crossbody Sling Bag - Stylish Cross Body Handbag for Girls &amp; Women - Adjustable Strap Shoulder Bag (SL5141)</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71I4Yx1anzL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CZPJRDQN?th=1</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2669,6 +2669,386 @@
       </c>
       <c r="E99" t="inlineStr"/>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GoSriKi Kurta Set Women Viscose Printed | Kurti Set Woman | Kurta Pant Dupatta 3 Piece Outfit | V-Neck Elbow Length Sleeve Straight Fit Ethnic Wear Ladies Dress Stylish Traditional Clothing</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61+SSCQ5K7L._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H3PSJZ9K?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>KLOSIA Women's Rayon Printed Anarkali Kurta and Pant with Dupatta Set</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51JtGs04X7L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FRFVFYD7?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ANNI Designer Women's Viscose Blend Straight Printed Kurta with Palazzo | Elbow Length Sleeve Kurti Set | Close Neck with Back Slit | Soft Comfortable Fabric | 2 Piece Outfit</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51CaJuDIWiL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GG459CD4?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ANNI Designer Women's Rayon Viscose Straight fit Printed Embroidered Kurta with Pant &amp; Dupatta | Ethnic Kurta Set for Women | Daily, Office &amp; Festive Traditional</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61RbrPzrjaL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G525155T?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>KZULLY | Dress for Women Western Maxi Style, Ethnic Look Outfit for Women, A Line Flared Pattern, Indo Western Dresses, One Piece Long Gown</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61ShDu8G-zL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GD1GGLLF?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Women's Pink Bandhani Print Tiered Maxi Dress, Short Sleeve, Square Neck, Cotton</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61RR8+DmkLL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GCNTLFMB?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Amayra Women's Pure Cotton Printed Straight Kurta Set with Palazzo Pants &amp; Dupatta- Ethnic Wear, White</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81IQzobx04L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FBG8S8BM?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>LookMark Women's Chikankari Embroidered Ethnic Gown, Ankle Length Flared Dress, 3/4 Sleeves, Traditional Indian Wear</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71+dHGqDzTL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CBX8GCM1?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Nermosa Women Embroidery Solid Anarkali Kurta and Pant Set with Dupatta</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71t36fW+BUL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G1HQS8NH?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Nermosa Women Printed Anarkali Kurta and Pant Set with Dupatta | Printed Kurta Set | Women Kurta Sets |</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61arSMdnL8L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H1HLVZDG?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>AASK Women Fancy Plain &amp; Solid Designer Dress for Women</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71ZyLRR01LL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CQNZLM3R?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Celary Women’s Cotton Blend Printed Night Suit Set||Soft &amp; Breathable Short Sleeve Top &amp; Ethnic Print Pyjama Set||Also Available in Plus Size||Korean Night Suit||Comfortable Home Wear &amp; Sleepwear</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61H0uYfY3cL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G3Q81J45?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Shasmi Girl's &amp; Women's Solid Color V-Neck A-Line Maxi Dress for Women | New Year Party Outfit | Waist Cinched Puff Sleeve Western | Elegant Casual Wear (Dress 246)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61OzjLUVZZL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FLK9RWQV?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Modestouze Attires Dress for Women Western Maxi Style, Indo Western Dresses, One Piece Long Gown, A Line Flared Pattern, Ethnic Look Outfit for Women</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Qzp3xNsFL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GK9LGLKR?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>MOKOSH Women’s Silk Embroidery Anarkali Kurta Pant with Dupatta</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61a52L8Yz-L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F94B99D6?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ANNI Designer Women’s Rayon Viscose Straight Solid Kurta with Palazzo Set | Sleeveless Ethnic Wear | Comfortable Two Piece Outfit for Office, Casual &amp; Daily Use</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51jOoX3aoQL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G4984Y9Q?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Nermosa Women Embroidery Solid A-Line Kurta and Pant Set with Dupatta</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71rjJMwzQaL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G6ZSVLPZ?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NAINVISH Women's Rayon Co-Ord Set | Printed Shirt and Pant Set for Women | Casual Two Piece Lounge Outfit | Western Outfit</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51NYs0EfSaL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G6DXCP75?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>GoSriKi Women's Rayon Viscose Ethnic Co-Ord Set | Kurta Pant Set | Kurta Palazzo Set | Stylish Cotton Suit Set for Women</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61v+nArmvAL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F9PTXTQX?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Leriya Fashion Dress for Women | Western Floral Printed One Piece Dress for Women midi | Casual Sleeveless Summer Dresses for Beach &amp; Stylish Party Outifits</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61O0Db6KRdL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GDQFY4HC?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2669,386 +2669,6 @@
       </c>
       <c r="E99" t="inlineStr"/>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>GoSriKi Kurta Set Women Viscose Printed | Kurti Set Woman | Kurta Pant Dupatta 3 Piece Outfit | V-Neck Elbow Length Sleeve Straight Fit Ethnic Wear Ladies Dress Stylish Traditional Clothing</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61+SSCQ5K7L._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H3PSJZ9K?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>KLOSIA Women's Rayon Printed Anarkali Kurta and Pant with Dupatta Set</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51JtGs04X7L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FRFVFYD7?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>ANNI Designer Women's Viscose Blend Straight Printed Kurta with Palazzo | Elbow Length Sleeve Kurti Set | Close Neck with Back Slit | Soft Comfortable Fabric | 2 Piece Outfit</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51CaJuDIWiL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GG459CD4?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>ANNI Designer Women's Rayon Viscose Straight fit Printed Embroidered Kurta with Pant &amp; Dupatta | Ethnic Kurta Set for Women | Daily, Office &amp; Festive Traditional</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61RbrPzrjaL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G525155T?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>KZULLY | Dress for Women Western Maxi Style, Ethnic Look Outfit for Women, A Line Flared Pattern, Indo Western Dresses, One Piece Long Gown</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61ShDu8G-zL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GD1GGLLF?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Women's Pink Bandhani Print Tiered Maxi Dress, Short Sleeve, Square Neck, Cotton</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61RR8+DmkLL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GCNTLFMB?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Amayra Women's Pure Cotton Printed Straight Kurta Set with Palazzo Pants &amp; Dupatta- Ethnic Wear, White</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81IQzobx04L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FBG8S8BM?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>LookMark Women's Chikankari Embroidered Ethnic Gown, Ankle Length Flared Dress, 3/4 Sleeves, Traditional Indian Wear</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71+dHGqDzTL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CBX8GCM1?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Nermosa Women Embroidery Solid Anarkali Kurta and Pant Set with Dupatta</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71t36fW+BUL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G1HQS8NH?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Nermosa Women Printed Anarkali Kurta and Pant Set with Dupatta | Printed Kurta Set | Women Kurta Sets |</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61arSMdnL8L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H1HLVZDG?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>AASK Women Fancy Plain &amp; Solid Designer Dress for Women</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71ZyLRR01LL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CQNZLM3R?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Celary Women’s Cotton Blend Printed Night Suit Set||Soft &amp; Breathable Short Sleeve Top &amp; Ethnic Print Pyjama Set||Also Available in Plus Size||Korean Night Suit||Comfortable Home Wear &amp; Sleepwear</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61H0uYfY3cL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G3Q81J45?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Shasmi Girl's &amp; Women's Solid Color V-Neck A-Line Maxi Dress for Women | New Year Party Outfit | Waist Cinched Puff Sleeve Western | Elegant Casual Wear (Dress 246)</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61OzjLUVZZL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FLK9RWQV?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Modestouze Attires Dress for Women Western Maxi Style, Indo Western Dresses, One Piece Long Gown, A Line Flared Pattern, Ethnic Look Outfit for Women</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61Qzp3xNsFL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GK9LGLKR?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>MOKOSH Women’s Silk Embroidery Anarkali Kurta Pant with Dupatta</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61a52L8Yz-L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F94B99D6?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>ANNI Designer Women’s Rayon Viscose Straight Solid Kurta with Palazzo Set | Sleeveless Ethnic Wear | Comfortable Two Piece Outfit for Office, Casual &amp; Daily Use</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51jOoX3aoQL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G4984Y9Q?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Nermosa Women Embroidery Solid A-Line Kurta and Pant Set with Dupatta</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71rjJMwzQaL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G6ZSVLPZ?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>NAINVISH Women's Rayon Co-Ord Set | Printed Shirt and Pant Set for Women | Casual Two Piece Lounge Outfit | Western Outfit</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51NYs0EfSaL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G6DXCP75?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>GoSriKi Women's Rayon Viscose Ethnic Co-Ord Set | Kurta Pant Set | Kurta Palazzo Set | Stylish Cotton Suit Set for Women</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61v+nArmvAL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F9PTXTQX?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Leriya Fashion Dress for Women | Western Floral Printed One Piece Dress for Women midi | Casual Sleeveless Summer Dresses for Beach &amp; Stylish Party Outifits</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61O0Db6KRdL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GDQFY4HC?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2669,6 +2669,466 @@
       </c>
       <c r="E99" t="inlineStr"/>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pigeon Aluminium Non Stick Tawa-Fry Pan Gift Set (Red) - Duo Pack</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/510yXR4GoNL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07KYPZHJ9</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>5 Layer Durable Nonstick Coating | Made with High End Italian Technology | Oil Free Cooking | Ergonomic Bakelite Handle | Free from Peel-Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tramontina Aura 4-Pc Cookware Set : 24cm Kadhai + Lid, 24cm Frypan, 28cm Dosa Tawa | Reinforced Ceramic Non-Stick | Quick &amp; Even Heat | Low-Oil Cooking | Gas &amp; Induction | Sea Green</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/612po7oNfOL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FL85J8KY?th=1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Effortless Food Release &amp; Healthier Cooking – Ceramic-reinforced interior ensures smooth food release, allowing you to cook with less oil for healthier meals and quicker cleanup. | Quick &amp; Even Heating – Cold-forged body delivers fast, consistent heat distribution, eliminating hotspots for perfectly cooked results every time. | All Cooktop Compatible – Designed for versatility, this cookware works flawlessly on gas, induction, ceramic, and glass cooktops | Easy to Clean &amp; Dishwasher Safe – Cleanup is a breeze with the dishwasher-safe design, saving you time and effort after every meal. | Stylish &amp; Functional Design – Available in vibrant Blue and Green finishes, this cookware adds a splash of color and charm to any modern kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|25 Cm Tawa,22 Cm Kadai,1 Glass Lid|Grey</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71bHYFW1TmL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYDJ892?th=1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Kadai, 1 Glass Lid</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Cookware Combo Set 2 Piece Non Stick Kadai Fry Pan Cast Iron Kitchen Use Durable Induction Gas Compatible Set Black Free Size</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31WanIyJQFL.jpg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GXDZZ9PQ</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Multi Purpose Cookware: Includes kadai sauce pan fry pan tawa and tadka pan for diverse cooking needs | Non Stick Surface: Ensures easy cooking with less oil and prevents food from sticking | Even Heat Distribution: Designed to cook food evenly for better taste and texture | Easy Maintenance: Simple to clean and maintain for regular kitchen use | Suitable for All Kitchens: Ideal for home restaurants hotels and professional cooking setups</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Amazon Solimo Aluminium 4 Piece Non-Stick Cookware Set | Granite Finish | Induction Base | PFOA Free | HTR Exterior Coating | 25 Cm Tawa, 22 Cm Kadai, 22 Cm Fry Pan, 1 Glass Lid | Grey</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71g3Y8X9hQL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZY9PTHF?th=1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: with die-cast aluminium, the fry pan provides high conductivity which enables quick heat distribution and even cooking | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | ELEGANT FINISH: It has a granite finish on the interior and the exterior which gives it an elegant look</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Impex Cook &amp; Serve Casserole Set 6 Pcs, Nonstick Granite Coated Cookware Set with Glass Lid, Induction &amp; Gas Compatible Aluminium Saucepan Combo 4.6L+2.7L+1.9L, PFOA Free Cookware for Kitchen</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/813UmqBf0IL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CW2YQC49?th=1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>🍳 5-LAYER SUPER GRANITE COATING: Premium granite-finish nonstick coating is 10X tougher than standard nonstick cookware, resisting scratches and wear from daily use while keeping food from sticking, so meals release effortlessly every time. | 🛡️ 100% PFOA FREE &amp; NON-TOXIC: Built with safe, food-grade PFOA-free construction, this cookware set ensures no harmful chemicals leach into your food, giving your family healthy, worry-free everyday cooking on every casserole in the set. | 🔥 INDUCTION &amp; GAS COMPATIBLE: Featuring an induction-bottom base, this Impex casserole set works seamlessly on induction cooktops, gas stoves and other cooking surfaces, making it a versatile addition to any modern or traditional kitchen. | 👀 TRANSPARENT GLASS LID: Each casserole comes with a toughened glass lid so you can monitor food while it cooks without lifting the lid, locking in heat, moisture and flavor for perfectly cooked curries, rice, soups and gravies every time. | 🍽️ COOK AND SERVE CONVENIENCE: Go straight from stovetop to dining table with this elegant cook-and-serve casserole set, saving time on transferring food to separate serving bowls while keeping meals warm for longer during family dinners. | 📦 6-PIECE COMBO SET FOR EVERY NEED: Includes 3 nonstick granite casseroles with glass lids in 4.6L, 2.7L and 1.9L capacities, perfect for cooking and serving everything from small side dishes to large family-size curries and biryanis. | ⚡ LIGHTWEIGHT ALUMINIUM BODY: Crafted from durable, heat-conductive aluminium, this cookware set heats up quickly and evenly while remaining lightweight and easy to lift, pour and handle, even when fully loaded with hot food. | 🥗 HEALTHY LOW-OIL COOKING: The super granite nonstick surface allows you to cook flavorful, healthy meals using minimal oil and butter, making this saucepan combo ideal for health-conscious families and everyday nutritious cooking. | 🧼 EASY TO CLEAN NONSTICK SURFACE: The smooth granite-coated interior wipes clean in seconds and resists stubborn stains and food residue, cutting down kitchen cleanup time and keeping your cookware looking new for longer. | 🎁 IDEAL KITCHEN &amp; GIFTING ESSENTIAL: A must-have cookware set for new homes, daily cooking or gifting on weddings, housewarmings and anniversaries, this Impex casserole combo makes a practical and elegant addition to any kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Hawkins Ceramic Nonstick 3-Piece Kitchen Gift Set - 1.75 L Deep Kadhai, 16 cm Frying Pan and 24 cm Tava, Grey (24ICGP)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Dx2YMMrZL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DPB512KB</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>New Hawkins Ceramic Nonstick Inside: Excellent release properties - Uses 36% less oil for Tasty but Healthy Dishes | Can cook crisper, tastier | No PTFE, PFOA, PFAS or Heavy Metals - Ceramic based revolutionary nonstick. More hygienic, more healthy | German Ceramic - High quality, lasts longer | 3.25 mm Extra-Thick - heats fast and evenly</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Hawkins 6-Piece Triply with Shielded Nonstick Gift Set | Induction &amp; Gas Compatible | Metal Spoon Friendly | Long-Lasting | with Lid | Silver (SNSGP1)|Induction and Gas Stove Compatible</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/812pw-1SxyL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FT8GJKDB</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>High quality German PFOA-free Nonstick | Nonstick locked firmly into the tough Hard Anodised surface with a unique patented process | Extra-thick, Tri-Ply metal spreads heat evenly, is more durable | Lasts longer than ordinary nonstick | Stay-cool, sturdy riveted handles - will not loosen</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Vinod Supreme Plus Non Stick Cookware Set Combo of 3 Pc | Frypan 1.6 LTR, Kadai 2.5 LTR with Common Lid &amp; 28 cm Dosa Tawa | 5 Ply Layer, 3 mm Thick | Induction and Gas Compatible | PFOA and PTFE Free</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61KvzLY93+L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4RZVS4C</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟑-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐂𝐎𝐌𝐁𝐎 = Crafted as a versatile set of 3 non stick combo, this premium non stick cookware set includes a kadai, fry pan, and dosa tawa designed for daily Indian cooking with balance, control, and consistent results. | 𝐇𝐄𝐀𝐕𝐘 𝐆𝐀𝐔𝐆𝐄 𝐍𝐎𝐍-𝐒𝐓𝐈𝐂𝐊 𝐏𝐄𝐑𝐅𝐎𝐑𝐌𝐀𝐍𝐂𝐄 = Built with a 3 mm thick 5-ply aluminium layer, this non stick pan set ensures even heat distribution and reliable cooking. Enjoy smooth food release and effortless flipping that supports traditional recipes with modern ease. | 𝐒𝐀𝐅𝐄 &amp; 𝐌𝐈𝐍𝐃𝐅𝐔𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆 𝐂𝐎𝐀𝐓𝐈𝐍𝐆 = Designed using pfoa and ptfe free non stick pans technology, the coating supports low-oil cooking while preserving taste. A reassuring choice for families who value health, safety, and everyday reliability. | 𝐌𝐔𝐋𝐓𝐈-𝐏𝐔𝐑𝐏𝐎𝐒𝐄 𝐈𝐍𝐃𝐈𝐀𝐍 𝐂𝐎𝐎𝐊𝐈𝐍𝐆 𝐒𝐄𝐓 = Thoughtfully designed as a non stick set for kitchen, this combo adapts seamlessly to frying, sautéing, and simmering. From breakfast to dinner, it supports diverse Indian meals with confidence and comfort. | 𝐓𝐑𝐀𝐃𝐈𝐓𝐈𝐎𝐍𝐀𝐋 𝐃𝐎𝐒𝐀 &amp; 𝐓𝐀𝐖𝐀 𝐄𝐗𝐂𝐄𝐋𝐋𝐄𝐍𝐂𝐄 = The wide dosa pan non stick surface and base are engineered for even browning. Prepare crisp dosas, cheelas, and rotis that feel homemade, authentic, and consistently perfect. | 𝐄𝐅𝐅𝐈𝐂𝐈𝐄𝐍𝐓 𝐊𝐀𝐃𝐀𝐈 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘𝐃𝐀𝐘 𝐑𝐄𝐂𝐈𝐏𝐄𝐒 = The deep kadai non stick design allows comfortable stirring and controlled cooking. Ideal for curries, sabzis, and tadkas, it delivers dependable performance rooted in classic Indian kitchen needs. | 𝐄𝐑𝐆𝐎𝐍𝐎𝐌𝐈𝐂 𝐇𝐀𝐍𝐃𝐋𝐄𝐒 &amp; 𝐂𝐎𝐍𝐓𝐑𝐎𝐋 = Designed with sturdy, riveted handles, this pan set combo non stick offers secure grip and balance. Experience confident handling during long cooking sessions without strain or instability. | 𝐄𝐀𝐒𝐘 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 &amp; 𝐃𝐀𝐈𝐋𝐘 𝐂𝐀𝐑𝐄 = The smooth surface of this non stick cookware sets resists food buildup and cleans easily with minimal effort. Simple care keeps the cookware looking refined and performing reliably over time. | 𝐀𝐒𝐒𝐔𝐑𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘 &amp; 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 𝐒𝐔𝐏𝐏𝐎𝐑𝐓 = Built to last, this cookware set combo non stick comes with a 12 manufacturer warranty for peace of mind. A dependable companion that blends durability, performance, and trust in everyday cooking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Prestige Omega Granite Aluminium Kitchen Set, 4-Pieces, Black</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Q5O9edctL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B01684OHYQ</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Material: Non-stick Aluminium; Size: Tawa Dia (280 Mm), Fry Pan Dia (240 Mm), Kadai (240 Mm), Milk Pan (160 Mm); Base type: Induction Base; Base thickness (in mm): 2.8; Included components: 4 Kitchen Set With Milk Pan; Colour: Black | Warranty: 2 Years; Included in warranty: Manufacturing defects will be covered in the warranty. Remaining things have been mentioned in the user manual; Not included in warranty: Mentioned in the manual | Durable Granite finish | Superior Non stick surface | Dishwasher safe | Metal spoon friendly | 5-layer non-stick cookware with German technology, Lid Included: Yes | Coating type: Non-Stick; No. of layers: 5 Layer; Finish: Granite Finish | Country of Origin: India.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>6 Pcs Pots and Pans Non Stick Cookware Combo Set Induction Ready, with Detachable Handle, Stackable Kitchen Cooking Set Removable Handles, Oven Safe, frypan Tea pan Utensils (Cream White)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Gi7O-fTbL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GP8M15MC?th=1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>DETACHABLE HANDLE SYSTEM FOR FLEXIBLE COOKING – Designed for convenience and everyday kitchen efficiency, the removable handle system allows easy attachment and detachment for cooking, serving, storage, and kitchen organization. Ideal for modern cookware setups. | SPACE SAVING &amp; STACKABLE KITCHEN SOLUTION – The detachable design helps create a compact and organized kitchen experience. Perfect for apartments, small kitchens, RVs, camping, and homes where storage space matters. | STRONG LOCKING MECHANISM &amp; COMFORTABLE GRIP – Built with a secure locking design that helps provide stability during cooking and handling. The ergonomic grip offers comfort and control for daily kitchen use. | INDUCTION READY COOKWARE COMPATIBILITY – Designed to support modern cooking needs and compatible cookware systems. Suitable for everyday meal preparation while helping maintain a clean and organized cooking space. | EASY TO CLEAN &amp; STORE – The detachable configuration simplifies cleaning and helps reduce kitchen clutter. Convenient for storing cookware and kitchen accessories in cabinets, drawers, and shelves. | VERSATILE KITCHEN ESSENTIAL FOR DAILY USE – A practical cookware solution for home chefs, students, families, and travel cooking setups. Designed for convenience, durability, and efficient kitchen organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Bergner Sienna Elite 6 Pcs Granite Non-Stick Cookware Set - 24cm Kadai with Lid, Casserole 24cm with Lid, Frypan 24cm, Tawa 28cm, Healthy Marble Coating, Less Oil Use, Cast Aluminium Induction Bottom</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/816IMhz4n9L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FNN15J7K?th=1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>🔶Premium Sienna Elite Series by Bergner : Elevate your kitchen with this elegant and high-performance 6-piece non-stick cookware set designed for everyday and gourmet cooking | 🍳 Complete Cookware Set for Every Meal : Includes : 28cm Tawa, 24cm Frypan, 24cm Kadai with Glass Lid, 24cm Casserole with Glass Lid – ideal for sautéing, frying, simmering &amp; more | 💪 Durable Cast Aluminium Body : Built with heavy-gauge cast aluminum for long-lasting strength, rust resistance &amp; quicker, even heat distribution across the surface | 🌿 Healthy Marble Non-Stick Coating : Enjoy oil-free cooking with Bergner’s PFOA-free marble coating, ensuring effortless food release and healthier meals every time | 🔥 Induction &amp; Gas Stove Compatible : Features a full induction bottom, compatible with induction cooktops, gas stoves, electric and vitro-ceramic – versatile for all kitchens | 🧼 Effortless Cleaning &amp; Maintenance : Non-stick surface makes it easy to clean after use. (Note: Hand wash recommended; not dishwasher safe.) | 🖐️ Soft-Touch Handles with Strong Grip : Ergonomic, stay-cool handles provide a comfortable, secure grip while cooking, flippingor serving | 💧 Flared Rim for Drip-Free Pouring : Smartly designed rim ensures easy, mess-free pouring of liquids like curries, saucesor soups | 🎁 Perfect Gift for Home Chefs : Ideal for housewarming, anniversary, birthdayor festive gifting, this elegant cookware set is both stylish and functional | ✅ 1-Year Manufacturer Warranty : Enjoy peace of mind with Bergner’s quality assurance and dedicated customer support</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Vinod Di Casa Signature Ceramic Non Stick Cookware Set - 4 pcs | 24 cm Kadai and Frying Pan, 27 cm Dosa Tawa | Soft Touch Wooden Handle | Less Oil Healthy Cooking | Induction Compatible | Toxin Free</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61bbjGbh6dL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GGC33JCG?th=1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>𝐒𝐈𝐆𝐍𝐀𝐓𝐔𝐑𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 = Crafted with advanced ceramic coating, this ceramic cookware set is designed as a complete kitchen essential. It delivers smooth heat flow and dependable performance, elevating everyday Indian cooking with confidence and elegance. | 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Engineered using toxin-free ceramic layers, this ceramic non stick cookware allows food to release effortlessly with minimal oil. Enjoy healthier meals that preserve taste, texture, and tradition without compromising safety. | 𝐕𝐄𝐑𝐒𝐀𝐓𝐈𝐋𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Thoughtfully curated as a nonstick cookware set combo, it includes a ceramic kadai, frying pan, and Dosa tawa. This balanced cookware set combo supports daily sabzi, roti, dosa, and gravy cooking with ease. | 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐊𝐀𝐃𝐀𝐈 𝐅𝐎𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆 = Built for Indian kitchens, the ceramic kadai for cooking offers depth, stability, and strength. Ideal for curries, stir-fries, and tadka, it blends modern durability with classic cooking needs. | 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐏𝐀𝐍 𝐒𝐄𝐓 = This refined non stick pan set brings together functionality and form. The balanced weight and ergonomic handles make everyday cooking comfortable, supporting long hours at the stove without strain or fatigue. | 𝐄𝐀𝐒𝐘 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = The smooth ceramic surface of this non stick cookware resists staining and food buildup. Gentle hand washing keeps the shine intact, making daily maintenance effortless and preserving long-term performance. | 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐑𝐄𝐀𝐃𝐘 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Designed for modern homes, this cookware set is compatible with induction and gas stoves. The sturdy base ensures stability and efficient heating, adapting seamlessly to evolving kitchen technologies. | 𝐑𝐄𝐋𝐈𝐀𝐁𝐋𝐄 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Backed by quality assurance, this non stick cookware set combo offer reflects lasting value. With dependable construction and 1 year warranty support, this kadai set for cooking brings peace of mind to every meal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Amazon Brand SOLIMO - 3 PCS Non-Stick COOKWARE SET | Aluminium</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71nriXKOrNL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07P912X7R</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>3 piece non-stick cookware set includes fry pan, flat tawa and kadhai with a glass lid for everyday cooking | Made using good quality virgin aluminium which is durable, long lasting, and offers even heat distribution | Food grade 2-way non-stick coating: Cooking surface has a 3 layered coating; outer layer has a finish with high temperature resistance (HTR) coating | Equipped with bakelite handles that offer safe and firm ergonomic grip | Ideal for preparing rotis, chapatis, dosa, stir-fries, pulao, sauteed vegetables, sear meats, fish, fry eggs and more | Compatible with gas stove and induction cooktops | Easy to clean and maintain; dishwasher safe | Comes with a 1-year warranty against manufacturing defects | Product Dimensions- Fry Pan:- Diameter: 220 mm (22 cm); Thickness: 3 mm; Depth: 45 mm (4.5 cm); Capacity: 1650 ml; Weight: 610 gm; Tawa:- Diameter: 265 mm (26.5 cm); Thickness: 3 mm; Depth: 13 mm (1.3 cm); Weight 615 gm; Kadhai:- Diameter: 220 mm (22 cm); Thickness: 3mm; Depth: 73 mm (7.3 cm); Capacity: 2500 ml; Weight: 1125 gm | Caution: For better longevity of the cookware, avoid using Metal Scrubber for coated non-stick utensils. Do not use metal spoons and ladles on coated non-stick utensils. For better and lasting coating durability, use only soft nylon scrubber and wooden /nylon ladles &amp; spoons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>The Better Home Non Stick Cookware Set (Tawa - 26cm, Fry Pan - 24cm, Kadai with Lid - 24cm) | Non Stick Pan Set | Induction Cookware | Cookware Set Combo | 2.8mm Thickness (Blue)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51+f68YcPhL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DS2N3XJM?th=1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ENHANCED USABILITY : Effortless meal prep with easy-to-clean non-stick cookware designed for family versatility and convenience. | IDEAL FOR ALL HEAT SOURCES : Compatible with gas and induction stoves, this set meets all your cooking needs, from roti to dosa. | VERSATILE USE CASES : Perfect for home cooking or BBQs, this set boosts your culinary skills, suitable for both beginners and pros. | PERFECT CAPACITY : Includes tawa (700ml), frypan (1750ml), and kadai (2500ml) with comfortable riveted soft-touch handles. | DESIGN CONSIDERATIONS : Thoughtfully designed for ease of use and maintenance, ensuring a user-friendly cooking experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Vinod Grandior Pro Hybrid Triply Stainless Steel Cookware Set - 4 pcs</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81mFtaFRHDL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HBCCG67L?th=1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>EVERYDAY MEALS, ONE SET : Move from breakfast dosas to sabzi and curries with a 28 cm tawa, 22 cm frypan and 22 cm kadai. Grandior Pro brings three useful cooking shapes together, so you can choose the right vessel for each dish. | HEXA SHIELD COOKING SURFACE : Raised stainless-steel peaks sit above protected non-stick valleys in the honeycomb surface. This combination supports easier everyday food release while keeping the textured cooking surface visible. | TRIPLY SAS CONSTRUCTION : Stainless steel, aluminium and stainless steel form the three-layer cookware body. The aluminium layer helps distribute heat, bringing practical heat-spreading construction to everyday home cooking. | ONE LID, TWO VESSELS : The common stainless-steel lid fits the 22 cm kadai and 22 cm frypan, giving you a covered-cooking option for either vessel. One lid is included, so the two vessels cannot both be covered at the same time. | BREAKFAST TO MAIN COURSE : Use the 28 cm, 4 mm thick dosa tawa for dosas, uttapam and chilla; choose the kadai for curries and sabzi, or the frypan for sauteing and shallow frying. The 4 mm thickness refers to the tawa only. | FITS YOUR COOKTOP ROUTINE : The set is compatible with gas, induction, electric, ceramic and halogen cooktops. Choose the vessel that suits your dish and cooking zone; the set brings matching cookware to different kitchen setups. | CLEANING MADE PRACTICAL : The three cookware vessels are dishwasher safe, giving you a cleaning option after everyday meals. Follow Vinod's product-specific care guidance when choosing utensils, heat settings and cleaning products. | KNOW EXACTLY WHAT IS INCLUDED : Receive a 22 cm kadai with 2.3 L capacity, a 22 cm frypan with 1.5 L capacity, a 28 cm dosa tawa and one common stainless-steel lid. This is three cookware vessels plus one lid, not four vessels. | 5-YEAR WARRANTY : Enjoy added peace of mind with the Vinod Grandior Pro cookware set, backed by a 60-month warranty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Amazon Basics Aluminum Non-Stick 15 Piece Cookware Set | 2-Way 3 Layer Non-Stick Coating | PFOA Free | High Temperature Resistant Exterior Coating, Black</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71oZ1-QYomL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B8D6GW8S?th=1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Make cooking a joyful process with this durable non-stick 15-piece cookware set | The pressed aluminium cookware body is ultra-conductive and corrosion-free, which enables quick heating and helps save energy | Stay-cool phenolic handles are heat-resistant and remain cool even at high cooking temperatures | USFDA and European Food Safety Authority (EFSA)-approved coatings are 100% free from PFOA, lead, cadmium, nickel, and arsenic | The 2-layered exterior coating makes it scratch-resistant; the 3-layered interior with water-based eco-friendly PFOA-free coating promotes healthy cooking</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set Detachable Handle |Granite Finish | Induction Base | Pfoa Free | High Temperature Resistant Exterior Coating | Black</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61WLcHiMuDL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZW3SG7G</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Kadai, 1 Glass Lid</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hawkins Quik Nonstick Induction 4 Piece Cookware Set of Deep Kadhai, Frying Pan, Saucepan and Stainless Steel Lid | Kitchen Gift Pack | Grey (IQGP1)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Ujg8yco+L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GD5QFJ19</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Healthy PFOA-free Nonstick inside - Healthy low oil cooking | Durable ceramic coating outside - stays looking new | 3mm Thick Pans - Food will not burn or stick | Rivet-less cooking surface - easy to stir, easy to clean | Deep shape - Stir-fry, High-walls. Cook large quantities</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Kreme Ceracook Ceramic Coated, Granite 13 Pc Cookware Set 2X Spatulas, ISI Certified Cookware Set, Forged, Gas &amp; Induction Use, Non Toxic PFAS &amp; PTFE Free, 1 Year Warranty, Olive Green</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71H++Fa6u8L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GY8HNHR3?th=1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>100% HEALTHY COOKING: Made from healthy ceramic coating, which is free from PFAS, PFOA, leads and chemicals. it ensures worry-free cooking and is sizzle-ready for hassle-free use. | MADE IN INDIA – MADE FOR INDIA: This cookware has designed and developed in India to cater to Indian cooking needs. | SUPERIOR QUALITY AND DESIGN: Our chef-grade Cookware is specially crafted for style, durability, and functionality. It features toxin free ceramic coating and a toughened glass lid. Ergonomic Bakelite Handles provide a soft-touch, cool and heat-proof grip. | VERSATILE &amp; QUICK COOKING: This induction cookware is also designed for effortless cooking gas stoves and heaters. Its 3mm thick aluminium body ensures uniform heat distribution for fast and evenly cooked meals, every time. | STAIN-FREE &amp; EASY CLEANING: Maintenance just got simpler and more efficient with this cooking utensil. It features a stain-free interior that requires 50% less water for cleaning. | INCLUDED COMPONENT: Kadhai 24cm with Glass Lid, Kadhai 26cm with Glass Lid, Fry Pan 24cm, Casserole 24cm with Glass Lid, Casserole 26cm, Sauce Pan 16cm with Glass Lid and 2 Silicone Spoons. | 1-YEAR WARRANTY: Enjoy your culinary journey with our one-year warranty. We proudly present you with the exceptional quality of our Kréme Ceracook Ceramic Cookware, for your complete satisfaction.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2742,22 +2742,22 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cookware Combo Set 2 Piece Non Stick Kadai Fry Pan Cast Iron Kitchen Use Durable Induction Gas Compatible Set Black Free Size</t>
+          <t>Amazon Solimo Aluminium 4 Piece Non-Stick Cookware Set | Granite Finish | Induction Base | PFOA Free | HTR Exterior Coating | 25 Cm Tawa, 22 Cm Kadai, 22 Cm Fry Pan, 1 Glass Lid | Grey</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31WanIyJQFL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71g3Y8X9hQL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GXDZZ9PQ</t>
+          <t>https://www.amazon.in/dp/B0BZY9PTHF?th=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Multi Purpose Cookware: Includes kadai sauce pan fry pan tawa and tadka pan for diverse cooking needs | Non Stick Surface: Ensures easy cooking with less oil and prevents food from sticking | Even Heat Distribution: Designed to cook food evenly for better taste and texture | Easy Maintenance: Simple to clean and maintain for regular kitchen use | Suitable for All Kitchens: Ideal for home restaurants hotels and professional cooking setups</t>
+          <t>HEAT CONDUCTIVITY: with die-cast aluminium, the fry pan provides high conductivity which enables quick heat distribution and even cooking | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | ELEGANT FINISH: It has a granite finish on the interior and the exterior which gives it an elegant look</t>
         </is>
       </c>
     </row>
@@ -2765,22 +2765,22 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Amazon Solimo Aluminium 4 Piece Non-Stick Cookware Set | Granite Finish | Induction Base | PFOA Free | HTR Exterior Coating | 25 Cm Tawa, 22 Cm Kadai, 22 Cm Fry Pan, 1 Glass Lid | Grey</t>
+          <t>Impex Cook &amp; Serve Casserole Set 6 Pcs, Nonstick Granite Coated Cookware Set with Glass Lid, Induction &amp; Gas Compatible Aluminium Saucepan Combo 4.6L+2.7L+1.9L, PFOA Free Cookware for Kitchen</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71g3Y8X9hQL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/813UmqBf0IL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0BZY9PTHF?th=1</t>
+          <t>https://www.amazon.in/dp/B0CW2YQC49?th=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>HEAT CONDUCTIVITY: with die-cast aluminium, the fry pan provides high conductivity which enables quick heat distribution and even cooking | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | ELEGANT FINISH: It has a granite finish on the interior and the exterior which gives it an elegant look</t>
+          <t>🍳 5-LAYER SUPER GRANITE COATING: Premium granite-finish nonstick coating is 10X tougher than standard nonstick cookware, resisting scratches and wear from daily use while keeping food from sticking, so meals release effortlessly every time. | 🛡️ 100% PFOA FREE &amp; NON-TOXIC: Built with safe, food-grade PFOA-free construction, this cookware set ensures no harmful chemicals leach into your food, giving your family healthy, worry-free everyday cooking on every casserole in the set. | 🔥 INDUCTION &amp; GAS COMPATIBLE: Featuring an induction-bottom base, this Impex casserole set works seamlessly on induction cooktops, gas stoves and other cooking surfaces, making it a versatile addition to any modern or traditional kitchen. | 👀 TRANSPARENT GLASS LID: Each casserole comes with a toughened glass lid so you can monitor food while it cooks without lifting the lid, locking in heat, moisture and flavor for perfectly cooked curries, rice, soups and gravies every time. | 🍽️ COOK AND SERVE CONVENIENCE: Go straight from stovetop to dining table with this elegant cook-and-serve casserole set, saving time on transferring food to separate serving bowls while keeping meals warm for longer during family dinners. | 📦 6-PIECE COMBO SET FOR EVERY NEED: Includes 3 nonstick granite casseroles with glass lids in 4.6L, 2.7L and 1.9L capacities, perfect for cooking and serving everything from small side dishes to large family-size curries and biryanis. | ⚡ LIGHTWEIGHT ALUMINIUM BODY: Crafted from durable, heat-conductive aluminium, this cookware set heats up quickly and evenly while remaining lightweight and easy to lift, pour and handle, even when fully loaded with hot food. | 🥗 HEALTHY LOW-OIL COOKING: The super granite nonstick surface allows you to cook flavorful, healthy meals using minimal oil and butter, making this saucepan combo ideal for health-conscious families and everyday nutritious cooking. | 🧼 EASY TO CLEAN NONSTICK SURFACE: The smooth granite-coated interior wipes clean in seconds and resists stubborn stains and food residue, cutting down kitchen cleanup time and keeping your cookware looking new for longer. | 🎁 IDEAL KITCHEN &amp; GIFTING ESSENTIAL: A must-have cookware set for new homes, daily cooking or gifting on weddings, housewarmings and anniversaries, this Impex casserole combo makes a practical and elegant addition to any kitchen.</t>
         </is>
       </c>
     </row>
@@ -2788,22 +2788,22 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Impex Cook &amp; Serve Casserole Set 6 Pcs, Nonstick Granite Coated Cookware Set with Glass Lid, Induction &amp; Gas Compatible Aluminium Saucepan Combo 4.6L+2.7L+1.9L, PFOA Free Cookware for Kitchen</t>
+          <t>Hawkins Ceramic Nonstick 3-Piece Kitchen Gift Set - 1.75 L Deep Kadhai, 16 cm Frying Pan and 24 cm Tava, Grey (24ICGP)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/813UmqBf0IL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61Dx2YMMrZL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CW2YQC49?th=1</t>
+          <t>https://www.amazon.in/dp/B0DPB512KB</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>🍳 5-LAYER SUPER GRANITE COATING: Premium granite-finish nonstick coating is 10X tougher than standard nonstick cookware, resisting scratches and wear from daily use while keeping food from sticking, so meals release effortlessly every time. | 🛡️ 100% PFOA FREE &amp; NON-TOXIC: Built with safe, food-grade PFOA-free construction, this cookware set ensures no harmful chemicals leach into your food, giving your family healthy, worry-free everyday cooking on every casserole in the set. | 🔥 INDUCTION &amp; GAS COMPATIBLE: Featuring an induction-bottom base, this Impex casserole set works seamlessly on induction cooktops, gas stoves and other cooking surfaces, making it a versatile addition to any modern or traditional kitchen. | 👀 TRANSPARENT GLASS LID: Each casserole comes with a toughened glass lid so you can monitor food while it cooks without lifting the lid, locking in heat, moisture and flavor for perfectly cooked curries, rice, soups and gravies every time. | 🍽️ COOK AND SERVE CONVENIENCE: Go straight from stovetop to dining table with this elegant cook-and-serve casserole set, saving time on transferring food to separate serving bowls while keeping meals warm for longer during family dinners. | 📦 6-PIECE COMBO SET FOR EVERY NEED: Includes 3 nonstick granite casseroles with glass lids in 4.6L, 2.7L and 1.9L capacities, perfect for cooking and serving everything from small side dishes to large family-size curries and biryanis. | ⚡ LIGHTWEIGHT ALUMINIUM BODY: Crafted from durable, heat-conductive aluminium, this cookware set heats up quickly and evenly while remaining lightweight and easy to lift, pour and handle, even when fully loaded with hot food. | 🥗 HEALTHY LOW-OIL COOKING: The super granite nonstick surface allows you to cook flavorful, healthy meals using minimal oil and butter, making this saucepan combo ideal for health-conscious families and everyday nutritious cooking. | 🧼 EASY TO CLEAN NONSTICK SURFACE: The smooth granite-coated interior wipes clean in seconds and resists stubborn stains and food residue, cutting down kitchen cleanup time and keeping your cookware looking new for longer. | 🎁 IDEAL KITCHEN &amp; GIFTING ESSENTIAL: A must-have cookware set for new homes, daily cooking or gifting on weddings, housewarmings and anniversaries, this Impex casserole combo makes a practical and elegant addition to any kitchen.</t>
+          <t>New Hawkins Ceramic Nonstick Inside: Excellent release properties - Uses 36% less oil for Tasty but Healthy Dishes | Can cook crisper, tastier | No PTFE, PFOA, PFAS or Heavy Metals - Ceramic based revolutionary nonstick. More hygienic, more healthy | German Ceramic - High quality, lasts longer | 3.25 mm Extra-Thick - heats fast and evenly</t>
         </is>
       </c>
     </row>
@@ -2811,22 +2811,22 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Hawkins Ceramic Nonstick 3-Piece Kitchen Gift Set - 1.75 L Deep Kadhai, 16 cm Frying Pan and 24 cm Tava, Grey (24ICGP)</t>
+          <t>Hawkins 6-Piece Triply with Shielded Nonstick Gift Set | Induction &amp; Gas Compatible | Metal Spoon Friendly | Long-Lasting | with Lid | Silver (SNSGP1)|Induction and Gas Stove Compatible</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61Dx2YMMrZL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/812pw-1SxyL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0DPB512KB</t>
+          <t>https://www.amazon.in/dp/B0FT8GJKDB</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>New Hawkins Ceramic Nonstick Inside: Excellent release properties - Uses 36% less oil for Tasty but Healthy Dishes | Can cook crisper, tastier | No PTFE, PFOA, PFAS or Heavy Metals - Ceramic based revolutionary nonstick. More hygienic, more healthy | German Ceramic - High quality, lasts longer | 3.25 mm Extra-Thick - heats fast and evenly</t>
+          <t>High quality German PFOA-free Nonstick | Nonstick locked firmly into the tough Hard Anodised surface with a unique patented process | Extra-thick, Tri-Ply metal spreads heat evenly, is more durable | Lasts longer than ordinary nonstick | Stay-cool, sturdy riveted handles - will not loosen</t>
         </is>
       </c>
     </row>
@@ -2834,22 +2834,22 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Hawkins 6-Piece Triply with Shielded Nonstick Gift Set | Induction &amp; Gas Compatible | Metal Spoon Friendly | Long-Lasting | with Lid | Silver (SNSGP1)|Induction and Gas Stove Compatible</t>
+          <t>Prestige Omega Granite Aluminium Kitchen Set, 4-Pieces, Black</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/812pw-1SxyL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61Q5O9edctL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0FT8GJKDB</t>
+          <t>https://www.amazon.in/dp/B01684OHYQ</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>High quality German PFOA-free Nonstick | Nonstick locked firmly into the tough Hard Anodised surface with a unique patented process | Extra-thick, Tri-Ply metal spreads heat evenly, is more durable | Lasts longer than ordinary nonstick | Stay-cool, sturdy riveted handles - will not loosen</t>
+          <t>Material: Non-stick Aluminium; Size: Tawa Dia (280 Mm), Fry Pan Dia (240 Mm), Kadai (240 Mm), Milk Pan (160 Mm); Base type: Induction Base; Base thickness (in mm): 2.8; Included components: 4 Kitchen Set With Milk Pan; Colour: Black | Warranty: 2 Years; Included in warranty: Manufacturing defects will be covered in the warranty. Remaining things have been mentioned in the user manual; Not included in warranty: Mentioned in the manual | Durable Granite finish | Superior Non stick surface | Dishwasher safe | Metal spoon friendly | 5-layer non-stick cookware with German technology, Lid Included: Yes | Coating type: Non-Stick; No. of layers: 5 Layer; Finish: Granite Finish | Country of Origin: India.</t>
         </is>
       </c>
     </row>
@@ -2857,22 +2857,22 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Vinod Supreme Plus Non Stick Cookware Set Combo of 3 Pc | Frypan 1.6 LTR, Kadai 2.5 LTR with Common Lid &amp; 28 cm Dosa Tawa | 5 Ply Layer, 3 mm Thick | Induction and Gas Compatible | PFOA and PTFE Free</t>
+          <t>6 Pcs Pots and Pans Non Stick Cookware Combo Set Induction Ready, with Detachable Handle, Stackable Kitchen Cooking Set Removable Handles, Oven Safe, frypan Tea pan Utensils (Cream White)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61KvzLY93+L._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71Gi7O-fTbL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0B4RZVS4C</t>
+          <t>https://www.amazon.in/dp/B0GP8M15MC?th=1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟑-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐂𝐎𝐌𝐁𝐎 = Crafted as a versatile set of 3 non stick combo, this premium non stick cookware set includes a kadai, fry pan, and dosa tawa designed for daily Indian cooking with balance, control, and consistent results. | 𝐇𝐄𝐀𝐕𝐘 𝐆𝐀𝐔𝐆𝐄 𝐍𝐎𝐍-𝐒𝐓𝐈𝐂𝐊 𝐏𝐄𝐑𝐅𝐎𝐑𝐌𝐀𝐍𝐂𝐄 = Built with a 3 mm thick 5-ply aluminium layer, this non stick pan set ensures even heat distribution and reliable cooking. Enjoy smooth food release and effortless flipping that supports traditional recipes with modern ease. | 𝐒𝐀𝐅𝐄 &amp; 𝐌𝐈𝐍𝐃𝐅𝐔𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆 𝐂𝐎𝐀𝐓𝐈𝐍𝐆 = Designed using pfoa and ptfe free non stick pans technology, the coating supports low-oil cooking while preserving taste. A reassuring choice for families who value health, safety, and everyday reliability. | 𝐌𝐔𝐋𝐓𝐈-𝐏𝐔𝐑𝐏𝐎𝐒𝐄 𝐈𝐍𝐃𝐈𝐀𝐍 𝐂𝐎𝐎𝐊𝐈𝐍𝐆 𝐒𝐄𝐓 = Thoughtfully designed as a non stick set for kitchen, this combo adapts seamlessly to frying, sautéing, and simmering. From breakfast to dinner, it supports diverse Indian meals with confidence and comfort. | 𝐓𝐑𝐀𝐃𝐈𝐓𝐈𝐎𝐍𝐀𝐋 𝐃𝐎𝐒𝐀 &amp; 𝐓𝐀𝐖𝐀 𝐄𝐗𝐂𝐄𝐋𝐋𝐄𝐍𝐂𝐄 = The wide dosa pan non stick surface and base are engineered for even browning. Prepare crisp dosas, cheelas, and rotis that feel homemade, authentic, and consistently perfect. | 𝐄𝐅𝐅𝐈𝐂𝐈𝐄𝐍𝐓 𝐊𝐀𝐃𝐀𝐈 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘𝐃𝐀𝐘 𝐑𝐄𝐂𝐈𝐏𝐄𝐒 = The deep kadai non stick design allows comfortable stirring and controlled cooking. Ideal for curries, sabzis, and tadkas, it delivers dependable performance rooted in classic Indian kitchen needs. | 𝐄𝐑𝐆𝐎𝐍𝐎𝐌𝐈𝐂 𝐇𝐀𝐍𝐃𝐋𝐄𝐒 &amp; 𝐂𝐎𝐍𝐓𝐑𝐎𝐋 = Designed with sturdy, riveted handles, this pan set combo non stick offers secure grip and balance. Experience confident handling during long cooking sessions without strain or instability. | 𝐄𝐀𝐒𝐘 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 &amp; 𝐃𝐀𝐈𝐋𝐘 𝐂𝐀𝐑𝐄 = The smooth surface of this non stick cookware sets resists food buildup and cleans easily with minimal effort. Simple care keeps the cookware looking refined and performing reliably over time. | 𝐀𝐒𝐒𝐔𝐑𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘 &amp; 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 𝐒𝐔𝐏𝐏𝐎𝐑𝐓 = Built to last, this cookware set combo non stick comes with a 12 manufacturer warranty for peace of mind. A dependable companion that blends durability, performance, and trust in everyday cooking.</t>
+          <t>DETACHABLE HANDLE SYSTEM FOR FLEXIBLE COOKING – Designed for convenience and everyday kitchen efficiency, the removable handle system allows easy attachment and detachment for cooking, serving, storage, and kitchen organization. Ideal for modern cookware setups. | SPACE SAVING &amp; STACKABLE KITCHEN SOLUTION – The detachable design helps create a compact and organized kitchen experience. Perfect for apartments, small kitchens, RVs, camping, and homes where storage space matters. | STRONG LOCKING MECHANISM &amp; COMFORTABLE GRIP – Built with a secure locking design that helps provide stability during cooking and handling. The ergonomic grip offers comfort and control for daily kitchen use. | INDUCTION READY COOKWARE COMPATIBILITY – Designed to support modern cooking needs and compatible cookware systems. Suitable for everyday meal preparation while helping maintain a clean and organized cooking space. | EASY TO CLEAN &amp; STORE – The detachable configuration simplifies cleaning and helps reduce kitchen clutter. Convenient for storing cookware and kitchen accessories in cabinets, drawers, and shelves. | VERSATILE KITCHEN ESSENTIAL FOR DAILY USE – A practical cookware solution for home chefs, students, families, and travel cooking setups. Designed for convenience, durability, and efficient kitchen organization.</t>
         </is>
       </c>
     </row>
@@ -2880,22 +2880,22 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Prestige Omega Granite Aluminium Kitchen Set, 4-Pieces, Black</t>
+          <t>Vinod Di Casa Signature Ceramic Non Stick Cookware Set - 4 pcs | 24 cm Kadai and Frying Pan, 27 cm Dosa Tawa | Soft Touch Wooden Handle | Less Oil Healthy Cooking | Induction Compatible | Toxin Free</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61Q5O9edctL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61bbjGbh6dL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B01684OHYQ</t>
+          <t>https://www.amazon.in/dp/B0GGC33JCG?th=1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Material: Non-stick Aluminium; Size: Tawa Dia (280 Mm), Fry Pan Dia (240 Mm), Kadai (240 Mm), Milk Pan (160 Mm); Base type: Induction Base; Base thickness (in mm): 2.8; Included components: 4 Kitchen Set With Milk Pan; Colour: Black | Warranty: 2 Years; Included in warranty: Manufacturing defects will be covered in the warranty. Remaining things have been mentioned in the user manual; Not included in warranty: Mentioned in the manual | Durable Granite finish | Superior Non stick surface | Dishwasher safe | Metal spoon friendly | 5-layer non-stick cookware with German technology, Lid Included: Yes | Coating type: Non-Stick; No. of layers: 5 Layer; Finish: Granite Finish | Country of Origin: India.</t>
+          <t>𝐒𝐈𝐆𝐍𝐀𝐓𝐔𝐑𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 = Crafted with advanced ceramic coating, this ceramic cookware set is designed as a complete kitchen essential. It delivers smooth heat flow and dependable performance, elevating everyday Indian cooking with confidence and elegance. | 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Engineered using toxin-free ceramic layers, this ceramic non stick cookware allows food to release effortlessly with minimal oil. Enjoy healthier meals that preserve taste, texture, and tradition without compromising safety. | 𝐕𝐄𝐑𝐒𝐀𝐓𝐈𝐋𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Thoughtfully curated as a nonstick cookware set combo, it includes a ceramic kadai, frying pan, and Dosa tawa. This balanced cookware set combo supports daily sabzi, roti, dosa, and gravy cooking with ease. | 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐊𝐀𝐃𝐀𝐈 𝐅𝐎𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆 = Built for Indian kitchens, the ceramic kadai for cooking offers depth, stability, and strength. Ideal for curries, stir-fries, and tadka, it blends modern durability with classic cooking needs. | 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐏𝐀𝐍 𝐒𝐄𝐓 = This refined non stick pan set brings together functionality and form. The balanced weight and ergonomic handles make everyday cooking comfortable, supporting long hours at the stove without strain or fatigue. | 𝐄𝐀𝐒𝐘 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = The smooth ceramic surface of this non stick cookware resists staining and food buildup. Gentle hand washing keeps the shine intact, making daily maintenance effortless and preserving long-term performance. | 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐑𝐄𝐀𝐃𝐘 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Designed for modern homes, this cookware set is compatible with induction and gas stoves. The sturdy base ensures stability and efficient heating, adapting seamlessly to evolving kitchen technologies. | 𝐑𝐄𝐋𝐈𝐀𝐁𝐋𝐄 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Backed by quality assurance, this non stick cookware set combo offer reflects lasting value. With dependable construction and 1 year warranty support, this kadai set for cooking brings peace of mind to every meal.</t>
         </is>
       </c>
     </row>
@@ -2903,229 +2903,22 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6 Pcs Pots and Pans Non Stick Cookware Combo Set Induction Ready, with Detachable Handle, Stackable Kitchen Cooking Set Removable Handles, Oven Safe, frypan Tea pan Utensils (Cream White)</t>
+          <t>The Better Home Non Stick Cookware Set (Tawa - 26cm, Fry Pan - 24cm, Kadai with Lid - 24cm) | Non Stick Pan Set | Induction Cookware | Cookware Set Combo | 2.8mm Thickness (Blue)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71Gi7O-fTbL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51+f68YcPhL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GP8M15MC?th=1</t>
+          <t>https://www.amazon.in/dp/B0DS2N3XJM?th=1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>DETACHABLE HANDLE SYSTEM FOR FLEXIBLE COOKING – Designed for convenience and everyday kitchen efficiency, the removable handle system allows easy attachment and detachment for cooking, serving, storage, and kitchen organization. Ideal for modern cookware setups. | SPACE SAVING &amp; STACKABLE KITCHEN SOLUTION – The detachable design helps create a compact and organized kitchen experience. Perfect for apartments, small kitchens, RVs, camping, and homes where storage space matters. | STRONG LOCKING MECHANISM &amp; COMFORTABLE GRIP – Built with a secure locking design that helps provide stability during cooking and handling. The ergonomic grip offers comfort and control for daily kitchen use. | INDUCTION READY COOKWARE COMPATIBILITY – Designed to support modern cooking needs and compatible cookware systems. Suitable for everyday meal preparation while helping maintain a clean and organized cooking space. | EASY TO CLEAN &amp; STORE – The detachable configuration simplifies cleaning and helps reduce kitchen clutter. Convenient for storing cookware and kitchen accessories in cabinets, drawers, and shelves. | VERSATILE KITCHEN ESSENTIAL FOR DAILY USE – A practical cookware solution for home chefs, students, families, and travel cooking setups. Designed for convenience, durability, and efficient kitchen organization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Bergner Sienna Elite 6 Pcs Granite Non-Stick Cookware Set - 24cm Kadai with Lid, Casserole 24cm with Lid, Frypan 24cm, Tawa 28cm, Healthy Marble Coating, Less Oil Use, Cast Aluminium Induction Bottom</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/816IMhz4n9L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FNN15J7K?th=1</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>🔶Premium Sienna Elite Series by Bergner : Elevate your kitchen with this elegant and high-performance 6-piece non-stick cookware set designed for everyday and gourmet cooking | 🍳 Complete Cookware Set for Every Meal : Includes : 28cm Tawa, 24cm Frypan, 24cm Kadai with Glass Lid, 24cm Casserole with Glass Lid – ideal for sautéing, frying, simmering &amp; more | 💪 Durable Cast Aluminium Body : Built with heavy-gauge cast aluminum for long-lasting strength, rust resistance &amp; quicker, even heat distribution across the surface | 🌿 Healthy Marble Non-Stick Coating : Enjoy oil-free cooking with Bergner’s PFOA-free marble coating, ensuring effortless food release and healthier meals every time | 🔥 Induction &amp; Gas Stove Compatible : Features a full induction bottom, compatible with induction cooktops, gas stoves, electric and vitro-ceramic – versatile for all kitchens | 🧼 Effortless Cleaning &amp; Maintenance : Non-stick surface makes it easy to clean after use. (Note: Hand wash recommended; not dishwasher safe.) | 🖐️ Soft-Touch Handles with Strong Grip : Ergonomic, stay-cool handles provide a comfortable, secure grip while cooking, flippingor serving | 💧 Flared Rim for Drip-Free Pouring : Smartly designed rim ensures easy, mess-free pouring of liquids like curries, saucesor soups | 🎁 Perfect Gift for Home Chefs : Ideal for housewarming, anniversary, birthdayor festive gifting, this elegant cookware set is both stylish and functional | ✅ 1-Year Manufacturer Warranty : Enjoy peace of mind with Bergner’s quality assurance and dedicated customer support</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Vinod Di Casa Signature Ceramic Non Stick Cookware Set - 4 pcs | 24 cm Kadai and Frying Pan, 27 cm Dosa Tawa | Soft Touch Wooden Handle | Less Oil Healthy Cooking | Induction Compatible | Toxin Free</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61bbjGbh6dL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GGC33JCG?th=1</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>𝐒𝐈𝐆𝐍𝐀𝐓𝐔𝐑𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 = Crafted with advanced ceramic coating, this ceramic cookware set is designed as a complete kitchen essential. It delivers smooth heat flow and dependable performance, elevating everyday Indian cooking with confidence and elegance. | 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Engineered using toxin-free ceramic layers, this ceramic non stick cookware allows food to release effortlessly with minimal oil. Enjoy healthier meals that preserve taste, texture, and tradition without compromising safety. | 𝐕𝐄𝐑𝐒𝐀𝐓𝐈𝐋𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Thoughtfully curated as a nonstick cookware set combo, it includes a ceramic kadai, frying pan, and Dosa tawa. This balanced cookware set combo supports daily sabzi, roti, dosa, and gravy cooking with ease. | 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐂𝐄𝐑𝐀𝐌𝐈𝐂 𝐊𝐀𝐃𝐀𝐈 𝐅𝐎𝐑 𝐂𝐎𝐎𝐊𝐈𝐍𝐆 = Built for Indian kitchens, the ceramic kadai for cooking offers depth, stability, and strength. Ideal for curries, stir-fries, and tadka, it blends modern durability with classic cooking needs. | 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐏𝐀𝐍 𝐒𝐄𝐓 = This refined non stick pan set brings together functionality and form. The balanced weight and ergonomic handles make everyday cooking comfortable, supporting long hours at the stove without strain or fatigue. | 𝐄𝐀𝐒𝐘 𝐌𝐀𝐈𝐍𝐓𝐄𝐍𝐀𝐍𝐂𝐄 𝐍𝐎𝐍 𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = The smooth ceramic surface of this non stick cookware resists staining and food buildup. Gentle hand washing keeps the shine intact, making daily maintenance effortless and preserving long-term performance. | 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐑𝐄𝐀𝐃𝐘 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐂𝐎𝐌𝐁𝐎 = Designed for modern homes, this cookware set is compatible with induction and gas stoves. The sturdy base ensures stability and efficient heating, adapting seamlessly to evolving kitchen technologies. | 𝐑𝐄𝐋𝐈𝐀𝐁𝐋𝐄 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 = Backed by quality assurance, this non stick cookware set combo offer reflects lasting value. With dependable construction and 1 year warranty support, this kadai set for cooking brings peace of mind to every meal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Amazon Brand SOLIMO - 3 PCS Non-Stick COOKWARE SET | Aluminium</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71nriXKOrNL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B07P912X7R</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>3 piece non-stick cookware set includes fry pan, flat tawa and kadhai with a glass lid for everyday cooking | Made using good quality virgin aluminium which is durable, long lasting, and offers even heat distribution | Food grade 2-way non-stick coating: Cooking surface has a 3 layered coating; outer layer has a finish with high temperature resistance (HTR) coating | Equipped with bakelite handles that offer safe and firm ergonomic grip | Ideal for preparing rotis, chapatis, dosa, stir-fries, pulao, sauteed vegetables, sear meats, fish, fry eggs and more | Compatible with gas stove and induction cooktops | Easy to clean and maintain; dishwasher safe | Comes with a 1-year warranty against manufacturing defects | Product Dimensions- Fry Pan:- Diameter: 220 mm (22 cm); Thickness: 3 mm; Depth: 45 mm (4.5 cm); Capacity: 1650 ml; Weight: 610 gm; Tawa:- Diameter: 265 mm (26.5 cm); Thickness: 3 mm; Depth: 13 mm (1.3 cm); Weight 615 gm; Kadhai:- Diameter: 220 mm (22 cm); Thickness: 3mm; Depth: 73 mm (7.3 cm); Capacity: 2500 ml; Weight: 1125 gm | Caution: For better longevity of the cookware, avoid using Metal Scrubber for coated non-stick utensils. Do not use metal spoons and ladles on coated non-stick utensils. For better and lasting coating durability, use only soft nylon scrubber and wooden /nylon ladles &amp; spoons.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>The Better Home Non Stick Cookware Set (Tawa - 26cm, Fry Pan - 24cm, Kadai with Lid - 24cm) | Non Stick Pan Set | Induction Cookware | Cookware Set Combo | 2.8mm Thickness (Blue)</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51+f68YcPhL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DS2N3XJM?th=1</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
           <t>ENHANCED USABILITY : Effortless meal prep with easy-to-clean non-stick cookware designed for family versatility and convenience. | IDEAL FOR ALL HEAT SOURCES : Compatible with gas and induction stoves, this set meets all your cooking needs, from roti to dosa. | VERSATILE USE CASES : Perfect for home cooking or BBQs, this set boosts your culinary skills, suitable for both beginners and pros. | PERFECT CAPACITY : Includes tawa (700ml), frypan (1750ml), and kadai (2500ml) with comfortable riveted soft-touch handles. | DESIGN CONSIDERATIONS : Thoughtfully designed for ease of use and maintenance, ensuring a user-friendly cooking experience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Vinod Grandior Pro Hybrid Triply Stainless Steel Cookware Set - 4 pcs</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81mFtaFRHDL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HBCCG67L?th=1</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>EVERYDAY MEALS, ONE SET : Move from breakfast dosas to sabzi and curries with a 28 cm tawa, 22 cm frypan and 22 cm kadai. Grandior Pro brings three useful cooking shapes together, so you can choose the right vessel for each dish. | HEXA SHIELD COOKING SURFACE : Raised stainless-steel peaks sit above protected non-stick valleys in the honeycomb surface. This combination supports easier everyday food release while keeping the textured cooking surface visible. | TRIPLY SAS CONSTRUCTION : Stainless steel, aluminium and stainless steel form the three-layer cookware body. The aluminium layer helps distribute heat, bringing practical heat-spreading construction to everyday home cooking. | ONE LID, TWO VESSELS : The common stainless-steel lid fits the 22 cm kadai and 22 cm frypan, giving you a covered-cooking option for either vessel. One lid is included, so the two vessels cannot both be covered at the same time. | BREAKFAST TO MAIN COURSE : Use the 28 cm, 4 mm thick dosa tawa for dosas, uttapam and chilla; choose the kadai for curries and sabzi, or the frypan for sauteing and shallow frying. The 4 mm thickness refers to the tawa only. | FITS YOUR COOKTOP ROUTINE : The set is compatible with gas, induction, electric, ceramic and halogen cooktops. Choose the vessel that suits your dish and cooking zone; the set brings matching cookware to different kitchen setups. | CLEANING MADE PRACTICAL : The three cookware vessels are dishwasher safe, giving you a cleaning option after everyday meals. Follow Vinod's product-specific care guidance when choosing utensils, heat settings and cleaning products. | KNOW EXACTLY WHAT IS INCLUDED : Receive a 22 cm kadai with 2.3 L capacity, a 22 cm frypan with 1.5 L capacity, a 28 cm dosa tawa and one common stainless-steel lid. This is three cookware vessels plus one lid, not four vessels. | 5-YEAR WARRANTY : Enjoy added peace of mind with the Vinod Grandior Pro cookware set, backed by a 60-month warranty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Amazon Basics Aluminum Non-Stick 15 Piece Cookware Set | 2-Way 3 Layer Non-Stick Coating | PFOA Free | High Temperature Resistant Exterior Coating, Black</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71oZ1-QYomL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0B8D6GW8S?th=1</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Make cooking a joyful process with this durable non-stick 15-piece cookware set | The pressed aluminium cookware body is ultra-conductive and corrosion-free, which enables quick heating and helps save energy | Stay-cool phenolic handles are heat-resistant and remain cool even at high cooking temperatures | USFDA and European Food Safety Authority (EFSA)-approved coatings are 100% free from PFOA, lead, cadmium, nickel, and arsenic | The 2-layered exterior coating makes it scratch-resistant; the 3-layered interior with water-based eco-friendly PFOA-free coating promotes healthy cooking</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set Detachable Handle |Granite Finish | Induction Base | Pfoa Free | High Temperature Resistant Exterior Coating | Black</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61WLcHiMuDL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BZW3SG7G</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Kadai, 1 Glass Lid</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Hawkins Quik Nonstick Induction 4 Piece Cookware Set of Deep Kadhai, Frying Pan, Saucepan and Stainless Steel Lid | Kitchen Gift Pack | Grey (IQGP1)</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71Ujg8yco+L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GD5QFJ19</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Healthy PFOA-free Nonstick inside - Healthy low oil cooking | Durable ceramic coating outside - stays looking new | 3mm Thick Pans - Food will not burn or stick | Rivet-less cooking surface - easy to stir, easy to clean | Deep shape - Stir-fry, High-walls. Cook large quantities</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Kreme Ceracook Ceramic Coated, Granite 13 Pc Cookware Set 2X Spatulas, ISI Certified Cookware Set, Forged, Gas &amp; Induction Use, Non Toxic PFAS &amp; PTFE Free, 1 Year Warranty, Olive Green</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71H++Fa6u8L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GY8HNHR3?th=1</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>100% HEALTHY COOKING: Made from healthy ceramic coating, which is free from PFAS, PFOA, leads and chemicals. it ensures worry-free cooking and is sizzle-ready for hassle-free use. | MADE IN INDIA – MADE FOR INDIA: This cookware has designed and developed in India to cater to Indian cooking needs. | SUPERIOR QUALITY AND DESIGN: Our chef-grade Cookware is specially crafted for style, durability, and functionality. It features toxin free ceramic coating and a toughened glass lid. Ergonomic Bakelite Handles provide a soft-touch, cool and heat-proof grip. | VERSATILE &amp; QUICK COOKING: This induction cookware is also designed for effortless cooking gas stoves and heaters. Its 3mm thick aluminium body ensures uniform heat distribution for fast and evenly cooked meals, every time. | STAIN-FREE &amp; EASY CLEANING: Maintenance just got simpler and more efficient with this cooking utensil. It features a stain-free interior that requires 50% less water for cleaning. | INCLUDED COMPONENT: Kadhai 24cm with Glass Lid, Kadhai 26cm with Glass Lid, Fry Pan 24cm, Casserole 24cm with Glass Lid, Casserole 26cm, Sauce Pan 16cm with Glass Lid and 2 Silicone Spoons. | 1-YEAR WARRANTY: Enjoy your culinary journey with our one-year warranty. We proudly present you with the exceptional quality of our Kréme Ceracook Ceramic Cookware, for your complete satisfaction.</t>
         </is>
       </c>
     </row>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2922,6 +2922,386 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Lavie Ushawu Small Satchel Bag</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/91+bYunDJuL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B3JBV7Y5</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Mochi Women Shoulder Bag</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51RMrnSZbHL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BS6Y8WC4?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Lavie Women's Quilt Eden Flap Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61zxfXGJ-zL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C77HTZS9?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Women's Handmade Macrame Crossbody Sling Bag Tote Bags Beautiful &amp; Fancy Ladies Purse For Girls Women's Mobile Pouch Friends Gifts Birthday Marriage Party and Events,1- Piece</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/715mDmSA1vL._SX695_.jpg</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HDDF7G1D?th=1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Lavie Women's Omnia Medium Satchel Bag | Ladies Purse Handbag</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81LpcMxUMwL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B096KSN29Z?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Lavie Woman's Broxa Flap Crossbody Sling Bag | Ladies Purse Handbag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61L+2HeKv-S._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08QTF8RPM?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Caprese TRACY S Large</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61OGd5IBEiL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08ZJZTCHR?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Lavie Women's Ficus Medium Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71k9FI0t6aS._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08NVF9V9L?th=1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Lavie Women's Beech Flap Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61TeUD4zUTL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F18HV94Q?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ROSS BROWN PU Synthetic Leather Women's Mini Satchel Bag | Ladies Purse Handbag- Mini</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81Fih1Bai-L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C97H56RF?th=1</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Lavie Women's Yalta Satchel Bag | Ladies Purse Handbag</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71EwockPQkL._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B097MXFVYL?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>WOMEN MARKS® Structured Handbag Design for Girls/Women with Detachable and Adjustable Shoulder Strap</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71TWQ6rCM+L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GTMPMXWN?th=1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Lavie Women's Faroe Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women | Rakhi Gift for Sister</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/91qQhj-qEmL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B097MWTSQV?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ZOUK Printed Women's Jute Handcrafted Vegan Leather Everyday Tote</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61CGkDInV5L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C7VMFVDC?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Mochi Women Synthetic Slingbag (66-7355)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71s0Fm-KprL._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09W1C1LTL?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ADISA Women's Girls Large Bucket Crossbody Sling Bag - Stylish Handbag for Woman with Adjustable Belt</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51uCFgyZOFL._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D7739W64?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ZOUK Harmony Sling Bag | Crossbody Bags for Women | Women's Handbags | Stylish | Vegan Leather Evening Bag | Travel &amp; Office Use | Purse and Wallet</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81BqH5RU59L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D6GSJ4NW?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Martucci Women’s Quilted Satchel Handbag – Elegant Faux Leather Top-Handle Purse with Gold-Tone Metal Handles and Adjustable Crossbody Strap</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71yZZtohJYL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G449CJ8Q?th=1</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ZOUK Jute Handcrafted Vegan Leather Women's Shoulder Luna Handbags</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71pfJ+iG53L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CL9NZF65?th=1</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ZOUK Stylish Office Laptop Bag | Tote Bag For Women Fits Upto 15.6 inch |Purse for Women | Vegan Leather Handbag | Daily &amp; Travel Use</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/815GRnV4NsL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09L79TM6D?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2964,17 +2964,17 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Lavie Women's Quilt Eden Flap Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women</t>
+          <t>Women's Handmade Macrame Crossbody Sling Bag Tote Bags Beautiful &amp; Fancy Ladies Purse For Girls Women's Mobile Pouch Friends Gifts Birthday Marriage Party and Events,1- Piece</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61zxfXGJ-zL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/715mDmSA1vL._SX695_.jpg</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0C77HTZS9?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0HDDF7G1D?th=1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -2983,17 +2983,17 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Women's Handmade Macrame Crossbody Sling Bag Tote Bags Beautiful &amp; Fancy Ladies Purse For Girls Women's Mobile Pouch Friends Gifts Birthday Marriage Party and Events,1- Piece</t>
+          <t>Lavie Women's Beech Flap Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/715mDmSA1vL._SX695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61TeUD4zUTL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0HDDF7G1D?th=1</t>
+          <t>https://www.amazon.in/dp/B0F18HV94Q?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3002,17 +3002,17 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lavie Women's Omnia Medium Satchel Bag | Ladies Purse Handbag</t>
+          <t>ROSS BROWN PU Synthetic Leather Women's Mini Satchel Bag | Ladies Purse Handbag- Mini</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81LpcMxUMwL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81Fih1Bai-L._SY695_.jpg</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B096KSN29Z?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0C97H56RF?th=1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3021,17 +3021,17 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lavie Woman's Broxa Flap Crossbody Sling Bag | Ladies Purse Handbag | Gift for Women</t>
+          <t>Lavie Women's Faroe Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women | Rakhi Gift for Sister</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61L+2HeKv-S._SY575_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/91qQhj-qEmL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B08QTF8RPM?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B097MWTSQV?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3040,17 +3040,17 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Caprese TRACY S Large</t>
+          <t>ZOUK Printed Women's Jute Handcrafted Vegan Leather Everyday Tote</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61OGd5IBEiL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61CGkDInV5L._SY695_.jpg</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B08ZJZTCHR?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0C7VMFVDC?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3059,17 +3059,17 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Lavie Women's Ficus Medium Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women</t>
+          <t>ADISA Women's Girls Large Bucket Crossbody Sling Bag - Stylish Handbag for Woman with Adjustable Belt</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71k9FI0t6aS._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51uCFgyZOFL._SY575_.jpg</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B08NVF9V9L?th=1</t>
+          <t>https://www.amazon.in/dp/B0D7739W64?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3078,17 +3078,17 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lavie Women's Beech Flap Satchel Bag | Satchel Handbag for Work | Ladies Purse | Stylish Shoulder Bag | Gift for Women</t>
+          <t>ZOUK Jute Handcrafted Vegan Leather Women's Shoulder Luna Handbags</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61TeUD4zUTL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71pfJ+iG53L._SY695_.jpg</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0F18HV94Q?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0CL9NZF65?th=1</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3097,210 +3097,20 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ROSS BROWN PU Synthetic Leather Women's Mini Satchel Bag | Ladies Purse Handbag- Mini</t>
+          <t>ZOUK Stylish Office Laptop Bag | Tote Bag For Women Fits Upto 15.6 inch |Purse for Women | Vegan Leather Handbag | Daily &amp; Travel Use</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81Fih1Bai-L._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/815GRnV4NsL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0C97H56RF?th=1</t>
+          <t>https://www.amazon.in/dp/B09L79TM6D?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Lavie Women's Yalta Satchel Bag | Ladies Purse Handbag</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71EwockPQkL._SY575_.jpg</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B097MXFVYL?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>WOMEN MARKS® Structured Handbag Design for Girls/Women with Detachable and Adjustable Shoulder Strap</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71TWQ6rCM+L._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GTMPMXWN?th=1</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr"/>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Lavie Women's Faroe Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women | Rakhi Gift for Sister</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/91qQhj-qEmL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B097MWTSQV?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>ZOUK Printed Women's Jute Handcrafted Vegan Leather Everyday Tote</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61CGkDInV5L._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0C7VMFVDC?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Mochi Women Synthetic Slingbag (66-7355)</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71s0Fm-KprL._SY575_.jpg</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09W1C1LTL?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr"/>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>ADISA Women's Girls Large Bucket Crossbody Sling Bag - Stylish Handbag for Woman with Adjustable Belt</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51uCFgyZOFL._SY575_.jpg</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D7739W64?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>ZOUK Harmony Sling Bag | Crossbody Bags for Women | Women's Handbags | Stylish | Vegan Leather Evening Bag | Travel &amp; Office Use | Purse and Wallet</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81BqH5RU59L._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D6GSJ4NW?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Martucci Women’s Quilted Satchel Handbag – Elegant Faux Leather Top-Handle Purse with Gold-Tone Metal Handles and Adjustable Crossbody Strap</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71yZZtohJYL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G449CJ8Q?th=1</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>ZOUK Jute Handcrafted Vegan Leather Women's Shoulder Luna Handbags</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71pfJ+iG53L._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CL9NZF65?th=1</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>ZOUK Stylish Office Laptop Bag | Tote Bag For Women Fits Upto 15.6 inch |Purse for Women | Vegan Leather Handbag | Daily &amp; Travel Use</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/815GRnV4NsL._SY695_.jpg</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09L79TM6D?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3112,6 +3112,466 @@
       </c>
       <c r="E120" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>12FOR COLLECTION Stainless Steel 2 Tier Countertop Kitchen Rack|Pantry Storage Organizer | Multipurpose Storage Organizer | Kitchen Racks | Kitchen Organizer | Kitchen Accessories Rack, Tiered Shelf</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61TGmD48a3L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZ7TB3R8</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>So It Is Easy To Hold Various Bottles, Cans, Jars, Etc. The 2-Tier Design Of This Spice Rack Shelf Is Aimed At Saving Your Space But Holding More Items. | 🗹 This dish rack is suitable for placing in the kitchen, dining table, pantry and any other room of the house. Perfect for storing spices, condiments, grains, or home items such as lotions, cleansers, soaps, shampoo, and more. | 🗹 This dish rack is suitable for placing in the kitchen, dining table, pantry and any other room of the house. Perfect for storing spices, condiments, grains, or home items such as lotions, cleansers, soaps, shampoo, and more. | This Shelf Holder Is Made Of Full Stainless Steel Frame With Chrome Plating, Ensuring Its Sturdiness And Durability. Therefore, This Cabinet Spice Rack Won't Tip Over Easily When You Use It.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2-Tier Stainless Steel Kitchen Storage Spice Rack, Container Organizer Counter top Stand Multipurpose Masala Stand for Kitchen Space Saver Rack (NHSP, Tiered Shelf), Silver</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71xcENEGMyL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CH6M5MXX</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>✅ Durable Stainless Steel Build – Strong, rust-resistant kitchen rack designed for long-lasting use. | ✅ 2-Tier Space-Saving Design – Ideal kitchen organizer rack that maximizes storage in compact kitchens. | ✅ Multipurpose Kitchen Stand – Use as a stand for kitchen storage rack for masala jars, spices, bottles, and containers. | ✅ Organized Kitchen Storage – Perfect kitchen stand organiser for countertops, shelves, or inside a kitchen storage cabinet. | ✅ Sleek &amp; Modern Look – Stylish kitchen rack stand that keeps your cooking essentials neat and accessible. | ✅ Versatile Use – Works as kitchen racks for storage, spice rack, or racks for storage of everyday kitchen items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Stainless Steel Kitchen Dish Rack Expandable Storage Shelves, Multipurpose Organizer Extend Up to 580 mm with Anti-Rust Nano Coating (Pack of 4) (NHSP), Countertop, Floating Shelves</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61rmL5QqxSL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CLVJDS6F?th=1</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>This Stainless Steel Shelf Can Be Of Best Use For Making Partitions Or Dividing The Space To Keep Maximum Products. This One-Piece Will Satisfy All Your Basic Needs For Purchasing Different Products For Separate Uses. | The Best Bathroom/Kitchen Accessories Which Is Totally Rust-Proof And Corrosion-Free Because Of Additional Layers Of Nickel-Chrome Mirror Finishing. We Recommend Using Wet &amp; Dry Clothes For Cleaning The Product Periodically To Maintain Its Shine And Keep It Durable. | This Rack Comes With Anti-Skid Rubber Fittings In Its Legs, Ensuring That Your Floor Stays Scratch-Free And Prevents The Rack From Slipping. You Can Start Using This Rack/Shelf As Soon As Your Receive The Product. It Can Be Placed On Kitchen/Bathroom/Cabinet/Office Floor/Platform. | It Has Simply The Best Design As It Has Spaces Between The Wires To Keep The Stored Products Ventilated. It Can Easily Store Products Above And Below The Stand. This Allows Users To Make Partitions And Get The Best Out Of Small Places In An Organized Way. | :-Smart Storage: Use Anywhere You Need To Keep Food, Pantry And Kitchen Items Organized; Perfect For Organizing Pasta, Packets, Extra Supplies Of Salt, Dressing And Vinegar, Macaroni And Cheese Boxes, Baking Supplies, Condiments And More; These Bins Also Work In Any Room Of Your Home!</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>4 Layer Multipurpose Storage Rack with Wheel, Plastic Kitchen Organizer Trolley, Bathroom, Living Room &amp; Home Storage Shelf, Space Saving Utility Stand</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61PGmlLrO3L._SY879_.jpg</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HL3CCQRN?th=1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>VERSATILE DESIGN: 4-tier rolling cart with mesh sides perfect for organizing and storing items in any room, featuring a modern black finish | MOBILE SOLUTION: Smooth-rolling casters allow easy movement between rooms, making it ideal for home, office, or craft room use | STURDY CONSTRUCTION: Durable metal frame with mesh side panels provides stability and ventilation while keeping items secure | SPACE-SAVING: Compact vertical design maximises storage in minimal floor space, with three spacious tiers for efficient organisation | PRACTICAL DIMENSIONS: Each tier offers ample storage space with mesh sides for visibility and easy access to stored items</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Kitchen Organizer Rack, Spice Rack Organizer, Kitchen Racks for Storage, Kitchen Stand Organiser for Spices, Masala Jars &amp; Bottles, Steel Countertop Rack</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81ECGsIEEqL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GTFQFYRP</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐎𝐑𝐆𝐀𝐍𝐈𝐙𝐄𝐑 𝐑𝐀𝐂𝐊 𝐅𝐎𝐑 𝐒𝐌𝐀𝐑𝐓 𝐒𝐓𝐎𝐑𝐀𝐆𝐄 - Keep your kitchen neat and organized with this practical kitchen organizer rack designed for everyday kitchen storage. Ideal for arranging spices, masala containers, bottles, jars and other kitchen accessories while making better use of available counter space. | 𝐒𝐏𝐈𝐂𝐄 𝐑𝐀𝐂𝐊 𝐎𝐑𝐆𝐀𝐍𝐈𝐙𝐄𝐑 𝐅𝐎𝐑 𝐃𝐀𝐈𝐋𝐘 𝐄𝐒𝐒𝐄𝐍𝐓𝐈𝐀𝐋𝐒 - Use it as a convenient spice rack organizer to keep frequently used masala boxes, spice jars, seasoning containers and kitchen essentials easily accessible. A useful spice rack for kitchen counters, shelves and cabinets. | 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐑𝐀𝐂𝐊𝐒 𝐅𝐎𝐑 𝐒𝐓𝐎𝐑𝐀𝐆𝐄 &amp; 𝐎𝐑𝐆𝐀𝐍𝐈𝐙𝐀𝐓𝐈𝐎𝐍 - Designed as a versatile kitchen storage organizer, this rack helps organize spices, jars, oil bottles and other everyday items. Suitable for homes that need compact kitchen racks for storage, kitchen shelves and countertop organization. | 𝐌𝐔𝐋𝐓𝐈𝐏𝐔𝐑𝐏𝐎𝐒𝐄 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐒𝐓𝐀𝐍𝐃 𝐎𝐑𝐆𝐀𝐍𝐈𝐒𝐄𝐑 - This kitchen stand organiser can be used for organizing masala containers, spice jars, cooking essentials and other household items. Use it as a masala organizer rack, kitchen stand or storage rack according to your daily needs. | 𝐂𝐎𝐌𝐏𝐀𝐂𝐓 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐒𝐓𝐎𝐑𝐀𝐆𝐄 𝐒𝐎𝐋𝐔𝐓𝐈𝐎𝐍 -A practical kitchen organizer for keeping your countertop, kitchen shelf or cabinet more व्यवस्थित. Suitable for use as a masala rack, spice rack, kitchen stand and storage organizer, making everyday kitchen items easier to find and access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>3 Tier Kitchen Wall Mounted Rack, Stainless Steel Wall Organizer for Spice Boxes, Masala Containers, Jars &amp; Utensils, Storage Shelf Stand for Home</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81N5kiBtx+L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HHFRS7FF</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>𝟑 𝐓𝐈𝐄𝐑 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐒𝐓𝐎𝐑𝐀𝐆𝐄: This kitchen racks 3 tier design provides separate storage levels for spice boxes, masala containers, jars, bottles and everyday kitchen essentials, helping keep items organised and easy to access. | 𝐖𝐀𝐋𝐋 𝐌𝐎𝐔𝐍𝐓𝐄𝐃 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐎𝐑𝐆𝐀𝐍𝐈𝐙𝐄𝐑 𝐑𝐀𝐂𝐊: Make better use of unused vertical space with this wall mounted kitchen organizer rack. The kitchen wall mounted rack design helps reduce countertop clutter and creates practical everyday storage. | 𝐌𝐔𝐋𝐓𝐈𝐏𝐔𝐑𝐏𝐎𝐒𝐄 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐖𝐀𝐋𝐋 𝐒𝐇𝐄𝐋𝐅: Use this kitchen wall mounted shelf as a spice rack, masala rack, jar holder or utensil storage solution. The open design keeps frequently used items visible and within easy reach. | 𝐏𝐑𝐀𝐂𝐓𝐈𝐂𝐀𝐋 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐒𝐓𝐎𝐑𝐀𝐆𝐄 𝐑𝐀𝐂𝐊 𝐎𝐑𝐆𝐀𝐍𝐈𝐒𝐄𝐑: Designed for everyday organisation, this wall mounted kitchen storage rack helps arrange different kitchen essentials in one dedicated storage area while saving valuable counter space. | 𝐂𝐇𝐄𝐂𝐊 𝐒𝐈𝐙𝐄 𝐁𝐄𝐅𝐎𝐑𝐄 𝐏𝐔𝐑𝐂𝐇𝐀𝐒𝐄: Please check the product dimensions and available installation space before ordering. This kitchen wall rack is intended to provide organised vertical storage for your selected kitchen area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Amazon Basics Multi-Purpose Large Organizer | Modular Storage Box for Clothes, Kitchen, Bedroom &amp; Living Room | Stackable Rack, Space-Saving Wardrobe Cabinet (Off White), 4 Piece, 37.5LX44.7WX27H cm</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/910+4jHnLQL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FXXVN5V3?th=1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>BUILT WITH ULTRA-STURDY PLASTIC: Crafted from high-strength PPCP plastic to withstand daily wear, ensuring long-lasting use. SAFE PACKAGING: Packaged with care to prevent damage during transit, so your Chester arrives in pristine condition. | LAB TESTED DURABILITY: Tested by an internationally accredited lab, Chester’s resilience meets global quality standards. | COLLAPSIBLE &amp; PORTABLE: Chester's collapsible design makes it easy to dismantle, store, or relocate as needed. | SECURE MAGNETIC DOOR LOCK: Protect items from dust and keeps contents securely in place preventing them from shifting or falling out. | VERSATILE &amp; ADAPTABLE DESIGN: Perfect for organizing toys, clothes, books, and more—Chester fits seamlessly in the kitchen, living room, bathroom, or garden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>TEX-RO Plastic Storage Rack for Bedroom/Shelf for Bedroom/Bathroom Storage Rack/Trolley for Kitchen Storage/Multipurpose Storage Rack (Black, 2 Layer)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/7182sHilcZL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FRZF7RVS?th=1</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Easy Mobility – This plastic kitchen rack with wheel moves smoothly, making it easy to shift between kitchen, dining, or storage areas without any hassle. | Multipurpose Use – This bathroom organiser stand and storage shelf is perfect for keeping your essentials tidy, works great as room organizer items for bedroom, and can also be used as a versatile room organiser for clutter-free living. | Durable &amp; Strong Build – Made from high-quality plastic, this storage rack is sturdy, long-lasting, and designed to handle daily household use. | Multipurpose Storage – Use it as a kitchen organizer, bathroom storage shelf, or room organizer – perfect for vegetables, groceries, toiletries, or household items. | Space-Saving Design – The slim and compact structure helps maximize storage in small spaces, keeping your home neat and organized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SAFAK 3 Tier Wooden Kitchen Organizer Rack for Countertop | Wooden Spice Rack Stand for Kitchen Counter | Kitchen Shelf Organizer &amp; Cabinet Shelf Riser | Decorative Masala Rack Storage Stand | Dark</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71swzxPftnL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GRVMYVQH?th=1</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>A wooden kitchen organizer is essential for any kitchen since it is both stylish and practical. The purpose of these organizers is to improve the efficiency and organization of your kitchen. To accommodate different storage needs, they are available in a range of sizes and forms. | Jars, cans, bottles, sugar, tea, spices, sauces, and other kitchen supplies can all be stored in these useful step organizers. Additionally, they are a great method to store things for your pooja room. | Because it doesn't require any additional building or equipment, this freestanding organizer is easy to use. | Because it makes room in cramped cabinets and pantries, this three-tiered organizer is a great tool for kitchen and pantry organization. | When necessary, a moist towel can be used to clean the step shelf organizer's nonslip shelf lining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Organizer Tray Office Drawer Dividers Storage Bins Multipurpose Desk for Makeup, Kitchen, Office, Bathroom, Bedroom Dreassing, Basket Rack MultiColor(23*8*5 CM) Pack Of 6 (Multi 6pcs)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71UDWR9wrBL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CR374476</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Combo of 6pcs multipurpose storage baskets set which is useful for one's daily activity. | Color : Available in assorted colors, Color will be shipped as pe availability, Material : Plastic | Portable, light weight stack-able. Can be kept in drawers, almirahs, kitchen cabinets, refrigerator, shelves etc. | The desk drawer organizer trays can be used for desk, drawers, kitchen, office and living room as well as for other applications. help you to create your own mix and match organizational system to fit in any drawers, cabinets, lockers and wardrobe closets</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>FireBees 2 Tier Kitchen Counter Organizer, Wooden Kitchen Organizer Rack for Spices &amp; Storage, Kitchen Shelf Organiser Stand, Masala Organizer Rack, Aesthetic Kitchen Organizer Items 33 x 16 x 25 cm</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/518T84qOyML._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GW9H1KC7</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Smart Kitchen Organization Solution - Upgrade your space with this versatile kitchen organizer designed to store spices, jars, and daily essentials neatly. Perfect for anyone looking for efficient kitchen organizers and storage. | Premium Wooden Design - Built with a sturdy frame, this wooden kitchen organizer rack adds a modern and aesthetic touch to your countertop while ensuring durability and long-term use. | Multi-Purpose Organizer Rack - Use it as a spice rack, masala organizer rack, or container organiser rack—ideal for kitchen, bathroom, or pantry storage. | Space-Saving 2 Tier Design - The compact 2 tier kitchen counter organiser maximizes vertical space, making it perfect for small kitchens or limited countertops. | Aesthetic &amp; Functional - This stylish kitchen stand wooden design blends beautifully with modern homes, making it one of the best aesthetic kitchen items for organized living. | Two-tier countertop organizer — Ideal for storing spices, condiments, oils, small jars, and kitchen accessories while keeping counters neat and accessible. | Dimensions — Compact tabletop design with two storage levels; suitable for kitchen counters, coffee stations, bathrooms, or pantry shelves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>GOLWYN Air Tight Containers For Kitchen Storage Set, Bpa Container For Kitchen Storage Set, Kitchen Organizer And Kitchen Accessories Items Storage for Home (1100 Ml Set Of 8)(Plastic)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71auAIxh1PL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B2SBK18B?th=1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Airtight kitchen storage containers set Keep Food Fresh----The lids with silicone gasket make these storage containers airtight, and the top flips open easily. Airtight storage system will always keep your food dry and fresh. All have the same lids make it easy to wash dry and reuse with ease. We can also use for spice containers for kitchen storage . Perfect ! plastic containers for kitchen storage . | Package Content: 8Pcs Container Jar Set With Cap | Material: Premium Quality Plastic | Airtight / 100% Leak Proof. | Capacity: 1100 ml | Color: transparent | BPA Free and Food Grade Material Plastic Boxes For Storage ---- pantry storage containers for kitchen airtight are made of durable plastic, BPA free, which have a longer life than many other brands plastic containers. Clear containers make it convenient to see what’s inside, you can easily get what you want without opening every container. Space saving storage box for kitchen .</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Cri8Hub Stainless Steel 2 Tiered Shelf Kitchen Rack - Spice Boxes Organizer –Kitchen Rack Stand - Cosmetic Organizer – Counter Top Organiser - Floor Mounted Shelf For Home(Multipurpose Rack)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71A5JJpZuDL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CV8348ZZ</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>:-STRONG AND DURABLE: Solid steel spice jar kitchen racks come with a hardwearing anti-rust coating. The stands have double support rods to provide each shelf with extra stability. | :-MULTIPLE USES: The uses of this dish rack kitchen organizer are truly endless. It can easily be used in a kitchen pantry, bathroom, or office to save space and organize a variety of items- from dishes to supplies, towels, and more. | :-ANTI-SKID FITTINGS: This storage shelf rack for the kitchen comes with Anti-skid fittings in its legs which ensures that your floor stays scratch-free and it prevents the utensils stand from slipping. | :-2 STURDY LEVELS: The kitchen shelf holder insert can hold numerous items on 2 sturdy levels. Keep your bowls, plates, or food neatly organized in your kitchen. | :- EASY CLEANING: This kitchen rack organizer is designed with easy clean properties and can be wiped clean with a soft cloth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Cri8Hub Heavy Duty Metal Stand 3-Tier Standing Rack for Home, Bathroom Countertop Storage Shelf, Cosmetic Organizer Holder Kitchen Spice Rack, (Black)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/519RVYDzpEL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F6NBFHX3</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>VERSATILE STORAGE: Three-tier standing rack perfect for organising spices, condiments, and toiletries in both kitchen and bathroom settings | DURABLE CONSTRUCTION: Sturdy black metal frame with raised edges on each shelf to prevent items from falling off | SPACE-SAVING DESIGN: Compact footprint whilst providing ample storage space across three levels for maximum organisation. Space-saving bathroom solution - Our shampoo holder for bathroom maximizes your space by organizing your bottles efficiently, allowing you to keep your bathroom neat and tidy without sacrificing convenience. | EASY ACCESS: Open shelf design allows quick visibility and access to all stored items, making cooking and daily routines more efficient | DIMENSIONS: Each shelf measures approximately 30 cm in length, 15 cm in width, with 15 cm spacing between tiers for accommodating various container sizes | Easy Use : Helps maintain a clean and clutter- free environment. Built with durable materials to ensure long lasting use. Holds a significant amount of weight without compromising stability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Kitchen Organizer Rack – Multi-Purpose Kitchen Stand for Countertop &amp; Cabinet Storage | Heavy-Duty Kitchen Rack Organizer for Spices, Utensils, Dishes &amp; Pantry Items (2 Tier Brown)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71+m2EQr+JL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GHZN2Y8C?th=1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>✔ MULTI-PURPOSE KITCHEN ORGANIZER Keep your kitchen neat and clutter-free. Perfect for organizing spices, jars, utensils, plates, bowls, cleaning supplies, and pantry essentials. | ✔ STRONG &amp; STABLE DESIGN Made from durable, heavy-duty material for long-lasting use. Sturdy construction ensures stability even when fully loaded. | ✔ SPACE-SAVING KITCHEN STAND Maximize countertop, cabinet, or pantry space. Ideal for small kitchens, apartments, and modern homes. | ✔ EASY TO ASSEMBLE &amp; CLEAN Quick and simple installation with minimal tools required. Smooth surface makes cleaning fast and hassle-free. | ✔ MODERN &amp; ELEGANT LOOK Sleek design complements any kitchen décor — perfect for countertops, cabinets, shelves, or under-sink storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>12FOR COLLECTION Stainless Steel 3-Tier Countertop Storage Rack For Corners, Multipurpose Kitchen Plate Dish Corner Shelf, Rack Stand Holder</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61eX3uIvTwL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09MYH9QC1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Stainless Steel, Color :- Silver :-Coated with multi-layer chrome plating that is tested to ensure a rust free life of the product. | Boost your kitchen cupboard storage quickly and easily with this three-tier corner plate rack. It maximises the vertical space in any cupboard, counter or under sink area with a large surface area suitable for plates of all sizes and other kitchen essentials. Crafted from robust stainless steel with a sleek chrome finish. It is 100% rust free! | Stainless Steel Multipurpose Kitchen Plate Dish Corner 3-Tier Storage Rack Holder for Kitchen Stand Shelves Kitchen Tray Pan Pot Utensils Chakla Belan Storage Cupboard Organizer for Home Stainless Steel Multipurpose Kitchen Plate Dish Corner 3-Tier Storage Rack Holder for Kitchen Stand Shelves Kitchen Tray Pan Pot Utensils Chakla Belan Storage Cupboard Organizer for Home | STRONG AND STURDY: It is highly strong and sturdy! Can accomodate weights of stainless steels plates and dishes very easily and other steel or other metal utensils! MATERIAL: Made up of high quality stainless steel with a beautiful chrome finish! It is 100% rust free! | MATERIAL: Made up of high quality stainless steel with a beautiful chrome finish! It is 100% rust free!</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>DALUCI Set of 2 Metal Bathroom Corner Shelf Rack | No Drilling Self Adhesive Wall Mounted Storage Organizer for Bathroom &amp; Kitchen | Rustproof Bathroom Shelves (8 &amp; 9 INCH, Black)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81VF4kpZlwL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G4RNDJF6?th=1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>No Drilling Bathroom Organizer Without Drill – Easy self adhesive installation with no tools or wall damage. Ideal metal bathroom corner shelf for rented homes and modern bathrooms. | Rustproof Heavy Duty Metal Bathroom Shelf – Premium coated metal construction designed for wet bathroom environments. Strong load-bearing wall mounted bathroom shelves. | Perfect Corner Storage (8 &amp; 9 Inch Shelves) – Smart corner design saves space while organizing shampoo bottles, soap, face wash, and daily bathroom accessories. | Bathroom &amp; Kitchen Storage Organizer – Can also be used as kitchen corner shelf for spices, cleaning items, or utility storage. | Pack of 2 Self Adhesive Bathroom Shelves – Includes 2 premium metal corner shelves with 4 strong adhesive mounting. Ideal bathroom accessories set for organized, clutter-free storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Shoper cart kitchen organizer rack, 2-Tier Spice Rack Organiser, Rustic Brown and Black, 30cm x 15.7cm x 26.4cm, Kitchen Counter Storage Shelf with Metal Frame</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61L6KxA55UL.jpg</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GKG8H377</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>COMPACT DESIGN: This 2-tier spice rack organiser measures 30cm x 15.7cm x 26.4cm, providing efficient vertical storage for your kitchen counter without taking up excessive space | STURDY CONSTRUCTION: Features a durable metal frame with rustic brown wooden shelves that combine industrial style with practical functionality for organising spices, condiments, and pantry essentials | VERSATILE STORAGE: Two spacious tiers accommodate various sized containers including spice jars, bottles, cans, and small kitchen items, helping keep your countertop neat and organised | STYLISH APPEARANCE: The rustic brown and black colour combination with X-shaped side supports adds a modern farmhouse aesthetic that complements various kitchen décor styles | MULTI-PURPOSE USE: Ideal for kitchen counters, pantries, cupboards, or bathroom storage, this rack organiser maximises space whilst keeping frequently used items within easy reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Stainless Steel 2-Tier Wall Mounted Storage Basket Rack, Chrome Finish,Kitchen and Bathroom Stainless Steel 2 Container Wall Mount Organizer For Kitchen Storage/Hanging Shelves/Rack (Double Self)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71eiZT4qCiL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H276M39L</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2-TIER DESIGN: Features two spacious basket tiers, allowing you to organise and store a wide range of items in your kitchen or bathroom efficiently. | STURDY CONSTRUCTION: Made from high-quality stainless steel with a polished chrome finish, ensuring long-lasting durability and resistance to rust and corrosion. | WALL MOUNTED: Designed for wall mounting with built-in brackets, keeping your countertops clutter-free and making the most of your vertical wall space. | VERSATILE STORAGE: Ideal for storing shampoos, conditioners, soaps, spices, and other daily essentials, making it suitable for both kitchen and bathroom use. | DIMENSIONS: Measures 31 cm (length) x 16 cm (width) x 33 cm (height), providing ample storage space while maintaining a compact and neat profile on your wall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TEX-RO Big Storage Box and Organiser | Storage &amp; Organizers | Organizer Storage Box for Kitchen, Clothes | Durable Storage Basket With Lid &amp; Plastic Basket for Storage (Pack of 3, multicolor)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81WyHjKqOqL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FDGS43Z7?th=1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Keep your home neat and organized with this plastic storage box and organiser plastic , perfect for every corner of your house. These storage boxes are ideal boxes for storage of clothes, toys, and household items. Each storage box with lid keeps your essentials easy to stack. Use this basket for clothes storage to arrange your wardrobe or laundry space efficiently. Made from high-quality plastic storage material, this plastic storage box for wardrobe ensures long-lasting durability and style for your home kitchen basket with lid. | Our product is perfect for multiple uses — whether you need large storage containers to organize your home, baskets for storage for daily essentials, organisers for kitchen storage to keep groceries neat, or a plastic wardrobe organizer for storage to arrange clothes efficiently with big storage boxes. It also serves as an organizer storage box plastic and storage organiser . this storage box plastic and plastic boxes for storage big size can store everything from toys to clothes. The storage basket with lid design makes ideal as kitchen organizers and storage or a plastic basket for kitchen. It’s also great as a big basket for storage, big boxes for storage, or toys baskets for storage. | Use this organiser box — a versatile, durable solution: big plastic boxes for storage large size organizer box for bulk items; toy storage box with lid large size for toys; cloth organizer for storage plastic and cloth storage box for clothes to keep garments neat; plastic box for clothes storage and plastic storage box organiser for easy stacking; storage box for kitchen big size, plastic basket for clothes or basket for kitchen storage; storage boxes with lid, box for storage plastic, plastic storage basket and storage box for clothes large — all-in-one. | Keep organise your home with this large plastic storage boxes, perfect as a storage box for toys large size and a multipurpose organizer for every corner of your home. This plastic organizer storage box works great as a storage basket for clothes, plastic container for clothes, or wardrobe storage box, offering ample space as a large storage box or big basket for storage large size. Whether you need a storage basket for kitchen, storage box and organiser kitchen, or plastic box for storage clothes, this durable plastic storage box for clothes and storage baskets design ensures long-lasting utility. Perfect store box solution for every home to keep things sorted and accessible. | This large basket for toys storage is a perfect multipurpose storage basket designed to keep your home neat and tidy. Made from durable basket plastic material, it doubles as a plastic cloth organizer for storage or cloth container for storage, ideal for clothes, toys, household essentials. The big plastic storage box design with a secure storage box plastic with lid , while its large storage box plastic capacity offers ample space for all your items. This versatile basket for storage with lid functions as both a utility box and storage box and organiser with lid, making it an all-in-one storage plastic box, basket organizer, and big size storage box solution for every room.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3116,22 +3116,22 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>12FOR COLLECTION Stainless Steel 2 Tier Countertop Kitchen Rack|Pantry Storage Organizer | Multipurpose Storage Organizer | Kitchen Racks | Kitchen Organizer | Kitchen Accessories Rack, Tiered Shelf</t>
+          <t>Stainless Steel Kitchen Dish Rack Expandable Storage Shelves, Multipurpose Organizer Extend Up to 580 mm with Anti-Rust Nano Coating (Pack of 4) (NHSP), Countertop, Floating Shelves</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61TGmD48a3L._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61rmL5QqxSL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0BZ7TB3R8</t>
+          <t>https://www.amazon.in/dp/B0CLVJDS6F?th=1</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>So It Is Easy To Hold Various Bottles, Cans, Jars, Etc. The 2-Tier Design Of This Spice Rack Shelf Is Aimed At Saving Your Space But Holding More Items. | 🗹 This dish rack is suitable for placing in the kitchen, dining table, pantry and any other room of the house. Perfect for storing spices, condiments, grains, or home items such as lotions, cleansers, soaps, shampoo, and more. | 🗹 This dish rack is suitable for placing in the kitchen, dining table, pantry and any other room of the house. Perfect for storing spices, condiments, grains, or home items such as lotions, cleansers, soaps, shampoo, and more. | This Shelf Holder Is Made Of Full Stainless Steel Frame With Chrome Plating, Ensuring Its Sturdiness And Durability. Therefore, This Cabinet Spice Rack Won't Tip Over Easily When You Use It.</t>
+          <t>This Stainless Steel Shelf Can Be Of Best Use For Making Partitions Or Dividing The Space To Keep Maximum Products. This One-Piece Will Satisfy All Your Basic Needs For Purchasing Different Products For Separate Uses. | The Best Bathroom/Kitchen Accessories Which Is Totally Rust-Proof And Corrosion-Free Because Of Additional Layers Of Nickel-Chrome Mirror Finishing. We Recommend Using Wet &amp; Dry Clothes For Cleaning The Product Periodically To Maintain Its Shine And Keep It Durable. | This Rack Comes With Anti-Skid Rubber Fittings In Its Legs, Ensuring That Your Floor Stays Scratch-Free And Prevents The Rack From Slipping. You Can Start Using This Rack/Shelf As Soon As Your Receive The Product. It Can Be Placed On Kitchen/Bathroom/Cabinet/Office Floor/Platform. | It Has Simply The Best Design As It Has Spaces Between The Wires To Keep The Stored Products Ventilated. It Can Easily Store Products Above And Below The Stand. This Allows Users To Make Partitions And Get The Best Out Of Small Places In An Organized Way. | :-Smart Storage: Use Anywhere You Need To Keep Food, Pantry And Kitchen Items Organized; Perfect For Organizing Pasta, Packets, Extra Supplies Of Salt, Dressing And Vinegar, Macaroni And Cheese Boxes, Baking Supplies, Condiments And More; These Bins Also Work In Any Room Of Your Home!</t>
         </is>
       </c>
     </row>
@@ -3139,22 +3139,22 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2-Tier Stainless Steel Kitchen Storage Spice Rack, Container Organizer Counter top Stand Multipurpose Masala Stand for Kitchen Space Saver Rack (NHSP, Tiered Shelf), Silver</t>
+          <t>Amazon Basics Multi-Purpose Large Organizer | Modular Storage Box for Clothes, Kitchen, Bedroom &amp; Living Room | Stackable Rack, Space-Saving Wardrobe Cabinet (Off White), 4 Piece, 37.5LX44.7WX27H cm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71xcENEGMyL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/910+4jHnLQL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CH6M5MXX</t>
+          <t>https://www.amazon.in/dp/B0FXXVN5V3?th=1</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>✅ Durable Stainless Steel Build – Strong, rust-resistant kitchen rack designed for long-lasting use. | ✅ 2-Tier Space-Saving Design – Ideal kitchen organizer rack that maximizes storage in compact kitchens. | ✅ Multipurpose Kitchen Stand – Use as a stand for kitchen storage rack for masala jars, spices, bottles, and containers. | ✅ Organized Kitchen Storage – Perfect kitchen stand organiser for countertops, shelves, or inside a kitchen storage cabinet. | ✅ Sleek &amp; Modern Look – Stylish kitchen rack stand that keeps your cooking essentials neat and accessible. | ✅ Versatile Use – Works as kitchen racks for storage, spice rack, or racks for storage of everyday kitchen items.</t>
+          <t>BUILT WITH ULTRA-STURDY PLASTIC: Crafted from high-strength PPCP plastic to withstand daily wear, ensuring long-lasting use. SAFE PACKAGING: Packaged with care to prevent damage during transit, so your Chester arrives in pristine condition. | LAB TESTED DURABILITY: Tested by an internationally accredited lab, Chester’s resilience meets global quality standards. | COLLAPSIBLE &amp; PORTABLE: Chester's collapsible design makes it easy to dismantle, store, or relocate as needed. | SECURE MAGNETIC DOOR LOCK: Protect items from dust and keeps contents securely in place preventing them from shifting or falling out. | VERSATILE &amp; ADAPTABLE DESIGN: Perfect for organizing toys, clothes, books, and more—Chester fits seamlessly in the kitchen, living room, bathroom, or garden.</t>
         </is>
       </c>
     </row>
@@ -3162,22 +3162,22 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Stainless Steel Kitchen Dish Rack Expandable Storage Shelves, Multipurpose Organizer Extend Up to 580 mm with Anti-Rust Nano Coating (Pack of 4) (NHSP), Countertop, Floating Shelves</t>
+          <t>SAFAK 3 Tier Wooden Kitchen Organizer Rack for Countertop | Wooden Spice Rack Stand for Kitchen Counter | Kitchen Shelf Organizer &amp; Cabinet Shelf Riser | Decorative Masala Rack Storage Stand | Dark</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61rmL5QqxSL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71swzxPftnL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CLVJDS6F?th=1</t>
+          <t>https://www.amazon.in/dp/B0GRVMYVQH?th=1</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>This Stainless Steel Shelf Can Be Of Best Use For Making Partitions Or Dividing The Space To Keep Maximum Products. This One-Piece Will Satisfy All Your Basic Needs For Purchasing Different Products For Separate Uses. | The Best Bathroom/Kitchen Accessories Which Is Totally Rust-Proof And Corrosion-Free Because Of Additional Layers Of Nickel-Chrome Mirror Finishing. We Recommend Using Wet &amp; Dry Clothes For Cleaning The Product Periodically To Maintain Its Shine And Keep It Durable. | This Rack Comes With Anti-Skid Rubber Fittings In Its Legs, Ensuring That Your Floor Stays Scratch-Free And Prevents The Rack From Slipping. You Can Start Using This Rack/Shelf As Soon As Your Receive The Product. It Can Be Placed On Kitchen/Bathroom/Cabinet/Office Floor/Platform. | It Has Simply The Best Design As It Has Spaces Between The Wires To Keep The Stored Products Ventilated. It Can Easily Store Products Above And Below The Stand. This Allows Users To Make Partitions And Get The Best Out Of Small Places In An Organized Way. | :-Smart Storage: Use Anywhere You Need To Keep Food, Pantry And Kitchen Items Organized; Perfect For Organizing Pasta, Packets, Extra Supplies Of Salt, Dressing And Vinegar, Macaroni And Cheese Boxes, Baking Supplies, Condiments And More; These Bins Also Work In Any Room Of Your Home!</t>
+          <t>A wooden kitchen organizer is essential for any kitchen since it is both stylish and practical. The purpose of these organizers is to improve the efficiency and organization of your kitchen. To accommodate different storage needs, they are available in a range of sizes and forms. | Jars, cans, bottles, sugar, tea, spices, sauces, and other kitchen supplies can all be stored in these useful step organizers. Additionally, they are a great method to store things for your pooja room. | Because it doesn't require any additional building or equipment, this freestanding organizer is easy to use. | Because it makes room in cramped cabinets and pantries, this three-tiered organizer is a great tool for kitchen and pantry organization. | When necessary, a moist towel can be used to clean the step shelf organizer's nonslip shelf lining.</t>
         </is>
       </c>
     </row>
@@ -3185,390 +3185,22 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4 Layer Multipurpose Storage Rack with Wheel, Plastic Kitchen Organizer Trolley, Bathroom, Living Room &amp; Home Storage Shelf, Space Saving Utility Stand</t>
+          <t>Organizer Tray Office Drawer Dividers Storage Bins Multipurpose Desk for Makeup, Kitchen, Office, Bathroom, Bedroom Dreassing, Basket Rack MultiColor(23*8*5 CM) Pack Of 6 (Multi 6pcs)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61PGmlLrO3L._SY879_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71UDWR9wrBL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0HL3CCQRN?th=1</t>
+          <t>https://www.amazon.in/dp/B0CR374476</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>VERSATILE DESIGN: 4-tier rolling cart with mesh sides perfect for organizing and storing items in any room, featuring a modern black finish | MOBILE SOLUTION: Smooth-rolling casters allow easy movement between rooms, making it ideal for home, office, or craft room use | STURDY CONSTRUCTION: Durable metal frame with mesh side panels provides stability and ventilation while keeping items secure | SPACE-SAVING: Compact vertical design maximises storage in minimal floor space, with three spacious tiers for efficient organisation | PRACTICAL DIMENSIONS: Each tier offers ample storage space with mesh sides for visibility and easy access to stored items</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Kitchen Organizer Rack, Spice Rack Organizer, Kitchen Racks for Storage, Kitchen Stand Organiser for Spices, Masala Jars &amp; Bottles, Steel Countertop Rack</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81ECGsIEEqL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GTFQFYRP</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐎𝐑𝐆𝐀𝐍𝐈𝐙𝐄𝐑 𝐑𝐀𝐂𝐊 𝐅𝐎𝐑 𝐒𝐌𝐀𝐑𝐓 𝐒𝐓𝐎𝐑𝐀𝐆𝐄 - Keep your kitchen neat and organized with this practical kitchen organizer rack designed for everyday kitchen storage. Ideal for arranging spices, masala containers, bottles, jars and other kitchen accessories while making better use of available counter space. | 𝐒𝐏𝐈𝐂𝐄 𝐑𝐀𝐂𝐊 𝐎𝐑𝐆𝐀𝐍𝐈𝐙𝐄𝐑 𝐅𝐎𝐑 𝐃𝐀𝐈𝐋𝐘 𝐄𝐒𝐒𝐄𝐍𝐓𝐈𝐀𝐋𝐒 - Use it as a convenient spice rack organizer to keep frequently used masala boxes, spice jars, seasoning containers and kitchen essentials easily accessible. A useful spice rack for kitchen counters, shelves and cabinets. | 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐑𝐀𝐂𝐊𝐒 𝐅𝐎𝐑 𝐒𝐓𝐎𝐑𝐀𝐆𝐄 &amp; 𝐎𝐑𝐆𝐀𝐍𝐈𝐙𝐀𝐓𝐈𝐎𝐍 - Designed as a versatile kitchen storage organizer, this rack helps organize spices, jars, oil bottles and other everyday items. Suitable for homes that need compact kitchen racks for storage, kitchen shelves and countertop organization. | 𝐌𝐔𝐋𝐓𝐈𝐏𝐔𝐑𝐏𝐎𝐒𝐄 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐒𝐓𝐀𝐍𝐃 𝐎𝐑𝐆𝐀𝐍𝐈𝐒𝐄𝐑 - This kitchen stand organiser can be used for organizing masala containers, spice jars, cooking essentials and other household items. Use it as a masala organizer rack, kitchen stand or storage rack according to your daily needs. | 𝐂𝐎𝐌𝐏𝐀𝐂𝐓 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐒𝐓𝐎𝐑𝐀𝐆𝐄 𝐒𝐎𝐋𝐔𝐓𝐈𝐎𝐍 -A practical kitchen organizer for keeping your countertop, kitchen shelf or cabinet more व्यवस्थित. Suitable for use as a masala rack, spice rack, kitchen stand and storage organizer, making everyday kitchen items easier to find and access.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr"/>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>3 Tier Kitchen Wall Mounted Rack, Stainless Steel Wall Organizer for Spice Boxes, Masala Containers, Jars &amp; Utensils, Storage Shelf Stand for Home</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81N5kiBtx+L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HHFRS7FF</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>𝟑 𝐓𝐈𝐄𝐑 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐒𝐓𝐎𝐑𝐀𝐆𝐄: This kitchen racks 3 tier design provides separate storage levels for spice boxes, masala containers, jars, bottles and everyday kitchen essentials, helping keep items organised and easy to access. | 𝐖𝐀𝐋𝐋 𝐌𝐎𝐔𝐍𝐓𝐄𝐃 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐎𝐑𝐆𝐀𝐍𝐈𝐙𝐄𝐑 𝐑𝐀𝐂𝐊: Make better use of unused vertical space with this wall mounted kitchen organizer rack. The kitchen wall mounted rack design helps reduce countertop clutter and creates practical everyday storage. | 𝐌𝐔𝐋𝐓𝐈𝐏𝐔𝐑𝐏𝐎𝐒𝐄 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐖𝐀𝐋𝐋 𝐒𝐇𝐄𝐋𝐅: Use this kitchen wall mounted shelf as a spice rack, masala rack, jar holder or utensil storage solution. The open design keeps frequently used items visible and within easy reach. | 𝐏𝐑𝐀𝐂𝐓𝐈𝐂𝐀𝐋 𝐊𝐈𝐓𝐂𝐇𝐄𝐍 𝐒𝐓𝐎𝐑𝐀𝐆𝐄 𝐑𝐀𝐂𝐊 𝐎𝐑𝐆𝐀𝐍𝐈𝐒𝐄𝐑: Designed for everyday organisation, this wall mounted kitchen storage rack helps arrange different kitchen essentials in one dedicated storage area while saving valuable counter space. | 𝐂𝐇𝐄𝐂𝐊 𝐒𝐈𝐙𝐄 𝐁𝐄𝐅𝐎𝐑𝐄 𝐏𝐔𝐑𝐂𝐇𝐀𝐒𝐄: Please check the product dimensions and available installation space before ordering. This kitchen wall rack is intended to provide organised vertical storage for your selected kitchen area.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Amazon Basics Multi-Purpose Large Organizer | Modular Storage Box for Clothes, Kitchen, Bedroom &amp; Living Room | Stackable Rack, Space-Saving Wardrobe Cabinet (Off White), 4 Piece, 37.5LX44.7WX27H cm</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/910+4jHnLQL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FXXVN5V3?th=1</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>BUILT WITH ULTRA-STURDY PLASTIC: Crafted from high-strength PPCP plastic to withstand daily wear, ensuring long-lasting use. SAFE PACKAGING: Packaged with care to prevent damage during transit, so your Chester arrives in pristine condition. | LAB TESTED DURABILITY: Tested by an internationally accredited lab, Chester’s resilience meets global quality standards. | COLLAPSIBLE &amp; PORTABLE: Chester's collapsible design makes it easy to dismantle, store, or relocate as needed. | SECURE MAGNETIC DOOR LOCK: Protect items from dust and keeps contents securely in place preventing them from shifting or falling out. | VERSATILE &amp; ADAPTABLE DESIGN: Perfect for organizing toys, clothes, books, and more—Chester fits seamlessly in the kitchen, living room, bathroom, or garden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>TEX-RO Plastic Storage Rack for Bedroom/Shelf for Bedroom/Bathroom Storage Rack/Trolley for Kitchen Storage/Multipurpose Storage Rack (Black, 2 Layer)</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/7182sHilcZL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FRZF7RVS?th=1</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Easy Mobility – This plastic kitchen rack with wheel moves smoothly, making it easy to shift between kitchen, dining, or storage areas without any hassle. | Multipurpose Use – This bathroom organiser stand and storage shelf is perfect for keeping your essentials tidy, works great as room organizer items for bedroom, and can also be used as a versatile room organiser for clutter-free living. | Durable &amp; Strong Build – Made from high-quality plastic, this storage rack is sturdy, long-lasting, and designed to handle daily household use. | Multipurpose Storage – Use it as a kitchen organizer, bathroom storage shelf, or room organizer – perfect for vegetables, groceries, toiletries, or household items. | Space-Saving Design – The slim and compact structure helps maximize storage in small spaces, keeping your home neat and organized.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>SAFAK 3 Tier Wooden Kitchen Organizer Rack for Countertop | Wooden Spice Rack Stand for Kitchen Counter | Kitchen Shelf Organizer &amp; Cabinet Shelf Riser | Decorative Masala Rack Storage Stand | Dark</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71swzxPftnL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GRVMYVQH?th=1</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>A wooden kitchen organizer is essential for any kitchen since it is both stylish and practical. The purpose of these organizers is to improve the efficiency and organization of your kitchen. To accommodate different storage needs, they are available in a range of sizes and forms. | Jars, cans, bottles, sugar, tea, spices, sauces, and other kitchen supplies can all be stored in these useful step organizers. Additionally, they are a great method to store things for your pooja room. | Because it doesn't require any additional building or equipment, this freestanding organizer is easy to use. | Because it makes room in cramped cabinets and pantries, this three-tiered organizer is a great tool for kitchen and pantry organization. | When necessary, a moist towel can be used to clean the step shelf organizer's nonslip shelf lining.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Organizer Tray Office Drawer Dividers Storage Bins Multipurpose Desk for Makeup, Kitchen, Office, Bathroom, Bedroom Dreassing, Basket Rack MultiColor(23*8*5 CM) Pack Of 6 (Multi 6pcs)</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71UDWR9wrBL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CR374476</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
           <t>Combo of 6pcs multipurpose storage baskets set which is useful for one's daily activity. | Color : Available in assorted colors, Color will be shipped as pe availability, Material : Plastic | Portable, light weight stack-able. Can be kept in drawers, almirahs, kitchen cabinets, refrigerator, shelves etc. | The desk drawer organizer trays can be used for desk, drawers, kitchen, office and living room as well as for other applications. help you to create your own mix and match organizational system to fit in any drawers, cabinets, lockers and wardrobe closets</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>FireBees 2 Tier Kitchen Counter Organizer, Wooden Kitchen Organizer Rack for Spices &amp; Storage, Kitchen Shelf Organiser Stand, Masala Organizer Rack, Aesthetic Kitchen Organizer Items 33 x 16 x 25 cm</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/518T84qOyML._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GW9H1KC7</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Smart Kitchen Organization Solution - Upgrade your space with this versatile kitchen organizer designed to store spices, jars, and daily essentials neatly. Perfect for anyone looking for efficient kitchen organizers and storage. | Premium Wooden Design - Built with a sturdy frame, this wooden kitchen organizer rack adds a modern and aesthetic touch to your countertop while ensuring durability and long-term use. | Multi-Purpose Organizer Rack - Use it as a spice rack, masala organizer rack, or container organiser rack—ideal for kitchen, bathroom, or pantry storage. | Space-Saving 2 Tier Design - The compact 2 tier kitchen counter organiser maximizes vertical space, making it perfect for small kitchens or limited countertops. | Aesthetic &amp; Functional - This stylish kitchen stand wooden design blends beautifully with modern homes, making it one of the best aesthetic kitchen items for organized living. | Two-tier countertop organizer — Ideal for storing spices, condiments, oils, small jars, and kitchen accessories while keeping counters neat and accessible. | Dimensions — Compact tabletop design with two storage levels; suitable for kitchen counters, coffee stations, bathrooms, or pantry shelves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr"/>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>GOLWYN Air Tight Containers For Kitchen Storage Set, Bpa Container For Kitchen Storage Set, Kitchen Organizer And Kitchen Accessories Items Storage for Home (1100 Ml Set Of 8)(Plastic)</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71auAIxh1PL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0B2SBK18B?th=1</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Airtight kitchen storage containers set Keep Food Fresh----The lids with silicone gasket make these storage containers airtight, and the top flips open easily. Airtight storage system will always keep your food dry and fresh. All have the same lids make it easy to wash dry and reuse with ease. We can also use for spice containers for kitchen storage . Perfect ! plastic containers for kitchen storage . | Package Content: 8Pcs Container Jar Set With Cap | Material: Premium Quality Plastic | Airtight / 100% Leak Proof. | Capacity: 1100 ml | Color: transparent | BPA Free and Food Grade Material Plastic Boxes For Storage ---- pantry storage containers for kitchen airtight are made of durable plastic, BPA free, which have a longer life than many other brands plastic containers. Clear containers make it convenient to see what’s inside, you can easily get what you want without opening every container. Space saving storage box for kitchen .</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Cri8Hub Stainless Steel 2 Tiered Shelf Kitchen Rack - Spice Boxes Organizer –Kitchen Rack Stand - Cosmetic Organizer – Counter Top Organiser - Floor Mounted Shelf For Home(Multipurpose Rack)</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71A5JJpZuDL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CV8348ZZ</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>:-STRONG AND DURABLE: Solid steel spice jar kitchen racks come with a hardwearing anti-rust coating. The stands have double support rods to provide each shelf with extra stability. | :-MULTIPLE USES: The uses of this dish rack kitchen organizer are truly endless. It can easily be used in a kitchen pantry, bathroom, or office to save space and organize a variety of items- from dishes to supplies, towels, and more. | :-ANTI-SKID FITTINGS: This storage shelf rack for the kitchen comes with Anti-skid fittings in its legs which ensures that your floor stays scratch-free and it prevents the utensils stand from slipping. | :-2 STURDY LEVELS: The kitchen shelf holder insert can hold numerous items on 2 sturdy levels. Keep your bowls, plates, or food neatly organized in your kitchen. | :- EASY CLEANING: This kitchen rack organizer is designed with easy clean properties and can be wiped clean with a soft cloth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr"/>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Cri8Hub Heavy Duty Metal Stand 3-Tier Standing Rack for Home, Bathroom Countertop Storage Shelf, Cosmetic Organizer Holder Kitchen Spice Rack, (Black)</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/519RVYDzpEL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F6NBFHX3</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>VERSATILE STORAGE: Three-tier standing rack perfect for organising spices, condiments, and toiletries in both kitchen and bathroom settings | DURABLE CONSTRUCTION: Sturdy black metal frame with raised edges on each shelf to prevent items from falling off | SPACE-SAVING DESIGN: Compact footprint whilst providing ample storage space across three levels for maximum organisation. Space-saving bathroom solution - Our shampoo holder for bathroom maximizes your space by organizing your bottles efficiently, allowing you to keep your bathroom neat and tidy without sacrificing convenience. | EASY ACCESS: Open shelf design allows quick visibility and access to all stored items, making cooking and daily routines more efficient | DIMENSIONS: Each shelf measures approximately 30 cm in length, 15 cm in width, with 15 cm spacing between tiers for accommodating various container sizes | Easy Use : Helps maintain a clean and clutter- free environment. Built with durable materials to ensure long lasting use. Holds a significant amount of weight without compromising stability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Kitchen Organizer Rack – Multi-Purpose Kitchen Stand for Countertop &amp; Cabinet Storage | Heavy-Duty Kitchen Rack Organizer for Spices, Utensils, Dishes &amp; Pantry Items (2 Tier Brown)</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71+m2EQr+JL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GHZN2Y8C?th=1</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>✔ MULTI-PURPOSE KITCHEN ORGANIZER Keep your kitchen neat and clutter-free. Perfect for organizing spices, jars, utensils, plates, bowls, cleaning supplies, and pantry essentials. | ✔ STRONG &amp; STABLE DESIGN Made from durable, heavy-duty material for long-lasting use. Sturdy construction ensures stability even when fully loaded. | ✔ SPACE-SAVING KITCHEN STAND Maximize countertop, cabinet, or pantry space. Ideal for small kitchens, apartments, and modern homes. | ✔ EASY TO ASSEMBLE &amp; CLEAN Quick and simple installation with minimal tools required. Smooth surface makes cleaning fast and hassle-free. | ✔ MODERN &amp; ELEGANT LOOK Sleek design complements any kitchen décor — perfect for countertops, cabinets, shelves, or under-sink storage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr"/>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>12FOR COLLECTION Stainless Steel 3-Tier Countertop Storage Rack For Corners, Multipurpose Kitchen Plate Dish Corner Shelf, Rack Stand Holder</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61eX3uIvTwL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09MYH9QC1</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Stainless Steel, Color :- Silver :-Coated with multi-layer chrome plating that is tested to ensure a rust free life of the product. | Boost your kitchen cupboard storage quickly and easily with this three-tier corner plate rack. It maximises the vertical space in any cupboard, counter or under sink area with a large surface area suitable for plates of all sizes and other kitchen essentials. Crafted from robust stainless steel with a sleek chrome finish. It is 100% rust free! | Stainless Steel Multipurpose Kitchen Plate Dish Corner 3-Tier Storage Rack Holder for Kitchen Stand Shelves Kitchen Tray Pan Pot Utensils Chakla Belan Storage Cupboard Organizer for Home Stainless Steel Multipurpose Kitchen Plate Dish Corner 3-Tier Storage Rack Holder for Kitchen Stand Shelves Kitchen Tray Pan Pot Utensils Chakla Belan Storage Cupboard Organizer for Home | STRONG AND STURDY: It is highly strong and sturdy! Can accomodate weights of stainless steels plates and dishes very easily and other steel or other metal utensils! MATERIAL: Made up of high quality stainless steel with a beautiful chrome finish! It is 100% rust free! | MATERIAL: Made up of high quality stainless steel with a beautiful chrome finish! It is 100% rust free!</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr"/>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>DALUCI Set of 2 Metal Bathroom Corner Shelf Rack | No Drilling Self Adhesive Wall Mounted Storage Organizer for Bathroom &amp; Kitchen | Rustproof Bathroom Shelves (8 &amp; 9 INCH, Black)</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81VF4kpZlwL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G4RNDJF6?th=1</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>No Drilling Bathroom Organizer Without Drill – Easy self adhesive installation with no tools or wall damage. Ideal metal bathroom corner shelf for rented homes and modern bathrooms. | Rustproof Heavy Duty Metal Bathroom Shelf – Premium coated metal construction designed for wet bathroom environments. Strong load-bearing wall mounted bathroom shelves. | Perfect Corner Storage (8 &amp; 9 Inch Shelves) – Smart corner design saves space while organizing shampoo bottles, soap, face wash, and daily bathroom accessories. | Bathroom &amp; Kitchen Storage Organizer – Can also be used as kitchen corner shelf for spices, cleaning items, or utility storage. | Pack of 2 Self Adhesive Bathroom Shelves – Includes 2 premium metal corner shelves with 4 strong adhesive mounting. Ideal bathroom accessories set for organized, clutter-free storage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr"/>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Shoper cart kitchen organizer rack, 2-Tier Spice Rack Organiser, Rustic Brown and Black, 30cm x 15.7cm x 26.4cm, Kitchen Counter Storage Shelf with Metal Frame</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61L6KxA55UL.jpg</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GKG8H377</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>COMPACT DESIGN: This 2-tier spice rack organiser measures 30cm x 15.7cm x 26.4cm, providing efficient vertical storage for your kitchen counter without taking up excessive space | STURDY CONSTRUCTION: Features a durable metal frame with rustic brown wooden shelves that combine industrial style with practical functionality for organising spices, condiments, and pantry essentials | VERSATILE STORAGE: Two spacious tiers accommodate various sized containers including spice jars, bottles, cans, and small kitchen items, helping keep your countertop neat and organised | STYLISH APPEARANCE: The rustic brown and black colour combination with X-shaped side supports adds a modern farmhouse aesthetic that complements various kitchen décor styles | MULTI-PURPOSE USE: Ideal for kitchen counters, pantries, cupboards, or bathroom storage, this rack organiser maximises space whilst keeping frequently used items within easy reach</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Stainless Steel 2-Tier Wall Mounted Storage Basket Rack, Chrome Finish,Kitchen and Bathroom Stainless Steel 2 Container Wall Mount Organizer For Kitchen Storage/Hanging Shelves/Rack (Double Self)</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71eiZT4qCiL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H276M39L</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2-TIER DESIGN: Features two spacious basket tiers, allowing you to organise and store a wide range of items in your kitchen or bathroom efficiently. | STURDY CONSTRUCTION: Made from high-quality stainless steel with a polished chrome finish, ensuring long-lasting durability and resistance to rust and corrosion. | WALL MOUNTED: Designed for wall mounting with built-in brackets, keeping your countertops clutter-free and making the most of your vertical wall space. | VERSATILE STORAGE: Ideal for storing shampoos, conditioners, soaps, spices, and other daily essentials, making it suitable for both kitchen and bathroom use. | DIMENSIONS: Measures 31 cm (length) x 16 cm (width) x 33 cm (height), providing ample storage space while maintaining a compact and neat profile on your wall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr"/>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>TEX-RO Big Storage Box and Organiser | Storage &amp; Organizers | Organizer Storage Box for Kitchen, Clothes | Durable Storage Basket With Lid &amp; Plastic Basket for Storage (Pack of 3, multicolor)</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81WyHjKqOqL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FDGS43Z7?th=1</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Keep your home neat and organized with this plastic storage box and organiser plastic , perfect for every corner of your house. These storage boxes are ideal boxes for storage of clothes, toys, and household items. Each storage box with lid keeps your essentials easy to stack. Use this basket for clothes storage to arrange your wardrobe or laundry space efficiently. Made from high-quality plastic storage material, this plastic storage box for wardrobe ensures long-lasting durability and style for your home kitchen basket with lid. | Our product is perfect for multiple uses — whether you need large storage containers to organize your home, baskets for storage for daily essentials, organisers for kitchen storage to keep groceries neat, or a plastic wardrobe organizer for storage to arrange clothes efficiently with big storage boxes. It also serves as an organizer storage box plastic and storage organiser . this storage box plastic and plastic boxes for storage big size can store everything from toys to clothes. The storage basket with lid design makes ideal as kitchen organizers and storage or a plastic basket for kitchen. It’s also great as a big basket for storage, big boxes for storage, or toys baskets for storage. | Use this organiser box — a versatile, durable solution: big plastic boxes for storage large size organizer box for bulk items; toy storage box with lid large size for toys; cloth organizer for storage plastic and cloth storage box for clothes to keep garments neat; plastic box for clothes storage and plastic storage box organiser for easy stacking; storage box for kitchen big size, plastic basket for clothes or basket for kitchen storage; storage boxes with lid, box for storage plastic, plastic storage basket and storage box for clothes large — all-in-one. | Keep organise your home with this large plastic storage boxes, perfect as a storage box for toys large size and a multipurpose organizer for every corner of your home. This plastic organizer storage box works great as a storage basket for clothes, plastic container for clothes, or wardrobe storage box, offering ample space as a large storage box or big basket for storage large size. Whether you need a storage basket for kitchen, storage box and organiser kitchen, or plastic box for storage clothes, this durable plastic storage box for clothes and storage baskets design ensures long-lasting utility. Perfect store box solution for every home to keep things sorted and accessible. | This large basket for toys storage is a perfect multipurpose storage basket designed to keep your home neat and tidy. Made from durable basket plastic material, it doubles as a plastic cloth organizer for storage or cloth container for storage, ideal for clothes, toys, household essentials. The big plastic storage box design with a secure storage box plastic with lid , while its large storage box plastic capacity offers ample space for all your items. This versatile basket for storage with lid functions as both a utility box and storage box and organiser with lid, making it an all-in-one storage plastic box, basket organizer, and big size storage box solution for every room.</t>
         </is>
       </c>
     </row>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3204,6 +3204,386 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>KLOSIA Women's Rayon Printed Anarkali Kurta and Pant with Dupatta Set</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51JtGs04X7L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FRFVFYD7?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GoSriKi Kurta Set Women Viscose Printed | Kurti Set Woman | Kurta Pant Dupatta 3 Piece Outfit | V-Neck Elbow Length Sleeve Straight Fit Ethnic Wear Ladies Dress Stylish Traditional Clothing</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61+SSCQ5K7L._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H3PSJZ9K?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ANNI Designer Women's Viscose Blend Straight Printed Kurta with Palazzo | Elbow Length Sleeve Kurti Set | Close Neck with Back Slit | Soft Comfortable Fabric | 2 Piece Outfit</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51CaJuDIWiL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GG459CD4?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ANNI Designer Women's Rayon Viscose Straight fit Printed Embroidered Kurta with Pant &amp; Dupatta | Ethnic Kurta Set for Women | Daily, Office &amp; Festive Traditional</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61RbrPzrjaL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G525155T?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>LookMark Women's Chikankari Embroidered Ethnic Gown, Ankle Length Flared Dress, 3/4 Sleeves, Traditional Indian Wear</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71+dHGqDzTL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CBX8GCM1?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Women's Pink Bandhani Print Tiered Maxi Dress, Short Sleeve, Square Neck, Cotton</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61RR8+DmkLL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GCNTLFMB?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>KZULLY | Dress for Women Western Maxi Style, Ethnic Look Outfit for Women, A Line Flared Pattern, Indo Western Dresses, One Piece Long Gown</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61ShDu8G-zL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GD1GGLLF?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Modestouze Attires Dress for Women Western Maxi Style, Indo Western Dresses, One Piece Long Gown, A Line Flared Pattern, Ethnic Look Outfit for Women</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Qzp3xNsFL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GK9LGLKR?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Shasmi Girl's &amp; Women's Solid Color V-Neck A-Line Maxi Dress for Women | New Year Party Outfit | Waist Cinched Puff Sleeve Western | Elegant Casual Wear (Dress 246)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/613oHkA9JjL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FLKC5GZN?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ANNI Designer Women’s Rayon Viscose Straight Solid Kurta with Palazzo Set | Sleeveless Ethnic Wear | Comfortable Two Piece Outfit for Office, Casual &amp; Daily Use</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51jOoX3aoQL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G4984Y9Q?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Amayra Women's Pure Cotton Printed Straight Kurta Set with Palazzo Pants &amp; Dupatta- Ethnic Wear, White</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81IQzobx04L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FBG8S8BM?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ANNI DESIGNER Farshi Salwar Suit for Women | Cotton Blend Embroidered Straight Kurta with Dupatta | Farsi Farasi Parsi Salwar Suit Indian Office Party Wedding Clothing Fashion 3 Piece</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51r7MEPorqL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HG5FNMHW?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Nermosa Women Embroidery Solid Anarkali Kurta and Pant Set with Dupatta</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71t36fW+BUL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G1HQS8NH?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>GoSriKi Women Salsa A-Line Kurta with Palazzo | Embroidered Kurta Set for Women | Round Neck A-Line Ethnic Kurta Palazzo Outfit for Casual Festive &amp; Party</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/618st+zD9fL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GM7ZQVY7?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>AASK Women Fancy Plain &amp; Solid Fit And Flare Knee Length Designer Dress for Women</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71ZyLRR01LL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CQNZLM3R?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Klosia Women Pure Cotton Kurta Palazzo Set | Sleeveless Printed Kurta with Palazzo Pants | Summer Friendly, Office Wear Co-Ord Set</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41YF5GlKMXL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GGHQSL6P?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Nermosa Women Embroidery Solid A-Line Kurta and Pant Set with Dupatta</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71rjJMwzQaL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G6ZSVLPZ?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Celary Women’s Cotton Blend Printed Night Suit Set||Soft &amp; Breathable Short Sleeve Top &amp; Ethnic Print Pyjama Set||Also Available in Plus Size||Korean Night Suit||Comfortable Home Wear &amp; Sleepwear</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61H0uYfY3cL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G3Q81J45?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NAINVISH Women's Rayon Co-Ord Set | Printed Shirt and Pant Set for Women | Casual Two Piece Lounge Outfit | Western Outfit</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51NYs0EfSaL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G6DVQR3J?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>GRECIILOOKS Maxi Dress for Women | Long One Piece Outfit | Casual Western and Stylish Party Outfit | Trendy Summer Fashion for Womens</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71fJKbCU4xL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FPB6TQ8R?th=1&amp;psc=1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3417,17 +3417,17 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ANNI DESIGNER Farshi Salwar Suit for Women | Cotton Blend Embroidered Straight Kurta with Dupatta | Farsi Farasi Parsi Salwar Suit Indian Office Party Wedding Clothing Fashion 3 Piece</t>
+          <t>Nermosa Women Embroidery Solid Anarkali Kurta and Pant Set with Dupatta</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51r7MEPorqL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71t36fW+BUL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0HG5FNMHW?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0G1HQS8NH?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -3436,17 +3436,17 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nermosa Women Embroidery Solid Anarkali Kurta and Pant Set with Dupatta</t>
+          <t>Nermosa Women Embroidery Solid A-Line Kurta and Pant Set with Dupatta</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71t36fW+BUL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71rjJMwzQaL._SX569_.jpg</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0G1HQS8NH?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0G6ZSVLPZ?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -3455,17 +3455,17 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GoSriKi Women Salsa A-Line Kurta with Palazzo | Embroidered Kurta Set for Women | Round Neck A-Line Ethnic Kurta Palazzo Outfit for Casual Festive &amp; Party</t>
+          <t>Celary Women’s Cotton Blend Printed Night Suit Set||Soft &amp; Breathable Short Sleeve Top &amp; Ethnic Print Pyjama Set||Also Available in Plus Size||Korean Night Suit||Comfortable Home Wear &amp; Sleepwear</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/618st+zD9fL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61H0uYfY3cL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GM7ZQVY7?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0G3Q81J45?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -3474,115 +3474,20 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AASK Women Fancy Plain &amp; Solid Fit And Flare Knee Length Designer Dress for Women</t>
+          <t>NAINVISH Women's Rayon Co-Ord Set | Printed Shirt and Pant Set for Women | Casual Two Piece Lounge Outfit | Western Outfit</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71ZyLRR01LL._SY741_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51NYs0EfSaL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CQNZLM3R?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/dp/B0G6DVQR3J?th=1&amp;psc=1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr"/>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Klosia Women Pure Cotton Kurta Palazzo Set | Sleeveless Printed Kurta with Palazzo Pants | Summer Friendly, Office Wear Co-Ord Set</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41YF5GlKMXL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GGHQSL6P?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr"/>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Nermosa Women Embroidery Solid A-Line Kurta and Pant Set with Dupatta</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71rjJMwzQaL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G6ZSVLPZ?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr"/>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Celary Women’s Cotton Blend Printed Night Suit Set||Soft &amp; Breathable Short Sleeve Top &amp; Ethnic Print Pyjama Set||Also Available in Plus Size||Korean Night Suit||Comfortable Home Wear &amp; Sleepwear</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61H0uYfY3cL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G3Q81J45?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr"/>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>NAINVISH Women's Rayon Co-Ord Set | Printed Shirt and Pant Set for Women | Casual Two Piece Lounge Outfit | Western Outfit</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51NYs0EfSaL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G6DVQR3J?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr"/>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>GRECIILOOKS Maxi Dress for Women | Long One Piece Outfit | Casual Western and Stylish Party Outfit | Trendy Summer Fashion for Womens</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71fJKbCU4xL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FPB6TQ8R?th=1&amp;psc=1</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3489,6 +3489,386 @@
       </c>
       <c r="E139" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Martucci Women’s Quilted Satchel Handbag – Elegant Faux Leather Top-Handle Purse with Gold-Tone Metal Handles and Adjustable Crossbody Strap</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71yZZtohJYL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G449CJ8Q</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Mochi Women Synthetic Slingbag (66-7355)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71s0Fm-KprL._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09W1C1LTL</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Carrylux Women's Soft PU Tote Bag | Large Single Compartment Shoulder Handbag | Office, College &amp; Casual</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61FfZyulIZL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GK34HKMN</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ADISA Women's Quilted Crossbody Sling Bag - Stylish Cross Body Handbag for Girls &amp; Women with Gold Chain (SL5059)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61jsDR7kaYL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09154JPWQ</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Pure Vegan Leather Tote Bag for Women, Fully Embossed, Handbag, Shoulder Bag, Black</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/714Xb1jFm2L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D8XQQD1P</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ADISA Women's Crossbody Sling Bag - Stylish Cross Body Handbag for Girls &amp; Women - Adjustable Strap Shoulder Bag (SL5141)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71I4Yx1anzL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CZPJRDQN</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Lavie Woman's Broxa Flap Crossbody Sling Bag | Ladies Purse Handbag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61L+2HeKv-S._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08QTF8RPM</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Lavie Women's Yalta Satchel Bag | Ladies Purse Handbag</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71EwockPQkL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B097MXFVYL</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Lavie Women's Emberlyn Crossbody Sling Bag | Ladies Purse Handbag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61GiQqm3XkL._SY575_.jpg</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DVLP96WP</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Caprese TRACY S Large</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61OGd5IBEiL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08ZJZTCHR</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Lyrovo Clutch Purse for Women Formal Dressy Evening Clutches Handbags Crossbody Bag for Wedding Cocktail Prom Elegance Charm</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61Qn7SrsJJL.jpg</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F6TZ572V?th=1</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Lavie Women's Ficus Medium Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71k9FI0t6aS._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08NVF9V9L</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Fostelo Luxe Westside Purse For Women Handbag</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81RRF-w1yVL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07D7W3YFT</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ZOUK Office Bag | Stylish Bags for Office Use | Laptop Bag 15.6 inch | Stylish Tote for Office Use | Purse for Women | Vegan Leather Handbag | Daily &amp; Travel Use |</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71iBiB-pnGL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07LB7V3MV</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Women’s Metallic Shoulder Bag – Croc-Embossed Patchwork Leather Look Handbag with Zipper Closure, Trendy Underarm Purse.</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51dFX521euL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GXVSDJ8C</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Mochi Women Casual PU Soft Body Zipper closure Solid Sling Bag</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81Y714RE3BL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FDB1ZC99</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>DANIEL CLARK Women's Stylish Handbags Combo (Set of 3)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/717u1Q0IGGL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0963DGWJ4</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>The Purple Tree Handcrafted Women's Tote Bag with Vegan Leather Handles &amp; Indian Prints, Shoulder Tote Bag and Handbag for Office and College (Pack of 1)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61oix3ol0eL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C9V6CJ9B</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Lavie Women's Kelissa Satchel Handbag | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61b92ZDJ1jL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F66SNH8H</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Metro Women Textured Top-Handle Bag</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61rHhqpaHgL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D9TD3LZ7</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E159"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3869,6 +3869,386 @@
       </c>
       <c r="E159" t="inlineStr"/>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>AUSK Women’s Casual Summer Polo Knit T-Shirt | Zip Collar Top | Half Sleeves | Ribbed Panel Design | Lightweight Comfort | Regular Fit</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71pxWUGWUaL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H1HW8GQ2</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Dream Beauty Fashion Women's Long Sleeve Slim Fit Top/T-Shirt Henley Neck Casual (Top-Saiyaara-1)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41-OdGcmZlL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FP9JDGP8</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Women Short Sleeve Polo T-Shirts, Lady's Summer Striped Shirt, Collar Neck Casual Tank Tops</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71WkX41n42L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G2MRNB2Q</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Pinkmint Women Short Kurti | Cotton Blend Printed Tunic Top | Trendy Casual Top | Casual &amp; Office Wear Ethnic Top for Jeans</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71YNLQOl2qL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FZC9HLPP</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>RIEKA Women's Embroidered Top for Women, Maroon V Neck Rayon, 3/4 Sleeve Casual Loose Fit Tunic, Boho Blouse for Women, Korean Style</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81Al1oK1jdL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H4RF1241</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>LITZO Shirts for Women - Korean Style Long Sleeve Button Down | Regular Fit Western Latest Stylish Office Wear Tops Women (NO-98-101)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61ptQCrrW1L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H6RPR52P</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Dream Beauty Fashion Women's Sweet Heart Neck Balloon/Puff Bishop Sleeve Elegant Casual Tee Top, 23" inches (BZF-Top Mantos-01)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61TcnMgHv4L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CG9HQYWL</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Gufrina Women’s Light Rose Floral Printed Button Down Shirt with Mandarin Collar and Relaxed Fit 3/4 Sleeves</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71+8o4O1WCL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FNX2BNYH</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Women’s Polo T-Shirt | Long Sleeve Casual T-Shirt for Womens || Soft Comfortable Korean Style Trendy Top for Women</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/511opfswW9L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GS9RSYBP</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Lycra Casual Wear Full Sleeve Top for Women, Top for Girls, Regular Fit</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31hk042J4zL.jpg</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CKPYS2QZ</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Women's Cotton Blend Korean Style 3/4 Sleeve Oversized Button Down|| Workwear Top Shirt for Office &amp; Casual Wear Women Shirt || Shirt for Woman || Top for Women (L-98-101)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61a770ncRFL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GP6R2N67</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>RIEKA Womens Floral Applique Embroidered Fancy Top with Mandarin Collar Button Down Front Half Sleeves Relaxed Fit Casual Tunic Top for Women</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71SaK12WYLL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H26984XN</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>RIEKA Womens Embroidered Korean Style Top and Tunic; V Neck| Floral Thread Embroidery| Three Quarter Puff Sleeves |Relaxed Fit Curved Hem| Casual Everyday Fusion Top</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81Bp-xQtPwL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HBBFZNH4</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PLADO Women's and Girls Georgette Top Maroon</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51HFndVZO5L._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09NGN2BT2</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Arayna Women's Pure Cotton Paisley Printed Tunic Top – Comfortable Everyday Wear</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81OS4czw-AL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DY1TRLF6</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>BLACK BUDDY Women's Cotton Blend Full Sleeve Collared V Neck T Shirt for Women | Regular Fit Solid Rib Knit Stretch Top | Casual Office College Formal T Shirt | S-XXL</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/512Ti61s36L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H8S755PW</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>LITZO Women Shirt || Shirt for Woman || Top for Women (L-187-190)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/510vA977VmL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GNN27RDL</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Max Women's Cotton Regular Fit Top</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61d3ftDKTFL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CYZK99NC</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>GRECIILOOKS Women French Crepe Bandhani Bandhej Kalka Printed Formal Shirt | Casual Stylish Office Top Full Sleeve Shirts | Trendy Summer Tops | Smart Casual Top for Women's Button Down Modern Fit</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/7156yifeGyL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H9H9ZKY4</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Leriya Fashion Tops for Woman | Women Solid Full Sleeve Top Rumble Ribbed Knit | Regular Fit V-Neck Style T Shirt for Woman | Chic Smart-Casual &amp; Everyday Wear T-Shirt</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/614V5yzYnBL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HF5DNSD8</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4249,6 +4249,386 @@
       </c>
       <c r="E179" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Preneum Girl's &amp; Women's Solid Color V-Neck A-Line Maxi Dress for Women | New Year Party Outfit | Waist Cinched Puff Sleeve Western | Elegant Casual Wear (Availble in Plus Size)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51i6M31WAbL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H8768K24</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>GRECIILOOKS Women Summer Rayon A-Line Midi Dress | Sleeveless Tiered Stappy Sun Dress with Bows and Hearts Print | Casual Square Neck Flared Maxi Dresses for Beach and Vacation</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71fJKbCU4xL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FPB6TQ8R</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>LITZO Women’s One Piece Dress - Georgette Solid Color Western Gown | Long Sleeve Round Neck Fit &amp; Flare Flared Hem Design | A-Line Maxi Dress for Women | New Year Party Outfit (NO-17-18)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51ctChJKc9L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H5CR73BV</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>GoSriKi Women Salsa A-Line Kurta with Palazzo | Embroidered Kurta Set for Women | Round Neck A-Line Ethnic Kurta Palazzo Outfit for Casual Festive &amp; Party</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/618st+zD9fL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GM7ZQVY7</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ANNI Designer Short Kurti for Women Latest Viscose Blend Printed Ethnic Tunic | Stylish Kurti Tops with Jeans Styling | Casual Office Wear | Trendy Indian Fashion for Woman</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61sYyNiVHdL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GQMSD4VT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>AASK Women Fancy Plain &amp; Solid Fit And Flare Knee Length Designer Dress for Women</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71ZyLRR01LL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CQNZLM3R</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SHANTVAN GALLERY Co Ord Set for Women Stylish Card Set Dress for Women Trendy Top with Plazo Pant Ladies Coord Outfit Modern Wear for Travel Office Casual Look Premium Two Piece Clothing Style</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61ajdBrtVmL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G5XCTWM3</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Zurity Women's V-Neck Sporty T-Shirt Dress | Stylish Striped Sleeve One Piece for Women | Casual Summer Knee Length Short Dress | Trendy Beach &amp; Resort Wear Western Dress (26 D-1-3)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41YZ61LApyL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GVP2VYXT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Leriya Fashion Dress for Women | Western One Piece Dress for Women Short &amp; Long | Half Sleeve Casual Summer Dresses for Beach &amp; Stylish Party Outifits Below The Knee</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71rA91nZS8L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GDMG4CG1</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Celary Woman's Co-Ord Set|Stylish Co Ord Set for Women with Floral Print &amp; Embroidered Kurta|Two Piece Set for Women|Trendy Casual Co Ords Set with Pants</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/516tsojBdGL._SX569_.jpg</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HDV9KXB5</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Zurity Dress for Women ||Bohemian Brown Print Casual Comfortable Women's Long Sleeve Maxi Dress|| Popular Autumn Apparel Fashion (D-03-05)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51gP0vCxEAL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GF957GT6</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Leriya Fashion Dress for Women | Western Floral Printed One Piece Dress for Women midi | Casual Sleeveless Summer Dresses for Beach &amp; Stylish Party Outifits</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61O0Db6KRdL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GDQFY4HC</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ANNI Designer Women’s Viscose Blend Printed Short Kurti | Straight Fit Casual Ethnic Top | Square Neck Full Sleeve Kurta Office College</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71rnJFRpMIL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GNMPTYNY</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Klosia Women Pure Cotton Kurta Palazzo Set | Sleeveless Printed Kurta with Palazzo Pants | Summer Friendly, Office Wear Co-Ord Set</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41YF5GlKMXL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GGHQSL6P</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>LITZO Dress for Women || Women’s Solid Pleated Maxi Dress || Modest Long Sleeve Loose Fit Flowy Gown for Casual, Office &amp; Brunch || Lightweight Comfortable Western Outfit (T-L-17-18)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61abwaouC7L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DQCMDBHV</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>GRECIILOOKS Summer Dress for Women Midi Dress for Woman | Sleeveless Striped Design | Maxi Dresses Stylish | Casual Western Vacation Dresses | Flowy A-Line Resort Wear for Brunch &amp; Beach Styling</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61m-sZfPnsL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H2QRCBSP</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Modestouze Attires Women's Floral Pattern Rayon Blend Maxi Dress with Sweetheart Neck Half Puff Sleeve Floor Length and Zipper Closure Type | Maxi Dress for Women Stylish | Dress for Women</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71eKFCtyXUL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G57VGJMH</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>GRECIILOOKS Co Ord Set For Women Stylish | Dress for Women | Trendy Summer Travel Outfit | Lightweight 2 Piece for Holiday Look &amp; Puja | A Line Dresses For Women | Stylish Midi Party Dress for Women | Winter Casual Wear</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51SllsCXWXL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CM17DWD5</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>TIVANTE Solid Asymmetrical Buckle Maxi Dress for Women || Western Dress for Women Dresses || one piece Dress</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31a3dpLJTrL.jpg</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H7RXPCLM</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Shasmi Girl's &amp; Women's Solid A-Line Ruched Puff Sleeve Maxi Long Evening One Piece Long Dress for Women Stylish (Dress 131)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61ctazYxu4L._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F9T9PP7Z</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E199"/>
+  <dimension ref="A1:E219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4629,6 +4629,386 @@
       </c>
       <c r="E199" t="inlineStr"/>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>GoSriKi Viscose Printed Kurta for Women | Kurti Set Woman | Kurta with Pant &amp; Dupatta | Straight Ethnic Suit | Indian Outfit Ladies Dress Stylish Traditional Clothing Party Office Fashion Look Style</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51C7n7ysoIL._AC_AIweblab1392912,T4_SF1358,1638_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G59JDRRR</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>LookMark Women's Rayon Printed Kurta Set with Dupatta Kurti with Pants Ethnic Traditional Outfit</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61UVk6rFvUL._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H5KTHGSK</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Nermosa Women's Hand Block Floral Printed Straight Kurta Set with Palazzo Pants &amp; Dupatta Ethnic Kurta Set for Casual Outings Day Events Summer Wear Festive</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41HNjyM2OmL._AC_AIweblab1392912,T4_SF988,1482_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H6K11C3H</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>GoSriKi Kurta Sets for Women Viscose Printed | Kurti Set for Woman | Kurta Pant Dupatta Set | A Line Kurti | Round Neck V-Slit 3/4 Sleeve Suit Set for Women Stylish Ethnic Outfit</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71zBxzukDgL._AC_AIweblab1392912,T4_SF1168,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GTVX18KW</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Amayra Women's Pure Cotton A-Line Kurta Set with Palazzo Pants &amp; Dupatta|Ethnic wear|Kurti Suit Set for Women</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81LWX3c50zL._AC_AIweblab1392912,T4_SF1226,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GLGBDVJY</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ANNI DESIGNER Farshi Salwar Suit for Women | Cotton Blend Printed Straight Kurta with Dupatta | Farsi Farasi Parsi Ethnic Indian Office Party Wedding Clothing Fashion Premium Traditional Look 3 Piece</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51bvwVMYOlL._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H3FSN57V</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Amayra Women's Pure Cotton Straight Kurta Set with Palazzo Pants &amp; Dupatta|Ethnic wear|Kurti Suit Set for Women</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81vCseZYquL._AC_AIweblab1392912,T4_SF1150,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GPC7B26V</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Women’s Floral Printed Kurta Palazzo Set with Dupatta | Ethnic Straight Kurta Suit for Women | Festive Regular Wear | Designer Pakistani Style Salwar Suit for Daily Wear</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61a7MDYVGuL._AC_AIweblab1392912,T4_SF1272,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GZ7X6XYQ</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>KLOSIA Women's Printed Straight Kurta and Pant with Dupatta Set</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/616i8sDpl8L._AC_AIweblab1392912,T4_SF1156,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GPQJR7VQ</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>GoSriKi Poly Kurta for Women | Kurti Set Woman | Kurta with Pant &amp; Dupatta | Straight Printed Suit | Ethnic Indian Outfit | Long Dress Party Office Traditional Clothing Fashion Style</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51P-78jX7UL._AC_AIweblab1392912,T4_SF1172,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H7SNGCNK</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>KLOSIA Women’s Floral Printed Sleeveless Kurta Palazzo Set | Round Neck Straight Kurta with Palazzo Pants | Casual Ethnic Co-Ord Set for Women</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51sLN7JdqfL._AC_AIweblab1392912,T4_SF1006,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HFZZDSJQ</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ANNI Designer Kurta Sets for Women Viscose Printed | Kurta Pant Dupatta Set | A-Line Kurti Set for Women | Round Neck 3/4 Sleeve Ethnic Suit | Designer Indian Kurti Outfit with Pants</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61fcQ1xXDdL._AC_AIweblab1392912,T4_SF1358,1694_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GT99T4WH</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>GoSriKi Poly Kurta for Women | Kurta with Narrow Pant &amp; Dupatta | Straight Solid Suit | Indian Ethnic Outfit Office Party Wedding Clothing Fashion Premium Traditional Style Look 3 Piece</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71YwUB3j14L._AC_AIweblab1392912,T4_SF1272,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GQTXCCMT</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Klosia Women Embroidery Solid Straight Kurta and Pant Set with Dupatta</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/719NauczPjL._AC_AIweblab1392912,T4_SF1208,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GM91511K</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Nermosa Women's Pure Viscose Block Printed Ethnic Wear Straight Kurta Set with Palazzo Pants &amp; Dupatta | Kurta Set for Women | 3 Piece Set</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71L-WyS26RL._AC_AIweblab1392912,T4_SF1076,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H3FDN9T6</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Yashika Women's Chikankari Georgette Embroidery Kurta Set with Pant and Dupatta | Traditional Ethnic Co-ord Set for Women | Office, Casual Wear</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61uoIZOXj0L._AC_AIweblab1392912,T4_SF990,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HDDF86CN</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ANNI DESIGNER Women's Viscose Straight Printed Kurta with Pant &amp; Dupatta</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61PHOMhPdCL._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0F8ZXJXLK</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>INDO ERA Women's Straight Cotton Kurta Palazzo with Dupatta Set | Cotton kurta sets for women</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71hHe9qwy3L._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09PRGR4KH</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ANNI DESIGNER Viscose Blend Co Ord Set for Women | Kurta with Palazzo | Kurti Set Woman | Printed Ethnic Outfit | Cord Style Indian Dress Office Party Traditional Clothing Fashion Premium Modern Look</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/510GrdNJJvL._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FQP68MCS</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Rayon Kurti Pant and Dupatta Set, Mustard Yellow with Red Dupatta, Embroidered V-Neck, 3-Piece Ethnic Wear</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51oR3Gn8-oL._AC_AIweblab1392912,T4_SF1112,1482_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GTYVC53S</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E219"/>
+  <dimension ref="A1:E239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5009,6 +5009,466 @@
       </c>
       <c r="E219" t="inlineStr"/>
     </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Impex Migo Non-Stick Cookware Set, 4 Pcs Induction Bottom 3mm Thick, 5-Layer Super Granite Coating, Frying Pan Kadai Tawa 24cm, Gas &amp; Induction Compatible, Festival Gift Set, 1 Yr Warranty</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81NDfQSapUL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CH2ZL47M</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟒-𝐏𝐈𝐄𝐂𝐄 𝐍𝐎𝐍𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓: Everything your kitchen needs in one Impex Migo cookware combo — frying pan, kadai pan and tawa pan plus accessories, perfect for daily Indian cooking, sautéing, frying, roasting and more, all in one set. | 🪨 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐍𝐎𝐍-𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Premium granite-finish nonstick coating applied in 5 durable layers ensures long-lasting nonstick performance, even food release, less oil cooking and constant heat distribution for healthier meals. | 🎨 𝐓𝐖𝐎-𝐒𝐈𝐃𝐄 𝐒𝐏𝐀𝐓𝐓𝐄𝐑 𝐃𝐄𝐒𝐈𝐆𝐍 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Stylish spatter-pattern coating on both interior and exterior gives this cookware set a modern, elegant look while adding an extra layer of coating durability against everyday kitchen wear and tear. | ⚡ 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐁𝐎𝐓𝐓𝐎𝐌: Sturdy 3mm thick induction-compatible base ensures even heat distribution, faster cooking and no hot spots, making this cookware set reliable for daily use on any modern Indian kitchen cooktop. | 🔥 𝐌𝐔𝐋𝐓𝐈-𝐂𝐎𝐎𝐊𝐓𝐎𝐏 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄 — GAS, ELECTRIC &amp; INDUCTION: Designed to work seamlessly across gas stoves, electric cooktops and induction cooktops, this Impex cookware set offers complete versatility for every kind of kitchen setup. | 🤚 𝐒𝐓𝐔𝐑𝐃𝐘 𝐂𝐇𝐑𝐎𝐌𝐄 𝐇𝐀𝐍𝐃𝐋𝐄𝐒 𝐖𝐈𝐓𝐇 𝐃𝐈𝐑𝐄𝐂𝐓 𝐑𝐈𝐕𝐄𝐓𝐈𝐍𝐆: Ergonomically designed chrome-finish handles are securely direct-riveted to each pan, offering a strong, comfortable and heat-resistant grip so you can cook safely every single day | 🍲 𝐕𝐄𝐑𝐒𝐀𝐓𝐈𝐋𝐄 𝐏𝐀𝐍 𝐕𝐀𝐑𝐈𝐄𝐓𝐘 — FRYING PAN, KADAI &amp; TAWA (24CM EACH): This set includes a 24cm frying pan for shallow frying, a 24cm kadai pan for deep frying and curries, and a 24cm tawa pan for rotis, dosas and parathas — total flexibility. | 🎁 𝐈𝐃𝐄𝐀𝐋 𝐅𝐄𝐒𝐓𝐈𝐕𝐀𝐋 &amp; 𝐎𝐂𝐂𝐀𝐒𝐈𝐎𝐍 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓: Beautifully designed and practically useful, this Impex Migo cookware set makes a thoughtful gift for Diwali, weddings, housewarmings, anniversaries or any festive celebration with family and friends. | ✨ 𝐋𝐎𝐍𝐆-𝐋𝐀𝐒𝐓𝐈𝐍𝐆 𝐃𝐔𝐑𝐀𝐁𝐈𝐋𝐈𝐓𝐘 &amp; 𝐄𝐀𝐒𝐘 𝐅𝐎𝐎𝐃 𝐑𝐄𝐋𝐄𝐀𝐒𝐄: The robust non-stick construction resists scratches from daily cooking, ensures smooth easy food release, simplifies cleaning after every meal and keeps performing reliably for years. | 🛡️ 𝐁𝐀𝐂𝐊𝐄𝐃 𝐁𝐘 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘: Cook with complete confidence knowing your Impex Migo cookware set is backed by a 1 Year Manufacturer Warranty, ensuring assured quality, reliable support and long-term value for your kitchen investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Induction Cast Iron Non Stick Cookware 2 Piece Set Fry Pan Kadai Kitchen Combo Gas Stove Compatible Durable Daily Use Black Free Size</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31CrkKQASNL.jpg</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GXF1J4ZN</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Multi Purpose Cookware: Includes kadai sauce pan fry pan tawa and tadka pan for diverse cooking needs | Non Stick Surface: Ensures easy cooking with less oil and prevents food from sticking | Even Heat Distribution: Designed to cook food evenly for better taste and texture | Easy Maintenance: Simple to clean and maintain for regular kitchen use | Suitable for All Kitchens: Ideal for home restaurants hotels and professional cooking setups</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Crystal 11 Pcs Non Stick Cookware Set with Storage Containers | Gas Stove Friendly | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 2 Containers &amp; Grater Set | PFOA Free Coating</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71q-5-ENFCL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41FFYYF</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Attractive white marble coated cookware combo | Gas stove compatible design for convenient cooking | Nonstick coating supports healthy cooking with less oil | Durable body for long-lasting usage | Elegant appearance suitable for every kitchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Vinod Grandior Pro Hybrid Triply Stainless Steel Cookware Set - 4 pcs</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81mFtaFRHDL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HBCCG67L</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>EVERYDAY MEALS, ONE SET : Move from breakfast dosas to sabzi and curries with a 28 cm tawa, 22 cm frypan and 22 cm kadai. Grandior Pro brings three useful cooking shapes together, so you can choose the right vessel for each dish. | HEXA SHIELD COOKING SURFACE : Raised stainless-steel peaks sit above protected non-stick valleys in the honeycomb surface. This combination supports easier everyday food release while keeping the textured cooking surface visible. | TRIPLY SAS CONSTRUCTION : Stainless steel, aluminium and stainless steel form the three-layer cookware body. The aluminium layer helps distribute heat, bringing practical heat-spreading construction to everyday home cooking. | ONE LID, TWO VESSELS : The common stainless-steel lid fits the 22 cm kadai and 22 cm frypan, giving you a covered-cooking option for either vessel. One lid is included, so the two vessels cannot both be covered at the same time. | BREAKFAST TO MAIN COURSE : Use the 28 cm, 4 mm thick dosa tawa for dosas, uttapam and chilla; choose the kadai for curries and sabzi, or the frypan for sauteing and shallow frying. The 4 mm thickness refers to the tawa only. | FITS YOUR COOKTOP ROUTINE : The set is compatible with gas, induction, electric, ceramic and halogen cooktops. Choose the vessel that suits your dish and cooking zone; the set brings matching cookware to different kitchen setups. | CLEANING MADE PRACTICAL : The three cookware vessels are dishwasher safe, giving you a cleaning option after everyday meals. Follow Vinod's product-specific care guidance when choosing utensils, heat settings and cleaning products. | KNOW EXACTLY WHAT IS INCLUDED : Receive a 22 cm kadai with 2.3 L capacity, a 22 cm frypan with 1.5 L capacity, a 28 cm dosa tawa and one common stainless-steel lid. This is three cookware vessels plus one lid, not four vessels. | 5-YEAR WARRANTY : Enjoy added peace of mind with the Vinod Grandior Pro cookware set, backed by a 60-month warranty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Bergner Sienna Elite 6 Pcs Granite Non-Stick Cookware Set - 24cm Kadai with Lid, Casserole 24cm with Lid, Frypan 24cm, Tawa 28cm, Healthy Marble Coating, Less Oil Use, Cast Aluminium Induction Bottom</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/816IMhz4n9L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FNN15J7K</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>🔶Premium Sienna Elite Series by Bergner : Elevate your kitchen with this elegant and high-performance 6-piece non-stick cookware set designed for everyday and gourmet cooking | 🍳 Complete Cookware Set for Every Meal : Includes : 28cm Tawa, 24cm Frypan, 24cm Kadai with Glass Lid, 24cm Casserole with Glass Lid – ideal for sautéing, frying, simmering &amp; more | 💪 Durable Cast Aluminium Body : Built with heavy-gauge cast aluminum for long-lasting strength, rust resistance &amp; quicker, even heat distribution across the surface | 🌿 Healthy Marble Non-Stick Coating : Enjoy oil-free cooking with Bergner’s PFOA-free marble coating, ensuring effortless food release and healthier meals every time | 🔥 Induction &amp; Gas Stove Compatible : Features a full induction bottom, compatible with induction cooktops, gas stoves, electric and vitro-ceramic – versatile for all kitchens | 🧼 Effortless Cleaning &amp; Maintenance : Non-stick surface makes it easy to clean after use. (Note: Hand wash recommended; not dishwasher safe.) | 🖐️ Soft-Touch Handles with Strong Grip : Ergonomic, stay-cool handles provide a comfortable, secure grip while cooking, flippingor serving | 💧 Flared Rim for Drip-Free Pouring : Smartly designed rim ensures easy, mess-free pouring of liquids like curries, saucesor soups | 🎁 Perfect Gift for Home Chefs : Ideal for housewarming, anniversary, birthdayor festive gifting, this elegant cookware set is both stylish and functional | ✅ 1-Year Manufacturer Warranty : Enjoy peace of mind with Bergner’s quality assurance and dedicated customer support</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Bergner Ivory Black Granite Non-Stick 4 Pcs Cookware Set - 24cm (2.5L) Kadai with Glass Lid, 24cm Frypan, 28cm Dosa Tawa, Forged Aluminium, Soft Touch Handle, PFOA Free, Induction and Gas Stove Ready</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81PIQSla1EL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0G5PRN1DP</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>⚫ Ivory Granite Series : Elegant design that adds a touch of sophistication to any kitchen | 🍳 4 Pcs Cookware Set : Includes a 24cm (2.5L) Kadai with Glass Lid, 24cm Frypan, and 28cm Dosa Tawa for versatile cooking | 🌱 3-Layer Marble Non-stick Healthy Coating : Cook with minimal oil for healthier meals and easy food release | 🔨 Forged Aluminium : Durable and long-lasting construction for daily use | ♨️ Even Heat Distribution : Ensures uniform cooking and consistent results every time | 🥗 Consumes Less Oil, Healthy Cooking : Perfect for health-conscious cooking with reduced oil for frying and sautéing | ✋ Wooden Soft Touch Handle with Excellent Grip : Stay comfortable and safe with heat-resistant, ergonomic handles | 🧼 Hand Wash Only (Not Dishwasher Safe) : For optimal care and longevity of the non-stick surface | 🔥 Gas, Electric, Vitro Ceramic, and Induction Compatible : Works on all stovetops, including induction, for ultimate convenience | 🛡️ 1-Year Warranty : Peace of mind with a 1-year warranty ensuring durability and quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set Detachable Handle |Granite Finish | Induction Base | Pfoa Free | High Temperature Resistant Exterior Coating | Black</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61WLcHiMuDL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZW3SG7G</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Kadai, 1 Glass Lid</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Bergner Ivory Granite Non-Stick 4 Pcs Cookware Set - 24cm/2.5L Kadai with Lid 24cm Frypan 28cm Dosa Tawa 3-Layer Marble Healthy Coating PFOA Free Forged Aluminium - Induction and Gas Stove Ready</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61I02u0TJWL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GF7FZGR8</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>🍳 Complete 4-Piece Cookware Set : Includes 24cm (2.5L) Kadai with Glass Lid 24cm Frypan &amp; 28cm Dosa Tawa – perfect for everyday Indian cooking | 🔘 Ivory Granite Series Design : Modern granite finish adds durability and a stylish look to your kitchen | 🧱 Forged Aluminium Construction : Strong warp-resistant build offers long-lasting performance and superior heat retention | 🌟 3-Layer Marble Non-Stick Coating : PFOA-free for safe cooking; ensures minimal oil use and easy food release | 🔥 Even Heat Distribution : No hot spots just consistent cooking results across all cookware pieces | 🥗 Healthy Cooking with Less Oil : Ideal for dosa stir-fry curries sautéing and more with reduced oil usage for a healthy lifestylecookware set cookware combo nonstick cookware set nonstick 4 pcs set 4 pcs cookware set best nonstick combo granite nonstick coating forged aluminium | 🌳 Soft-Touch Rivetless Wooden Handles : Ergonomic heat-resistantand elegant for a comfortable grip | 🥄 Glass Lid with Steam Vent : Keeps moisture and nutrients locked in while allowing pressure control during cooking | 🌀 Compatible with All Cooktops : Works on gas induction electricand vitro ceramic stoves | 🛡️ 1-Year Manufacturer Warranty : Reliable quality assurance from Bergner for complete peace of mind</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Induction Base Cast Iron Non Stick Cookware Set of 5 Kadai Fry Pan Tawa Saucepan Tadka Pan Kitchen Combo Set Black Free Size</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31AWpoJd84L.jpg</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GXDZNPR2</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Multi Purpose Cookware: Includes kadai sauce pan fry pan tawa and tadka pan for diverse cooking needs | Non Stick Surface: Ensures easy cooking with less oil and prevents food from sticking | Even Heat Distribution: Designed to cook food evenly for better taste and texture | Easy Maintenance: Simple to clean and maintain for regular kitchen use | Suitable for All Kitchens: Ideal for home restaurants hotels and professional cooking setups</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Amazon Basics Aluminum Non-Stick 15 Piece Cookware Set | 2-Way 3 Layer Non-Stick Coating | PFOA Free | High Temperature Resistant Exterior Coating, Black</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71oZ1-QYomL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B8D6GW8S</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Make cooking a joyful process with this durable non-stick 15-piece cookware set | The pressed aluminium cookware body is ultra-conductive and corrosion-free, which enables quick heating and helps save energy | Stay-cool phenolic handles are heat-resistant and remain cool even at high cooking temperatures | USFDA and European Food Safety Authority (EFSA)-approved coatings are 100% free from PFOA, lead, cadmium, nickel, and arsenic | The 2-layered exterior coating makes it scratch-resistant; the 3-layered interior with water-based eco-friendly PFOA-free coating promotes healthy cooking</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Bergner Copper+ Non Stick Cookware Set 4 Pcs - 24cm (2.3L) Kadai with Lid, 24cm (1.5L) Frypan and 25cm Tawa, 3-Layer Non-Stick Coating, PFOA Free, Bakelite Handles - Induction and Gas Stove Ready</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71PteE9UxqL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HGM81N8G</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>🍳 4-Piece Cookware Set : Includes 24cm Kadai with Lid (2.3L), 24cm Fry Pan and 25cm Tawa for everyday cooking needs | 🥘 3-Layer Non-Stick Coating : High-performance 3-layer coating helps provide smooth cooking with minimal oil | 🔥 Induction &amp; Gas Compatible : Designed for induction cooktops and compatible with all types of gas stoves | 🛡️ Heavy Gauge Construction : Sturdy construction supports even heat distribution and helps reduce food burning | 🥗 Healthy Cooking : PFOA-free non-stick coating supports low-oil cooking for healthier everyday meals | 🖐️ Bakelite Handles : Heat-resistant Bakelite handles provide a comfortable and secure grip while cooking | 👀 Tempered Glass Lid : Durable tempered glass lid with steam hole helps monitor food while it cooks | 🍲 Versatile Cookware : Ideal for frying, sautéing, simmering, making curries, rotis, dosas and everyday meals | ✨ Premium Copper Brown Finish : Stylish copper brown exterior with a black cooking surface adds a modern touch to your kitchen | 🧼 Easy Cooking &amp; Cleaning : Smooth non-stick surface helps make cooking convenient and cleaning easier after use</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Hawkins Quik Nonstick Induction 4 Piece Cookware Set of Deep Kadhai, Frying Pan, Saucepan and Stainless Steel Lid | Kitchen Gift Pack | Grey (IQGP1)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71Ujg8yco+L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GD5QFJ19</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Healthy PFOA-free Nonstick inside - Healthy low oil cooking | Durable ceramic coating outside - stays looking new | 3mm Thick Pans - Food will not burn or stick | Rivet-less cooking surface - easy to stir, easy to clean | Deep shape - Stir-fry, High-walls. Cook large quantities</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Amazon Basics Ceramic Non Stick Cookware Set 3 Pieces | 28cm Dosa Tawa, 24cm Fry Pan, 24cm Kadai with Glass Lid (2.3L) | Gas &amp; Induction Compatible | Wooden Finish Bakelite Handle | Ivory</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71P4TioZa-L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GTMNVQ4Z</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>3-Piece Cookware Set: Includes dosa tawa, fry pan &amp; kadai with lid. | Ceramic Non-Stick: Easy food release with low-oil cooking. | Even Heat Distribution: Ensures consistent cooking results. | Gas &amp; Induction Compatible: Suitable for all cooktops. | Tempered Glass Lids with Steam Vent: Helps retain heat and monitor cooking. | Ergonomic Handles: Comfortable and safe grip while cooking. | Easy to Clean: Low maintenance and hassle-free use. | Care Tip: Pre heat max 2 mins then cook on low to medium heat with light oil for longer durability. | Non Toxic Coating: PFOA free, PTFE free and BPA free stain resistant coating for safe everyday cooking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Amazon Brand SOLIMO - 3 PCS Non-Stick COOKWARE SET | Aluminium</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51Ql6IsQTzL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07P912X7R</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>3 piece non-stick cookware set includes fry pan, flat tawa and kadhai with a glass lid for everyday cooking | Made using good quality virgin aluminium which is durable, long lasting, and offers even heat distribution | Food grade 2-way non-stick coating: Cooking surface has a 3 layered coating; outer layer has a finish with high temperature resistance (HTR) coating | Equipped with bakelite handles that offer safe and firm ergonomic grip | Ideal for preparing rotis, chapatis, dosa, stir-fries, pulao, sauteed vegetables, sear meats, fish, fry eggs and more | Compatible with gas stove and induction cooktops | Easy to clean and maintain; dishwasher safe | Comes with a 1-year warranty against manufacturing defects | Product Dimensions- Fry Pan:- Diameter: 220 mm (22 cm); Thickness: 3 mm; Depth: 45 mm (4.5 cm); Capacity: 1650 ml; Weight: 610 gm; Tawa:- Diameter: 265 mm (26.5 cm); Thickness: 3 mm; Depth: 13 mm (1.3 cm); Weight 615 gm; Kadhai:- Diameter: 220 mm (22 cm); Thickness: 3mm; Depth: 73 mm (7.3 cm); Capacity: 2500 ml; Weight: 1125 gm | Caution: For better longevity of the cookware, avoid using Metal Scrubber for coated non-stick utensils. Do not use metal spoons and ladles on coated non-stick utensils. For better and lasting coating durability, use only soft nylon scrubber and wooden /nylon ladles &amp; spoons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Bergner Aloe 4 Pcs Non-Stick Cookware Set of 24cm (2.5L) Kadai with Glass Lid, 24cm Fry Pan, 25cm Tawa, Bakelite Handles, 3-Layer Superior Non-Stick Coating, PFOA Free - Induction and Gas Stove Ready</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/819YbZK9sGL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HK16KG2M</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>🍳 4-piece complete cookware set : Includes 24cm Kadai with lid (2.5L), 24cm fry pan and 25cm tawa - everything you need for everyday cooking | 🛡️ 3-layer superior non-stick coating : Ensures minimal oil usage, easy food release and effortless cleaning every time | 🔥 Heavy gauge construction : Enables even heat distribution, prevents food from burning and helps retain nutrients in food | 🚫 PFOA free material : Prevents harmful chemicals from leaching into food, keeping your cooking safe and healthy | 🖐️ Bakelite handles for excellent grip : Stay cool to touch and provide a comfortable, secure hold while cooking | ⚡ Induction friendly : Compatible with all types of cooktops, including induction, gas, vitroceramic and halogen | 🔍 Tempered glass lid with steam hole : Lets you monitor food while it cooks and helps release excess steam | 🌿 Healthy cooking certified : No cadmium, no lead, no PFOA - safe for you and your family | 🧼 Hand wash recommended : Not dishwasher safe - a quick hand wash keeps the non-stick coating in top condition for longer | 🛠️ 1 year warranty : Backed by Bergner's assurance of durability and long-lasting performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Prestige Svachh Granite Non-Stick 3-Piece Set Cookware |Dual Non-Stick Delight|Omni Tawa - 28cm Dia, Kadai with GlassLid - 24cm Dia, Fry Pan - 24cm Dia|Gas and Induction Compatible|Easy Care</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61SnP+JylSL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D5YM8SM6</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>DUAL NON-STICK DELIGHT : Durable non stick coating inside and outside for an effortless cleaning. | EASY CARE: Non-Stick Inside &amp; Outside for easy cleaning. Simply soak in soapy water &amp; rinse | EVEN HEAT DISTRIBUTION: Quick, Uniform Heating with Remarkable Durability | CONTENTS: Omni Tawa : 28cm Diameter, Kadai with Lid: 24cm Diameter, Fry Pan: 24cm Diameter | COMPATIBLE: Suitable for usage on Gas and Induction</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Wonderchef Royal Velvet 5Pc Non-Stick Cookware Set for Kitchen, Fry Pan 24cm, Mini Fry Pan 14cm, Wok with Lid 24cm, Dosa Tawa 24cm, Non-Toxic, Gas Stove &amp; Induction Friendly, 2-Yr Warranty, Purple</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/619aKEsYe4L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B00XVQ0J8I</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Coating type: Non-Stick | NON-STICK EXCELLENCE - Savor the benefits of healthy cooking with minimal oil, thanks to the proprietary METATUFF non-stick coating that delivers scratch resistance and effortless cleaning. MetaTuff 5-layer non-stick coating is 100% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | EFFORTLESS COOKING - Revolutionize your cooking experience with the durable, easy-to-handle Wonderchef Royal Velvet set that takes the hassle out of daily meal preparation | COLLECTIVE SET - Kadhai with Lid, Fry Pan, Dosa Tawa let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | VERSATILITY AT ITS FINEST - With the ability to be used on both gas stoves and induction cooktops, this cookware set ensures flexibility and convenience in your kitchen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Lifelong 3 Piece Forged Cookware Set With Common Lid |2.2L Kadhai with Lid 24cm |Ceramic Coated |1.4L Fry Pan 24cm | 1.2L Tawa 26cm |Induction &amp; Gas Compatible | Non-Riveted Handle | Non-Stick Coating</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/5155aqiCAYL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FL2K6L6H</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Versatile 3-piece cookware set – Includes a 2.2L kadhai with lid (24cm), 1.4L fry pan (24cm), and 1.2L tawa (26cm) to handle all your everyday cooking needs. Perfect for sautéing, frying, simmering, and more. An all-in-one solution for daily Indian and continental cooking. | Common glass lid for added convenience – The single tempered glass lid fits both the kadhai and fry pan, allowing easy cooking, heat retention, and visible monitoring without lifting the lid. Reduces clutter and offers space-saving practicality in your kitchen. | Non-riveted handles for better hygiene – Smooth, screw-free handles offer a secure and comfortable grip while cooking. Easier to clean and safer for long-term use in busy kitchens. Eliminates food buildup and rust issues seen in riveted designs. | PFOA-free non-stick coating – Cook with less oil and enjoy effortless food release. The toxin-free, scratch-resistant coating ensures healthier meals and easy cleanup after every use. Built for durability, it maintains performance over time. | Compatible with induction &amp; gas – Works efficiently on both induction cooktops and gas stoves, providing flexibility for all kitchen setups. Even heat distribution enhances cooking results. Great for both modern and traditional cooking environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Hawkins Futura Nonstick Kitchen Gift Set - 2 L Stir-Fry Pan with Glass Lid, 17 cm Frying Pan with Stainless Steel Lid and 22 cm Tava, Black (24NSGP)</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61-fGGnjDxL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DRVNWKJH</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>PFOA Free Non-stick coating locked into tough Hard Anodised Aluminium - lasts longer | The cookware set consisting a Stir-Fry Pan with glass lid, a Frying Pan with stainless steel lid and a Tava caters to most of your cooking needs | The pans are made from heavy gauge pure, virgin metal - last longer | The pans are offered with elegant, comfortable handles which are permanently riveted to the Pans - will not loosen | The lids trap flavors, cook faster and make food tastier</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Impex Aluminium Migo Nonstick Granite 6 Pcs Induction Bottom Cookware Set 3 Mm Thick,Festival Gift Set Mfkt 6,5-Layer Super Granite Coated Cookware Set,Hammer Tone Exterior Finish,1 Yr Warranty, Grey</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81q152DZrLL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CH3BMNN6</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Complete 6-Piece Cookware Set: Elevate your culinary experience with a comprehensive 6-piece cookware collection, featuring versatile pieces for various cooking needs. | Durable 5-Layer Super Granite Coating: Crafted with a robust 5-layer super granite nonstick coating, this cookware set ensures longevity, even heat distribution, and easy food release. | Uniform 24 cm Size: Each piece in this set features a uniform size of 24 cm, offering consistency in your cooking and serving. | Induction-Compatible Design: The cookware pieces come with induction-compatible bottoms, making them suitable for use on gas, electric, and induction cooktops, providing flexibility in your kitchen. | Dishwasher Safe: This cookware set is dishwasher safe, saving you valuable time and effort on post-cooking cleaning.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E239"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3550,17 +3550,17 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ADISA Women's Quilted Crossbody Sling Bag - Stylish Cross Body Handbag for Girls &amp; Women with Gold Chain (SL5059)</t>
+          <t>Pure Vegan Leather Tote Bag for Women, Fully Embossed, Handbag, Shoulder Bag, Black</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61jsDR7kaYL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/714Xb1jFm2L._SY695_.jpg</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B09154JPWQ</t>
+          <t>https://www.amazon.in/dp/B0D8XQQD1P</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -3569,17 +3569,17 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pure Vegan Leather Tote Bag for Women, Fully Embossed, Handbag, Shoulder Bag, Black</t>
+          <t>ADISA Women's Crossbody Sling Bag - Stylish Cross Body Handbag for Girls &amp; Women - Adjustable Strap Shoulder Bag (SL5141)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/714Xb1jFm2L._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71I4Yx1anzL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0D8XQQD1P</t>
+          <t>https://www.amazon.in/dp/B0CZPJRDQN</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -3588,17 +3588,17 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ADISA Women's Crossbody Sling Bag - Stylish Cross Body Handbag for Girls &amp; Women - Adjustable Strap Shoulder Bag (SL5141)</t>
+          <t>Lavie Woman's Broxa Flap Crossbody Sling Bag | Ladies Purse Handbag | Gift for Women</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71I4Yx1anzL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61L+2HeKv-S._SY575_.jpg</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0CZPJRDQN</t>
+          <t>https://www.amazon.in/dp/B08QTF8RPM</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -3607,17 +3607,17 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lavie Woman's Broxa Flap Crossbody Sling Bag | Ladies Purse Handbag | Gift for Women</t>
+          <t>Lavie Women's Yalta Satchel Bag | Ladies Purse Handbag</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61L+2HeKv-S._SY575_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71EwockPQkL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B08QTF8RPM</t>
+          <t>https://www.amazon.in/dp/B097MXFVYL</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -3626,17 +3626,17 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Lavie Women's Yalta Satchel Bag | Ladies Purse Handbag</t>
+          <t>Caprese TRACY S Large</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71EwockPQkL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61OGd5IBEiL._SY695_.jpg</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B097MXFVYL</t>
+          <t>https://www.amazon.in/dp/B08ZJZTCHR</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -3645,17 +3645,17 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Lavie Women's Emberlyn Crossbody Sling Bag | Ladies Purse Handbag | Gift for Women</t>
+          <t>Lyrovo Clutch Purse for Women Formal Dressy Evening Clutches Handbags Crossbody Bag for Wedding Cocktail Prom Elegance Charm</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61GiQqm3XkL._SY575_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61Qn7SrsJJL.jpg</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0DVLP96WP</t>
+          <t>https://www.amazon.in/dp/B0F6TZ572V?th=1</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -3664,17 +3664,17 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Caprese TRACY S Large</t>
+          <t>Lavie Women's Ficus Medium Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61OGd5IBEiL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71k9FI0t6aS._SY695_.jpg</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B08ZJZTCHR</t>
+          <t>https://www.amazon.in/dp/B08NVF9V9L</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -3683,17 +3683,17 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lyrovo Clutch Purse for Women Formal Dressy Evening Clutches Handbags Crossbody Bag for Wedding Cocktail Prom Elegance Charm</t>
+          <t>GoSriKi Women Salsa A-Line Kurta with Palazzo | Embroidered Kurta Set for Women | Round Neck A-Line Ethnic Kurta Palazzo Outfit for Casual Festive &amp; Party</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61Qn7SrsJJL.jpg</t>
+          <t>https://m.media-amazon.com/images/I/618st+zD9fL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0F6TZ572V?th=1</t>
+          <t>https://www.amazon.in/dp/B0GM7ZQVY7</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -3702,17 +3702,17 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lavie Women's Ficus Medium Satchel Handbag for Women | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women</t>
+          <t>AASK Women Fancy Plain &amp; Solid Fit And Flare Knee Length Designer Dress for Women</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71k9FI0t6aS._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71ZyLRR01LL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B08NVF9V9L</t>
+          <t>https://www.amazon.in/dp/B0CQNZLM3R</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -3721,17 +3721,17 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Fostelo Luxe Westside Purse For Women Handbag</t>
+          <t>Leriya Fashion Dress for Women | Western Floral Printed One Piece Dress for Women midi | Casual Sleeveless Summer Dresses for Beach &amp; Stylish Party Outifits</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81RRF-w1yVL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61O0Db6KRdL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B07D7W3YFT</t>
+          <t>https://www.amazon.in/dp/B0GDQFY4HC</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -3740,17 +3740,17 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ZOUK Office Bag | Stylish Bags for Office Use | Laptop Bag 15.6 inch | Stylish Tote for Office Use | Purse for Women | Vegan Leather Handbag | Daily &amp; Travel Use |</t>
+          <t>Klosia Women Pure Cotton Kurta Palazzo Set | Sleeveless Printed Kurta with Palazzo Pants | Summer Friendly, Office Wear Co-Ord Set</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71iBiB-pnGL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41YF5GlKMXL._SY741_.jpg</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B07LB7V3MV</t>
+          <t>https://www.amazon.in/dp/B0GGHQSL6P</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -3759,1713 +3759,160 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Women’s Metallic Shoulder Bag – Croc-Embossed Patchwork Leather Look Handbag with Zipper Closure, Trendy Underarm Purse.</t>
+          <t>Crystal 11 Pcs Non Stick Cookware Set with Storage Containers | Gas Stove Friendly | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 2 Containers &amp; Grater Set | PFOA Free Coating</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51dFX521euL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71q-5-ENFCL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0GXVSDJ8C</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+          <t>https://www.amazon.in/dp/B0H41FFYYF</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Attractive white marble coated cookware combo | Gas stove compatible design for convenient cooking | Nonstick coating supports healthy cooking with less oil | Durable body for long-lasting usage | Elegant appearance suitable for every kitchen</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mochi Women Casual PU Soft Body Zipper closure Solid Sling Bag</t>
+          <t>Vinod Grandior Pro Hybrid Triply Stainless Steel Cookware Set - 4 pcs</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/81Y714RE3BL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/81mFtaFRHDL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0FDB1ZC99</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
+          <t>https://www.amazon.in/dp/B0HBCCG67L</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>EVERYDAY MEALS, ONE SET : Move from breakfast dosas to sabzi and curries with a 28 cm tawa, 22 cm frypan and 22 cm kadai. Grandior Pro brings three useful cooking shapes together, so you can choose the right vessel for each dish. | HEXA SHIELD COOKING SURFACE : Raised stainless-steel peaks sit above protected non-stick valleys in the honeycomb surface. This combination supports easier everyday food release while keeping the textured cooking surface visible. | TRIPLY SAS CONSTRUCTION : Stainless steel, aluminium and stainless steel form the three-layer cookware body. The aluminium layer helps distribute heat, bringing practical heat-spreading construction to everyday home cooking. | ONE LID, TWO VESSELS : The common stainless-steel lid fits the 22 cm kadai and 22 cm frypan, giving you a covered-cooking option for either vessel. One lid is included, so the two vessels cannot both be covered at the same time. | BREAKFAST TO MAIN COURSE : Use the 28 cm, 4 mm thick dosa tawa for dosas, uttapam and chilla; choose the kadai for curries and sabzi, or the frypan for sauteing and shallow frying. The 4 mm thickness refers to the tawa only. | FITS YOUR COOKTOP ROUTINE : The set is compatible with gas, induction, electric, ceramic and halogen cooktops. Choose the vessel that suits your dish and cooking zone; the set brings matching cookware to different kitchen setups. | CLEANING MADE PRACTICAL : The three cookware vessels are dishwasher safe, giving you a cleaning option after everyday meals. Follow Vinod's product-specific care guidance when choosing utensils, heat settings and cleaning products. | KNOW EXACTLY WHAT IS INCLUDED : Receive a 22 cm kadai with 2.3 L capacity, a 22 cm frypan with 1.5 L capacity, a 28 cm dosa tawa and one common stainless-steel lid. This is three cookware vessels plus one lid, not four vessels. | 5-YEAR WARRANTY : Enjoy added peace of mind with the Vinod Grandior Pro cookware set, backed by a 60-month warranty.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DANIEL CLARK Women's Stylish Handbags Combo (Set of 3)</t>
+          <t>Bergner Sienna Elite 6 Pcs Granite Non-Stick Cookware Set - 24cm Kadai with Lid, Casserole 24cm with Lid, Frypan 24cm, Tawa 28cm, Healthy Marble Coating, Less Oil Use, Cast Aluminium Induction Bottom</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/717u1Q0IGGL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/816IMhz4n9L._SX679_.jpg</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0963DGWJ4</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
+          <t>https://www.amazon.in/dp/B0FNN15J7K</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>🔶Premium Sienna Elite Series by Bergner : Elevate your kitchen with this elegant and high-performance 6-piece non-stick cookware set designed for everyday and gourmet cooking | 🍳 Complete Cookware Set for Every Meal : Includes : 28cm Tawa, 24cm Frypan, 24cm Kadai with Glass Lid, 24cm Casserole with Glass Lid – ideal for sautéing, frying, simmering &amp; more | 💪 Durable Cast Aluminium Body : Built with heavy-gauge cast aluminum for long-lasting strength, rust resistance &amp; quicker, even heat distribution across the surface | 🌿 Healthy Marble Non-Stick Coating : Enjoy oil-free cooking with Bergner’s PFOA-free marble coating, ensuring effortless food release and healthier meals every time | 🔥 Induction &amp; Gas Stove Compatible : Features a full induction bottom, compatible with induction cooktops, gas stoves, electric and vitro-ceramic – versatile for all kitchens | 🧼 Effortless Cleaning &amp; Maintenance : Non-stick surface makes it easy to clean after use. (Note: Hand wash recommended; not dishwasher safe.) | 🖐️ Soft-Touch Handles with Strong Grip : Ergonomic, stay-cool handles provide a comfortable, secure grip while cooking, flippingor serving | 💧 Flared Rim for Drip-Free Pouring : Smartly designed rim ensures easy, mess-free pouring of liquids like curries, saucesor soups | 🎁 Perfect Gift for Home Chefs : Ideal for housewarming, anniversary, birthdayor festive gifting, this elegant cookware set is both stylish and functional | ✅ 1-Year Manufacturer Warranty : Enjoy peace of mind with Bergner’s quality assurance and dedicated customer support</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>The Purple Tree Handcrafted Women's Tote Bag with Vegan Leather Handles &amp; Indian Prints, Shoulder Tote Bag and Handbag for Office and College (Pack of 1)</t>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set Detachable Handle |Granite Finish | Induction Base | Pfoa Free | High Temperature Resistant Exterior Coating | Black</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61oix3ol0eL._SX679_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/61WLcHiMuDL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0C9V6CJ9B</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
+          <t>https://www.amazon.in/dp/B0BZW3SG7G</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Kadai, 1 Glass Lid</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lavie Women's Kelissa Satchel Handbag | Satchel Bag for Work | Ladies purse | Stylish Shoulder Bag | Gift For Women</t>
+          <t>Amazon Basics Aluminum Non-Stick 15 Piece Cookware Set | 2-Way 3 Layer Non-Stick Coating | PFOA Free | High Temperature Resistant Exterior Coating, Black</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61b92ZDJ1jL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71oZ1-QYomL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0F66SNH8H</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
+          <t>https://www.amazon.in/dp/B0B8D6GW8S</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Make cooking a joyful process with this durable non-stick 15-piece cookware set | The pressed aluminium cookware body is ultra-conductive and corrosion-free, which enables quick heating and helps save energy | Stay-cool phenolic handles are heat-resistant and remain cool even at high cooking temperatures | USFDA and European Food Safety Authority (EFSA)-approved coatings are 100% free from PFOA, lead, cadmium, nickel, and arsenic | The 2-layered exterior coating makes it scratch-resistant; the 3-layered interior with water-based eco-friendly PFOA-free coating promotes healthy cooking</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Metro Women Textured Top-Handle Bag</t>
+          <t>Hawkins Quik Nonstick Induction 4 Piece Cookware Set of Deep Kadhai, Frying Pan, Saucepan and Stainless Steel Lid | Kitchen Gift Pack | Grey (IQGP1)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/61rHhqpaHgL._SY695_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/71Ujg8yco+L._SX679_.jpg</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0D9TD3LZ7</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
+          <t>https://www.amazon.in/dp/B0GD5QFJ19</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Healthy PFOA-free Nonstick inside - Healthy low oil cooking | Durable ceramic coating outside - stays looking new | 3mm Thick Pans - Food will not burn or stick | Rivet-less cooking surface - easy to stir, easy to clean | Deep shape - Stir-fry, High-walls. Cook large quantities</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>AUSK Women’s Casual Summer Polo Knit T-Shirt | Zip Collar Top | Half Sleeves | Ribbed Panel Design | Lightweight Comfort | Regular Fit</t>
+          <t>Amazon Brand SOLIMO - 3 PCS Non-Stick COOKWARE SET | Aluminium</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/71pxWUGWUaL._SX569_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51Ql6IsQTzL._SX679_.jpg</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0H1HW8GQ2</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr"/>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Dream Beauty Fashion Women's Long Sleeve Slim Fit Top/T-Shirt Henley Neck Casual (Top-Saiyaara-1)</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41-OdGcmZlL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FP9JDGP8</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr"/>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Women Short Sleeve Polo T-Shirts, Lady's Summer Striped Shirt, Collar Neck Casual Tank Tops</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71WkX41n42L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G2MRNB2Q</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr"/>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Pinkmint Women Short Kurti | Cotton Blend Printed Tunic Top | Trendy Casual Top | Casual &amp; Office Wear Ethnic Top for Jeans</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71YNLQOl2qL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FZC9HLPP</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>RIEKA Women's Embroidered Top for Women, Maroon V Neck Rayon, 3/4 Sleeve Casual Loose Fit Tunic, Boho Blouse for Women, Korean Style</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81Al1oK1jdL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H4RF1241</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>LITZO Shirts for Women - Korean Style Long Sleeve Button Down | Regular Fit Western Latest Stylish Office Wear Tops Women (NO-98-101)</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61ptQCrrW1L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H6RPR52P</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr"/>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Dream Beauty Fashion Women's Sweet Heart Neck Balloon/Puff Bishop Sleeve Elegant Casual Tee Top, 23" inches (BZF-Top Mantos-01)</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61TcnMgHv4L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CG9HQYWL</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr"/>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Gufrina Women’s Light Rose Floral Printed Button Down Shirt with Mandarin Collar and Relaxed Fit 3/4 Sleeves</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71+8o4O1WCL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FNX2BNYH</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr"/>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Women’s Polo T-Shirt | Long Sleeve Casual T-Shirt for Womens || Soft Comfortable Korean Style Trendy Top for Women</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/511opfswW9L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GS9RSYBP</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr"/>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Lycra Casual Wear Full Sleeve Top for Women, Top for Girls, Regular Fit</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31hk042J4zL.jpg</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CKPYS2QZ</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr"/>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Women's Cotton Blend Korean Style 3/4 Sleeve Oversized Button Down|| Workwear Top Shirt for Office &amp; Casual Wear Women Shirt || Shirt for Woman || Top for Women (L-98-101)</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61a770ncRFL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GP6R2N67</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr"/>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>RIEKA Womens Floral Applique Embroidered Fancy Top with Mandarin Collar Button Down Front Half Sleeves Relaxed Fit Casual Tunic Top for Women</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71SaK12WYLL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H26984XN</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr"/>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>RIEKA Womens Embroidered Korean Style Top and Tunic; V Neck| Floral Thread Embroidery| Three Quarter Puff Sleeves |Relaxed Fit Curved Hem| Casual Everyday Fusion Top</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81Bp-xQtPwL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HBBFZNH4</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr"/>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>PLADO Women's and Girls Georgette Top Maroon</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51HFndVZO5L._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09NGN2BT2</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr"/>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Arayna Women's Pure Cotton Paisley Printed Tunic Top – Comfortable Everyday Wear</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81OS4czw-AL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DY1TRLF6</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr"/>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>BLACK BUDDY Women's Cotton Blend Full Sleeve Collared V Neck T Shirt for Women | Regular Fit Solid Rib Knit Stretch Top | Casual Office College Formal T Shirt | S-XXL</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/512Ti61s36L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H8S755PW</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr"/>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>LITZO Women Shirt || Shirt for Woman || Top for Women (L-187-190)</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/510vA977VmL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GNN27RDL</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr"/>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Max Women's Cotton Regular Fit Top</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61d3ftDKTFL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CYZK99NC</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr"/>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>GRECIILOOKS Women French Crepe Bandhani Bandhej Kalka Printed Formal Shirt | Casual Stylish Office Top Full Sleeve Shirts | Trendy Summer Tops | Smart Casual Top for Women's Button Down Modern Fit</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/7156yifeGyL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H9H9ZKY4</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr"/>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Leriya Fashion Tops for Woman | Women Solid Full Sleeve Top Rumble Ribbed Knit | Regular Fit V-Neck Style T Shirt for Woman | Chic Smart-Casual &amp; Everyday Wear T-Shirt</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/614V5yzYnBL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HF5DNSD8</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr"/>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Preneum Girl's &amp; Women's Solid Color V-Neck A-Line Maxi Dress for Women | New Year Party Outfit | Waist Cinched Puff Sleeve Western | Elegant Casual Wear (Availble in Plus Size)</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51i6M31WAbL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H8768K24</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr"/>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>GRECIILOOKS Women Summer Rayon A-Line Midi Dress | Sleeveless Tiered Stappy Sun Dress with Bows and Hearts Print | Casual Square Neck Flared Maxi Dresses for Beach and Vacation</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71fJKbCU4xL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FPB6TQ8R</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr"/>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>LITZO Women’s One Piece Dress - Georgette Solid Color Western Gown | Long Sleeve Round Neck Fit &amp; Flare Flared Hem Design | A-Line Maxi Dress for Women | New Year Party Outfit (NO-17-18)</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51ctChJKc9L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H5CR73BV</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr"/>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>GoSriKi Women Salsa A-Line Kurta with Palazzo | Embroidered Kurta Set for Women | Round Neck A-Line Ethnic Kurta Palazzo Outfit for Casual Festive &amp; Party</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/618st+zD9fL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GM7ZQVY7</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr"/>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>ANNI Designer Short Kurti for Women Latest Viscose Blend Printed Ethnic Tunic | Stylish Kurti Tops with Jeans Styling | Casual Office Wear | Trendy Indian Fashion for Woman</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61sYyNiVHdL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GQMSD4VT</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr"/>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>AASK Women Fancy Plain &amp; Solid Fit And Flare Knee Length Designer Dress for Women</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71ZyLRR01LL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CQNZLM3R</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr"/>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SHANTVAN GALLERY Co Ord Set for Women Stylish Card Set Dress for Women Trendy Top with Plazo Pant Ladies Coord Outfit Modern Wear for Travel Office Casual Look Premium Two Piece Clothing Style</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61ajdBrtVmL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G5XCTWM3</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr"/>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Zurity Women's V-Neck Sporty T-Shirt Dress | Stylish Striped Sleeve One Piece for Women | Casual Summer Knee Length Short Dress | Trendy Beach &amp; Resort Wear Western Dress (26 D-1-3)</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41YZ61LApyL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GVP2VYXT</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr"/>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Leriya Fashion Dress for Women | Western One Piece Dress for Women Short &amp; Long | Half Sleeve Casual Summer Dresses for Beach &amp; Stylish Party Outifits Below The Knee</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71rA91nZS8L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GDMG4CG1</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr"/>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Celary Woman's Co-Ord Set|Stylish Co Ord Set for Women with Floral Print &amp; Embroidered Kurta|Two Piece Set for Women|Trendy Casual Co Ords Set with Pants</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/516tsojBdGL._SX569_.jpg</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HDV9KXB5</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr"/>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Zurity Dress for Women ||Bohemian Brown Print Casual Comfortable Women's Long Sleeve Maxi Dress|| Popular Autumn Apparel Fashion (D-03-05)</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51gP0vCxEAL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GF957GT6</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr"/>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Leriya Fashion Dress for Women | Western Floral Printed One Piece Dress for Women midi | Casual Sleeveless Summer Dresses for Beach &amp; Stylish Party Outifits</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61O0Db6KRdL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GDQFY4HC</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr"/>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>ANNI Designer Women’s Viscose Blend Printed Short Kurti | Straight Fit Casual Ethnic Top | Square Neck Full Sleeve Kurta Office College</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71rnJFRpMIL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GNMPTYNY</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr"/>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Klosia Women Pure Cotton Kurta Palazzo Set | Sleeveless Printed Kurta with Palazzo Pants | Summer Friendly, Office Wear Co-Ord Set</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41YF5GlKMXL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GGHQSL6P</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr"/>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>LITZO Dress for Women || Women’s Solid Pleated Maxi Dress || Modest Long Sleeve Loose Fit Flowy Gown for Casual, Office &amp; Brunch || Lightweight Comfortable Western Outfit (T-L-17-18)</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61abwaouC7L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DQCMDBHV</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr"/>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>GRECIILOOKS Summer Dress for Women Midi Dress for Woman | Sleeveless Striped Design | Maxi Dresses Stylish | Casual Western Vacation Dresses | Flowy A-Line Resort Wear for Brunch &amp; Beach Styling</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61m-sZfPnsL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H2QRCBSP</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr"/>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Modestouze Attires Women's Floral Pattern Rayon Blend Maxi Dress with Sweetheart Neck Half Puff Sleeve Floor Length and Zipper Closure Type | Maxi Dress for Women Stylish | Dress for Women</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71eKFCtyXUL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G57VGJMH</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr"/>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>GRECIILOOKS Co Ord Set For Women Stylish | Dress for Women | Trendy Summer Travel Outfit | Lightweight 2 Piece for Holiday Look &amp; Puja | A Line Dresses For Women | Stylish Midi Party Dress for Women | Winter Casual Wear</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51SllsCXWXL._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CM17DWD5</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr"/>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>TIVANTE Solid Asymmetrical Buckle Maxi Dress for Women || Western Dress for Women Dresses || one piece Dress</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31a3dpLJTrL.jpg</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H7RXPCLM</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr"/>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Shasmi Girl's &amp; Women's Solid A-Line Ruched Puff Sleeve Maxi Long Evening One Piece Long Dress for Women Stylish (Dress 131)</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61ctazYxu4L._SY741_.jpg</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F9T9PP7Z</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr"/>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>GoSriKi Viscose Printed Kurta for Women | Kurti Set Woman | Kurta with Pant &amp; Dupatta | Straight Ethnic Suit | Indian Outfit Ladies Dress Stylish Traditional Clothing Party Office Fashion Look Style</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51C7n7ysoIL._AC_AIweblab1392912,T4_SF1358,1638_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G59JDRRR</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr"/>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>LookMark Women's Rayon Printed Kurta Set with Dupatta Kurti with Pants Ethnic Traditional Outfit</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61UVk6rFvUL._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H5KTHGSK</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr"/>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Nermosa Women's Hand Block Floral Printed Straight Kurta Set with Palazzo Pants &amp; Dupatta Ethnic Kurta Set for Casual Outings Day Events Summer Wear Festive</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41HNjyM2OmL._AC_AIweblab1392912,T4_SF988,1482_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H6K11C3H</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr"/>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>GoSriKi Kurta Sets for Women Viscose Printed | Kurti Set for Woman | Kurta Pant Dupatta Set | A Line Kurti | Round Neck V-Slit 3/4 Sleeve Suit Set for Women Stylish Ethnic Outfit</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71zBxzukDgL._AC_AIweblab1392912,T4_SF1168,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GTVX18KW</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr"/>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Amayra Women's Pure Cotton A-Line Kurta Set with Palazzo Pants &amp; Dupatta|Ethnic wear|Kurti Suit Set for Women</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81LWX3c50zL._AC_AIweblab1392912,T4_SF1226,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GLGBDVJY</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr"/>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>ANNI DESIGNER Farshi Salwar Suit for Women | Cotton Blend Printed Straight Kurta with Dupatta | Farsi Farasi Parsi Ethnic Indian Office Party Wedding Clothing Fashion Premium Traditional Look 3 Piece</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51bvwVMYOlL._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H3FSN57V</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr"/>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Amayra Women's Pure Cotton Straight Kurta Set with Palazzo Pants &amp; Dupatta|Ethnic wear|Kurti Suit Set for Women</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81vCseZYquL._AC_AIweblab1392912,T4_SF1150,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GPC7B26V</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr"/>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Women’s Floral Printed Kurta Palazzo Set with Dupatta | Ethnic Straight Kurta Suit for Women | Festive Regular Wear | Designer Pakistani Style Salwar Suit for Daily Wear</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61a7MDYVGuL._AC_AIweblab1392912,T4_SF1272,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GZ7X6XYQ</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr"/>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>KLOSIA Women's Printed Straight Kurta and Pant with Dupatta Set</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/616i8sDpl8L._AC_AIweblab1392912,T4_SF1156,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GPQJR7VQ</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr"/>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>GoSriKi Poly Kurta for Women | Kurti Set Woman | Kurta with Pant &amp; Dupatta | Straight Printed Suit | Ethnic Indian Outfit | Long Dress Party Office Traditional Clothing Fashion Style</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51P-78jX7UL._AC_AIweblab1392912,T4_SF1172,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H7SNGCNK</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr"/>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>KLOSIA Women’s Floral Printed Sleeveless Kurta Palazzo Set | Round Neck Straight Kurta with Palazzo Pants | Casual Ethnic Co-Ord Set for Women</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51sLN7JdqfL._AC_AIweblab1392912,T4_SF1006,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HFZZDSJQ</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr"/>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>ANNI Designer Kurta Sets for Women Viscose Printed | Kurta Pant Dupatta Set | A-Line Kurti Set for Women | Round Neck 3/4 Sleeve Ethnic Suit | Designer Indian Kurti Outfit with Pants</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61fcQ1xXDdL._AC_AIweblab1392912,T4_SF1358,1694_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GT99T4WH</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr"/>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>GoSriKi Poly Kurta for Women | Kurta with Narrow Pant &amp; Dupatta | Straight Solid Suit | Indian Ethnic Outfit Office Party Wedding Clothing Fashion Premium Traditional Style Look 3 Piece</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71YwUB3j14L._AC_AIweblab1392912,T4_SF1272,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GQTXCCMT</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr"/>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Klosia Women Embroidery Solid Straight Kurta and Pant Set with Dupatta</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/719NauczPjL._AC_AIweblab1392912,T4_SF1208,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GM91511K</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr"/>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Nermosa Women's Pure Viscose Block Printed Ethnic Wear Straight Kurta Set with Palazzo Pants &amp; Dupatta | Kurta Set for Women | 3 Piece Set</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71L-WyS26RL._AC_AIweblab1392912,T4_SF1076,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H3FDN9T6</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr"/>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Yashika Women's Chikankari Georgette Embroidery Kurta Set with Pant and Dupatta | Traditional Ethnic Co-ord Set for Women | Office, Casual Wear</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61uoIZOXj0L._AC_AIweblab1392912,T4_SF990,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HDDF86CN</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr"/>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>ANNI DESIGNER Women's Viscose Straight Printed Kurta with Pant &amp; Dupatta</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61PHOMhPdCL._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0F8ZXJXLK</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr"/>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>INDO ERA Women's Straight Cotton Kurta Palazzo with Dupatta Set | Cotton kurta sets for women</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71hHe9qwy3L._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B09PRGR4KH</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr"/>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>ANNI DESIGNER Viscose Blend Co Ord Set for Women | Kurta with Palazzo | Kurti Set Woman | Printed Ethnic Outfit | Cord Style Indian Dress Office Party Traditional Clothing Fashion Premium Modern Look</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/510GrdNJJvL._AC_AIweblab1392912,T4_SF1318,1758_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FQP68MCS</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr"/>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Rayon Kurti Pant and Dupatta Set, Mustard Yellow with Red Dupatta, Embroidered V-Neck, 3-Piece Ethnic Wear</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51oR3Gn8-oL._AC_AIweblab1392912,T4_SF1112,1482_PQ60_.jpg?aicid=detailPage-mediaBlock</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GTYVC53S</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr"/>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Impex Migo Non-Stick Cookware Set, 4 Pcs Induction Bottom 3mm Thick, 5-Layer Super Granite Coating, Frying Pan Kadai Tawa 24cm, Gas &amp; Induction Compatible, Festival Gift Set, 1 Yr Warranty</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81NDfQSapUL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CH2ZL47M</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟒-𝐏𝐈𝐄𝐂𝐄 𝐍𝐎𝐍𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓: Everything your kitchen needs in one Impex Migo cookware combo — frying pan, kadai pan and tawa pan plus accessories, perfect for daily Indian cooking, sautéing, frying, roasting and more, all in one set. | 🪨 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐍𝐎𝐍-𝐒𝐓𝐈𝐂𝐊 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Premium granite-finish nonstick coating applied in 5 durable layers ensures long-lasting nonstick performance, even food release, less oil cooking and constant heat distribution for healthier meals. | 🎨 𝐓𝐖𝐎-𝐒𝐈𝐃𝐄 𝐒𝐏𝐀𝐓𝐓𝐄𝐑 𝐃𝐄𝐒𝐈𝐆𝐍 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Stylish spatter-pattern coating on both interior and exterior gives this cookware set a modern, elegant look while adding an extra layer of coating durability against everyday kitchen wear and tear. | ⚡ 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐁𝐎𝐓𝐓𝐎𝐌: Sturdy 3mm thick induction-compatible base ensures even heat distribution, faster cooking and no hot spots, making this cookware set reliable for daily use on any modern Indian kitchen cooktop. | 🔥 𝐌𝐔𝐋𝐓𝐈-𝐂𝐎𝐎𝐊𝐓𝐎𝐏 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄 — GAS, ELECTRIC &amp; INDUCTION: Designed to work seamlessly across gas stoves, electric cooktops and induction cooktops, this Impex cookware set offers complete versatility for every kind of kitchen setup. | 🤚 𝐒𝐓𝐔𝐑𝐃𝐘 𝐂𝐇𝐑𝐎𝐌𝐄 𝐇𝐀𝐍𝐃𝐋𝐄𝐒 𝐖𝐈𝐓𝐇 𝐃𝐈𝐑𝐄𝐂𝐓 𝐑𝐈𝐕𝐄𝐓𝐈𝐍𝐆: Ergonomically designed chrome-finish handles are securely direct-riveted to each pan, offering a strong, comfortable and heat-resistant grip so you can cook safely every single day | 🍲 𝐕𝐄𝐑𝐒𝐀𝐓𝐈𝐋𝐄 𝐏𝐀𝐍 𝐕𝐀𝐑𝐈𝐄𝐓𝐘 — FRYING PAN, KADAI &amp; TAWA (24CM EACH): This set includes a 24cm frying pan for shallow frying, a 24cm kadai pan for deep frying and curries, and a 24cm tawa pan for rotis, dosas and parathas — total flexibility. | 🎁 𝐈𝐃𝐄𝐀𝐋 𝐅𝐄𝐒𝐓𝐈𝐕𝐀𝐋 &amp; 𝐎𝐂𝐂𝐀𝐒𝐈𝐎𝐍 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓: Beautifully designed and practically useful, this Impex Migo cookware set makes a thoughtful gift for Diwali, weddings, housewarmings, anniversaries or any festive celebration with family and friends. | ✨ 𝐋𝐎𝐍𝐆-𝐋𝐀𝐒𝐓𝐈𝐍𝐆 𝐃𝐔𝐑𝐀𝐁𝐈𝐋𝐈𝐓𝐘 &amp; 𝐄𝐀𝐒𝐘 𝐅𝐎𝐎𝐃 𝐑𝐄𝐋𝐄𝐀𝐒𝐄: The robust non-stick construction resists scratches from daily cooking, ensures smooth easy food release, simplifies cleaning after every meal and keeps performing reliably for years. | 🛡️ 𝐁𝐀𝐂𝐊𝐄𝐃 𝐁𝐘 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘: Cook with complete confidence knowing your Impex Migo cookware set is backed by a 1 Year Manufacturer Warranty, ensuring assured quality, reliable support and long-term value for your kitchen investment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr"/>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Induction Cast Iron Non Stick Cookware 2 Piece Set Fry Pan Kadai Kitchen Combo Gas Stove Compatible Durable Daily Use Black Free Size</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31CrkKQASNL.jpg</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GXF1J4ZN</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Multi Purpose Cookware: Includes kadai sauce pan fry pan tawa and tadka pan for diverse cooking needs | Non Stick Surface: Ensures easy cooking with less oil and prevents food from sticking | Even Heat Distribution: Designed to cook food evenly for better taste and texture | Easy Maintenance: Simple to clean and maintain for regular kitchen use | Suitable for All Kitchens: Ideal for home restaurants hotels and professional cooking setups</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr"/>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Crystal 11 Pcs Non Stick Cookware Set with Storage Containers | Gas Stove Friendly | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 2 Containers &amp; Grater Set | PFOA Free Coating</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71q-5-ENFCL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0H41FFYYF</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>Attractive white marble coated cookware combo | Gas stove compatible design for convenient cooking | Nonstick coating supports healthy cooking with less oil | Durable body for long-lasting usage | Elegant appearance suitable for every kitchen</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr"/>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Vinod Grandior Pro Hybrid Triply Stainless Steel Cookware Set - 4 pcs</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81mFtaFRHDL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HBCCG67L</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>EVERYDAY MEALS, ONE SET : Move from breakfast dosas to sabzi and curries with a 28 cm tawa, 22 cm frypan and 22 cm kadai. Grandior Pro brings three useful cooking shapes together, so you can choose the right vessel for each dish. | HEXA SHIELD COOKING SURFACE : Raised stainless-steel peaks sit above protected non-stick valleys in the honeycomb surface. This combination supports easier everyday food release while keeping the textured cooking surface visible. | TRIPLY SAS CONSTRUCTION : Stainless steel, aluminium and stainless steel form the three-layer cookware body. The aluminium layer helps distribute heat, bringing practical heat-spreading construction to everyday home cooking. | ONE LID, TWO VESSELS : The common stainless-steel lid fits the 22 cm kadai and 22 cm frypan, giving you a covered-cooking option for either vessel. One lid is included, so the two vessels cannot both be covered at the same time. | BREAKFAST TO MAIN COURSE : Use the 28 cm, 4 mm thick dosa tawa for dosas, uttapam and chilla; choose the kadai for curries and sabzi, or the frypan for sauteing and shallow frying. The 4 mm thickness refers to the tawa only. | FITS YOUR COOKTOP ROUTINE : The set is compatible with gas, induction, electric, ceramic and halogen cooktops. Choose the vessel that suits your dish and cooking zone; the set brings matching cookware to different kitchen setups. | CLEANING MADE PRACTICAL : The three cookware vessels are dishwasher safe, giving you a cleaning option after everyday meals. Follow Vinod's product-specific care guidance when choosing utensils, heat settings and cleaning products. | KNOW EXACTLY WHAT IS INCLUDED : Receive a 22 cm kadai with 2.3 L capacity, a 22 cm frypan with 1.5 L capacity, a 28 cm dosa tawa and one common stainless-steel lid. This is three cookware vessels plus one lid, not four vessels. | 5-YEAR WARRANTY : Enjoy added peace of mind with the Vinod Grandior Pro cookware set, backed by a 60-month warranty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr"/>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Bergner Sienna Elite 6 Pcs Granite Non-Stick Cookware Set - 24cm Kadai with Lid, Casserole 24cm with Lid, Frypan 24cm, Tawa 28cm, Healthy Marble Coating, Less Oil Use, Cast Aluminium Induction Bottom</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/816IMhz4n9L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FNN15J7K</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>🔶Premium Sienna Elite Series by Bergner : Elevate your kitchen with this elegant and high-performance 6-piece non-stick cookware set designed for everyday and gourmet cooking | 🍳 Complete Cookware Set for Every Meal : Includes : 28cm Tawa, 24cm Frypan, 24cm Kadai with Glass Lid, 24cm Casserole with Glass Lid – ideal for sautéing, frying, simmering &amp; more | 💪 Durable Cast Aluminium Body : Built with heavy-gauge cast aluminum for long-lasting strength, rust resistance &amp; quicker, even heat distribution across the surface | 🌿 Healthy Marble Non-Stick Coating : Enjoy oil-free cooking with Bergner’s PFOA-free marble coating, ensuring effortless food release and healthier meals every time | 🔥 Induction &amp; Gas Stove Compatible : Features a full induction bottom, compatible with induction cooktops, gas stoves, electric and vitro-ceramic – versatile for all kitchens | 🧼 Effortless Cleaning &amp; Maintenance : Non-stick surface makes it easy to clean after use. (Note: Hand wash recommended; not dishwasher safe.) | 🖐️ Soft-Touch Handles with Strong Grip : Ergonomic, stay-cool handles provide a comfortable, secure grip while cooking, flippingor serving | 💧 Flared Rim for Drip-Free Pouring : Smartly designed rim ensures easy, mess-free pouring of liquids like curries, saucesor soups | 🎁 Perfect Gift for Home Chefs : Ideal for housewarming, anniversary, birthdayor festive gifting, this elegant cookware set is both stylish and functional | ✅ 1-Year Manufacturer Warranty : Enjoy peace of mind with Bergner’s quality assurance and dedicated customer support</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr"/>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Bergner Ivory Black Granite Non-Stick 4 Pcs Cookware Set - 24cm (2.5L) Kadai with Glass Lid, 24cm Frypan, 28cm Dosa Tawa, Forged Aluminium, Soft Touch Handle, PFOA Free, Induction and Gas Stove Ready</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81PIQSla1EL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0G5PRN1DP</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>⚫ Ivory Granite Series : Elegant design that adds a touch of sophistication to any kitchen | 🍳 4 Pcs Cookware Set : Includes a 24cm (2.5L) Kadai with Glass Lid, 24cm Frypan, and 28cm Dosa Tawa for versatile cooking | 🌱 3-Layer Marble Non-stick Healthy Coating : Cook with minimal oil for healthier meals and easy food release | 🔨 Forged Aluminium : Durable and long-lasting construction for daily use | ♨️ Even Heat Distribution : Ensures uniform cooking and consistent results every time | 🥗 Consumes Less Oil, Healthy Cooking : Perfect for health-conscious cooking with reduced oil for frying and sautéing | ✋ Wooden Soft Touch Handle with Excellent Grip : Stay comfortable and safe with heat-resistant, ergonomic handles | 🧼 Hand Wash Only (Not Dishwasher Safe) : For optimal care and longevity of the non-stick surface | 🔥 Gas, Electric, Vitro Ceramic, and Induction Compatible : Works on all stovetops, including induction, for ultimate convenience | 🛡️ 1-Year Warranty : Peace of mind with a 1-year warranty ensuring durability and quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr"/>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set Detachable Handle |Granite Finish | Induction Base | Pfoa Free | High Temperature Resistant Exterior Coating | Black</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61WLcHiMuDL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0BZW3SG7G</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | MICROWAVE-SAFE: Upon removing the handles the cookware becomes microwave-safe | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Kadai, 1 Glass Lid</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr"/>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Bergner Ivory Granite Non-Stick 4 Pcs Cookware Set - 24cm/2.5L Kadai with Lid 24cm Frypan 28cm Dosa Tawa 3-Layer Marble Healthy Coating PFOA Free Forged Aluminium - Induction and Gas Stove Ready</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61I02u0TJWL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GF7FZGR8</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>🍳 Complete 4-Piece Cookware Set : Includes 24cm (2.5L) Kadai with Glass Lid 24cm Frypan &amp; 28cm Dosa Tawa – perfect for everyday Indian cooking | 🔘 Ivory Granite Series Design : Modern granite finish adds durability and a stylish look to your kitchen | 🧱 Forged Aluminium Construction : Strong warp-resistant build offers long-lasting performance and superior heat retention | 🌟 3-Layer Marble Non-Stick Coating : PFOA-free for safe cooking; ensures minimal oil use and easy food release | 🔥 Even Heat Distribution : No hot spots just consistent cooking results across all cookware pieces | 🥗 Healthy Cooking with Less Oil : Ideal for dosa stir-fry curries sautéing and more with reduced oil usage for a healthy lifestylecookware set cookware combo nonstick cookware set nonstick 4 pcs set 4 pcs cookware set best nonstick combo granite nonstick coating forged aluminium | 🌳 Soft-Touch Rivetless Wooden Handles : Ergonomic heat-resistantand elegant for a comfortable grip | 🥄 Glass Lid with Steam Vent : Keeps moisture and nutrients locked in while allowing pressure control during cooking | 🌀 Compatible with All Cooktops : Works on gas induction electricand vitro ceramic stoves | 🛡️ 1-Year Manufacturer Warranty : Reliable quality assurance from Bergner for complete peace of mind</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr"/>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Induction Base Cast Iron Non Stick Cookware Set of 5 Kadai Fry Pan Tawa Saucepan Tadka Pan Kitchen Combo Set Black Free Size</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31AWpoJd84L.jpg</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GXDZNPR2</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Multi Purpose Cookware: Includes kadai sauce pan fry pan tawa and tadka pan for diverse cooking needs | Non Stick Surface: Ensures easy cooking with less oil and prevents food from sticking | Even Heat Distribution: Designed to cook food evenly for better taste and texture | Easy Maintenance: Simple to clean and maintain for regular kitchen use | Suitable for All Kitchens: Ideal for home restaurants hotels and professional cooking setups</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr"/>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Amazon Basics Aluminum Non-Stick 15 Piece Cookware Set | 2-Way 3 Layer Non-Stick Coating | PFOA Free | High Temperature Resistant Exterior Coating, Black</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71oZ1-QYomL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0B8D6GW8S</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Make cooking a joyful process with this durable non-stick 15-piece cookware set | The pressed aluminium cookware body is ultra-conductive and corrosion-free, which enables quick heating and helps save energy | Stay-cool phenolic handles are heat-resistant and remain cool even at high cooking temperatures | USFDA and European Food Safety Authority (EFSA)-approved coatings are 100% free from PFOA, lead, cadmium, nickel, and arsenic | The 2-layered exterior coating makes it scratch-resistant; the 3-layered interior with water-based eco-friendly PFOA-free coating promotes healthy cooking</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr"/>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Bergner Copper+ Non Stick Cookware Set 4 Pcs - 24cm (2.3L) Kadai with Lid, 24cm (1.5L) Frypan and 25cm Tawa, 3-Layer Non-Stick Coating, PFOA Free, Bakelite Handles - Induction and Gas Stove Ready</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71PteE9UxqL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HGM81N8G</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>🍳 4-Piece Cookware Set : Includes 24cm Kadai with Lid (2.3L), 24cm Fry Pan and 25cm Tawa for everyday cooking needs | 🥘 3-Layer Non-Stick Coating : High-performance 3-layer coating helps provide smooth cooking with minimal oil | 🔥 Induction &amp; Gas Compatible : Designed for induction cooktops and compatible with all types of gas stoves | 🛡️ Heavy Gauge Construction : Sturdy construction supports even heat distribution and helps reduce food burning | 🥗 Healthy Cooking : PFOA-free non-stick coating supports low-oil cooking for healthier everyday meals | 🖐️ Bakelite Handles : Heat-resistant Bakelite handles provide a comfortable and secure grip while cooking | 👀 Tempered Glass Lid : Durable tempered glass lid with steam hole helps monitor food while it cooks | 🍲 Versatile Cookware : Ideal for frying, sautéing, simmering, making curries, rotis, dosas and everyday meals | ✨ Premium Copper Brown Finish : Stylish copper brown exterior with a black cooking surface adds a modern touch to your kitchen | 🧼 Easy Cooking &amp; Cleaning : Smooth non-stick surface helps make cooking convenient and cleaning easier after use</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr"/>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Hawkins Quik Nonstick Induction 4 Piece Cookware Set of Deep Kadhai, Frying Pan, Saucepan and Stainless Steel Lid | Kitchen Gift Pack | Grey (IQGP1)</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71Ujg8yco+L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GD5QFJ19</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Healthy PFOA-free Nonstick inside - Healthy low oil cooking | Durable ceramic coating outside - stays looking new | 3mm Thick Pans - Food will not burn or stick | Rivet-less cooking surface - easy to stir, easy to clean | Deep shape - Stir-fry, High-walls. Cook large quantities</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr"/>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Amazon Basics Ceramic Non Stick Cookware Set 3 Pieces | 28cm Dosa Tawa, 24cm Fry Pan, 24cm Kadai with Glass Lid (2.3L) | Gas &amp; Induction Compatible | Wooden Finish Bakelite Handle | Ivory</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/71P4TioZa-L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0GTMNVQ4Z</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>3-Piece Cookware Set: Includes dosa tawa, fry pan &amp; kadai with lid. | Ceramic Non-Stick: Easy food release with low-oil cooking. | Even Heat Distribution: Ensures consistent cooking results. | Gas &amp; Induction Compatible: Suitable for all cooktops. | Tempered Glass Lids with Steam Vent: Helps retain heat and monitor cooking. | Ergonomic Handles: Comfortable and safe grip while cooking. | Easy to Clean: Low maintenance and hassle-free use. | Care Tip: Pre heat max 2 mins then cook on low to medium heat with light oil for longer durability. | Non Toxic Coating: PFOA free, PTFE free and BPA free stain resistant coating for safe everyday cooking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr"/>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Amazon Brand SOLIMO - 3 PCS Non-Stick COOKWARE SET | Aluminium</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/51Ql6IsQTzL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
           <t>https://www.amazon.in/dp/B07P912X7R</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>3 piece non-stick cookware set includes fry pan, flat tawa and kadhai with a glass lid for everyday cooking | Made using good quality virgin aluminium which is durable, long lasting, and offers even heat distribution | Food grade 2-way non-stick coating: Cooking surface has a 3 layered coating; outer layer has a finish with high temperature resistance (HTR) coating | Equipped with bakelite handles that offer safe and firm ergonomic grip | Ideal for preparing rotis, chapatis, dosa, stir-fries, pulao, sauteed vegetables, sear meats, fish, fry eggs and more | Compatible with gas stove and induction cooktops | Easy to clean and maintain; dishwasher safe | Comes with a 1-year warranty against manufacturing defects | Product Dimensions- Fry Pan:- Diameter: 220 mm (22 cm); Thickness: 3 mm; Depth: 45 mm (4.5 cm); Capacity: 1650 ml; Weight: 610 gm; Tawa:- Diameter: 265 mm (26.5 cm); Thickness: 3 mm; Depth: 13 mm (1.3 cm); Weight 615 gm; Kadhai:- Diameter: 220 mm (22 cm); Thickness: 3mm; Depth: 73 mm (7.3 cm); Capacity: 2500 ml; Weight: 1125 gm | Caution: For better longevity of the cookware, avoid using Metal Scrubber for coated non-stick utensils. Do not use metal spoons and ladles on coated non-stick utensils. For better and lasting coating durability, use only soft nylon scrubber and wooden /nylon ladles &amp; spoons.</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr"/>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Bergner Aloe 4 Pcs Non-Stick Cookware Set of 24cm (2.5L) Kadai with Glass Lid, 24cm Fry Pan, 25cm Tawa, Bakelite Handles, 3-Layer Superior Non-Stick Coating, PFOA Free - Induction and Gas Stove Ready</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/819YbZK9sGL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0HK16KG2M</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>🍳 4-piece complete cookware set : Includes 24cm Kadai with lid (2.5L), 24cm fry pan and 25cm tawa - everything you need for everyday cooking | 🛡️ 3-layer superior non-stick coating : Ensures minimal oil usage, easy food release and effortless cleaning every time | 🔥 Heavy gauge construction : Enables even heat distribution, prevents food from burning and helps retain nutrients in food | 🚫 PFOA free material : Prevents harmful chemicals from leaching into food, keeping your cooking safe and healthy | 🖐️ Bakelite handles for excellent grip : Stay cool to touch and provide a comfortable, secure hold while cooking | ⚡ Induction friendly : Compatible with all types of cooktops, including induction, gas, vitroceramic and halogen | 🔍 Tempered glass lid with steam hole : Lets you monitor food while it cooks and helps release excess steam | 🌿 Healthy cooking certified : No cadmium, no lead, no PFOA - safe for you and your family | 🧼 Hand wash recommended : Not dishwasher safe - a quick hand wash keeps the non-stick coating in top condition for longer | 🛠️ 1 year warranty : Backed by Bergner's assurance of durability and long-lasting performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr"/>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Prestige Svachh Granite Non-Stick 3-Piece Set Cookware |Dual Non-Stick Delight|Omni Tawa - 28cm Dia, Kadai with GlassLid - 24cm Dia, Fry Pan - 24cm Dia|Gas and Induction Compatible|Easy Care</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61SnP+JylSL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0D5YM8SM6</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>DUAL NON-STICK DELIGHT : Durable non stick coating inside and outside for an effortless cleaning. | EASY CARE: Non-Stick Inside &amp; Outside for easy cleaning. Simply soak in soapy water &amp; rinse | EVEN HEAT DISTRIBUTION: Quick, Uniform Heating with Remarkable Durability | CONTENTS: Omni Tawa : 28cm Diameter, Kadai with Lid: 24cm Diameter, Fry Pan: 24cm Diameter | COMPATIBLE: Suitable for usage on Gas and Induction</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr"/>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Wonderchef Royal Velvet 5Pc Non-Stick Cookware Set for Kitchen, Fry Pan 24cm, Mini Fry Pan 14cm, Wok with Lid 24cm, Dosa Tawa 24cm, Non-Toxic, Gas Stove &amp; Induction Friendly, 2-Yr Warranty, Purple</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/619aKEsYe4L._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B00XVQ0J8I</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Coating type: Non-Stick | NON-STICK EXCELLENCE - Savor the benefits of healthy cooking with minimal oil, thanks to the proprietary METATUFF non-stick coating that delivers scratch resistance and effortless cleaning. MetaTuff 5-layer non-stick coating is 100% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | EFFORTLESS COOKING - Revolutionize your cooking experience with the durable, easy-to-handle Wonderchef Royal Velvet set that takes the hassle out of daily meal preparation | COLLECTIVE SET - Kadhai with Lid, Fry Pan, Dosa Tawa let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | VERSATILITY AT ITS FINEST - With the ability to be used on both gas stoves and induction cooktops, this cookware set ensures flexibility and convenience in your kitchen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr"/>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Lifelong 3 Piece Forged Cookware Set With Common Lid |2.2L Kadhai with Lid 24cm |Ceramic Coated |1.4L Fry Pan 24cm | 1.2L Tawa 26cm |Induction &amp; Gas Compatible | Non-Riveted Handle | Non-Stick Coating</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/5155aqiCAYL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0FL2K6L6H</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>Versatile 3-piece cookware set – Includes a 2.2L kadhai with lid (24cm), 1.4L fry pan (24cm), and 1.2L tawa (26cm) to handle all your everyday cooking needs. Perfect for sautéing, frying, simmering, and more. An all-in-one solution for daily Indian and continental cooking. | Common glass lid for added convenience – The single tempered glass lid fits both the kadhai and fry pan, allowing easy cooking, heat retention, and visible monitoring without lifting the lid. Reduces clutter and offers space-saving practicality in your kitchen. | Non-riveted handles for better hygiene – Smooth, screw-free handles offer a secure and comfortable grip while cooking. Easier to clean and safer for long-term use in busy kitchens. Eliminates food buildup and rust issues seen in riveted designs. | PFOA-free non-stick coating – Cook with less oil and enjoy effortless food release. The toxin-free, scratch-resistant coating ensures healthier meals and easy cleanup after every use. Built for durability, it maintains performance over time. | Compatible with induction &amp; gas – Works efficiently on both induction cooktops and gas stoves, providing flexibility for all kitchen setups. Even heat distribution enhances cooking results. Great for both modern and traditional cooking environments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr"/>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Hawkins Futura Nonstick Kitchen Gift Set - 2 L Stir-Fry Pan with Glass Lid, 17 cm Frying Pan with Stainless Steel Lid and 22 cm Tava, Black (24NSGP)</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/61-fGGnjDxL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0DRVNWKJH</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>PFOA Free Non-stick coating locked into tough Hard Anodised Aluminium - lasts longer | The cookware set consisting a Stir-Fry Pan with glass lid, a Frying Pan with stainless steel lid and a Tava caters to most of your cooking needs | The pans are made from heavy gauge pure, virgin metal - last longer | The pans are offered with elegant, comfortable handles which are permanently riveted to the Pans - will not loosen | The lids trap flavors, cook faster and make food tastier</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr"/>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Impex Aluminium Migo Nonstick Granite 6 Pcs Induction Bottom Cookware Set 3 Mm Thick,Festival Gift Set Mfkt 6,5-Layer Super Granite Coated Cookware Set,Hammer Tone Exterior Finish,1 Yr Warranty, Grey</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/81q152DZrLL._SX679_.jpg</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/dp/B0CH3BMNN6</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Complete 6-Piece Cookware Set: Elevate your culinary experience with a comprehensive 6-piece cookware collection, featuring versatile pieces for various cooking needs. | Durable 5-Layer Super Granite Coating: Crafted with a robust 5-layer super granite nonstick coating, this cookware set ensures longevity, even heat distribution, and easy food release. | Uniform 24 cm Size: Each piece in this set features a uniform size of 24 cm, offering consistency in your cooking and serving. | Induction-Compatible Design: The cookware pieces come with induction-compatible bottoms, making them suitable for use on gas, electric, and induction cooktops, providing flexibility in your kitchen. | Dishwasher Safe: This cookware set is dishwasher safe, saving you valuable time and effort on post-cooking cleaning.</t>
         </is>
       </c>
     </row>

--- a/data/amazon_products.xlsx
+++ b/data/amazon_products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E160"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3916,6 +3916,386 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>DANIEL CLARK Women's Stylish Handbags Combo (Set of 3)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/717u1Q0IGGL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0963DGWJ4</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>WOMEN MARKS® Structured Handbag Design for Girls/Women with Detachable and Adjustable Shoulder Strap</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71TWQ6rCM+L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GTMPMXWN</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Fargo PU Women's Sling Bag Handbag For Women</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71KDJYxxMJL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D4DVRFYM</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Lady Quinton Stylish Sling Bag | Handbags For Women</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/713ZBQLO42L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DVBZZTFN</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Tote Bags for Women, Premium Shoulder Tote | Elegant PU Leather Purse | Spacious Everyday Carry with Adjustable Strap for Office, Shopping &amp; Travel | Black</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31wR1p5IuIL.jpg</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DCHM378P</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ZOUK Women's Office Essential Bag | Jute | Vegan Leather Handcrafted Tote Bag With Double Handle Shoulder Strap</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61-+y-5fJAL._SY741_.jpg</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DGQNLJX7</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Women Handbag for Daily Use | Stylish Shoulder Bag with Spacious Storage for Shopping Travel and Casual Outings3</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41m-dij0U7L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HMH87PQG</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>EXOTIC Studded hand bag for women</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61NhaCR1UDL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09WVQVS2X</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Dual Tone Large Capacity Croco Pattern Tote Handbags Purses Shoulder Bag For Womens</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61UD04fHLGL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0HL4PHDSK</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ALSU Women's Wallet | Stylish Purse for with Phone Pocket,4 Card Pocket and Multiple Compartment| Party Clutch for Girl | Lock Closure | Travel Hand Purse for Women| Office Bag for Women</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61WVYr4LkiL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B08M435QQY</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>EXOTIC Women Feminina Solid Top Handle Tote Hand Bag</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71NopnO547L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D2DKZXWK</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Keywest Luxe Penguin Hand Bags For Women Stylish</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51msRUjkMuL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GKFVZN2K</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Lavie Women's Emberlyn Crossbody Sling Bag | Ladies Purse Handbag | Gift for Women</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61tGm7mT5ZL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DVLS8NZK</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>WORLD STAR Women's Small PU Leather Tote Handbag | Top Handle Shoulder Bag for Women | Stylish Mini Office Purse for Daily Use, Shopping &amp; Travel | Brown</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61nAiuqq-vL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CSYZSQSJ</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Women’s Metallic Shoulder Bag – Croc-Embossed Patchwork Leather Look Handbag with Zipper Closure, Trendy Underarm Purse.</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51dFX521euL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GXVSDJ8C</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Fargo Matrix Tote Bag for Women | Vegan Leather Handbag with 15-Inch Laptop Compartment, Smooth Zip | Stylish Office, College &amp; Daily Use Tote | Made in India</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/515y-yv-tQL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GF2X617Z</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SIJJEEL Women's Handbag Synthetic Leather Shoulder Bag with Bear Charm Tote One Size Women's Shoulder Bag Faux Leather Tote</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51Dyn+hZz5L._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0GH23KQ4K</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Aisna Handbags for women 3 sapcious partitions and 3 pockets</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71LUh1l9YKL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07Q7S37HT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>The Purple Tree Handcrafted Women's Tote Bag with Vegan Leather Handles &amp; Indian Prints, Shoulder Tote Bag and Handbag for Office and College (Pack of 1)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61oix3ol0eL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C9V6CJ9B</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ADISA Women's Quilted Crossbody Sling Bag - Stylish Cross Body Handbag for Girls &amp; Women with Gold Chain (SL5059)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61jsDR7kaYL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09154JPWQ</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
